--- a/data/results/seleccion_umbral_etiquetado.xlsx
+++ b/data/results/seleccion_umbral_etiquetado.xlsx
@@ -1,37 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karen\Documents\analisis_columnas_opinion_git\data\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karen\Documents\HumanidadesDigitales_git\data\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C12CF6C-9A91-4DC9-B204-9D561E5B6C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224DF34E-35A4-4093-B9E0-3E7B73F752D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$120</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -56,718 +40,718 @@
     <t>valido_ciencia</t>
   </si>
   <si>
-    <t>10005_0</t>
-  </si>
-  <si>
-    <t>2709_1</t>
-  </si>
-  <si>
-    <t>7375_2</t>
-  </si>
-  <si>
-    <t>13145_2</t>
-  </si>
-  <si>
-    <t>5475_2</t>
-  </si>
-  <si>
-    <t>8914_1</t>
-  </si>
-  <si>
-    <t>11223_2</t>
-  </si>
-  <si>
-    <t>12009_0</t>
-  </si>
-  <si>
-    <t>7897_0</t>
-  </si>
-  <si>
-    <t>845_0</t>
-  </si>
-  <si>
-    <t>10190_0</t>
-  </si>
-  <si>
-    <t>9844_0</t>
-  </si>
-  <si>
-    <t>2286_1</t>
-  </si>
-  <si>
-    <t>6880_0</t>
-  </si>
-  <si>
-    <t>4770_1</t>
-  </si>
-  <si>
-    <t>193_1</t>
-  </si>
-  <si>
-    <t>3031_1</t>
-  </si>
-  <si>
-    <t>2063_0</t>
-  </si>
-  <si>
-    <t>3479_1</t>
-  </si>
-  <si>
-    <t>5012_2</t>
-  </si>
-  <si>
-    <t>7891_0</t>
-  </si>
-  <si>
-    <t>12973_0</t>
-  </si>
-  <si>
-    <t>5300_1</t>
-  </si>
-  <si>
-    <t>5333_1</t>
-  </si>
-  <si>
-    <t>1289_0</t>
-  </si>
-  <si>
-    <t>5512_0</t>
-  </si>
-  <si>
-    <t>3357_1</t>
-  </si>
-  <si>
-    <t>13666_1</t>
-  </si>
-  <si>
-    <t>8329_2</t>
-  </si>
-  <si>
-    <t>469_1</t>
-  </si>
-  <si>
-    <t>7797_1</t>
-  </si>
-  <si>
-    <t>7634_0</t>
-  </si>
-  <si>
-    <t>3425_0</t>
-  </si>
-  <si>
-    <t>10298_1</t>
-  </si>
-  <si>
-    <t>10431_0</t>
-  </si>
-  <si>
-    <t>5301_0</t>
-  </si>
-  <si>
-    <t>11621_0</t>
-  </si>
-  <si>
-    <t>9445_0</t>
+    <t>10740_2</t>
+  </si>
+  <si>
+    <t>13523_2</t>
+  </si>
+  <si>
+    <t>12676_3</t>
+  </si>
+  <si>
+    <t>1757_5</t>
+  </si>
+  <si>
+    <t>11591_1</t>
+  </si>
+  <si>
+    <t>897_2</t>
+  </si>
+  <si>
+    <t>12652_1</t>
+  </si>
+  <si>
+    <t>6472_1</t>
+  </si>
+  <si>
+    <t>11508_2</t>
+  </si>
+  <si>
+    <t>7983_1</t>
+  </si>
+  <si>
+    <t>3973_2</t>
+  </si>
+  <si>
+    <t>3290_3</t>
+  </si>
+  <si>
+    <t>5097_3</t>
+  </si>
+  <si>
+    <t>675_1</t>
+  </si>
+  <si>
+    <t>7823_2</t>
+  </si>
+  <si>
+    <t>12496_2</t>
+  </si>
+  <si>
+    <t>627_2</t>
+  </si>
+  <si>
+    <t>12606_3</t>
+  </si>
+  <si>
+    <t>10749_4</t>
+  </si>
+  <si>
+    <t>13314_3</t>
+  </si>
+  <si>
+    <t>7543_3</t>
+  </si>
+  <si>
+    <t>10792_1</t>
+  </si>
+  <si>
+    <t>8896_3</t>
+  </si>
+  <si>
+    <t>9734_1</t>
+  </si>
+  <si>
+    <t>9121_1</t>
+  </si>
+  <si>
+    <t>13422_0</t>
+  </si>
+  <si>
+    <t>4712_2</t>
+  </si>
+  <si>
+    <t>1802_2</t>
+  </si>
+  <si>
+    <t>2824_2</t>
+  </si>
+  <si>
+    <t>7395_2</t>
+  </si>
+  <si>
+    <t>13045_0</t>
+  </si>
+  <si>
+    <t>2753_1</t>
+  </si>
+  <si>
+    <t>4319_0</t>
+  </si>
+  <si>
+    <t>883_3</t>
+  </si>
+  <si>
+    <t>9751_3</t>
+  </si>
+  <si>
+    <t>11919_1</t>
+  </si>
+  <si>
+    <t>9907_3</t>
+  </si>
+  <si>
+    <t>6352_0</t>
+  </si>
+  <si>
+    <t>3833_0</t>
+  </si>
+  <si>
+    <t>10419_0</t>
+  </si>
+  <si>
+    <t>6211_0</t>
+  </si>
+  <si>
+    <t>3626_2</t>
+  </si>
+  <si>
+    <t>9684_3</t>
+  </si>
+  <si>
+    <t>1730_2</t>
+  </si>
+  <si>
+    <t>8012_0</t>
+  </si>
+  <si>
+    <t>4190_3</t>
+  </si>
+  <si>
+    <t>8813_0</t>
+  </si>
+  <si>
+    <t>13629_0</t>
+  </si>
+  <si>
+    <t>8134_1</t>
+  </si>
+  <si>
+    <t>8208_1</t>
+  </si>
+  <si>
+    <t>4110_2</t>
+  </si>
+  <si>
+    <t>3438_4</t>
+  </si>
+  <si>
+    <t>11987_1</t>
+  </si>
+  <si>
+    <t>12881_2</t>
+  </si>
+  <si>
+    <t>6143_3</t>
+  </si>
+  <si>
+    <t>12648_0</t>
+  </si>
+  <si>
+    <t>13313_10</t>
+  </si>
+  <si>
+    <t>12535_1</t>
+  </si>
+  <si>
+    <t>12313_4</t>
+  </si>
+  <si>
+    <t>4998_2</t>
+  </si>
+  <si>
+    <t>2088_1</t>
+  </si>
+  <si>
+    <t>5465_0</t>
+  </si>
+  <si>
+    <t>3521_5</t>
+  </si>
+  <si>
+    <t>11214_1</t>
+  </si>
+  <si>
+    <t>5849_1</t>
+  </si>
+  <si>
+    <t>12829_1</t>
   </si>
   <si>
     <t>10453_0</t>
   </si>
   <si>
-    <t>8164_0</t>
-  </si>
-  <si>
-    <t>6407_0</t>
-  </si>
-  <si>
-    <t>13246_0</t>
-  </si>
-  <si>
-    <t>11079_1</t>
-  </si>
-  <si>
-    <t>2563_0</t>
-  </si>
-  <si>
-    <t>11762_0</t>
-  </si>
-  <si>
-    <t>10339_1</t>
-  </si>
-  <si>
-    <t>7453_1</t>
-  </si>
-  <si>
-    <t>9052_0</t>
-  </si>
-  <si>
-    <t>7163_0</t>
-  </si>
-  <si>
-    <t>13159_1</t>
-  </si>
-  <si>
-    <t>12013_2</t>
-  </si>
-  <si>
-    <t>13359_1</t>
-  </si>
-  <si>
-    <t>13509_2</t>
-  </si>
-  <si>
-    <t>7676_2</t>
-  </si>
-  <si>
-    <t>9117_1</t>
-  </si>
-  <si>
-    <t>12546_1</t>
-  </si>
-  <si>
-    <t>9006_1</t>
-  </si>
-  <si>
-    <t>5047_2</t>
-  </si>
-  <si>
-    <t>5465_0</t>
-  </si>
-  <si>
-    <t>6825_1</t>
-  </si>
-  <si>
-    <t>1188_0</t>
-  </si>
-  <si>
-    <t>7835_0</t>
-  </si>
-  <si>
-    <t>2003_1</t>
-  </si>
-  <si>
-    <t>4289_0</t>
-  </si>
-  <si>
-    <t>3051_0</t>
-  </si>
-  <si>
-    <t>10488_1</t>
-  </si>
-  <si>
-    <t>4798_2</t>
-  </si>
-  <si>
-    <t>3727_0</t>
-  </si>
-  <si>
-    <t>6914_0</t>
-  </si>
-  <si>
-    <t>12702_1</t>
-  </si>
-  <si>
-    <t>63_0</t>
-  </si>
-  <si>
-    <t>4514_0</t>
-  </si>
-  <si>
-    <t>6973_2</t>
-  </si>
-  <si>
-    <t>1877_0</t>
-  </si>
-  <si>
-    <t>2715_1</t>
-  </si>
-  <si>
-    <t>1286_3</t>
-  </si>
-  <si>
-    <t>9917_2</t>
-  </si>
-  <si>
-    <t>6945_1</t>
-  </si>
-  <si>
-    <t>11378_1</t>
-  </si>
-  <si>
-    <t>8153_1</t>
-  </si>
-  <si>
-    <t>4166_0</t>
-  </si>
-  <si>
-    <t>11378_0</t>
-  </si>
-  <si>
-    <t>4552_0</t>
-  </si>
-  <si>
-    <t>6991_2</t>
-  </si>
-  <si>
-    <t>4602_0</t>
-  </si>
-  <si>
-    <t>1978_1</t>
-  </si>
-  <si>
-    <t>5937_0</t>
-  </si>
-  <si>
-    <t>6542_2</t>
-  </si>
-  <si>
-    <t>7630_0</t>
-  </si>
-  <si>
-    <t>4766_1</t>
-  </si>
-  <si>
-    <t>8356_4</t>
-  </si>
-  <si>
-    <t>3737_1</t>
-  </si>
-  <si>
-    <t>2993_3</t>
-  </si>
-  <si>
-    <t>10159_0</t>
-  </si>
-  <si>
-    <t>10861_0</t>
-  </si>
-  <si>
-    <t>6735_1</t>
-  </si>
-  <si>
-    <t>2769_1</t>
-  </si>
-  <si>
-    <t>228_1</t>
-  </si>
-  <si>
-    <t>10704_0</t>
-  </si>
-  <si>
-    <t>5352_1</t>
-  </si>
-  <si>
-    <t>3368_1</t>
-  </si>
-  <si>
-    <t>7430_2</t>
-  </si>
-  <si>
-    <t>12792_2</t>
-  </si>
-  <si>
-    <t>13372_1</t>
-  </si>
-  <si>
-    <t>9617_2</t>
-  </si>
-  <si>
-    <t>4729_1</t>
-  </si>
-  <si>
-    <t>4321_0</t>
-  </si>
-  <si>
-    <t>13347_1</t>
-  </si>
-  <si>
-    <t>11259_1</t>
-  </si>
-  <si>
-    <t>787_1</t>
-  </si>
-  <si>
-    <t>12488_0</t>
-  </si>
-  <si>
-    <t>805_1</t>
-  </si>
-  <si>
-    <t>13142_1</t>
-  </si>
-  <si>
-    <t>6214_1</t>
-  </si>
-  <si>
-    <t>10882_1</t>
-  </si>
-  <si>
-    <t>12687_1</t>
-  </si>
-  <si>
-    <t>8817_2</t>
-  </si>
-  <si>
-    <t>7682_0</t>
-  </si>
-  <si>
-    <t>10409_2</t>
-  </si>
-  <si>
-    <t>En la mayoría de las veces, casi siempre, fracasan los gobiernos, las políticas que implementan y desarrollan a partir de sus propuestas y programas electorales y de gobierno, para tratar los males de diverso orden que sobrevienen a las naciones como comunidades sociales en sus sistemas y modelos institucional y jurídico, político, productivo y económico en general. De igual manera, en el social, ambiental y el de explotación de los recursos naturales, los servicios públicos y de salud, el empleo, la educación, la ciencia y la tecnología, la cultura y las humanidades, la política exterior, y la interior en lo que tiene que ver con las relaciones, protección, inclusión y respeto a las diferencias de las comunidades indígenas, afrodescendientes y minorías étnicas al interior del territorio que conforma la nación. Tanto en el ámbito particular como en el de su conjunto, cuanto se colige históricamente es que las naciones son arrastradas a sus crisis, fracasos, por un torbellino de políticas improvisadas, coyunturales, en función de intereses particulares a los que les sirve de marco una institucionalidad débil, manipulable, y en la misma dirección de aquellos y del poder que las detenta y condiciona en una relación política predominante. Estados Unidos de Norteamérica, para citar el caso de la nación más poderosa de la tierra, no registra en su génesis incidente histórico alguno que dé en calificarse de fracaso en su ya largo y sostenido proceso de crecimiento y afianzamiento en el que estas dos categorías son susceptibles de medir el desarrollo de una nación en las diferentes variables que confluyen en él, y consecuentemente sus éxitos o fracasos, pues estos resultan de las políticas que den en aplicarse para consolidarlo o inmovilizarlo. No obstante la gravedad de la situación, no quiere ello decir que USA, la nación más poderosa de</t>
-  </si>
-  <si>
-    <t>de promover o tomar medidas fuertes para enfrentarlo. Por el contrario, Gore no solo tenía muy claro el desafío del cambio climático, sino que tenía un fuerte compromiso en combatirlo, por lo que hubiera puesto toda su voluntad y todo el poder de Estados Unidos para lograr acuerdos globales en ese tema. Además, como hace 18 años el calentamiento global no era tan grave y no existía tanta división en Estados Unidos sobre el tema entre republicanos y demócratas, es probable que la elección de Gore habría permitido que el mundo hubiese adoptado e implementado, hace años, un acuerdo robusto para enfrentar el cambio climático. Entonces 700 votos en Florida definieron el destino del mundo, tal vez para siempre, pues algunos científicos consideran que ya es muy difícil evitar que el calentamiento global supere los 1,5 grados, que es el objetivo mínimo para evitar catástrofes ambientales irreversibles. Esta votación en Florida es un buen ejemplo de la teoría del caos o del efecto mariposa, según la cual, dadas ciertas circunstancias, el simple aleteo de una mariposa puede ocasionar un huracán devastador. 700 votos en Florida cambiaron el mundo, infortunadamente en la dirección equivocada. Pero además de ilustrar la teoría del caos, esa elección presidencial pone en evidencia un desequilibrio fundamental: aunque la elección del presidente o del Congreso de Estados Unidos afecta a todo el mundo, nadie, fuera de los ciudadanos de ese país, tiene derecho a participar en esa decisión. ¿No es esto una clara injusticia? ¿No deberían tener los ciudadanos de todo el mundo y no solo el señor Putin alguna incidencia en las elecciones en Estados Unidos? Estas preguntas pueden parecer absurdas, a tal punto estamos acostumbrados a que los derechos políticos dependan de ser nacional del país implicado. Pero si tomamos en serio el ideal democrático,</t>
-  </si>
-  <si>
-    <t>más probable que las compren para dejar sacar un cargamento, a que las compren para que no eliminen unos cultivos que fácilmente pueden reemplazarse con otros. La ridícula situación en la que nos encontramos es que el presidente manda fumigar cultivos de coca con el glifosato de Estados Unidos, mientras los narcos le mandan comprar votos. Esto es un problema que viene de la profunda corrupción del uribismo, pero también es una dinámica estructural. El caso más exitoso de sustitución de cultivos, y que a menudo se usa como ejemplo de éxito, ha sido el de la amapola en Tailandia: uno de los países que, no obstante, tiene los más altos niveles de consumo y venta de drogas en la región, y donde el narcotráfico se castiga con pena de muerte. Es decir, ni siquiera en el país modelo de sustitución de cultivos, donde hay una de las legislaciones antidrogas más fuertes del mundo, sigue siendo uno de los epicentros del narcotráfico en el Sudeste Asiático. En Afganistán, donde el ejército norteamericano lleva casi 20 años en una guerra a sangre y fuego, el narcotráfico aumenta. Una salida es legalizar el cultivo de coca y centrar el trabajo de las autoridades en los eslabones que van de los laboratorios a la exportación y el lavado de dinero. Siendo realistas, sin embargo, dado que los niveles más altos son los que mueven la mayor cantidad de dinero, es probable que sigan siendo los menos combatidos. El peso de la lucha antidrogas siempre procurará centrarse en el eslabón más débil. Es lo fácil para una guerra que nadie pretende ganar ni acabar. Twitter: siempre procurará centrarse en el eslabón más débil. Es lo fácil para una guerra que nadie pretende ganar ni acabar. Twitter:</t>
-  </si>
-  <si>
-    <t>la de otros países del mundo. Tanto el Departamento de Estado como las Naciones Unidas coinciden en que donde operó la sustitución, decrecieron los cultivos. La Contraloría sostiene que el Gobierno Santos creó nada más que tres instituciones transitorias para esclarecer la verdad con justicia y no repetición y avezados economistas aseguran que los recursos para la implementación en 2019 existen y están asegurados. El más sensato corte de cuentas sería volver a los lejanos municipios de la Colombia rural equipados de acciones de respuesta rápida que garanticen la sostenibilidad de los programas de paz. Ni la reincorporación ni las crecientes expectativas sociales ni los asesinatos de líderes sociales aguantan más merchandising político. Requieren tal vez más sensatez y acción política. El desangre de la paz en manos de la retórica es prolongar el tan asentado relato de luchas inconclusas, esperanzas sucumbidas y codiciosas lenidades. Le demostraríamos a los países garantes Cuba y Noruega, acompañantes Venezuela y Chile y a generosos donantes Canadá, la Unión Europea y Suecia que sus esfuerzos por detener la sangre de nuestros muertos terminaron confrontándose a la ignominia de nuestra indiferencia. Porque a pesar de imperfecciones, resultaría ilógico que quienes ayudamos a construir la paz nos dedicáramos también a sepultarla. Desfinanciarla, burocratizarla o paralizarla hubiera equivalido a perpetuar las causas que originaron el conflicto. Llamarnos a engaños es señalar que su fragilidad se cimienta en omisiones pero paradójicamente también en demasiadas ejecuciones. Antes de que sea tarde, inyectémosle, ponderación y realismo a este debate. Impulsar la paz empieza por volcarse en lo que es y puede ser. No en lo que fue. la paz empieza por volcarse en lo que es y puede ser. No en lo que fue.</t>
-  </si>
-  <si>
-    <t>generación de energía, el manejo de la flora en los océanos, los índices de natalidad, los hábitos alimenticios y de consumo, y otros pocos, si bien todos los datos indican que los árboles y la cobertura forestal son centrales en esta batalla. Y no es por llover sobre mojado, pero la ganadería extensiva es de lejos el peor pecado de los trópicos, para el cual existe una cura que progresa a un ritmo exasperantemente lento: la ganadería silvopastoril. Al menos yo no pienso dejar de lado mi obsesión con este tema. email protected 878072 20190827T14:26:5405:00 column 20190827T16:04:3505:00 email protected none El norte y el sur de un único planeta 38 3616 3654 1</t>
-  </si>
-  <si>
-    <t>controlarlo por medio de una regulación, tal como se hace con el alcohol, o prohibirlo y enfrentar sus consecuencias: mafias, corrupción, mala calidad del producto, etc. Este último es el camino que se ha escogido y se ha hecho en nombre de la protección de los niños y de los jóvenes, cuando en realidad este es el camino que menos los protege. Es verdad que la legalización no los salva del consumo, pero les evita los males asociados al mercado ilegal. No es una decisión ideal, pero es la mejor posible y, como decía Raymond Aron, lo que importa no es tanto la lucha del bien contra el mal, sino de lo preferible contra lo detestable. ¿Cómo es posible que siga en pie una política tan irracional? Pues porque existe un grupo muy poderoso de personas, en su gran mayoría compuesto por políticos conservadores, que son incapaces de ver la lógica perversa de la represión o, aún más probable, que, viéndola, la desconocen de manera olímpica. Los políticos viven de vender emociones, más que ideas, y en el caso de la derecha lo que venden es miedo, autoridad y represión, entre otras cosas. La gente que vota por ellos se contenta con saber que defienden esas emociones proclamándolas en leyes y discursos. Poco importa que tal cosa la proclamación no resuelva nada en la realidad, que todo siga igual o peor, que la gente sufra incluso más; lo único que les importa es que el principio haya sido ungido y la emoción, satisfecha. Ellos saben que mucha gente prefiere una ley represiva que resuelve todo en el papel, sin resolver nada en la práctica, a una política regulatoria que resuelve todo, o casi todo, en la práctica, pero sin emoción para proclamar y sin ley para promulgar. Llevamos casi 60 la emoción, satisfecha. Ellos saben que mucha gente prefiere una ley represiva que resuelve todo en el papel, sin resolver nada en la práctica, a una política regulatoria que resuelve todo, o casi todo, en la práctica, pero sin emoción para proclamar y sin ley para promulgar. Llevamos casi 60 años sin que sea posible que se legalicen las drogas. Hay probablemente otras causas, pero una de ellas es la enorme influencia de políticos conservadores que construyen problemas con la idea de que ellos son útiles para conseguir los votos que aseguran su futuro político.</t>
-  </si>
-  <si>
-    <t>echó esta mañana es de plástico. La bolsa en la que viene el pan tajado es plástica. Las sillas de los buses son plásticas. Todo es plástico; ahora, hasta las playas. ¿Qué hacer? ¿Cómo nos vamos a deshacer de todo el plástico que cada día compramos en la tienda o el supermercado y, a la larga, termina contaminando el planeta? Mañana o pasado, cuando vaya de compras, échele una mirada a la góndola del supermercado: el plástico se convirtió en el empaque necesario para contenerlo todo. Al menos en un acto de contrición, vale la pena pensarlo dos veces antes de comprar lo que sea en envase plástico. PreguntaSuelta: ¿será que los brasileros de Odebrecht sí van a contar todo, todito, todo lo que saben sobre los sobornos de la Ruta del Sol II?</t>
-  </si>
-  <si>
-    <t>El visionario Marshall McLuhan predijo el asunto hace cinco décadas. Se imaginó el mundo alrededor de los medios electrónicos, especialmente de la televisión; un planeta conectado por circuitos electromagnéticos para bien o mal de la tribu. El internet, las redes sociales, los soportes audiovisuales, hoy en el reinado del coronavirus y del celular, confirmaron su visión, aunque no previó sus contornos apocalípticos, pues la incertidumbre nos ha llevado a vivir en una aldea global delirante, elemental, informada, ramplona, ilustrada, creativa, paranoica y también con mucho humor, que nos hace más vivible esta temporada en el encierro. En esta multitud de mensajes, también expresamos cómo somos: pura humanidad. Las imágenes, los memes, los pequeños discursos, los análisis sesudos son disparos a la atmósfera que nos convocan. Hagamos un repaso al azar: el coronasutra nos enseña las posiciones sexuales que evitan el contagio. Una imagen contundente: los seres humanos enjaulados en nuestras casas y los animales mirándonos como nosotros los miramos a ellos en el zoológico. Una mujer voluptuosa bailando con cadencia caribeña Mi gente, de Héctor Lavoe, que eleva las fibras más profundas del deseo. También artículos interesantes y en contravía, como los del filósofo esloveno Slajov Zizek y el pensador surcoreano Byung Chul Han, o la congelación del salario de los congresistas durante la cuarentena, qué buena idea. Un link para visitar las obras maestras del Museo del Prado en Madrid; películas, en fin, un mundo a la carta como en un restaurante descomunal. Jabalíes visitando las calles solitarias de Barcelona, pavos reales, ahora sí, pavoneándose por una Madrid acuartelada y en emergencia. O una manada de ciervos vagando curiosa por Tokio. Más de quinientos delfines rosados en las aguas pacíficas de Bahía Solano, brincando felices, porque el ser humano ha abandonado el mar. O aquellos monos furiosos y hambrientos</t>
-  </si>
-  <si>
-    <t>El confinamiento nos arrebata el horizonte. Todo lo tenemos demasiado cerca, empezando por nosotros mismos, y por eso es tan difícil dejar de oír nuestro propio eco al reflexionar sobre lo que está ocurriendo. Lo vimos cuando los intelectuales públicos más famosos del momento, Zizek, Agamben, Preciado, salieron en tromba a predecir los cambios a los que nos abocaba el virus. No hubo uno que no viera en la pandemia la confirmación de sus teorías o de sus anhelos revolucionarios. Sus reflexiones hacían pensar que estos filósofos llevaban muchísimo más tiempo confinados, sin ver el horizonte, aunque no en su casa, sino en las páginas de un libro de Michel Foucault o bajo la cerradura oxidada de su ideología. Esta salida en falso, sin embargo, ponía de manifiesto algo fabuloso, y es que la enfermedad es un hecho médico que afecta al cuerpo, sin duda, pero no solamente. La peste muy rápidamente se convierte en una metáfora que estimula e infecta la imaginación, y por eso nadie se resigna a no extraer alguna lección moral de los males que nos trae, y por eso ahora tenemos hordas de reeducadores esperando que purguemos nuestros vicios y salgamos de la cuarentena convertidos en mejores personas. Algo debe estar diciéndonos el virus sobre nuestro estilo de vida o sobre los desmanes de la globalización y del capitalismo. La pandemia no puede ser un hecho más de la naturaleza, un acontecimiento ciego y sordo, un bicho amoral que sólo busca expandirse, como la voluntad schopenhaueriana. Tiene que ser por algo y para algo; su legado no puede ser sólo la muerte y la pobreza. Así es nuestra imaginación: no se resigna a que la devastación se lo lleve todo. Si hago este pequeño análisis es porque yo no me quedo atrás. Soy el primero</t>
-  </si>
-  <si>
-    <t>Tocar la pantalla era un imposible, para ello era necesario ser hombre y hombre con deseos de descargar la vejiga. Sólo ellos podían tentar la gigantesca imagen situada al lado del exclusivo orinal. Aquel baño inalcanzable para las mujeres estaba justo a la derecha de la inmensa pared donde ocurría la vida a color, desaforada, y con final previsible. Para la hija de la taquillera, la noche que pudo palpar la polvareda dejada por los caballos en los desiertos del Oeste fue una noche milagrosa. Aún hoy, una arritmia gozosa la agobia ante el recuerdo del prodigio palpado en la noche de la infancia. El Teatro Diana, con su techo que dejaba caer luceros o chubascos, según el antojo atmosférico, era el templo donde fue posible saborear y oler la felicidad. Allí los ojos de una Medusa petrificando a diestra y siniestra. Allí el rojo atemorizante de los ambientes japoneses. Allí el amarillo del Oeste y la furia del verbo y las manos de María Félix. Allí las lágrimas jugosas de Sarita Montiel. Allí el ocre de los atardeceres en que guerreros romanos hacían de la guerra la única manera de habitar el mundo. Todo era posible en el Teatro Diana, hasta la desnudez que colmaba el aire de toda clase de befas y abucheos. Todo era posible, incluso rehacer la trama de la vida; rehacer, por ejemplo, el beso interrumpido por la cinta averiada, o la muerte detenida del bandido a la que sobrevenían de inmediato las manos todopoderosas de Mañe Mico, o tal vez ¿Alfredo?, corrigiendo la falla técnica. Dice John J. Junieles que dijo Manuel Puig: Yo fui al cine y allí encontré una realidad que me gustó. Hubo un momento, no sé cómo sucedió, en que yo decidí que la realidad era esa ficción, y que</t>
-  </si>
-  <si>
-    <t>Decía André Malraux, ese narrador y ensayista francés de pensamiento profundo y vertical como una estalactita que cala hondo y se queda pegado en los rincones de la memoria, decía, o se preguntaba a sí mismo: ¿Qué relación hay entre el hombre y el mito que ese hombre encarna?. ¿Cuál es el verdadero? Se llegan a fusionar o, al contrario, se confunden y convierten en existencias paralelas, como las sombras que jamás se nos despegan, pero no las podemos tocar ni salir de ellas. Me pregunto lo mismo ahora con la muerte prematura de Maradona, ese ídolo del fútbol, ese ser humano convertido en semidios por la masa, arrasado por ella, aplaudido, esa masa que lo llevó a la cima traidora de la fama escindiéndolo para siempre de su verdadero yo, fracturándolo en pedazos, caído como Ícaro cuando incendió sus alas por querer tocar el Sol. Pienso en Pambelé, en María Eugenia Dávila, Whitney Houston, Marilyn Monroe, Jimmy Salcedo, Michael Jackson, Amy Winehouse, Philip Seymour y Mike Tyson. Tantos empujados por la inmisericorde multitud que los llevó a la gloria, les permitió tener yates, jets, autos, piscinas, joyas, alabastros, mujeres, hombres, y los condenó a aislarse de su esencia, a olvidarse de sus temores, su soledad en medio del bullicio, sus angustias íntimas que los llevaron a buscar callar dolores internos con el consumo de drogas y alcohol, para poder reírse como Garrick, aquel que reía en el llanto y lloraba a carcajadas. La droga y el alcohol siempre son los triunfadores. Nadie les mete el gol de la victoria. Son las sustancias adictivas las que ganan siempre metiendo los autogoles que necesitan hasta ganar la partida, mutilando vidas y sueños, sin importarles quiénes son sus víctimas, sin distinguir raza, profesión o credo, sin respetar riquezas ni aplausos. El suicidio</t>
-  </si>
-  <si>
-    <t>Un ejemplo paradigmático del ilimitado alcance de la seducción es extremo, arbitrario e irrepetible. Pero no deja de ser ilustrativo. El personaje, símbolo de la Belle Époque, se llamó Agustina, luego Carolina, pero se inmortalizó como la Bella Otero sin ser particularmente hermosa. Su insólita carrera la resume bien una escena el 4 de noviembre de 1898. En una habitación del lujoso Hotel Casino París en Montecarlo, se reunieron con ella varios miembros de la realeza europea. Asistieron el zar Nicolás II de Rusia, Leopoldo II de Bélgica, Eduardo de Gales heredero de la reina Victoria Alberto I de Mónaco y Nicolás de Montenegro. El propósito de tan exclusiva cumbre: celebrarle los 30 años a la Bella Otero, amante de todos ellos. Hija de una madre soltera con siete hijos de distinto padre, Agustina Otero fue violada a los 11 años por el zapatero de Valga, un pequeño pueblo de Galicia. Sin haber pasado un solo día por la escuela, se fugó a los 14 años con Paco Colli, un vividor catalán que fue su amante, su maestro de danza y su proxeneta. En algún momento, Paco cometió el error de enamorarse, proponerle matrimonio y, según ella, estropearlo todo. De todas maneras, siguió actuando en cabarets de mala muerte y atendiendo los clientes que él le conseguía. Paco se preocupó por buscarlos cada vez más pudientes. A los pocos años, cuando las cosas parecían marchar, insistió en convencerla de que dejara el oficio. Él ya podría mantenerla, pero ella se negó de nuevo. En Montpellier ya había recibido una buena oferta matrimonial de un industrial de Lyon y la había rechazado. Fue en esas andanzas que, en Marsella, conoció a quien crearía una leyenda a su alrededor. Ernest Jurgens, un nativo de Chicago y empresario del espectáculo en Nueva York,</t>
-  </si>
-  <si>
-    <t>su órbita, en virtud de la fuerza centrífuga, hacia las profundidades del espacio, pero nadie sabe cómo se propaga ni cuál su vehículo, aunque ya le tienen nombre, gravitón , una partícula más sutil que los neutrinos y más buscada que el bosón de Higgs, la partícula que inventó la masa. La gravedad fue noticia el año pasado, cuando tres físicos estadounidenses obtuvieron el Nobel de Física por su descubrimiento de las ondas gravitacionales del choque de dos agujeros negros ocurrido hace 1.300 millones de años, coronando así un trabajo de más de 1.000 científicos de 23 nacionalidades durante los últimos 40 años. La paciencia de estos cazafantasmas se vio recompensada el 14 de septiembre de 2015, cuando las reliquias ondulares del colosal choque fueron detectadas por primera vez en la historia con los interferómetros láser de los norteamericanos. En 2004 la gravedad fue noticia en Colombia por obra de Fernando Vallejo. En la primera página de su Manualito de imposturología física , el energúmeno paisa propuso una unidad para medir la estupidez, el Aquino, en honor de santo Tomás, y evaluó en Aquinos la estupidez de los santos de la Iglesia y los genios de la física. Páginas después viene la revelación: la fórmula de la gravitación de Newton no es enteramente suya porque el valor de G solo pudo ser calculado en 1798, 71 años después de la muerte de Newton, por Henry Cavendish. Era una precisión erudita, importantísima, una primicia de primera plana, pero nadie le paró bolas. Para la fecha, Vallejo ya era un loco furioso que escupía en el Capitolio y en las iglesias acciones justas y casi piadosas, pero también insultaba a Gabo, que estaba al borde de la canonización lameculos de los poderosos, lo llamaba. Cuando los lectores leyeron su desprecio por las</t>
-  </si>
-  <si>
-    <t>La pregunta aparece referida siempre a otros cuerpos del universo, pero nos pareció inteligente y oportuno que no sé quién la formulara con relación a nuestro planeta. En efecto, a la luz de tantas embarradas y tantos despropósitos humanos y, por otra parte, conmovedoras demostraciones de sensibilidad animal que nos muestra la red, caben dudas sobre la índole del animal superior que creemos ser. La escena del perrito me llegó en un whasapazo cuando también rodaba por la red la tremenda situación de los bosques abrasados. El can, dotado de una especie de medias rojas como protección del suelo caliente, consigue traer fuera de la conflagración a los animales en riesgo. Mientras tanto, el prepotente y antipático jefe de un país dominante, con su voz impostada y su talante fastidioso, ordena la muerte de un general extranjero, y, cuando el país ofendido responde con menos saña, se ofende como se ofende un facineroso cuando lo pillan en actos punibles. ¿Cuál fuera la reacción de los países obsecuentes si, por ejemplo, el presidente venezolano Nicolás Maduro ordenara el asesinato de un militar suramericano? Es de suponerlo, lo sabemos, no nos hagamos tarugos: en coro se señalaría el hecho como criminal intromisión y como digno de rechazo universal. Pero como se trata del patrón, todos agachan la cabeza y se comen el sapo. Entonces, en este momento cabe hacer un parangón entre las conductas humana y animal, con desventaja en la calificación de la primera. Ello se refleja claramente en los incendios de bosques en varios lugares del mundo, que hacen evidente la torpe acción del hombre, de modo tan irracional que poco a poco se pone en peligro la continuidad de la vida, de la civilización humana sobre la Tierra. Y estas calamidades persisten como resultado de la conducta propia de</t>
-  </si>
-  <si>
-    <t>con una superficie de tabiques piramidales resortados y ensamblados con la técnica del box in box como los panales de huevos de los estudios de grabación pobres, que absorben hasta un 99 de los ruidos del recinto. Es la mejor aproximación lograda hasta ahora al grado cero del sonido. Un lugar endemoniado donde no existe la reverberación. La cámara antisonido. Los que la han utilizado dicen que es angustiosa, tan asfixiante como estar en medio de una oscuridad absoluta. En las antípodas de los silentes están los ruidosos. Siempre deben tener algo sonando cerca. Un radio, un televisor, algo. Pertenecen al grupo esos decoradores que padecen horror al vacío. No pueden ver un espacio libre porque de inmediato ponen allí una mata, un cuadro, una cenefa, una viñeta. Algo. Lo cierto es que sin silencios precisos todo es caos. Sin pausas, todo es barullo. La música es inseparable del ritmo, una sucesión de sonidos separados con intervalos cortos de silencios simétricos. El cine es una alternación de fotogramas y pantallas en blanco, invisibles por el fenómeno de la persistencia de las imágenes en la retina. Entre plato y plato, el lava sus papilas con pan, vino o cítricos frapeados. El perfumista lava sus mucosas aspirando café finamente molido. El fotógrafo encuadra, es decir, privilegia un fragmento del mundo y silencia el resto. Escribir es tachar. Y pausar. El doble espacio, las comas y los puntos son pausas, silencios. La literatura es un mensaje encriptado cuyo sentido oscila entre lo que el autor dice y lo que el lector adivina. Hemingway la imaginó como un iceberg: el texto, la parte visible, está sostenido sobre una masa invisible de sucesos implícitos. Los pitagóricos amaban el silencio, túnel que llevaba a la trascendencia metafísica. Antes de ser admitido en la secta, el aspirante el autor dice y lo que el lector adivina. Hemingway la imaginó como un iceberg: el texto, la parte visible, está sostenido sobre una masa invisible de sucesos implícitos. Los pitagóricos amaban el silencio, túnel que llevaba a la trascendencia metafísica. Antes de ser admitido en la secta, el aspirante debía pasar largas pruebas de silencio para alcanzar el magisterio de la palabra exacta sin ruidos, decimos hoy. Al principio fue el verbo, dicen las Escrituras. Falso, al principio fue el silencio, y así será el final.</t>
-  </si>
-  <si>
-    <t>siglo XIX, la física postulaba que sólo había una fuerza, la gravedad. Con el desarrollo del electromagnetismo se consideran dos fuerzas fundamentales: la gravedad y el campo electromagnético. En el siglo XX, los desarrollos en el conocimiento de los componentes del átomo llevan a postular cuatro fuerzas : gravedad, electromagnética, fuerza débil que explica la desintegración espontánea de los átomos y fuerza fuerte que explica por qué el núcleo no explota en un instante. No aparece ninguna fuerza de características espirituales. Los productores de la La guerra de las galaxias emplean con gran éxito el concepto místico y religioso de la fuerza; es clara la aparición de las fuerzas del bien y del mal, y los jedis son los profetas de las fuerzas del bien. No plantean en su religión la existencia de dioses del bien y del mal, sino el concepto de fuerza, que no es un dios sino una idea espiritual, una energía que en el caso de ser la fuerza buena permea todo y mantiene el orden en el universo. La fuerza mala son los siths y su profeta Darth Vader. Muchas personas ven en la saga una verdad religiosa. Esto no es de extrañar, el fundador de la religión denominada cienciología, Ron Hubbard 19111986, era un escritor de cuentos de ciencia ficción. Declaró a un grupo de seguidores, no solo por razones religiosas sino también económicas, que no era simple imaginación lo escrito, sino una verdad revelada. IA News informó que en el censo de 2001 en el Reino Unido se le preguntó a la población qué religión profesaba: más de 300.000 personas respondieron que su religión era la de los jedis y su dios la fuerza: fue en ese momento la cuarta religión más profesada. En el censo de 2011 descendió al séptimo puesto, durante en el Reino Unido se le preguntó a la población qué religión profesaba: más de 300.000 personas respondieron que su religión era la de los jedis y su dios la fuerza: fue en ese momento la cuarta religión más profesada. En el censo de 2011 descendió al séptimo puesto, durante el 2001 y el 2011 no hubo muchas películas de Star Wars. Es de esperarse que con las nuevas realizaciones mejore la posición de la religión fuerza y así lo muestre el censo del 2021.</t>
-  </si>
-  <si>
-    <t>los que ha reflexionado largo tiempo. Sabe que solo se puede escribir sobre cosas que uno ha llevado largo tiempo en la cabeza y en el corazón. Nadie puede decir, digamos, voy a investigar esta noche sobre partículas de altas energías porque tengo que hacer un ensayo físico mañana. No. Como diría san Agustín, no es bueno investigar pero es bueno haber investigado. Un buen ensayista tiene que saberlo todo sobre su materia, incluso qué es lo que los lectores saben por ejemplo, que Montaigne es el padre, para no andar repitiendo vejeces. El ensayo exige primicias y, algo que olvidan muchos, tensión. Sin tensión, la reflexión resulta flácida, enciclopédica. Académica, en el sentido tedioso del adjetivo. Pedirle rigor es un contrasentido porque el ensayo es eso, una prueba, un ejercicio, no una monografía. Es un boceto, no un óleo. Una cometa, no un ladrillo. No sentencia, especula. No repta a punta de penosos silogismos: vuela. La erudición, que es un punto de llegada en el tratado y las monografías, para el ensayista es apenas el comienzo, el trampolín donde se apoya para salvar los vacíos de la ciencia o del espíritu o sus propios límites. Exigirle rigor a un ensayista es como pedirle bibliografía a un poema o normas APA a un diagramador. El ensayista tiene licencia de irresponsabilidad. Por eso puede ir más allá del científico y escribir poéticas como Borges o metafísicas como Hawking, Steiner, Harari y Sagan. Así fue como descubrieron que el desastre de la Biblioteca de Alejandría no fue el incendio de grandes obras, sino la pérdida de un verso, la línea capaz de poner una sonrisa en los labios de Dios; que somos diestros, no zurdos, porque así nuestro puñal está más cerca del corazón del enemigo; que el lenguaje es comunicación, claro,</t>
-  </si>
-  <si>
-    <t>Batir es un arte. Lograr unas claras de huevo a punto de nieve, batiendo a mano, como hacían las abuelas, es una proeza de la física y la maña. Pero no solo son las claras, un buen chocolate, dicen en las calles, necesita tres buenas subidas que dependen de cómo se bata para lograr esa espuma deliciosa de un gran chocolate caliente. Además de estas delicias de siempre, la técnica de batir ha facilitado nuestra vida. No solo la batidora y la licuadora nos colaboran, hoy en día hay un sinfín de artículos de cocina, de todas las gamas, que nos han permitido jugar con las mezclas de frutas, verduras y lácteos que, sin dudarlo, nos han facilitado la vida. Y tengo que decirlo, también han ayudado a volvernos más creativos y a aprovechar al máximo los frutos de los árboles y la tierra. Los sorbetes, como el clásico de curuba o el de mora en leche, los smoothies cada vez más diversos y sorprendentes en las mezclas que se inventan en cada libro y receta que leo, los batidos, los jugos, las agüitas muy mexicanas como las del Chavo del 8, todos terminan siendo una delicia gastronómica gracias a la creatividad y las ganas de hacer algo refrescante con unos pocos ingredientes. Échele frutica, algo de verduras, súmele un chorrito de agua de coco, leche en sus múltiples variedades o una cucharada de helado, no le ponga azúcar las frutas tienen suficiente y tendrá la solución para un buen sorbo de energía. Si usted es muy saludable, réstele el helado, súmele una cucharada de proteína y tendrá una deliciosa bebida para recuperarse del entrenamiento o complementar unas onces energéticas. Lo que en el mundo conocemos como juicing, o la tendencia de los jugos, ha abierto la puerta para lograr</t>
-  </si>
-  <si>
-    <t>suma estrambótica. Las flatulencias, como usted sabe, son partículas en suspensión, etéreas y volátiles pero materia al fin, es decir, masa dotada de peso y fragancia, materia contante y sonante. Cada que la diva expedía un pedillo, pasaba lo que pasa cuando pee un santo impoluto o una fea anónima: sus efluvios vagaban inéditos porque la mayoría de esas partículas eran expulsadas a la atmósfera y flotaban por ahí, confundidas con el polen, cascarones de ácaros, pelillos muy livianos, escamas cutáneas, partículas de alimentos o de plásticos y todo el sinnúmero de cositas invisibles que flotan en el aire, pero siempre quedaban algunas partículas atrapadas en los encajes de los panties de la chica que hizo transpirar a dramaturgos, presidentes, magnates y héroes de béisbol. El sueco limpia la mesa con una servilleta. El resto fue fácil. Un biólogo rescató de los encajes las bacterias responsables del divino bouquet y cultivó esas reliquias en su laboratorio, donde se reprodujeron como conejos, como lo habría hecho ella misma de no haber tropezado con tanto cabrón en su corta vida. Gracias a los desvelos de este genio, el museo podrá ofrecer a sus visitantes flatos genuinos de Marilyn. Usted dirá que todo esto es fetiche, escatología; que lo sublime, lo irrepetible era ella misma y su culo duro y rosado. Tiene razón, pero recuerde que los originales son para unos pocos privilegiados, los demás tenemos que conformarnos con pósters, con los ecos y las sombras de las cosas. La hora de mi vuelo llegó y tuve que despedirme del sueco, decisión que me reprocho todos los días. ¿Qué habrá sido de su proyecto? Es probable que el museo ya esté funcionando bajo alguna fachada inofensiva y discreta. O descomunal. A veces las cosas se pueden esconder dejándolas muy visibles, como la carta</t>
-  </si>
-  <si>
-    <t>de Walt Whitman, que cito en su lengua de origen para entender su estructura con más facilidad: I celebrate myself, And what I you shall , For every atom to me as good to you, I and invite my soul, I lean and at my ease observing a spear of summer grass. Las repeticiones, tanto del sujeto el yo como de los verbos subrayados, construyen su música interna, y esa música interna, a su vez, da sentido al fondo, a la celebración que anuncia el primer verso. Dos , dos en dos conjugaciones distintas y dos hacen de pilastras para levantar la estructura. Se repite, como una oración, esa exaltación del yo. De otro lado, cada afirmación parece abrirse a otra, de modo que la celebración nunca acaba y se vuelve meditativa. Comienza en el yo y termina en la hierba . El poema sirve para rumiar. Algo similar sucede en los versos del inglés William Blake la traducción es de Fernando Castanedo en Cátedra: Durante la siembra, aprende; en la cosecha, enseña; y en invierno, disfruta. Conduce tu carro y tu arado sobre los huesos de los muertos. El camino del exceso lleva al palacio de la sabiduría. Prudencia es una doncella vieja, rica y fea, y a la que corteja Ineptitud. El que desea pero no actúa cría podredumbre. Se suma a la musicalidad y la meditación un tono de solemne didactismo. Blake está enseñando algo: cada línea es en realidad un aforismo, una unidad independiente, sentenciosa y circular. Tiene un color bíblico, como el de Whitman, y carga reminiscencias de los versículos. De hecho, este bloque que pertenece a se titula De modo que el verso libre o al menos su rama más interesante no es tan libre: se afinca en una musicalidad poética y en una</t>
-  </si>
-  <si>
-    <t>Dábamos por hecho que los bombillos siempre prendían y el agua siempre corría, sin embargo, hoy cuando el agua salió fría por un momento y la luz no prendió, fui consciente de las cosas que dábamos por hecho son esas cosas a la mano, de las que habla Martin Heidegger. Una categoría que se entiende, cuando las cosas que dábamos por hecho no funcionan y ahí es cuando somos conscientes por fin de su existencia. Es el acto de adquirir conciencia de todo cuanto dábamos por hecho. Tal cual como nos pasa ahora, empezamos a ser conscientes de cosas que antes eran invisibles ante nosotros. Lo que era normal en el día a día, ahora lo pensamos como un privilegio, como el simple hecho de salir de casa. Antes podíamos andar por el mundo sin restricciones, ahora pensar en viajar puede traernos, la nostalgia del último viaje que hicimos o el anhelo del próximo que ansiamos tener. Sin embargo, la imposibilidad de conectarnos con la naturaleza o de viajar a una playa, montaña o rio, ha provocado no solo la abismal caída del sector turístico, sino que ha traído consecuencias directas a nuestro bienestar; nos ha provocado ansiedad, irritabilidad y estrés. Sin saberlo somos víctimas del llamado trastorno por déficit de naturaleza o TDN, que aunque muchos por vivir en una ciudad ya sufrían, ahora todos por estar confinados, empezamos a saborear. No es un secreto que el turismo es uno de los sectores más afectados por la Covid 19, según las cifras de la organización Mundial del Turismo OMT, 1 de cada 10 empleos en el mundo corresponde a este sector. Por eso distintos actores del sector ya están ocupados en buscar soluciones para activarlo cuando el mundo regrese a la normalidad. Mientras esto pasa, el turismo se reinventa</t>
-  </si>
-  <si>
-    <t>¿El Cesar, un laboratorio de convivencia? Es increíble, casi un absurdo, sabiendo que fue uno de los departamentos más golpeados por el conflicto armado, primero por la guerrilla y luego por los paracos. No en vano allí nacieron Simón Trinidad y Jorge 40. Pero fue justo esta dimensión gigante del conflicto, sumada a la necesidad de convertir esta región en referente de reconciliación, lo que llevó a Sergio Jaramillo y a su asesor, Diego Bautista, a implementar allí desde hace casi un año una idea que, luego del plebiscito por la paz, se convirtió en un sueño urgente, cuyos resultados se dieron a conocer el pasado lunes en un ejercicio muy bien acogido en el Cesar, previo al lanzamiento público que se hará en los próximos días. El proceso comenzó cuando Bautista visitaba la región de los Montes de María trabajando para la Fundación Semana. Allí conoció a John Paul Lederach, experto mediador de conflictos. Juntos quisieron cristalizar la teoría que el gurú en construcción de paz escribió en La imaginación moral, su libro más conocido, pero la fragmentación social y la desconfianza en esa región llevaron al traste el intento. Vinculado luego como asesor de Sergio Jaramillo, Bautista comenzó a recorrer el país durante el proceso de paz con la idea de conocer lo que los colombianos pensaban al respecto y traducirlo luego en temas de la agenda en La Habana. Debido a la enorme desconfianza, marcada tanto por el conflicto mismo como por la ausencia de Estado, durante ese proceso fue imposible reunir los diversos intereses y derechos que se contraponían en un mismo territorio. Esta desconfianza era de tal magnitud que lo obligaba a desayunar con el sector privado, pasar el día con los líderes sociales y cenar con el sector público. Era imposible tenerlos juntos a</t>
-  </si>
-  <si>
-    <t>Son 21 exhibiciones: están el majestuoso cóndor, la enorme águila arpía, los flamencos, las guacamayas, loros, pelícanos diversos, tucanes y tantas otras especies. El recorrido se realiza por senderos bien construidos y mantenidos entre los manglares y el bosque seco tropical del Caribe colombiano. Un fascinante espectáculo de color y naturaleza. El avistamiento de aves se ha convertido en uno de los renglones más dinámicos del turismo internacional. Para Cartagena es un activo enorme. Sin embargo, el gobierno local poco hace por promover y consolidar esta excelente iniciativa privada, que yo calificaría de quijotesca. Este es el tipo de bien público que la ciudad necesita para atraer un turismo educado, familiar, que le aporte al desarrollo local. Me parece que el Aviario de Barú no ha recibido todo el reconocimiento que se merece. Ojalá los medios de comunicación le den mucho despliegue a esta obra fruto de la tenacidad de sus promotores. Las malas noticias reciben una cobertura desproporcionada. El aviario es un ejemplo de buenas noticias. Miles y miles de colombianos visitan cada año Cartagena, y todos deberían poder conocer este oasis de respeto por el medio ambiente. La entrada no es económica, pero sospecho que está muy subsidiada en virtud del respaldo económico de empresarios colombianos que han querido apoyar esta iniciativa que protege el patrimonio de nuestro país. Queda uno muy satisfecho con esta visita a un lugar de excelencia para el ecoturismo. ¡Aplausos para estos colombianos que trabajan callados! 876454 20190817T00:00:5305:00 column 20190817T00:15:0105:00 email protected none La Colombia que trabaja 24 3191 3215 La Colombia que trabaja 24 3191 3215</t>
-  </si>
-  <si>
-    <t>archipiélago de San Bernardo, a hora y media de Cartagena, que él mismo denominó La Gaviota y cuya existencia insulta, además de la normatividad, la pobreza de los habitantes del vecino Santa Cruz del Islote. Pues bien, Pretelt amplió recientemente el daño ecológico y, con este, las instalaciones de su casa, aunque sobre ese bien pesan dos investigaciones en Parques Nacionales, una de 2015 y otra de 2018, por construcción de barrera y relleno con afectación de pastos marinos y corales, la primera; y por reparación de una casa, aumento a tres plantas y nueva estructura de protección sin licencia ambiental ni licencia de construcción, la segunda. No obstante que el exvicerrector y cofundador de la progubernamental Universidad Sergio Arboleda dio clases de Derecho por años, ha ignorado, olímpicamente, la Resolución 1424 de 1996 hace 23 años del Ministerio de Ambiente en que se ordena la suspensión de las construcciones en el área del Parque Nacional Natural Los Corales del Rosario, en las islas del Rosario y el archipiélago de San Bernardo ver . Nada vale si se trata de Pretelt: pillados en flagrancia, tres de sus obreros fueron detenidos y conducidos a Cartagena, en operación conjunta entre funcionarios de Parques, Policía y Armada cuando adelantaban la reparación de la casa: muy pronto fueron dejados en libertad por falta de pruebas. Pero ahí no se detiene la historia. En la Agencia Nacional de Tierras, antes Incoder, antes Unidad Nacional de Tierras, hay un expediente contra Pretelt Chaljub desde febrero de 2008 que pretende recuperar el bien indebidamente ocupado, denominado La Gaviota. Desde entonces, servidores de esas entidades han intentado notificar al implicado Pretelt sin lograrlo; han fijado edictos emplazatorios; han ordenado y ejecutado inspecciones oculares; ha desaparecido la investigación y vuelto a aparecer. Y cuando finalmente terminó su trámite y</t>
-  </si>
-  <si>
-    <t>La escena en vivo domina la música. Los conciertos y los distintos festivales musicales que han tomado fuerza en Colombia están marcando una línea importante para el camino sonoro y están demostrando que estamos siendo partícipes de un crecimiento notorio en la asistencia a estos eventos. El Monterey Pop Festival y el Festival de Woodstock son recordados como los dos encuentros musicales pioneros a nivel mundial. Ambos se celebraron a finales de la década de los 60 en 1967 y 1969 respectivamente y fueron símbolos de una generación joven que buscaba transmitir mensajes de unión y cambio a través de la cultura. El primer acercamiento festivalero en Colombia se dio en Antioquia. La Estrella fue la casa del Festival de Ancón en junio de 1971, una especie de Woodstock criollo. Terrón de Sueños, la Gran Sociedad del Estado, Columna de Fuego y Los Mosters, entre muchos otros, fueron los Santana, Hendrix, Jefferson Airplane y Creedence Clearwater Revival de un encuentro musical que intentó dar un primer espacio relevante a la música. Pero mientras en el mundo aparecían Glastonbury, Rock in Rio, Lollapalooza y Coachella, Colombia seguía siendo un país ahogado en un pozo. El gran Concierto de Conciertos, realizado en el Estadio El Campín en septiembre de 1988, está en la mente de los bogotanos como el primer gran evento musical en la capital. Desde Compañía Ilimitada, pasando por Franco De Vita y Los Prisioneros hasta el cierre del argentino Miguel Mateos, y a pesar de los problemas logísticos con la programación y con los artistas en los camerinos, Bogotá sintió por primera vez en su historia que era posible ver y sentir la música. La tarea era esa, organizar un encuentro cultural y de identificación juvenil. Con esa idea, en 1995 nació un hijo que ya se ha convertido</t>
-  </si>
-  <si>
-    <t>Entre los periodistas existe un código para clasificar una noticia: Paisaje. Una palabra que resume uno de los principios del oficio, que la noticia sea lo nuevo. Como cuando uno sale de paseo con la familia y se entusiasma con la primera vaca que ve con su ternerito. Les toma foto. Pero cuando llega a su destino las vacas son paisaje. Eso era la embarcación Open Arms que en español traduce Brazos Abiertos cuando el mundo se enteró de su desgracia. El barco, que pertenece a una ONG con base en Barcelona, llevaba 40 días patrullando el Mediterráneo en un esfuerzo por evitar que este merezca el título de el mar de sangre, pues en sus aguas han muerto casi 700 personas en lo que va del año, en especial frente a la costa de Libia. En la madrugada del 2 de agosto, cuando aún no amanecía, dieron con su razón de ser. Encontraron dos precarias embarcaciones cargadas con migrantes africanos que naufragaban. En la primera venían 55 personas, en la segunda 69. Hasta ahí, era paisaje. Incluso lo que pasó después sonaba a un titular tantas veces repetido. El gobierno italiano, por orden de su ministro del Interior, el ultraderechista Matteo Salvini, negó la entrada a los migrantes, argumentando que su país no será un campo de refugiados. Tal vez Salvini no sabía o no le importaba y me inclino más por esta segunda opción lo que sucedía a bordo del barco. El Open Arms era un infierno. Sus pasajeros eran víctimas de la guerra que no soportaban un desplante más de la humanidad. Lo advirtió la tripulación desde el mismo día en que los recogió. En estos momentos la emergencia es psicológica, trinó esa noche uno de los médicos que trabaja con la ONG y contó que los</t>
-  </si>
-  <si>
-    <t>profundidad? Es sublime. Una sirena que nada con la sutileza de una fragata portuguesa, sin su dañina ponzoña, mientras baja hacia la oscuridad de las aguas. Segura, diestra, elegante, hermosa. ¡Hija de Neptuno! Repito y repito el video, dominado por tanta belleza casi irreal. Lo pongo en slow motion y alrededor de Sofíagómezuribe me parece ver escualos y lestrigones y cíclopes y pitones. Veo quelidras, báculos y faras, todas acuáticas, y cencros y anfisbenas y demás criaturas de La odisea , de Homero. Y eso, sin dosis mínima. En estos días, un tuitero le dijo que no batiera más marcas. Respeta a Poseidón, dios de los mares, le advirtió. Ella le respondió con naturalidad: Poseidón es mi papá y me da permiso.... Ochenta y seis metros, o sea, más o menos un edificio de 34 pisos, sin contar el sótano, ida y vuelta. Y todo sin respirar: dos minutos y 57 segundos. Hagan la prueba, damas y caballeros. Tomen aire, tápense la nariz y aguanten ¿Cuánto tiempo soportaron? Van bien. Ahora solo les falta aprender a nadar. Emoticón de carita sacando la lengua. Rabito: Lo decisivo jamás se muestra, ni siquiera se comunica, o no en su momento; al contrario, se esconde y se silencia siempre, o durante muchísimo tiempo: si acaso se cuenta cuando ya no interesa, cuando es pasado remoto, y a la gente el pasado le trae sin cuidado, cree que no le afecta y que no puede cambiarse, y lleva razón con esto último. Javier Marías. Berta Isla , septiembre de 2017. Rabillo: Lo que pasa prosiguió Nocio es que son unos católicos. Son unos católicos viejos, fanáticos, siniestros. Y no lo saben. Lástima que la Iglesia católica tenga tanta prisa por adecuarse a los nuevos tiempos: si se endureciese, si volviese a ser intransigente y</t>
-  </si>
-  <si>
-    <t>sus intereses e hicieron un despliegue militar en el área. Pasando a nuestro hemisferio, Colombia y los Estados Unidos firmaron en 1972 un tratado mediante el cual se puso fin al condominio que, sobre el cayo de Quitasueño y los de Roncador y Serrana pertenecientes al archipiélago de San Andrés, se había pactado desde 1928. Sin embargo, en el tratado, los Estados Unidos sólo retiraron sus pretensiones sobre los cayos, pero no reconocieron expresamente que eran colombianos. Exigieron además derechos de pesca para sus buques en áreas marítimas del archipiélago. Para completar, declararon que Quitasueño no emergía en pleamar y que por lo tanto no era susceptible de soberanía, lo que era un tácito respaldo a las pretensiones de Nicaragua. Durante la primera fase del diferendo entre Colombia y Nicaragua respecto a la soberanía sobre el archipiélago de San Andrés y la delimitación marítima común en la Corte Internacional de Justicia, Nicaragua sostuvo la misma posición de los Estados Unidos con respecto a Quitasueño. Sin embargo, en su fallo de 2012 el alto tribunal rechazó la pretensión nicaragüense, y de pasada la de los Estados Unidos, señalando que Quitasueño pertenecía a Colombia y que no obstante que es una roca que solo emerge un par de metros sobre el mar, era una isla y que pertenecía a nuestro país. Por consiguiente, genera 3.500 kilómetros cuadrados de mar territorial e incluso zona contigua. Es curioso que precisamente después del fallo de la Corte en el litigio colombonicaragüense, China acelerara las obras de relleno en los cayos y bajos del Mar de la China, en los cuales ha construido edificaciones y pistas de aterrizaje e instalado plataformas para lanzamiento de cohetes colocando las relaciones chinonorteamericanas en estado crítico. Decano de la facultad de Gobierno, Ciencia Política y Relaciones Internacionales de la universidad de relleno en los cayos y bajos del Mar de la China, en los cuales ha construido edificaciones y pistas de aterrizaje e instalado plataformas para lanzamiento de cohetes colocando las relaciones chinonorteamericanas en estado crítico. Decano de la facultad de Gobierno, Ciencia Política y Relaciones Internacionales de la universidad del Rosario.</t>
-  </si>
-  <si>
-    <t>la alcaldesa Claudia López, que trate de ponerla contra las cuerdas por supuestamente privatizar la salud, está bien que el exburgomaestre defienda su gestión al mando del distrito, que convoque al paro y a que la gente se tome las calles de manera pacifica. Petro está haciendo lo que trataron otros, pero que no los dejaron. Los eliminaron a balazos. En ese sentido, es un sobreviviente que a su manera busca que Colombia, por fin, de un salto a la modernidad. Porque ese es otro problema de la interpretación del discurso de quienes hacen oposición: las palabras caen en ese profundo vacío de prejuicios ideológicos. Y sus enemigos sí, enemigos, porque todavía en el ejercicio de la política en Colombia no hay adversarios oyen sólo lo que se imaginan: un Chávez sin botas ni charreteras, dispuesto a expropiar, sin ton ni son, desde el grupo Aval hasta la más humilde tienda de barrio. No entienden que la izquierda, de tanta lucha bañada en sangre, se curó de maximalismos. Que ya nadie busca instaurar el socialismo, ni siquiera el del siglo XXI. Al final, Petrosky no tenía cáncer pero sí demostró que confía más en los médicos cubanos que en los colombianos como lo reveló en su blog Patricia Janiot. Algo que, por supuesto, no es una primicia, porque así como el senador de la Colombia Humana se va a la isla de los Castro a tratarse su problema de salud, hay otros con grandes recursos económicos que buscan curarse de cáncer o por lo menos tener un diagnostico para ellos confiable en Huston, Nueva York o Miami, y no en la Fundación Santa Fé o en el Instituto Nacional de Cancerología de Bogotá. La acción política de Petro y también la de los dirigentes regionales y los desmovilizados de las</t>
-  </si>
-  <si>
-    <t>salas de emergencia antes de ser atendidos, y miles esperando ambulancias. También anotó la carta que se había convertido en rutina que los pacientes esperaran hasta 12 horas en tarimas en los corredores antes de asignarles una cama adecuada. Dijo, además, que 120 pacientes por día se atendían en los corredores, muchos de ellos con tratamientos humillantes, como problemas ginecológicos, a la vista de los demás pacientes. Resulta tentador creer que estos casos extremos de horror son de rara ocurrencia. Pero la norma parece ser que los sistemas de salud socializados viven en un estado de crisis permanente. En la primera semana de 2018, no menos del 97 de los centros de salud ingleses reportaron congestiones tan severas que se tornaron inseguros. Resumo lo que ha respondido la señora primera ministra. La congestión se debe al pico sin precedentes de una enfermedad estacional, la influenza, en esta época del año. Tampoco se debe desconocer el envejecimiento de la población. Los verdaderos culpables son los gobiernos locales que no han construido más hospitales. El señor Pickering no ofrece soluciones, tan solo se limita a afirmar que mientras permanezca la salud organizada como un monopolio estatal financiado por los contribuyentes, fracasará como han fracasado todos los monopolios similares. Sugiere al finalizar que la reforma fundamental estriba en darles en Gran Bretaña más libertades tanto a los administradores de la salud como a los consumidores. Tiene razón, las soluciones no son nada fáciles. Sugiere, acaso, ¿participación de la empresa privada con la supervisión eficaz y prudente del Estado? eficaz y prudente del Estado?</t>
-  </si>
-  <si>
-    <t>de aislamiento preventivo obligatorio? No podemos pecar de ingenuos, mucho menos en este país donde reina la ley del codazo y, mediante este proceder, no nos importa a qué o quién nos llevemos por delante. Puede ser también que por estos días nos estemos dando cuenta de que el sistema de salud que se aplica en nuestro país es peor que el mismo COVID19. Por algo un compatriota que no quiso ser repatriado aseguró que prefería una tumba en China y no una EPS en Colombia. Todos sabemos lo mal que resultó el poner la salud a la orden del mercado, y todos sabemos que corregir este error será una tarea titánica, que por supuesto el Gobierno Nacional no asumirá, porque para eso se requiere tener algo que el primer mandatario ha dejado muy claro que le falta: decisión y carácter. Seamos sinceros, milagros no habrá. En este sentido, tampoco esperemos que los bancos sean más benevolentes, que la clase empresarial tenga sentido de humanidad, porque, al contrario, esta será la oportunidad de oro para que comiencen a aplicar la idea de la ministra Alicia Arango de contratar por horas a unas personas de estratos 3, 2 y 1 que, al no tener más opción para llevarles de comer a sus hijos, sin duda lo aceptarán. Gracias, doctora Arango. Tampoco se puede pretender que el presidente Duque demuestre que llegó al Palacio de Nariño para gobernar y no para ser gobernado por otro, porque lo hemos de seguir viendo por televisión en esa especie de Alo, presidente, con poses poco naturales, robotizado repitiendo un libreto, leyendo un teleprónter que otro escribe, anunciando decretos e ideas que en el papel suenan bonitos, pero llevados a la realidad son, como bien lo dijo el colega Juan Roberto Vargas, carreta, como las famosas</t>
-  </si>
-  <si>
-    <t>El doctor Bruce Aylward es el asesor sénior del director general de la Organización Mundial de la Salud OMS y uno de los especialistas más reconocidos globalmente en la lucha contra la pandemia de COVID19. Lideró la misión de la OMS que en febrero pasado visitó China, para estudiar la efectividad de la respuesta del país al coronavirus, recomendando las medidas que tomó Beijing en la lucha contra el virus. En reciente entrevista para Time , afirmó que China, habiendo identificado el virus en enero, acometió una respuesta integral implementando toda la batería de acciones al tiempo, de suerte que, después de tres meses, estarán saliendo de la pandemia a finales de marzo. A la pregunta ¿qué vislumbra que ocurrirá en el semestre inmediato?, respondió: Depende de lo que hagamos como países y como sociedades. Si hacemos pruebas de cada caso individual y aislamiento inmediato de los casos, seremos capaces de mantener el conteo bajo. Si se confía solamente en las medidas del cierre total cuarentenas sin buscar cada caso, cada vez que las suspendan, el virus retornará en oleadas. Respecto a las cuarentenas, las identificó como una forma para comprar tiempo, estableciendo estas enormes parálisis del aparato productivo nacional. Agregó: Realmente no paran el virus; lo suprimen, lo ralentizan. Enfatizó en que es un desperdicio no usar ese tiempo para organizar la estrategia del tamizaje y manejar a escala individual los casos que van a ser fundamentales para suspender la pandemia. En caso de no hacerlo así, el virus nos va a poner fuera de juego, circulará calladamente entre los habitantes y permitiremos que vuelva de nuevo, afirmó Aylward. Interrogado sobre ¿cuál debe ser la prioridad de un país después de haber bloqueado la actividad ciudadana?, respondió categóricamente: Tamizaje, tamizaje, tamizaje tamizar a cada uno, tamizar a los sospechosos.</t>
-  </si>
-  <si>
-    <t>En mi pasada columna examiné dos supuestos del decreto del presidente Duque que autoriza a la policía a destruir cualquier cantidad de droga encontrada en requisas: que la represión lograría reducir el abuso de sustancias psicoactivas y que todos los consumidores de estas sustancias tienen o causan graves problemas. Mostré que ambos son prejuicios sin fundamento empírico. En esta columna señalo otro prejuicio de este decreto y sus graves efectos negativos en la práctica. El Gobierno y quienes apoyan la medida suponen que se trata de una novedosa estrategia para incrementar la seguridad ciudadana, pues facilitaría el combate al microtráfico y protegería a los niños de las drogas. El presidente Duque ha dicho que por eso ese decreto se fundamenta en el lema: Primero los niños. Pero nada de eso parece cierto. Si bien la medida no es novedosa, pues el Código de Policía ya autorizaba a los agentes a destruir la droga incautada, no se debe minimizar el impacto del decreto, porque la autorización legal del código se ha vuelto ahora prácticamente una orden presidencial de incrementar las requisas policiales para incautar y destruir droga. Y efectivamente, después de promulgado el decreto, estamos viviendo una sobredosis de ese tipo de requisas. Algunos objetarán que eso no es malo, con el argumento de que esos operativos ayudan a desarticular el microtráfico y protegen a los niños. El presidente va en esa dirección, pues dijo que la primera semana de aplicación del decreto había permitido recuperar de las garras del narcotráfico 136 parques y 172 entornos educativos. Pero no es fácil entender la lógica de esta estrategia de seguridad. Si la policía recibe información de que hay microtráfico en un parque o en un entorno escolar, puede actuar inteligentemente contra estas organizaciones, por ejemplo vigilando la zona para filmar a sus</t>
-  </si>
-  <si>
-    <t>Médicos para Mercados Emergentes de la farmacéutica, aseguró en Caracol Radio que las vacunas se entregarían según orden de pedido. Dijo que países como Costa Rica, Panamá, Perú y Chile se habían anticipado y que Colombia apenas estaba en conversaciones. Pero la mayor prueba de lentitud es la demora del Gobierno para darle mensaje de urgencia a la ley que permite comprar vacunas a riesgo. El proyecto lo radicó el 28 de julio el representante Ricardo Ferro, pero el mensaje de urgencia llegó dos meses y 21 días después. On the record, el ministro de Salud aseguraba que había que esperar cuál era la vacuna más segura. Off the record, decía que el proyecto, que también presentaron el senador Luis Fernando Velasco y el representante Carlos Ardila, era muy importante. Hubo un duro debate de control político en el que se advirtió lo que iba a suceder. No hay una estrategia diplomática para la negociación de vacunas en fase III y es necesario ajustar el marco jurídico que permita la compra de dosis suficientes, insistió José Daniel López. Pero entonces nadie reaccionó. Hoy en día Colombia está, junto con la mayoría de países africanos, entre los últimos que tendrán vacunas. Mientras tanto, el Gobierno anuncia una nueva reforma tributaria para cubrir los costos de la pandemia y parece no tener conciencia de que es más barato invertir en vacunas que en UCI. Todavía estamos en el reto de saber si las vacunas son ciento por ciento efectivas, si se requiere una, dos o cuántas dosis, cómo se va a universalizar y si hay algún tratamiento, dijo Duque el 3 de diciembre. Tanta prevención y acción para no saber que esa información ya la tiene el mundo. una, dos o cuántas dosis, cómo se va a universalizar y si hay algún tratamiento, dijo Duque el 3 de diciembre. Tanta prevención y acción para no saber que esa información ya la tiene el mundo.</t>
-  </si>
-  <si>
-    <t>La gestión del Gobierno Nacional alrededor de la adquisición de 40 millones de dosis de vacunas, 10 millones de Pfizer, 10 de Astrazeneca y 20 por la plataforma COVAX, merece un reconocimiento de la sociedad. Hay buen ministro de Salud, Fernando Ruiz, sobrio, que inspira confianza, buen comunicador y articulador de esfuerzos con los mandatarios locales. Y, sin duda, un enhorabuena a su jefe, el presidente Duque, independiente de cualquier otro tipo de objeciones que muchos tengamos en otros ámbitos. Se percibe una luz en este oscuro 2021, un túnel que jamás hubiéramos imaginado en la Nochebuena de hace un año. Sin embargo, el proceso de vacunación hay que verlo en su complejidad. Ya muchos piensan que de ésta salimos ya, que pronto estaremos de vuelta a la normalidad plena. Pensamiento mágico, parejo a la indisciplina social. Cuando el presidente dice que en febrero se inicia la aplicación de las vacunas, está refiriéndose a un largo camino que tomará muchos meses para coronar con la cobertura universal de la población. Durante los próximos meses el mundo seguirá inmerso en la ola creciente de contagios y muertes, en la saturación de los aparatos hospitalarios de urgencias en distintas latitudes. Las reacciones de parte de los gobiernos están a la vista. En Alemania se ha ordenado el cierre de todos los negocios con excepción de farmacias, supermercados y algunas sucursales bancarias. Londres ha quedado aislado y naciones europeas han prohibido, por algunas semanas, el ingreso de súbditos británicos. Y así sucesivamente Son varios los aspectos que debemos considerar, entre ellos dos: la fase de alza en los contagios en la que nos encontramos, primero, y el complejo proceso de distribución de la vacuna, segundo. Primero: alguien comparó la vacuna contra el Covid con un extinguidor apagando un incendio; podrá ser de primera</t>
-  </si>
-  <si>
-    <t>El reloj de la crisis climática nos muestra este segundo en el que escribo que nos quedan 15 años, 3 meses y 2 días para alcanzar la temperatura de 1,5 C de recalentamiento global. En el minuto en que usted abra el vínculo, estaremos emitiendo 40 millones de toneladas métricas de CO a la atmósfera terrestre. Con esta bomba de tiempo entre las células estoy leyendo dos informes de tonos muy disímiles: el último reporte del Grupo Intergubernamental de Expertos sobre el Cambio Climático IPPC y el boletín reciente de los activistas corajudos de Extinction Rebellion. El segundo comienza con urgencia sincera y con humor inglés. Felicitaciones, sobrevivió usted al mes más caliente jamás registrado. Y nos recuerda que algo no anda bien cuando en estos días en Suecia, arriba del círculo ártico, la temperatura llegó a 35 C, hubo incendios forestales en Siberia y desapareció con el rugido de la crisis climática el primer glaciar de Islandia, el Okjkull, o abreviado en sarcasmo, el Ok, que no está ok. Desde luego ante este reporte de cariz justificadamente alarmante, el informe del IPPC es en contraste de una pachorra sorprendente que raya en lo baboso; está redactado como para ser leído en voz alta en la Casa de Nariño. El tema es crucial, ciertamente: la gestión sostenible de los suelos de la tierra, la seguridad alimentaria, la desertificación y la necesidad del cambio a cultivos y dietas sostenibles. Pero si llega a nuestros gobernantes, por ejemplo, se tomarán otros 200 años hipotéticos en resolver estos asuntos, cuando si quedan 30 de bienestar en el planeta no quedan muchos más, a no ser que mañana el sistema diera un vuelco, lo que es muy improbable que suceda. ¿Qué va a pasar entonces y qué hacer? Afortunadamente nadie tiene la respuesta. Lo</t>
-  </si>
-  <si>
-    <t>En la edición del 8 de junio último, en este periódico el avezado periodista Leopoldo Villar Borda hizo un recuento de lo ocurrido en Bogotá los días 8 y 9 de junio de 1954, fechas ingratas en la historia del país y, particularmente, en la del martirologio estudiantil. Como él lo registra, los acontecimientos luctuosos sucedidos en la Ciudad Universitaria y en la carrera séptima con calle 13 fueron y seguirán siendo motivo de investigación y de controvertidos comentarios. Precisamente, su análisis da lugar a algunas precisiones, que es lo que pretendo hacer en la presente columna. Como testigo de excepción que fui de lo acontecido, considero que es de mi obligación seguir haciendo aportes a la búsqueda de la verdad de una ignominiosa página de nuestra historia. Para entonces yo era estudiante de medicina en la Universidad Nacional y presidente de la Federación Médica Estudiantil. Varios de mis compañeros fueron inmolados en aquellas aciagas fechas. En tributo a su memoria escribo estas líneas aclaratorias. En los días previos al 8 y el 9 de junio existía malestar en la Facultad de Odontología, pues su decano se había identificado con la política oficial de autorizar el ejercicio de la profesión a quienes venían haciéndolo en calidad de teguas o empíricos. Los pichones de odontólogos expresaban su inconformidad de manera ruidosa frente al despacho del decano. Este, en la tarde del jueves 8 de junio, temeroso de que el bullicio terminara en asonada, comunicó su sospecha a la Secretaría General, de donde salió la solicitud telefónica de que la Policía hiciera acto de presencia en el campus para aplacar los ánimos exaltados de los estudiantes. No fue, pues, que los policías ingresaran a la Ciudad Universitaria motu proprio. Como era de esperar, un grupo de estudiantes se percató de su presencia</t>
-  </si>
-  <si>
-    <t>El primero de cada mes Tras reapertura el 1 de septiembre el plan del segmento gastronómico es volver a ganar confianza de comensales. El Colombiano. Se dice que a principios del año 2019 pasó por estos lares un personaje que predicaba el cambio obligatorio de la forma del primer día de cada mes con el numeral cardinal un y se prohibía el numeral ordinal primero. Mucha gente creyó en su perorata. La Real Academia Española no ha implantado norma diferente; aunque en España se usan ambas formas. La forma aceptada para los ordinales es 1. y otra para los numerales ordinales: 1. Los acrónimos Sé que me voy a ganar unos cuantos enemigos, procuraré no ser doloroso y se trata de unos que se ven. Varias veces lo he dicho: los acrónimos son palabras que se forman con letras de su nombre real. Por ejemplo: Mintic viene de Ministerio de Tecnologías de la Información y Comunicaciones, no son necesarias en mayúsculas las tres últimas letras. Si se trata del ministro, va en todo en minúscula: mintic. El caso en que a la Índer nadie le pone tilde se debe que en las vallas de propaganda el punto de la i forma la cabeza de un jugador que completa el aviso; cambiarle la cabeza por una tilde sería difícil. De plural a singular Tres de cada cuatro personas en edad de retiro no recibe ningún ingreso laboral o pensional. El Colombiano. El gazapo está influenciado por los aquellos en los que las cantidades se reparten por porcentajes en los que son contados en singular, siendo en plural así: si son tres los que no reciben y uno los que sí reciben. Las pilas Pilas pues transeúntes y autoridades. El Colombiano. Aquí faltan dos comas: la primera muestra lo que hay que las cantidades se reparten por porcentajes en los que son contados en singular, siendo en plural así: si son tres los que no reciben y uno los que sí reciben. Las pilas Pilas pues transeúntes y autoridades. El Colombiano. Aquí faltan dos comas: la primera muestra lo que hay que hacer y la segunda es la coma del vocativo a quienes deben alertarse y los que deben hacer el arreglo. Pilas, pues, transeúntes y autoridades. gazapera.com</t>
-  </si>
-  <si>
-    <t>Sobre un suelo que empieza a cuartearse, se esparcen profusamente hojas amarillentas como de un otoño que apenas rozara estos parajes y dejara destellos a su paso. Hojas rojizas de almendros que el viento ni siquiera se molesta en desprender cansadas de vagar entre ramas, la fuerza de su ánima vegetal las deja caer. De suspirar sin esperanzas por un otoño remoto, incapaz de aposentarse entre el verde rotundo del invierno y el pardo marchito de un verano que empieza a rondar por los alares de la casa solariega que aún llevo como un caparazón de amor, de vida, sobre mi vida entera. Un verano tímido, lento y parsimonioso, que poco a poco se va metiendo entre las cosas, hurga en el rústico fogón de cenizas de otro tiempo, en algún tizón que alumbre la memoria de una infancia que nunca acaba de pasar. De un cántico de luz que en lo más hondo del alma deja en nosotros su inasible melodía; los colores invisibles de un arcoíris que apacigua pestes y contagios de un cielo azul de diciembre sin una nube que lo manche, al que mi madre saluda en el fervor de sus 102 años De alguna lluvia remota que en lo más alto del verano germine en flores amarillas con aromas de eternidad para espantar el aire de vejez que nos habita por instantes. Una mujer de tez blanca y ojos verdes vuelve de su infancia cada noche para contarnos de la luna y de los bosques que la cuidan cuando es llena; de pájaros gigantes y reinas de trapo coronadas por príncipes plebeyos. En las madrugadas, papá calzando sus abarcas de tres puntas, vistiendo sus coletas, multiplicando con sus manos de campesino para sus hijos y mamá un pan que nunca fue amargo por escaso que</t>
-  </si>
-  <si>
-    <t>Llegará el día, más pronto que tarde, cuando salgamos de este tiempo sin tiempo, en el que queramos que alguien nos conteste del otro lado de la línea. Alguien que cuando le preguntemos esto o aquello se quede pensando un par de segundos y nos responda. Lo que sea, pero que nos responda y que podamos contrapreguntarle, y si es el caso, luego, sin prisas, conversar de la vida, o de la nada, o del cielo plomizo y las gotas de lluvia que empiezan a caer. O del silencio. Y llegará el día en el que queramos comprar una camiseta que solo sea esa, ni más bonita ni menos bonita que las otras, solo esa, hecha por las manos de alguien, y cosida con un dedal y una aguja usadas decenas de veces, esa y solo esa, y que por ser esa nos diga y nos grite que es auténtica, única, hecha por humanos y para humanos. Llegará el día en el que queramos que las noticias parezcan surgidas de un periodista, con sus ritmos y sus palabras y sus tonos y sus verdades y sus mentiras, también. Que parezcan el fruto de la decisión de un humano, y no el de una máquina que le dicte qué escribir, dónde poner las palabras que más venden, de qué extensión hacer los párrafos, por dónde comenzar la noticia y en qué lugar hacer un giro que llame la atención del lector, y llegará el día en el que queramos que haya lectores que elijan un texto porque se identificaron con él, porque les recordó una película, porque era distinto a los demás, porque no entendieron bien el título, porque estuvo escrita con todas las palabra y todos los artículos, o sencillamente, porque era una historia de un ser anodino, humano por</t>
-  </si>
-  <si>
-    <t>La ciudad de Washington, capital de EE.UU., está viviendo un nuevo invierno de su descontento, como diría Shakespeare. Los árboles carecen de hojas, los días son fríos y breves, y la nieve empieza a blanquear las calles y aceras. Pero lo más evidente son las diferencias esenciales que batallan por adueñarse del espíritu de la nación. Hoy estas saltan a la vista y se aprecian en la cercanía de un par de estructuras físicas. En esta ciudad hay apenas una milla de distancia entre dos edificios, una residencia y un monumento, pero parece la distancia entre dos galaxias opuestas, como si pertenecieran a universos antagónicos. Es sólo una milla, en efecto, pero no todas las millas son iguales, y no todas miden lo mismo. En la residencia vive el presidente actual, Donald Trump, republicano; y el monumento es la estructura erigida a la memoria de otro presidente republicano, Abraham Lincoln. Y hasta ahí llegan las semejanzas. El resto es radicalmente diferente. Porque mientras Lincoln elevó el país y lo inspiró con su oratoria, Trump lo hunde en las cloacas. Incluso su discurso oficial en estos días fue sobre inodoros y alcantarillas. Mientras Lincoln enfrentó la mayor guerra civil de la historia del país, la más brutal y sangrienta, con tal de salvar la patria y unificar su pueblo, Trump desde su primer día de gobierno se ha empeñado en polarizar y dividir al país, y ensanchar la brecha que existe entre la ciudadanía con tal de animar su base política. Mientras Lincoln aceptó el costo tan terrible de ese conflicto para acabar con la esclavitud y erradicar el racismo, Trump no hace más que fomentarlo, de frente y desde el púlpito de la Presidencia, como cuando elogió a los neonazis de Charlottesville y cuando les dijo a tres mujeres del</t>
-  </si>
-  <si>
-    <t>Estamos perdiendo la batalla contra el cambio climático, así lo indicó enérgicamente hace pocos días la vicesecretaria general de la ONU, Amina Mohammed. Estamos perdiendo la batalla contra el cambio climático, así lo indicó enérgicamente hace pocos días la vicesecretaria general de la ONU, Amina Mohammed, durante un discurso en la Universidad Tshinghua en Beijing, China, en el que agregó además que no debemos dar por sentado este planeta, pues es el único que tenemos. Esta es una preocupación legítima y urgente de la humanidad, y aunque no es reciente, nos debe convocar a los líderes empresariales ahora más que nunca. Desde nuestras acciones, que deben trascender las obligatorias, estamos llamados a desincentivar cualquier actividad peligrosa y contaminante en nuestra operación que ponga en riesgo la sostenibilidad del planeta, y a unirnos para hacer una contribución efectiva a el logro de los Objetivos de Desarrollo Sostenible, a través de la protección de la biodiversidad, el recurso hídrico, la mitigación y adaptación al cambio climático y la integración social. En ese sentido, y a pesar de que ISA no es gran emisor de Gases Efecto Invernadero, pues genera un promedio de 48.000 toneladas al año de emisiones directas de CO2, mientras que otras industrias generan en promedio 6 millones de toneladas al año, creamos en 2016, Conexión Jaguar. Se trata del programa de sostenibilidad bandera de ISA y sus aliados técnicos, South Pole Group y Panthera, que contribuye a la conservación de la biodiversidad y a la mitigación del cambio climático. El programa consiste por un lado en la implementación del componente de carbono en proyectos de recuperación y preservación de bosques, para la reducción de emisiones de Gases de Efecto Invernadero GEI en zonas prioritarias para la protección, recuperación y conexión de los hábitats naturales, que coinciden con los territorios</t>
-  </si>
-  <si>
-    <t>verbos y floreciera el primer idioma, del que por supuesto desconocemos desarrollo, vocabulario o geografía. Plagiando a Gabriel García Márquez, nada en aquel entonces tenía nombre y, para referirse a cualquier cosa, había necesidad de señalarla. Sostiene, pues, el doctor Dunbar que los seres humanos estamos cerebralmente diseñados para relacionarnos. La hipótesis del cerebro social se fundamenta en observaciones medibles. Existe una correlación directa entre el tamaño de la corteza cerebral la materia gris de los orangutanes, los gorilas y los chimpancés, por un lado, y el número promedio de miembros en sus correspondientes grupos sociales. Mientras más grande es la corteza cerebral, mayor parece ser la necesidad de socializar de nuestros primos primates. Por comparación, el cerebro humano es descomunal y, extrapolando cifras, nuestro grupo social debería constar de unas 150 personas. Retornemos a los mensajes. Si un texto contiene lo que queremos expresar, ¿por qué resulta más provechoso conversarlo? Las comunicaciones, sugieren los psicólogos, son más corporales y tonales que verbales, y los oídos escuchan apenas una fracción de lo que nuestros interlocutores quieren compartir. La comunicación va, pues, mucho más allá de lo que se pronuncia o escribe. De hecho, antes del desarrollo del lenguaje, como ya lo mencionamos, nuestros lejanos ancestros de alguna forma se comunicaban a punta de expresiones faciales, señales, gruñidos y garrotazos. El psicólogo iranínorteamericano Albert Mehrabian sugiere que el 55 de la comunicación es corporal; el 38 , tonal y tan solo el 7 la porción que podría escribirse se transmite con las palabras pronunciadas. Podemos entonces concluir que, aunque muchos mensajes pueden ser interesantes, divertidos o motivantes, ningún documento electrónico reemplaza una charla alrededor de un café, un apretón de manos, el abrazo al final del encuentro o la lectura del rostro del amigo cuando le contamos una buena noticia. Si</t>
-  </si>
-  <si>
-    <t>La apuesta de la actualidad es la captura de la atención de millones de internautas. Los niños y jóvenes tienen prácticamente perdido este juego. Nacen con otros órganos, su paisaje es una pantallita, el dedo pulgar es el rey de la selva. Están cautivos desde antes de estar conscientes. El proceso es el siguiente. Cada individuo anda prendido a su equipo que es a la vez reproductor de sonido, enciclopedia, teclado para concertar citas y estar al tanto de los planes de amistad, campo de juegos, banco a distancia, computador, control remoto de su casa ah, también teléfono, ese aborrecible adminículo para hablar con el prójimo. El mejor entorno para contemplar esta hipnosis pública son los buses urbanos. No hay persona desconectada, nadie olvida los audífonos. Hombres y mujeres viajan con cables colgantes que esclavizan el oído, órgano por donde penetran los recolectores de la vigilancia universal. Los ojos pican sobre videos y teclados. Afuera se borran los jardines y adentro los compañeros de viaje. Esta rutina es diversión. Se asume como actividad libre cuyo contenido cada cual elige, con los reflejos de autoprotección en el piso. ¿Protegerse de qué, si una vez comprados aparato y plan de navegación todo es gratis, ilimitado, voluntario? Además, nadie quiere quedarse atrás ni perder instante de la novedad pública y cercana. El mundo ya no es una aldea global como a finales del XX. Ahora es una colección de burbujas sin país, sin tiempo, sin fronteras físicas. Una burbuja para cada habitante, que es rey en medio de muchos reyes entre los cuales no hay colisión ni discordia. Paraíso de paraísos que en secreto evolucionan igual que la expansión del universo. ¡Alto ahí! Esta interpretación cosmológica es apenas un remedo espurio de la acuñada por los físicos del big bang . En efecto,</t>
-  </si>
-  <si>
-    <t>Entre sus catorce y sus dieciséis años, este columnista desarrolló un notable interés por las palomas, uno de los vertebrados más planetarios solo están ausentes de las regiones polares y de los grandes desiertos y, como aficionado accidental, investigó su biología, crio y mantuvo unos cuántos ejemplares en el patio de su casa paterna, y llevó registro detallado de sus hábitos y sus comportamientos. De entre estos, una conducta en particular, la homosexualidad de los machos, llega como anillo al dedo para abrir esta nota. Las palomas conforman uniones muy sólidas, desde el inicio de la relación hasta la desaparición de uno de los cónyuges. No obstante, cuando las hembras están incubando, muchos de los palomos se vuelven homosexuales de tiempo parcial, a pesar de ser, por lo demás, unos excelentes esposos que ayudan en todo, desde la construcción del nido a compartir, pasando por la participación en la incubación y la alimentación de los pichones, hasta llegar a la expulsión violenta de los críos del nido, cuando lo necesitan para una nueva camada y los hijos se encuentran listos para sobrevivir por sí mismos. Décadas después, cuando ya las tempranas aficiones se convirtieron en memorias remotas, este columnista aprendió que la conducta homosexual de mis palomos estaba bien lejos de ser excepcional y, en las décadas recientes, ha sido observada en más de un millar de especies vertebradas. Esta manifestación homosexual en tantas especies condujo, casi de manera espontánea, a la hipotética presencia de un gen específico en el reino animal cuya expresión predispondría a sus dueños para la homosexualidad. No es así, sin embargo. Un estudio, publicado en agosto pasado, acabó con toda posibilidad de que el gen gay como fue denominado realmente existiera. La investigación demostró que la genética sí tiene una contribución en la orientación homosexual,</t>
-  </si>
-  <si>
-    <t>del diente de león, el mismo que pisamos al caminar, bajo el abrigo del tibio sol sabanero. Aprendí sus versos sin proponérmelo, y fue así como, al escribir esta columna nostálgica, no tuve necesidad de buscar entre otros libros los suyos para recordarlo. Nunca han salido de mi mente atribulada, aunque no me crispan como los fatales de mi preferido latino, Horacio, sino que me conectan con los albores de la edad y con la hermandad del aire y del paisaje. Sé muy bien que la vida de De Roux no la sintetizo fácilmente, aunque para mí es plena como poeta de la naturaleza, compañera nuestra en el trascurso de la vida. Fue teólogo especializado, a tal punto que la seriedad del escriturista y el tinte severo de sus estudios parecieran ajenos a su frescura juvenil y no le permití y así se lo dije en más de una ocasión, sin que tal vez lo tomara en serio que modificara una sola frase o palabra de su prístina inspiración. Usted no me puede borrar lo que yo ya me sé de memoria. No sé si el universo poético latino e hispánico reconocerá algún día al más apreciable de sus vates. Por el momento sólo me queda mirar el amanecer de la sabana y, parodiando su poema dedicado al padre Daniel Restrepo, ver que una paloma corta la luz de la mañana, llevando el sol naciente sobre sus alas blancas. Murió el amigo y consejero inigualable en la aurora del pasado jueves 3 de diciembre. jueves 3 de diciembre.</t>
-  </si>
-  <si>
-    <t>organizado excursiones de reconocimiento de la naturaleza junto con excombatientes, que son quienes conocen mejor que nadie los territorios y las veredas. En una de las visitas a Anorí, Antioquia excombatientes acompañados por el biólogo Diego Calderón encontraron varias especies desconocidas de orquídeas, una palma, un ratón, un lagarto e insectos. Este, de colores y cantos, es el cielo de 2020, pero no será quizá el de 2021. Expediciones como la de Anorí solo continuarán si, en cumplimiento del Acuerdo, se construye bienestar rural. Y, en momentos en que ministros y ministras se empeñan en concentrar la tierra, desproteger a excombatientes y negar que hubo conflicto, puede intuirse que el cielo de nuestro futuro será más de zancudos que de aves. La propia ciudad de Cali, donde se celebró la llegada del tororoi bailador, está hoy cundida de Aedes aegypti . Este es un insecto que no necesita de mucha descripción: además de sus líneas blancas y negras, es silencioso, vuela bajo y tiene tres pares de patas. Es el vector principal para el dengue, el chikunguña y el zika, se reproduce principalmente en agua almacenada o estancada y prospera en contextos de crecimiento demográfico y urbanización rápida en áreas tropicales. Estudios han advertido que el cambio climático podría aumentar su proliferación en nuevas áreas, ya que el aumento del calor puede afectar la temperatura y la distribución del agua estancada. En Colombia, el dengue ha sido endémico desde la década de 1990 y el país tuvo el mayor número de casos de virus de Zika en el mundo después de Brasil. El trabajo de la profesora Claudia RomeroVivas ha demostrado que el agua almacenada doméstica contribuye a altos porcentajes del total de población del zancudo en sectores urbanos y periurbanos. En particular, los barrios donde el suministro de servicios</t>
-  </si>
-  <si>
-    <t>¿Alguien conoce el sabor de las uvas del páramo o el bilimbili? Desde hace más de un año y medio, Gian Paolo Dáguer recibe mensajes diarios de campesinos e interesados en la tierra que le escriben desde cualquier pueblo de Colombia. Muchos le envían imágenes de frutas con texturas y colores desconocidos que prácticamente no existen porque no han sido nombradas. Le preguntan por ellas, qué hacer. Este ingeniero ambiental cuenta que su interés por las frutas comenzó cuando era niño y las probaba junto al abuelo en sus visitas al campo. Su curiosidad por el tema lo llevó a crear junto a otras personas la organización Frutas de Colombia para estudiar y divulgar lo aprendido. Le llama la atención que un país con tanta biodiversidad como el nuestro no conozca bien sus plantas y árboles. Un regalo desconocido, la exuberancia de la tierra sin provecho. Además de frutas, él y un grupo de personas que lo siguen recolectan semillas para evitar la desaparición de ciertas plantas. Y es que ante la falta de conocimiento sobre una especie, suele ocurrir algo común: al no conocer las frutas y semillas, un campesino recibe una oferta para convertir su territorio en monocultivo, situación que en muchos casos termina con la biodiversidad y trae riesgos para el ecosistema. Si valoramos más nuestras frutas, en los pueblos se las ofrecerían a los turistas en lugar de bebidas artificiales, cocinarían con ellas, prepararían recetas, estarían en las loncheras de los niños, podrían ser exportadas o, en el caso menor o inmediato, la gente del mismo pueblo las aprovecharía como alimento. Además de conocimiento en el país faltan expertos y logística, la ausencia de voluntad o explicación se ve en nuestras instituciones. De acuerdo con cifras publicadas por la DIAN a comienzos de este año, en</t>
-  </si>
-  <si>
-    <t>Berrionditos, de vacaciones les tenemos estos dichos que ya casi nadie dice. Pilar por el afrecho: hacer un trabajo por migajas. Antes se pilaba el maíz en un pilón y el afrecho se le tiraba a las gallinas. Ganar el mínimo. Sacarle capul a una calavera: hacer chistes hasta de lo miedoso. Ejemplo: Tola está tan vieja que cuando la vayan a cremar primero la tienen que ablandar con cáscaras de papaya. Dárselas de café con leche: aparentar más de lo que se es, creerse la vaca que más caga. Ejemplo: desde que quedó de diputao, esa caranga resucitada se las da de mucho café con leche. Caranga resucitada: pobretón que llega a tener modito, a ser pudiente, y que mira por encima del hombro a sus antiguos compañeros de Sisbén. A media caña: tomar trago moderadamente y estar todo el día copetón, sin emborrachase. Ejemplo: este berriondo Gobierno no se aguanta sino a media caña. Se perdió chicha, calabazo y miel: cuando se pierde todo, como la clase media con la reforma tributaria. Dios no castiga ni con palo ni con rejo: decimos las mamaes cuando a un hijo desobediente le pasa cacho. Cacho: suceso maluco. Pide más que un gato en un machucadero de carne: así piensa el Gobierno del Comité de Paro. En las casas se tenían dos piedras pa machucar la carne dura. Llevar la matadura debajo de la enjalma: cargar una pena con dignidá, sin mostrar dolor, como Uribe con su popularidá, más caída que teta de gitana. Irse con ese manto a misa: confiar pendejamente. Ejemplo: Duque promete menos impuestos, más salario mínimo. ¡Váyase con ese manto a misa! Coger el monte: así dice una mamá desesperada cuando su recua de hijos la tienen cabezona: ¡Estoy que cojo el monte! También quería decir ise</t>
-  </si>
-  <si>
-    <t>esfuerzos, en realidad lo único que logró fue un cese al fuego temporal e incompleto. Cuando a comienzos de este año tuvo dudas de la conveniencia de prorrogarlo, la realización de dos ataques contra instalaciones policiales en Barranquilla y Cartagena fue la forma elegida por la contraparte para inducirle a ceder; por supuesto, las autoridades no le caminaron a ese mecanismo de persuasión. Tampoco logró la administración Santos sentar en la mesa de Quito a todos los frentes guerrilleros; el del Chocó nunca estuvo representado. El actual gobierno no ha cancelado el proceso de negociación; se ha limitado a no designar, por ahora, sus voceros en la mesa habanera, mandando, simultáneamente, una señal clara: la ventana temporal para negociar es restringida. Ese mensaje consiste en la presentación al Congreso de una iniciativa para proscribir que el narcotráfico sea considerado conexo al delito de rebelión para efectos de que sus responsables gocen de un tratamiento punitivo benévolo; y para clausurar la posibilidad de que integrantes de movimientos armados puedan hacer parte de organismos de representación popular antes de haber servido las penas que la justicia transicional les imponga. Como estas medidas no pretenden menoscabar los derechos adquiridos de las FARC el presidente Duque así lo ha reconocido es evidente que su aprobación por el Congreso implicaría quemar las naves; amigos y adversarios quedarían notificados de que esas herramientas, que fueron fundamentales para lograr el acuerdo con las Farc, dejarían de estar disponibles. Imaginemos que, en estas circunstancias, el ELN, en contra de la postura intransigente que le ha sido usual, se allana a cerrar un acuerdo con el Gobierno antes de que se promulgue la propuesta de ley en curso. En tal caso, se abriría un complejo debate: ¿Se requerirá la modificación de las normas que le dieron entrada al Acuerdo</t>
-  </si>
-  <si>
-    <t>vayan mujeres en condición de vulnerabilidad. Y denuncien. No olvidemos defender a los niños. Los coronavioladores andan por ahí cerca. De otro lado, el virus de la corrupción tampoco tiene vacuna. Increíble y repudiable que los corruptos, sepulcros blanqueados, estén aprovechando esta emergencia para robarse la plata de los contratos de las compras de elementos urgentes y comida por parte del Estado, según denuncian la Procuraduría, la Contraloría y la Fiscalía. Los pícaros cobraron bolsas de leche a 13.000 pesos; un pequeño atún, a 19.000, y así, sobrecostos como arroz, hasta con 50 por ciento más en millonarias compras. Que los sinvergüenzas paguen cárcel, pues es un atentado contra la vida, contra la confianza de los donantes, un irrespeto a millones que hacen sacrificios. Que haya justicia y nos muestren la cara de los Judas, pues aquí seguimos como Jesús, crucificados en medio de los ladrones.</t>
-  </si>
-  <si>
-    <t>olvidaron de la política. ¿Cuándo se echaron a la gente encima? Cuando empezaron a demoler con explosivos pueblos habitados por campesinos pobres para hacerse a una decena de fusiles. ¿Cuándo se enemistaron con la gente de las ciudades? Cuando volvieron el secuestro una actividad a gran escala. ¿Qué imagen prevaleció en la memoria de los colombianos? ¿Cuál, Viejo Topo? ¿La de Tirofijo en Marquetalia luchando junto a un puñado de campesinos pobres, calzando alpargatas, mal armados y llenos de coraje o la del Mono Jojoy luciendo un lustroso uniforme Made in USA y mostrando al mundo a cientos de prisioneros? Los colombianos, Viejo Topo, se quedaron con la última imagen. Las elecciones de 2018 sentenciaron. Un pobrísimo resultado para los vástagos de Tirofijo. El partido Farc, desde la legalidad, trata de enmendar con la política los excesos que cometieron con las armas. Condenado a galeras. El galeote fijado al remo mediante una cadena. La cadena del pasado. ¿Es posible salir de esa esclavitud? Sí. El destino le sonrió a BenHur, el príncipe judío. ¿Cuándo se jodió el ELN, Viejo Topo? Cuando empezó a recorrer tardíamente la peor época de las Farc. Salvo unos cuantos frikis, la mayoría de colombianos no asocia a la actual cúpula del ELN con los sacerdotes católicos Camilo Torres, por ejemplo que se echaron al monte a luchar por las enseñanzas de Cristo. El Cristo Redentor de los pobres. Los millones de colombianos no creen que Gabino, el máximo jefe del ELN, sea capaz de tocar una guitarra e interpretar unas jotas españolas. Lo ven, al lado de sus camaradas de comando, como un hombre envejecido que no tiene más remedio que seguirle el juego a unos chicos díscolos que a veces les da por colocar bombas, secuestrar a un cristiano que no tiene ni en</t>
-  </si>
-  <si>
-    <t>imposiciones y maniobras que han realizado los amigos del proyecto y los abogados de las Farc para forzar un acuerdo a su conveniencia e insertarlo en la Constitución y la ley, dividió, polarizó y sigue enfrentando rabiosamente a los colombianos. Desde los primeros días, a medida que se comenzaron a divulgar las definiciones en materia de tierras, participación política, drogas ilícitas, víctimas del conflicto, fin del conflicto y demás, surgió el descontento en varios sectores del país y el rechazo parcial o total a lo acordado. La nueva polémica por la objeción de seis artículos de la ley estatutaria de la JEP refresca en la memoria colectiva que en el plebiscito de octubre de 2016, que buscaba dar legitimidad al proceso mediante el voto popular, ganó el No. Que después de ello el Gobierno de Juan Manuel Santos pasó por encima del resultado, no convocó a los colombianos para construir consensos y lograr un nuevo acuerdo que los reuniera a todos. Optó por imponer el suyo a como diera lugar, con retoques leves realizados a puerta cerrada y lo llevó a refrendación al Congreso donde controlaba las mayorías. De ahí surgió una nueva normatividad que tuvo un discutible visto bueno a la venezolana de la Corte Constitucional. Quedamos con un acuerdo de gobierno y no de Estado, claramente dirigido a acomodar el orden jurídico a los anhelos de las Farc y que es objeto de tantos cuestionamientos y reservas jurídicas, institucionales y políticas, que es incapaz de convocar y reunir a la totalidad de los colombianos. El narcotráfico y la minería criminal son los principales factores de perturbación que enfrenta el país, como generadores de violencia. Esto unido con el compromiso con las víctimas, con los habitantes de las zonas afectadas por la violencia y con los desmovilizados de las</t>
-  </si>
-  <si>
-    <t>glifosato y otros pesticidas tiene legados que no conocemos entre la naturaleza humana y la no humana. Estos van desde la muerte de los peces hasta el marchitar de los cultivos de pancoger, las alergias en la piel, la pérdida de embarazos e incluso el desarrollo de ciertos cánceres. La petición hecha esta semana por la senadora del Centro Democrático María del Rosario Guerra de la Espriella, para que la cuarentena y militarización en el contexto la pandemia sea aprovechada para fumigar con glifosato regiones como el Catatumbo y el Cauca, nos dice mucho sobre el presente y el futuro, las clases dirigentes, el valor de unas y otras vidas y nuestras relaciones con la naturaleza.</t>
-  </si>
-  <si>
-    <t>padecen arriba de su noveno piso los clamores de quienes ruegan ayuda desde las aceras con voces de tenores invencibles. Las radios y televisores revientan alarmas sobre infectados y agonizantes sin oxígeno. Repiten la monserga: lávense las manos, quédense en casa, conserven la distancia. Como si las restricciones obsesivas curaran el hastío. Propagan, eso sí, naderías sobre la gresca embaucadora del fútbol y leguleyadas sobre la detención del eterno. Resultado: un país enfermo de desazón. La Javeriana realizó una encuesta sobre ansiedad y depresión entre jóvenes de 18 a 24 años, de los cuales dos terceras partes tienen estos síntomas. A propósito de las recomendaciones de las autoridades de salud, su decano de medicina, psiquiatra, sicoanalista, epidemiólogo, Carlos Gómez Restrepo declaró en El Espectador del domingo pasado que se está empezando y se están haciendo los mejores esfuerzos se tienen que tomar decisiones de acuerdo con el momento. Pienso que está llegando el momento de la salud mental. Caramba, ¿apenas está llegando el momento? No. La salud mental es componente innato de la salud orgánica. Desde el primer instante en que se decidió blindar el cuerpo contra el coronavirus, debió considerarse qué caminos tomarían la imaginación, el deseo, el espanto, los sentimientos, las pesadillas, el erotismo, el desasosiego y demás exaltaciones que hacen del hombre un animal tembloroso. arturoguerreror.com</t>
-  </si>
-  <si>
-    <t>olvida que hoy ruedan cerca de 500.000 motocicletas por Bogotá, una situación muy distinta a la de hace 30 años, cuando para frenar a los sicarios de Pablo Escobar se prohibió por primera vez el parrillero. Pasaron todos estos años y Bogotá, en lugar de intervenir las barriadas y las condiciones de vida que expulsan a esos chicos y chicas a ser parte del hampa, sigue buscando cuesta arriba las respuestas a la inseguridad, haciendo aún más caótica la ya insoportable movilidad en Bogotá. El impacto de prohibir al parrillero será poco, dicen desde alguna secretaría del distrito, la medida solo afectará al 0,5 por ciento de las personas que vivimos en Bogotá. Entonces, me pregunto, ¿para qué sirve esto además de crear trancones por cuenta de miles de moteros emberracados? Más allá de lo ineficaz que se ve la medida desde el punto de vista operativo, es más absurda cuando se observa la ignorancia que carga desde el fondo. Para la Secretaría de Seguridad de Bogotá no importa si quien conduce la moto es hombre o es mujer, pero supone que la persona móvil, la que va en la parrilla, la encargada de asaltar, atracar o disparar, no es nunca una mujer. Se puede ser parrillera, pero no parrillero. ¿De dónde acá los asaltantes, atracadores y asesinos son solo hombres?¿No vieron Rosario Tijeras? ¿Qué habría sido de Clyde sin Bonnie? ¿Quién dijo que el mundo del hampa es solo de hombres? ¿Acaso no han visto los miles de miles de videos que aparecen en Google si busca mujer atracadora? Si las mujeres pudimos estudiar, trabajar, votar y ser elegidas, si queremos caminar por el mundo igual que los hombres, también hay que reconocer que las mujeres también pueden robar, atracar, disparar y ser cabecillas de banda, quién dijo que</t>
-  </si>
-  <si>
-    <t>con origen en la ciudad francesa de Gap. Una encantadora sorpresa encontrar algunas chuguas confitadas incorporadas al ratatouille. Un hit esta fusión francocundiboyacense. De postres dos opciones de crme brlée, una de vainilla de Antioquia y otra de café y del polvo mambé. Una delicia. Otra exitosa fusión galocolombiana. Cocina auténtica francesa, con utilización de ingredientes locales, muy placentera al paladar y a la vista. Tiene la enorme bondad de contar con domiciliarios propios. A pesar del transporte y el tiempo que demanda, los platos se preservan muy bien. Un gran aplauso para su chef Damian Noirard por su tenacidad en activar el restaurante en esta coyuntura, ejemplarmente y brindando alta calidad. Evaluación VSEG Valor Social Empresarial Gastronómico: Excelente, con honores. Teléfonos: 322 857 7702 y 477 7555. Calle 16A 273, La Candelaria, Bogotá. santjustbogota.com</t>
-  </si>
-  <si>
-    <t>mejor de mis días a la búsqueda de la fragancia madre y cuando la encuentre la envasaré en un frasquito que será una gema discreta, claro, y la pondré a los pies de mi esposa, lo prometo. El resto será fácil. El perfumista identificará los olores y el aromatólogo los agrupará en familias bien definidas y ambos harán con ellos lo que ya hicieron los físicos y los pintores con la luz, los físicos y los músicos con los sonidos, y los químicos y los cocineros con los sabores, y los poetas descubrirán el verdadero y antiguo nombre de cada olor, de cada matiz. Entonces el lenguaje podrá al fin nombrarlos y la especie olerá mejor. Por razones estrictamente personales, esta columna reaparecerá en enero. 872958 20190727T02:30:0005:00 column 20190727T02:30:0105:00 email protected none La fragancia madre 18 3853 3871</t>
-  </si>
-  <si>
-    <t>Para nadie es un secreto que la gasolina es imprescindible no solo para el procesamiento que convierte la coca en cocaína, sino también para que funcionen los laboratorios escondidos en lugares inexpugnables. Allí se requieren plantas eléctricas para alimentar, entre otros, los hornos microondas que deben trabajar permanentemente. Para decirlo de manera simple: si no hay gasolina, no hay cocaína. Por eso la denuncia hecha por Francisco Lourido, el candidato a la Gobernación del Valle, debe ser tenida en cuenta. Sucede que las ventas de gasolina andan disparadas en los departamentos donde se procesa el alcaloide y el Gobierno no ha tomado cartas en el asunto. Las estaciones de gasolina en esos lugares se han multiplicado geométricamente, ante los ojos y oídos de quienes andan persiguiendo a los responsables de este delito. Ejemplos hay muchos: mientras que en el Valle del Cauca con más de 4,7 millones de habitantes existen 473 bombas de gasolina, en Nariño con solo 1,8 millones de almas hay 481 estaciones y en Putumayo hay 106 estaciones y solo viven 360.000 personas. ¿Para qué tanta gasolina? ¡Blanco es, gallina lo pone! Pero hay más: en los departamentos limítrofes con otros países, el galón de gasolina cuesta 3.000 menos que en el centro del país, debido a que existe un subsidio fronterizo, que ignoro por qué y para qué. O sea que dicho subsidio lo asume el Gobierno y lo pagamos todos los que compramos gasolina. Es decir, que podríamos hasta ser cómplices de tan atrabiliaria medida que solo beneficia ¡y de qué manera! a los mencionados laboratorios. Lo anterior para no cuestionar el papel que juegan los distribuidores y expendedores, pues es imposible que no sepan a dónde va a parar la gasolina que venden, cómplices también de esta cadena que es preciso desarticular. 878437 20190830T00:00:5305:00 que solo beneficia ¡y de qué manera! a los mencionados laboratorios. Lo anterior para no cuestionar el papel que juegan los distribuidores y expendedores, pues es imposible que no sepan a dónde va a parar la gasolina que venden, cómplices también de esta cadena que es preciso desarticular. 878437 20190830T00:00:5305:00 column 20190830T00:15:0105:00 email protected none Gasolina para la coca 21 1950 1971</t>
-  </si>
-  <si>
-    <t>pero el Ejército no apoyó esta investigación por considerar que esa arma no era compatible con el honor de los militares en la batalla. En los años 30, Alemania tenía un avanzado desarrollo científico y, aunque la llegada de los nazis al poder expulsó a muchos de los grandes creadores de la física atómica, quedaron investigadores de la talla de Heisenberg, quien dirigió el laboratorio que buscaba poner a punto la bomba atómica y montarla sobre los cohetes V2 diseñados por Wernher von Braun. Esto, unido al frustrado desarrollo en Tokio, hubiera modificado, al menos durante un tiempo, el curso de la guerra. Aunque no se tiene certeza histórica, existe la creencia de que Heisenberg habría realizado el cálculo más importante de la bomba atómica: la masa crítica, pero no lo entregó al Ejército nazi, por el bien de la humanidad. La tecnología para construir la bomba atómica es de dominio público; el cálculo de la masa crítica está al alcance de un buen estudiante de maestría en física; si no quiere resolver las ecuaciones, existen programas que lo hacen y se obtiene la cifra de 52 kg de uranio 235. Los otros aspectos corresponden a la tecnología de explosivos convencionales. Aunque la cifra de 52 kg parece pequeña, se requiere una enorme capacidad industrial para concentrar el uranio 238, que se encuentra en la naturaleza, en uranio 235. Las grandes centrífugas subterráneas de Irán trabajan 24 horas diarias para obtener gramo a gramo los 52 kg requeridos para cada bomba. Irán considera que la forma de defender su territorio es con la disuasión nuclear. Basta comparar la invasión a Irak, que se ejecutó con base en mentiras sobre la existencia de armas de destrucción masiva, con las negociaciones con Corea del Norte, pues este país puede tomar retaliaciones nucleares bomba. Irán considera que la forma de defender su territorio es con la disuasión nuclear. Basta comparar la invasión a Irak, que se ejecutó con base en mentiras sobre la existencia de armas de destrucción masiva, con las negociaciones con Corea del Norte, pues este país puede tomar retaliaciones nucleares contra los aliados estadounidenses Corea del Sur y Japón. Así, el equilibrio del terror está permitiendo controlar una guerra masiva.</t>
-  </si>
-  <si>
-    <t>Se dice que Colombia es un país conservador, godo. Que siempre vota por la derecha, que tiene como color el azul de metileno. ¿Alguien sabe qué es eso de metileno? Toda la vida se ha usado este término en la política pero, con excepción de médicos y químicos, no hay quién explique qué le agrega el metileno al azul. Esta ignorancia quiere decir algo: que aquí las verdades se toman como indiscutibles y eternas, aunque no se comprendan. Valdría la pena entonces proponer en esta campaña presidencial una encuesta escueta cuya única pregunta fuera: ¿votaría usted en metileno? Ja, se armaría la grande con los resultados. Los encuestados tendrían que pensar, mirar un diccionario, acudir a Google. Este pequeño acto de investigación introduciría la duda y echaría por tierra la seguridad de que somos un país godo. ¿Derechosos? No, los colombianos somos más bien precavidos, resabiados. Tantas veces nos han engañado, tantas veces nos asesinaron, tantas veces nos obligaron al rebusque de una chaza en la calle, que ningún partido se nos acomoda. Le tenemos miedo a todo, a la derecha y a la izquierda, a los paracos y a los mamertos. Desde los flancos históricos nos han disparado. Por eso nos matamos trabajando en la informalidad 16 horas diarias. Y nos encerramos en la casa a sacar adelante la familia. Los ricos, de otra parte, tienen más miedo que el pobrerío. Su espanto se llama expropiación. Son minoría, son los que tienen plata y cosas. Las han tenido de toda una vida. No se preguntan de dónde las sacaron, solo temen perderlas. Entonces se atrincheran, aceitan las maquinarias que siempre les han funcionado. Unos y otros, adinerados y proletos, se alarman ante cualquier cambio drástico. Los primeros aprovechan los pésimos ejemplos de regímenes que prometieron producir un hombre nuevo</t>
-  </si>
-  <si>
-    <t>La página web del Comando Militar de las Fuerzas Armadas anunció con bombo esta semana que la Armada incautó un total de 1,2 toneladas de clorhidrato de cocaína, tras una operación de alto nivel por aire, mar y tierra. Las toneladas fueron manipuladas de inmediato por la Fiscalía que se encargó de practicar pruebas para confirmar la composición de lo incautado. La operación que tuvo lugar en uno de los brazos del río Naya, en su paso por Buenaventura, habría impedido que las organizaciones narcotraficantes recibieran más de 40 millones de dólares, producto de la venta del alcaloide en el mercado internacional. La noticia se reprodujo con orgullo en televisión y radio en donde oficiales pidieron a la ciudadanía de Buenaventura denunciar cualquier actividad sospechosa a las líneas 146 y 147 disponibles las 24 horas del día. Oficiales y funcionarios también recalcaron que ante la pandemia mundial, Colombia mantiene sus esfuerzos contra el narcotráfico en el Pacífico. Quizá esos son y han sido los principales esfuerzos del Estado colombiano en Buenaventura. Tal vez esa suma de tecnologías y operaciones por tierra, mar y aire, en persecución de sembradíos y clorhidratos, sea de las únicas formas en que distintos gobiernos se han interesado en llegar de manera cotidiana y generosa a esta ciudad. Con o sin pandemia, el Estado hace presencia por medio de las Fuerzas Armadas que vigilan el puerto para, por una parte, castigar el narco y, por otra, proteger las inversiones privadas del puerto. Buenaventura, que se ha urbanizado de manera desigual desde que se convirtió en el principal puerto marítimo del país en los años de 1920, se ha enfrentado a graves crisis de acceso a agua, salud y empleo durante la última década. En el caso del agua, pese a estar inserta en una red de</t>
-  </si>
-  <si>
-    <t>de Alejandro. Esta influía en la paz, la guerra, las drogas y la salud: las aspersiones de glifosato. Otro día Alejandro anunció que unos expertos la Agencia Internacional para el Estudio del Cáncer IRAC dijeron que un químico usado contra las maticas de droga podía ser cancerígeno. Por supuesto no faltaron los críticos; intimidantes y amenazantes, pues ese químico servía para atacar la droga que financiaba al enemigo de guerra. El profe Alejandro estuvo del lado de la salud. Le explicaba: Estas batallas fueron por la salud de otros. De gente distante que no podía acceder a un medicamento, de gente en regiones muy lejanas a su residencia a la que el Estado le bombardeaba con un químico mortal. Unos desconocidos, por ellos era la lucha, la honestidad intelectual y el fuerte debate. En junio de 2017 al ministro le diagnosticaron cáncer. Teniendo dinero de sobra para un tratamiento en el exterior, se sometió a su sistema de salud en Colombia. El medicamento Rituximab, del que te hablé, Isabel, terminó siendo el primero que le ponían al comienzo de cada ciclo de medicamentos. Él les había mejorado la vida a extraños y ahora tenía que vivir su legado. Y hay más... el glifosato. Los estudios de Alejandro en su batalla mostraban la asociación entre la exposición al glifosato y un tipo de cáncer, el linfoma no Hodgkin, precisamente el linfoma que él padecía. Isabel no creía la coincidencia. Esta es la lección en economía y en ética, que las ideas se someten a un solo criterio ético para buscar con ellas mejorar la vida de extraños como si fuera la vida propia, o inclusive algo más importante, como la vida de los niños, la vida de mi prima. EconomíaParaMiPrima se someten a un solo criterio ético para buscar con ellas mejorar la vida de extraños como si fuera la vida propia, o inclusive algo más importante, como la vida de los niños, la vida de mi prima. EconomíaParaMiPrima</t>
-  </si>
-  <si>
-    <t>La Fundación Musical de Colombia; su presidenta, Doris Morera de Castro, y su empoderado equipo directivo y ejecutor mantienen encendida la llama nutricia de una vocación que hace de Ibagué, justamente, la ciudad musical de Colombia. Este miércoles 20 de marzo se realizó, en el Teatro Tolima, el concierto inaugural de la versión número 33 del Festival de Duetos, con el cual los habitantes de Ibagué enseñan su propia tradición y rinden homenaje a la memoria de Garzón y Collazos, el dueto insignia de una cultura musical que los hijos del Tolima grande guardan en el alma. Visitar Ibagué por estos días y refundirse con su gente, mientras en las tarimas de sus parques y plazas se escucha la voz de los duetos y, a petición de estos, todo el mundo canta, es un espectáculo para el sentimiento. La música andina colombiana que Garzón y Collazos recogieron desde cuando eran estudiantes del Conservatorio de Ibagué, hace casi 100 años, es al mismo tiempo talento y emoción. El del maestro Castilla, de Milciades Garavito, , son poemas proyectados sobre el pentagrama, que invaden el aire en múltiples voces y expresan identidad tolimense. La poesía está unida al canto. Alguna vez le oí decir al poeta Camacho Ramírez que música y poesía expresan una sola sustancia. La poesía no solo es lenguaje, también es música. Y la música exige el verso. La lírica griega nació y vivió unida a la música. Probablemente fue así en las más evolucionadas culturas precolombinas. En todo caso, es así en el Tolima. Si usted viene a Ibagué durante estos días encontrará que la relación entre poesía y música es un misterio, que solo se resuelve con otro misterio: la simbiosis entre música y poesía. Y usted lo descubre, simplemente, oyendo cantar, porque quienes cantan llevan en</t>
-  </si>
-  <si>
-    <t>El viernes 7 de diciembre, día de las velitas, se confirmó que una luz que brilló en Colombia durante muchos años se apagó definitivamente: Belisario, el poeta que amaba a Kavafis y supo emprender su viaje a Ítaca, sin temor a lestrigones, cíclopes ni al airado Poseidón. Que supo detenerse en el camino enriqueciendo sus jornadas, sabiendo que Ítaca le daría la travesía y no podía darle más Hombre que entendió el sentido de las Ítacas en toda su profundidad. Lo recuerdo, primero, como el amigo intelectual, ávido de conocimiento, enamorado de las palabras y los libros. Su sentido del humor a veces cáustico y cortante. Su alegría de vivir y su capacidad de sorprenderse, de descubrir lo bello en las cosas aparentemente más banales. Esa risa espontánea. Ese rictus de preocupación y severidad cuando las circunstancias lo merecían. Primero fue el amigo. Posteriormente, el jefe de Estado que me sorprendió al ofrecerme la dirección del Instituto Colombiano de Cultura, acabando yo de regresar de acompañar a un hijo que atravesaba con estoicismo la agresividad de un cáncer de huesos en un viaje al fondo del dolor. Recuerdo que le pregunté por qué me lo ofrecía a mí, y esa respuesta perentoria: Necesito la cultura para la guacherna. Usted lo puede lograr. Nos vemos pasado mañana en mi posesión. Una experiencia inolvidable que culminamos con la presentación de toda nuestra riqueza cultural autóctona en Estocolmo para acompañar a Gabriel García Márquez. Belisario Betancur supo combinar su idealismo romántico con la severidad pragmática del gobernante. Dueño absoluto de su silencio, jamás esclavo de palabras vanas ni demagógicas. Recibió con casta las inculpaciones de sucesos trágicos que jamás promovió. Al lado de Rosa Helena Álvarez gobernó con mesura y sin soberbia y logró el primer acuerdo de paz que le abrió nuevos</t>
-  </si>
-  <si>
-    <t>las que se refieren a aspectos genéricos de La Mesa, las que constituyen vívidos retratos de personajes notables por alguna razón y las que tratan de aspectos y temas diversos, entre ellos los referentes a la naturaleza, tan rica en el lugar y tan agudamente percibida por el ingeniero agrónomo de la Universidad Nacional que es Alfredo. Verdaderas historias son todas porque corresponden a experiencias directas de Alfredo, esto es, vivencias con nombres, sitios y momentos reales. Lo más interesante de la original prosa de Navarrete es que no solo describe admirablemente sino que caracteriza certeramente, relaciona pasado y presente y en ocasiones proyecta lo que puede y debe ser. Ello con agilidad impresionante y máxima economía de palabras. Pocas de las historias pasan de dos páginas. Alfredo ama La Mesa la cual, aclara, inapropiadamente se conoce como de Juan Díaz. La Mesa fue fundada en el sitio de Guayabal, el 16 de diciembre de 1679, 70 años después de la muerte del tal Juan. La Mesa, ciudad de los ocobos, amable y cordial. Mis flores, dos veces al año, tapizaban los andenes con su colorido y perfume que alegraban el corazón de los mesunos y daban resplandor a la belleza de las damas y niñas del Colegio de la Presentación que, engreídas, caminaban a estudiar o para asistir a la homilía de los domingos, días de fiesta o todos los primeros viernes. Alfredo ama a la gente de su pueblo, la mayor parte de las historias, treinta y cuatro, se refieren a personajes pasados y actuales. Desde Ranchoepaja o ClinClan, hasta Mario, el fotógrafo, pasando por las señoritas Guarnizo, las Espinosa, el Doctor Pedro León, Don Chimbilo, Pacho Loco, la Chata Aleja, el maestro Carlos El Mono Palacios, el Choro, y los Apodos Mesunos 358! El acontecer cotidiano para</t>
-  </si>
-  <si>
-    <t>somos una especie inquieta que se resiste a desaprender lo esencial. Se abre una claraboya que ventila nuevas ideas, y a veces recuperamos cosas que creíamos olvidadas, o totalmente perdidas. El paseo de esta mañana me trajo las memorias de Aída Bortnik, que solía caminar por las calles de Madrid con el también guionista Juan Carlos Frugone. Dos amigos compartiendo el infortunio del exilio argentino de los años 70, que iban al cine los días de damas porque no tenían dinero para más, unidos por el sudor de sus manos entrelazadas y por la devoción que sentían por el maestro Fellini. Soñadores con poquísimas monedas, sí, pero definitivamente vivos. email protected</t>
-  </si>
-  <si>
-    <t>En mi libro Latifundio y poder político, historia de las haciendas de Sucre, publicado por Cinep en 1976, estudié la formación del sistema económico y las estructuras de poder del latifundio ganadero en las antiguas sabanas de Bolívar y los Montes de María, la región del golfo de Morrosquillo y de La Mojana. Yo quería entender por qué había surgido con tanta fuerza el movimiento campesino de la ANUC, asociación creada por el presidente Carlos Lleras Restrepo para darle apoyo popular a la reforma agraria. Las 303 fincas mayores de 500 hectáreas tenían un área de 360.000 hectáreas, un 40 del departamento, y la mayor parte pertenecía a nueve clanes familiares dueños de tierra en Sucre. Todos los clanes, además, estaban unidos entre sí por enlaces matrimoniales, de manera que el monopolio de la tierra estaba garantizado para las siguientes generaciones. Los clanes principales eran los de las familias Pérez, Badel, Támara, García, Martelo, De la Ossa, Olmos, Vergara y Gómez. Sus miembros eran, además, los jefes políticos, notarios y jueces, los dueños de la salud, el transporte, el comercio y, por supuesto, la ganadería. Aunque la estructura de la gran propiedad venía desde las mercedes de tierras y las composiciones, o compras de tierra a la Corona española, se concentró aún más con las reformas liberales de mediados del siglo XIX y luego con la ley de tierras de López Pumarejo, en 1936, que los terratenientes usaron a su favor para conseguir los títulos con juicios de pertenencia ante los jueces civiles, que eran legales para titular tierras privadas pero no los baldíos. Pero el verdadero secreto del éxito del sistema de las haciendas ganaderas fue el monopolio de la tierra, que permitió la subordinación del campesinado como arrendatarios por pastos, que les permitía desmontar, quemar la vegetación y</t>
-  </si>
-  <si>
-    <t>Aburrá Aburrá reordenará su territorio. El Colombiano. ¿Quién es Aburrá? Lamentablemente, este es un ejemplo del egoísmo de nosotros los paisas. Veamos lo que, según la Real Academia Española, significa área metropolitana: Unidad territorial dominada por una gran ciudad o metrópoli en cuyo entorno se integran otros núcleos de población, formando una unidad funcional, con frecuencia institucionalizada. He puesto la última frase con negrilla porque es de allí donde comienzan las ridiculeces me perdonan, porque la verdad es dolorosa.¿De dónde salió el nombre de Aburrá, si la ciudad en torno de la cual se creó es Medellín? ¿Por qué quieren cambiarle el nombre al río Medellín por Aburrá? No saben que el río Medellín tiene otro nombre, desde su nacimiento: río Porce, así lo llamaron los españoles. De las ocho áreas institucionalizadas, según Wikipedia, sólo dos no llevan el nombre de su ciudad: la de Aburrá y Centro Occidente. En las del mundo son parecidas las diferencias. Hay otro problema parecido: el área metropolitana de Rionegro, que no oriental, no está institucionalizada. En la década del 80 del siglo pasado, alguien de las Empresas Departamentales de Antioquia pensó que era tiempo de unir los teléfonos de la futura segunda área metropolitana la de Rionegro. Los municipios que la formarían serían Rionegro, La Ceja, El Retiro, La Unión, Carmen de Viboral, Guarne, San Vicente, Marinilla y El Santuario. Esa unión no prosperó y los teléfonos departamentales de aquella época ya no son del Departamento. Comillas En Irak no hubo Nochebuena. El Espectador. No son necesarias las comillas. El titular quiso decir que no se festejó la noche como otras veces. El adjetivo El segundo nivel se adecuará como parqueadero de bicicletas con 88 espacios para las mismas. Nuestro Metro. Este gazapo es muy común. Resulta que el adjetivo mismo no tiene Espectador. No son necesarias las comillas. El titular quiso decir que no se festejó la noche como otras veces. El adjetivo El segundo nivel se adecuará como parqueadero de bicicletas con 88 espacios para las mismas. Nuestro Metro. Este gazapo es muy común. Resulta que el adjetivo mismo no tiene oficio como pronombre a pesar de que varios escritores así lo usan. email protected</t>
-  </si>
-  <si>
-    <t>a un galimatías político que a un racional ejemplo a seguir. ¿Fujimori? ¿Uribe? ¿Kuczynski? ¿Duque? El escritor Vargas Llosa, en cambio, me trae gratificantes recuerdos. En mis años de estudiante La guerra del fin del mundo me hizo entender más que cualquier tratado sobre el milenarismo y la tenencia de la tierra la endémica y miserable relación entre terratenientes y los pobres del campo en Latinoamérica. El sueño del celta, me hizo imaginar al despiadado régimen de esclavitud que los caucheros impusieron a los indígenas amazónicos. La desgarradora Historia de Mayta me hizo reflexionar sobre las limitaciones del maximalismo revolucionario. Lituma en Los Andes me hizo ver la perversa corrupción política y el drama de los desaparecidos. Y así La tentación de lo imposible, el ensayo de Vargas Llosa sobre Los miserables de Víctor Hugo, creo que retrata muy bien los desvaríos políticos del fecundo escritor peruano. En la obra, Vargas Llosa describe a Víctor Hugo el genio decimonónico como a un narrador desmesurado, vanidoso, excesivo y caprichoso que lleva el relato como le viene en gana y se vuelve en el protagonista principal de la novela, dejando a los personajes en simples arquetipos alejados del mundo real. Es lo que le está pasando al político Vargas Llosa: presumir de hombresiglo como lo fue Víctor Hugo en su época. Sugerencia: Leer la virtuosa narrativa de Mario Vargas Llosa y echar al olvido sus ocurrentes consejos políticos.</t>
-  </si>
-  <si>
-    <t>Hace unos días la revista The Atlantic publicó un artículo que habla de la naturalidad con la que nos acostumbramos a ignorar mensajes de texto y correos electrónicos. El artículo reflexiona sobre cómo es cada vez más común que vivamos entre monólogos pese a que la definición básica de una conversación supone algún tipo de respuesta del receptor. Hoy en día es facilísimo comunicarnos, y entre emoticones y mensajes de voz, cada vez esa comunicación se asemeja más a la comunicación cara a cara. Con una diferencia: el tiempo de respuesta se alarga, a veces indefinidamente. Es sin duda paradójico que entre más instantáneo se hace el envío de mensajes, más lenta se hace la comunicación. A veces, incluso, se vuelve incierta. No sabemos cuánto se demorará la otra persona en responder a nuestro mensaje, si es que lo hace, ni tampoco sabemos cuánto nos demoraremos nosotros. Revisamos el celular en promedio unas 40 o 50 veces en el día sólo para ver mensajes pendientes al lado de los íconos. Es más, pareciera haberse construido un entendimiento tácito de que no es necesario responder inmediatamente o en absoluto a los mensajes que nos llegan. Hasta ahora, la mayoría de críticas al mundo digital tienen que ver con quien envía el mensaje. Nos indignamos con los políticos o los trolls que se vuelven agresivos y atacan violentamente por las redes sociales. Criticamos a los emisores que, al no tener una persona en frente, se envalentonan y en medio de la anonimidad virtual se sienten con el derecho de insultar sin más a otros. Pero, al concentrarnos en el emisor, hemos olvidado que hay otra parte que está fallando y son los receptores. Estamos dejando de tomarnos en serio a ese otro que nos envió un mensaje. Por algún motivo asumimos que</t>
-  </si>
-  <si>
-    <t>Son ejércitos. Cientos de hombres que esperan sentados en el suelo, sobre unas escaleras, en una zona verde, casi siempre en grupo, con sus implementos extendidos a su alrededor, a veces comiendo la ración del día en su coca de plástico, a veces simplemente esperando la orden de empezar su batalla. Están por todas partes, una verdadera invasión urbana: son los mensajeros de Rappi, esas figuras representativas de la llamada economía colaborativa que impulsan las plataformas tecnológicas. Presentados por la empresa como emprendedores independientes que encuentran en su plataforma oportunidades de ingresos extra, en realidad son jóvenes desempleados que al no tener empleadores difícilmente pueden organizarse, armar sindicatos o presentar pliego de peticiones. Rappi es, a menudo, un asidero para los desesperados. Ya se han denunciado sus precarias condiciones de trabajo: deben comprar su uniforme, su caja, usar su bicicleta o su moto. A cambio reciben el 100 del servicio y las propinas. Son un síntoma. De los nuevos rumbos del capitalismo salvaje. De la magnitud del desempleo, sobre todo de la gente más joven. De la necesidad de trabajar de cientos de personas, así sea en condiciones muy duras: bajo la lluvia, con una competencia feroz y tarifas de domicilio que se han ido reduciendo. A veces estamos 12 horas trabajando y nos salen sólo tres pedidos, dijo un rappitendero a . De cómo se puede crear empresa con un mínimo de capital e infraestructura, apoyados en la fuerza de trabajo y en la ley de la oferta y la demanda. En leemos que los trabajadores de oficina deben aportar sus propios equipos electrónicos y no tienen cafetería ni pausas de descanso. Pero, además, los rappitenderos se han convertido en una verdadera invasión del espacio público y un peligro para los peatones. Las plataformas tecnológicas vinieron para quedarse, tienen</t>
-  </si>
-  <si>
-    <t>las mujeres vulneran los derechos humanos, afectan la dignidad de las personas. Así mismo, se han sancionado estudiantes agresores. Como una de sus estrategias para afrontar esta problemática, la UPN adoptó a través de la Resolución rectoral 1175 de agosto del 2018 el Protocolo para la Prevención y Atención de las Violencias contra las Estudiantes, favoreciendo una vía de protección de los derechos de las mujeres para garantizar un espacio universitario libre de violencias. Con un año de implementación, hemos evidenciado un importante avance en el acompañamiento y apoyo de las estudiantes, consideramos que es importante continuar trabajando en la mejora e implementación de estos protocolos como una estrategia para crear canales de comunicación ágiles y efectivos para denunciar este tipo de sucesos. Sin embargo, somos conscientes de que la mera implementación de estas rutas de atención no es suficiente para superar la problemática, pues nuestro trabajo debe estar enfocado en generar una transformación cultural tanto a nivel institucional como en la sociedad, que permita abandonar las comprensiones patriarcales y machistas sobre las que se establecen las relaciones con los otros y que aún permean cada dimensión de lo social. Si bien es importante tomar medidas estacionales para garantizar la transversalización de la equidad de género, también cuestionarnos sobre las causas que motivan las acciones violentas, un asunto importante que nos debe interesar. Aunque no existe una causa única a la que pueda atribuirse una conducta agresiva, sí existe en general una serie de factores de riesgo que pueden hacer surgir la aparición y posterior mantenimiento de la violencia de género. Dentro de ellos, una variable predominante es la situación de desigualdad real en la que puede encontrarse la mujer respecto al hombre, en diferentes sentidos: fuerza física, dependencia económica, aislamiento, etc. Otras situaciones están asociadas a factores socioculturales, ya</t>
-  </si>
-  <si>
-    <t>Decisiones sobre la mesa para el presidente Duque y su ministro de Hacienda. Diríase que estos han sido ocho años para olvidar en materia de CTeI, si no fuera porque debemos sacar las lecciones. El debilitamiento de Colciencias por la increíble rotación de directores, la mala experiencia con el Fondo de CTeI de regalías y el traslado de 1,3 billones de este a vías terciarias fueron los hechos más notables. Aun si se lo propusiera, le quedaría difícil al próximo gobierno hacerlo peor. La buena noticia es que, a juzgar por el énfasis en CTeI de las propuestas del presidente electo, es probable que el nuevo gobierno se proponga hacerlo mejor. Este llega con al menos cinco ideas a partir de las cuales podría darse un diálogo que nos lleve al giro que el país necesita en CTeI. i Evolución institucional de Colciencias; ii reconfiguración del Fondo CTeI de regalías; iii focos prioritarios de investigación; iv 35 Ph.D. por cada millón de habitantes por mucho, estamos en 10, y v la más conocida de aumentar la inversión en IDi a mínimo el 1,5 del PIB, con incentivos para la iniciativa privada en la investigación aplicada. Dos proyectos de ley en curso le brindan al gobierno Duque la posibilidad de abrir el diálogo con la comunidad científica. El primero es el que crea el Ministerio de Ciencia, Tecnología e Innovación, de iniciativa parlamentaria, con un primer debate en la Cámara. El profesor Moisés Wasserman, exrector de la Universidad Nacional de Colombia, lo ha ponderado. Curiosamente para los científicos, el nuevo gobierno llega con una idea de potencial más ambicioso. Reza así: Colciencias debe convertirse en Departamento Nacional de Conocimiento, CTeI, con independencia institucional para dar estabilidad de largo plazo a los procesos de investigación, y autonomía para articular con las universidades</t>
-  </si>
-  <si>
-    <t>mujeres, jóvenes o no tan jóvenes, de todas las regiones y todos los orígenes y todas las creencias, con excelente formación académica y con amor sentido por su tierra. Colombia sí tiene talento. Por eso la asamblea de la Fundación Razón Pública está integrada por 131 personas de distintas profesiones, regiones, universidades y convicciones. Con esto se aseguran dos cosas importantes: que este proyecto no tiene dueños y que aquí caben todas las opiniones serias. ¿Y cómo se financia todo eso? Razón Pública ha vivido de los 1.127 expertos a quienes no se les paga ni un centavo. Los miembros del consejo editorial y el director de la revista trabajamos gratis, y con mucho gusto. Los fundadores y asociados contribuyen con dinero, tenemos convenios con universidades y apoyos de algunas fundaciones. Pero eso no es suficiente, y a diferencia de los medios comerciales, Razón Pública no tiene pauta publicitaria ni quiere cobrar por el acceso a sus páginas. En estos tiempos de polarización, manipulación y falsas noticias, creemos que es aún más necesario mantener y mejorar un medio independiente y abierto a toda la ciudadanía, donde haya argumentos en lugar de insultos y las razones hablen en vez de las pasiones. Por eso espero que consulte y utilice la revista: es para quienes quieran ser parte del diálogo ciudadano. También por eso necesitamos su donación. Le ruego hacerlo ya para que no se le olvide. Puede hacerlo a través del portal de Razón Pública . Director de la revista digital Razón Pública. Razón Pública.</t>
-  </si>
-  <si>
-    <t>una inversión muy rentable socialmente. No tan al margen: soy partidario de crear universidades públicas 5marzo2016, con un régimen nuevo de principios, reglas e incentivos modificados respecto de los actuales, si la situación fiscal lo permite y en un horizonte escalonado de reformas. Si la gratuidad total de las matrículas es mala idea, y pueden ver la experiencia de Chile, hay que mantener el principio de solidaridad social e intergeneracional por el cual los beneficios privados de la educación superior pública son compartidos parcial o marginalmente. Ahora, en algunas universidades hay que bajar las matrículas, como en la del Chocó, o ajustar la política, como en la del Cauca, de acuerdo con la Corte Constitucional. Una manera clara de entenderlo sería generar en las instituciones de educación terciaria públicas, incluido el SENA, un recibo de matrícula con el valor real de la inversión acumulada que la sociedad está haciendo en el estudiante y la fracción del costo que este está pagando, que en centenares de miles de casos no es significativa. La diferencia entre lo invertido por la sociedad y lo aportado por la familia del alumno crearía conciencia de devolver o retribuir a la sociedad, es decir, a aquellos que ni siquiera tienen recibo de matrícula porque es la sociedad la que les está debiendo, por ejemplo la educación obligatoria que promete la Constitución. Ese recibo social de matrícula podría descontar de la deuda con la sociedad el valor de aportes de tesis de grado a la innovación, la productividad y la equidad, pero esto implica otra concepción del contrato social y de la responsabilidad de la educación superior con el proyecto de país. Y del cambio social: para enfrentar la increíblemente aceptada deserción y promover la equidad regional hay que proveer vivienda estudiantil, bienestar universitario y otros servicios</t>
-  </si>
-  <si>
-    <t>herramienta que facilita el contacto entre productores y consumidores, allí se encuentran los nombres de las huertas, su ubicación, el teléfono y los productos y los servicios que ofrecen. Nos urge empezar a sembrar y plantar la duda en quienes desconocen este movimiento y así contribuir un poco a esta importante revolución. El huerto no solucionará sus problemas, sus deudas y sus dudas, pero quizás cambie su orden de prioridades en la vida. De pronto lo arrastre al concepto slow life. Puede que ese tiempo que pase en contacto con la naturaleza, con su familia y obteniendo recursos de la tierra solo con su maña y esfuerzo, lo lleve a construir una vínculo sano con su comida y su entorno, el cual le aseguro dará buenos frutos.</t>
-  </si>
-  <si>
-    <t>cambios hormonales importantes y tanto hombres como mujeres sentimos cómo nuestros cuerpos comienzan a deteriorarse y la mente a desacelerar. Es también el periodo en que nos volvemos conscientes de nuestro desenlace. La muerte se hace presente en nuestras vidas, pues es el momento en que los padres empiezan a enfermarse seriamente y a morir. La infancia y la juventud no nos preparan para esto. No sabemos cómo asumir nuestro deterioro, ni cómo enfrentar la pérdida de nuestros seres más queridos. Ahora que la ciencia y la medicina están logrando que vivamos muchos años, debemos aprender, conocer y disfrutar de cada etapa, enfrentar los cambios con dignidad y construir una sociedad que valore y respete todos los momentos. Envejecer no puede ser denigrante. Mientras el cuerpo, la mente y las ganas de vivir estén, debemos generar todas las condiciones para que cada ser humano en cualquier etapa que se encuentre pueda disfrutar la vida cómoda y dignamente. El gobierno, la ciencia, la cultura y la religión en ningún momento deberían ser obstáculos para lograr esto. Todo lo contrario, deberían ser caminos para ayudar a conseguirlo. Como en otras culturas, a mi gusto más evolucionadas, ojalá llegara el momento en que aprendamos a apreciar tanto la juventud como la vejez, y la vida como la muerte. Tengo la suerte de no haber tenido que enfrentar la muerte prematuramente, y aunque no me siento bien preparada ni para asumir mi deterioro, ni el de los seres que amo, sé que tengo una enorme responsabilidad de estar y acompañar a vivir a los que quiero en sus afecciones y pérdidas. Ha sido una etapa difícil. La enfermedad y la muerte nos están rondando. A todos mis amigos que sufren por esta razón en estos momentos, de corazón, acá estoy. Cuentan conmigo. Mi compromiso enorme responsabilidad de estar y acompañar a vivir a los que quiero en sus afecciones y pérdidas. Ha sido una etapa difícil. La enfermedad y la muerte nos están rondando. A todos mis amigos que sufren por esta razón en estos momentos, de corazón, acá estoy. Cuentan conmigo. Mi compromiso hoy es con ustedes.</t>
-  </si>
-  <si>
-    <t>del cuerpo de regular y controlar la presencia de bacterias algunas no tan nocivas sobre la piel y, además, permite que esos microorganismos empiecen a hacerse más y más resistentes a esos productos e, incluso, a algunos más poderosos, como los antibióticos. En conclusión: el gel antibacterial, tan en boga en nuestro tiempo, no es más que un excelente truco para vender algo que científicamente no es tan bueno. Y así pasa con infinidad de cosas que nos rodean. ¿Acaso no hay algo más inútil que ir por la vida poniéndole al perro de la casa un saquito porque hace frío? ¿O poniéndole zapatos porque va a salir a la calle? ¿No es un absurdo que a finales de la segunda década del siglo veintiuno, muchos sigan considerando que el uso o no uso de traje y corbata permite definir la estatura moral y social de una persona, cuando en realidad la corbata no es más que un accesorio trivial e inútil? Sin duda, el padre de la infortunadamente famosa Jenny Ambuila, funcionario de la Dian y ahora señalado de haberse enriquecido con dineros del contrabando, usaba corbata en sus reuniones. Seguro utilizaba el uniforme de la persona honesta, porque según piensan algunos alguien que usa traje es mejor persona que alguien que anda en tenis y camiseta. Nada más errado. Ni un Lamborghini, ni un bolso Chanel, ni unos zapatos Herms ni una billetera Louis Vuitton son la persona que los usa. Todo es un embuste. Y quien compra esas marcas para sentirse más que los demás cae exactamente en el mismo error que aquel que usa el gel antibacterial para matar los gérmenes: ni el gel le salva a uno la vida, ni las marcas de lujo lavan el dinero conseguido luego de clavarles una puñalada por la</t>
-  </si>
-  <si>
-    <t>al posterior, que es el de la Ilustración; pero en cualquier caso, que me hablaran más de todo eso. Que me adiestraran para escribir, aprendiendo a corregir y no simplemente pasando ideas de la mente al papel. Que me explicaran que los seres humanos estamos predispuestos genéticamente, con una mezcla de impulsos nobles y mezquinos, pero sin que la genética nos marque necesariamente el destino. Que me hablaran más de arte y de literatura. Que me revelaran los secretos básicos del cerebro, para entender que somos seres emocionales más que racionales y que con mucha frecuencia lo que creemos verdadero es una simple adaptación de lo que deseamos. Que me mostraran cómo la colaboración puede ser más rentable que el egoísmo. Que me dijeran lo mucho que los hombres nos parecemos a los simios machos, en la manera como nos excedemos en el ataque a los enemigos, recurrimos a la violencia, dominamos a las hembras y nos embelesamos con el poder; todo ello, sabiendo que la cultura y el sentido moral nos pueden liberar de esas semejanzas. Que me entrenaran para pensar a partir de problemas, no solo de teorías. Que me explicaran cómo funciona la sociedad de consumo. Que me pusieran a leer los secretos de la felicidad que hay en Epicuro, Montaigne, Erasmo y Hume. Que me enseñaran a disfrutar del silencio. Que me dijeran que los animales que tienen un sistema nervioso complejo sufren como nosotros y por eso merecen nuestra compasión. Que me contaran más historias de la mitología griega y menos de la historia sagrada. Que me dieran una mejor educación sentimental, para gozar del cuerpo y sus placeres, sin diablos agazapados, ni infiernos amenazantes. Que me enseñaran a pegar botones. Que me hablaran más de las virtudes y menos de los mandamientos. Que me</t>
-  </si>
-  <si>
-    <t>En 1984, el gran entomólogo, sociobiólogo y doble ganador del Premio Pulitzer, Edward O. Wilson, retomando la idea de Erich Fromm según la cual el ser humano tiene un condicionamiento psicológico que lo atrae naturalmente hacia la vida, acuñó el término biofilia. Biofilia es la tendencia innata que nos conecta a los humanos con la naturaleza y con la vida, siendo este instinto producto de nuestra evolución biológica y parte de los mecanismos que le aseguran a los animales eusociales tales como el ser humano aquella sensibilidad y conexión estrecha con el medio ambiente, la cual es imprescindible para su supervivencia. Propuesta por uno de los científicos más importantes del último siglo, la biofilia ha sido desarrollada, adaptada e incorporada por saberes tan diversos como la psicología evolutiva, los estudios medioambientales, la ciencia política, la geografía humana y el diseño urbanístico. En los últimos años los diseños biofílicos tales como los bosques urbanos, y los edificios y fachadas verdes, han ido ganando popularidad en grandes capitales, demostrado sus bondades en materia económica, de conservación energética, sostenibilidad ecológica y arquitectónica y, sobre todo, incidiendo positivamente en la salud mental de los ciudadanos. Los árboles son necesarios para el bienestar de los habitantes de cualquier ciudad pues, además de lo anterior, un árbol adulto puede absorber hasta 150 kilogramos de dióxido de carbono al año, secuestrando el carbono y filtrando el oxígeno. No ocurre lo mismo con los árboles jóvenes como aquellos de no más de metro y medio con los que la administración de Bogotá está reemplazando los árboles que ha talado, pues su capacidad de retención y procesamiento de CO2 es tan solo una fracción de la de los árboles adultos. Un árbol maduro también contribuye a mitigar la contaminación de fuente no puntual, que es aquella que producen las</t>
-  </si>
-  <si>
-    <t>¿Ha caído en el embrujo del gel antibacterial? ¿Es de esos que cargan en su bolso, cartera o bolsillo un pequeño frasquito plástico con un producto incoloro y a veces inodoro que se promociona como la mejor solución para combatir los microorganismos que nos rodean y podrían convertirse en una amenaza para la salud? Si respondió que sí, esta columna es para usted. Si respondió que no, igual le aconsejo que siga leyendo porque este no es un escrito sobre bacterias, microbios y nuestra constante lucha por permanecer saludables, sino más bien una reflexión respecto a la manera como hemos llenado nuestra vida de cosas, productos y hasta personas que poco sirven. O, al menos, que poco nos aportan. Como un ejercicio plenamente humano, cada tanto deberíamos detenernos a reflexionar sobre aquellos objetos o personas que resultan inútiles para nuestra vida y hacer tal y como ocurre cuando se revisa el armario y se sacan las viejas chaquetas, los pantalones desgastados o las camisas molidas que sabemos que nunca más vamos a usar. Lo inútil se va, se bota, de ahí que inicie con el ejemplo del gel antibacterial. Hace unos días, la investigadora Gabriele Berg, de la Universidad de Graz, en Austria, presentó un estudio en el cual concluye que el exceso de higiene, en lugar de ser bueno para la salud de los humanos, resulta absolutamente nocivo. La doctora Berg explica que el uso del gel antibacterial va en contravía de lo que promueve, pues elimina la capacidad del cuerpo de regular y controlar la presencia de bacterias algunas no tan nocivas sobre la piel y, además, permite que esos microorganismos empiecen a hacerse más y más resistentes a esos productos e, incluso, a algunos más poderosos, como los antibióticos. En conclusión: el gel antibacterial, tan en boga</t>
-  </si>
-  <si>
-    <t>He aquí un gran invento: la cunaataúd para niños desnutridos. A medida que la meces, el crío, en vez de dormirse, se muere. La desnutrición, como casi todo en la existencia, se puede contemplar a la luz de las teorías o de las emociones. Teóricamente hablando, el síndrome que presentan estas criaturas se debe a la escasez de calorías que corren por sus cuerpos. Podemos afirmar que ingieren pocas proteínas y pocos hidratos de carbono, por lo que padecen también un déficit de hierro, vitaminas, yodo, etcétera. De ahí su postración no es que estén echándose la siesta. Allá donde reina la pobreza, la desnutrición empieza en el espermatozoide, que llega a destino agotado, como si hubiera subido siete pisos sin detenerse a respirar. Pero tampoco el óvulo, si tenemos en cuenta el hambre de la portadora, lo recibe en buenas condiciones. Significa que el encuentro, más que sumar, resta. Y no será porque en el mundo no haya calorías. Está lleno de ellas, pero se encuentran mal repartidas. Hay acaparadores de calorías como hay acumuladores de chatarra. Cuando el presidente de un banco se jubila, le dan calorías para seis o siete generaciones. Y quien dice el presidente de un banco dice el de una hidroeléctrica o el de una gasística, no sé. Tendrían que vivir mil vidas para consumirlas. Otros, en cambio, han de conformarse con las que les proporciona la ingestión de un escarabajo o una mosca flaca atrapada al vuelo. Esto último es teoría económica. Y nos hemos quedado sin espacio para hablar de las emociones. Muérete, niño, muérete ya, que si no el coco te llevará. Juan José Millás. Sin palabras. Este magistral artículo de Millás, uno de los escritores españoles más importantes sus obras están traducidas a más de 20 idiomas, describe con una</t>
-  </si>
-  <si>
-    <t>desarrolla su sistema neuronal en meses ya más avanzados del embarazo. Esta visión es más cercana a los postulados aristotélicos, que ya desde entonces concebían la vida desde la formación completa del cuerpo. A pesar de los avances científicos, hoy en día la domesticación de las mujeres sigue vigente: al entregarnos el poder de decidir sobre nuestras facultades se abriría el camino hacia nuestra completa emancipación. Ante dicho temor, tan arcaico y ancestral, no hay argumento científico que valga. Sin embargo, invito a las mujeres a seguir en la lucha. Recuperar nuestra naturaleza instintiva abriría las puertas de nuestra celda ancestral y nos devolvería la posibilidad de utilizar nuestros poderes a favor de los ciclos naturales de la vida y la muerte. , email protected</t>
-  </si>
-  <si>
-    <t>La crítica más demoledora que he visto a la estrella judicial colombiana es una fotonovela realizada por una profesora norteamericana. Fácil de leer y asimilar, el Viaje a través del desafío del diseño de la tutela de la Corte Constitucional Colombiana es obra de Margaret Hagan, directora del Legal Design Lab de Stanford y conferencista en la escuela de leyes de esa universidad. Hagan vino a visitar a Santiago Pardo, un exalumno suyo que montó en la Universidad de los Andes un laboratorio semejante. Este constitucionalista está trabajando con Santiago de Francisco, profesor de diseño, en un proyecto con la Corte Constitucional CC para redefinir cómo las personas interactúan con esta y cómo se procesan los casos. Lo hacen para una clase de derecho y la CC les da amplio acceso para observar, hacer entrevistas, revisar, elaborar prototipos y pruebas in situ. Definitivamente una imagen vale más que mil palabras. La primera fotografía es del plácido entorno, con vista panorámica sobre Bogotá, donde se conciben ideas geniales para arreglar problemas nacionales. Al bajar al mundo real se ve un camión con los bultos de expedientes que llegan desde todo el país y que nadie volverá a mirar. Dentro de la sede de la CC se aprecia el gigantesco espacio en donde estudiantes de derecho en pasantía, necesariamente de Bogotá y probablemente de Uniandes y otras facultades de élite, hacen una selección de las tutelas que serán revisadas por la CC. Ahí se alcanza a sospechar cómo llegan las modas intelectuales del exterior a la jurisprudencia y por qué muchos debates se centran en las preocupaciones intensas de unas cuantas mentes brillantes, que convencen a los medios y a la opinión pública ilustrada de que se trata de asuntos fundamentales para el futuro de Colombia. No sorprendería que en el futuro</t>
-  </si>
-  <si>
-    <t>se practicaran pruebas relacionadas durante el trámite de extradición como los testimonios, sino que, de manera más general, pretendía que ninguna prueba incluida la documental fuera utilizada para decidir. En este contexto, y dado que la prohibición no está restringida a nadie en particular, debe entenderse que cobija a todos los sujetos e intervinientes procesales y a los propios magistrados. Solo de esa manera se respetaría el espíritu de la disposición, que de manera general veta el uso de cualquier material probatorio, con independencia de si es aportado por el Estado que solicita la extradición, o por los abogados defensores del requerido; aceptar las pruebas de una sola de las partes no solo carecería de respaldo normativo, sino que supondría un inadmisible desequilibrio entre quienes intervienen en el proceso. Si ese fue el propósito del Congreso, entonces la JEP, al recibir los documentos relacionados con un trámite de extradición, debe inadmitir y devolver todos los que tengan la condición de pruebas; por ejemplo, debe excluir los que acrediten la identidad de la persona requerida, los que evidencien la existencia de una acusación formal contra ella en un tribunal extranjero, y los que permitan soportar la probable existencia del delito por el que la persona es reclamada. Increíblemente, la introducción de esta prohibición legal significaría que la JEP debería decidir sobre las extradiciones sin tomar en cuenta ninguna de las pruebas en las que el país requirente fundamenta su solicitud. No cabe duda de que los antiguos romanos subestimaron la inventiva de nuestros legisladores. de nuestros legisladores.</t>
-  </si>
-  <si>
-    <t>Los triunfos de Claudia López en Bogotá y Daniel Quintero en Medellín representan cambios de gran magnitud en contextos en los que parecían atoradas las esperanzas de millones. Bogotá y Medellín dieron la pauta, pese a que los oráculos de las firmas encuestadoras indicaban otros resultados. Algunos, a juzgar por sus comentarios en redes, no han comprendido y siguen anclados en el cuento tonto del castrochavismo, supuesto protagonista del triunfo de López y Quintero, tanto como de las manifestaciones en Chile y en Quito. Allá ellos. Otros, del otro lado del espectro, se encargan de demeritar la victoria en Bogotá y de atribuirse, de forma abusiva, el triunfo en la capital paisa. Los liderazgos de corte caudillista, de uno y otro lado, fueron derrotados. Los resultados del domingo son aire fresco para una mayoría harta de la política tradicional. López y Quintero son políticos del siglo XXI, propios de las sociedades del conocimiento. No solo por su incuestionable preparación académica y profesional. Comprenden que el debate se debe centrar en argumentos, que los gobernantes construyen sobre lo construido, que el respeto por la diferencia es esencial en una democracia, que deben gobernar para todos. Saben que el cambio resultante de la revolución tecnológica, la interdependencia creciente en el mundo global que nos obliga al respeto por la diversidad, así como el cambio climático son fuerzas ineludibles que nos obligan a hacer política de manera diferente. El campanazo de Chile, el país de mostrar por su estabilidad macroeconómica y el recetario aplicado en materia pensional, educativa y de la salud, debe ser tomado en serio. Parafraseando a alguien en los 90: Es la inequidad, estúpido. López y Quintero, distintos entre sí, han planteado plataformas incluyentes, de respeto por la diferencia y la pluralidad. Cuarta revolución industrial, lenguaje esotérico para las maquinarias</t>
-  </si>
-  <si>
-    <t>el éxito de Iván Duque y su gobierno hacia delante. Será determinante que el mandatario, hombre joven, de buenas maneras e intenciones, sepa conectar con estos sentimientos y pase a segundo plano las voces cercanas que le hacen creer que se trata únicamente de algo personal, foráneo y malévolo. El mandatario está en la capacidad de comprender lo que ya le están mostrando los autodenominados líderes del Comité del Paro, que con su absurda lista de pedidos revelan que sus verdaderas intenciones no son los jóvenes, sino mermelada y una soterrada agenda política radical. Presidente, quíteles la bandera de las marchas a los trasnochados de siempre y diferéncielos del mensaje legítimo de los más jóvenes; si no lo hace, Petro, el Eln y otros vetustos intereses de siempre secuestrarán a nuestras juventudes y, con ello, el futuro del único país que tenemos.</t>
-  </si>
-  <si>
-    <t>Leamos y escribamos para afianzar nuestro ser histórico, nuestra originalidad, nuestra lucha y, también, nuestros éxitos. Introducción. Reflexionando en estos difíciles días, me pregunté: ¿Cómo podría contribuir a la recreación de los lectores de El Espectador con un tema que los distraiga creativamente? Me acordé entonces de la columna más significativa que he escrito. ¿Cuál? Veamos una pequeña historia. A raíz de la columna que publiqué en El Espectador el 22 de agosto de 2006, recibí el 23 un mail de agradecimiento por parte de un escritor profesional antioqueño, que se iba a suicidar el día anterior porque estaba frustrado con el ejercicio de su profesión pero que, al leer la columna, lo había impulsado a rectificar su decisión Un tiempo después, recibí una gentil y profesional nota, de la coordinadora editorial de la Revista Innovación Educativa de México D.F., Alicia Lepre Larrosa, donde me solicitaba autorización para publicar la columna en una próxima revista, en su sección: Subrayado. Procedí a condensar la versión original, la envié y fue publicada en el Volumen 7, Número 41 de noviembre diciembre de 2007. Así que esta versión es la que he fraccionado y compartiré en tres entregas con los lectores. Esta es la primera. Anotaciones preliminares . ¿Por qué leer y escribir, hoy? Porque desde hace milenios los seres humanos han buscado en medio del proceso evolutivo transmitir a los descendientes aspectos sustantivos de sus huellas. A partir del salto cualitativo de los descendientes de los protocatarrinos, los antepasados del hombre comenzaron a expresar signos que permitieron afianzar su presencia en la Tierra y en el Universo. En la actualidad, para un ser humano consciente no solo se trata de nacer, crecer y reproducirse, sino de plasmar testimonios sobre el conocimiento, el saber y la existencia, para ser prolongados por otros: los</t>
-  </si>
-  <si>
-    <t>graves acusaciones de Soto? La opacidad y desorden de este engendro institucional no ayudan a responder preguntas elementales. Recurrí a quienes creí tenían buen conocimiento y quedé sorprendido por sus dudas y silencios. Según la sección especializada de , uno de los riesgos de Montoya es afrontar un juicio adversarial en el Tribunal para la Paz, parte de la JEP. La acusación dependería de la Unidad de Investigación y Acusación, también endógena, que presentaría todas las pruebas que lo incriminen. Obviamente, la defensa del general podrá controvertir esos elementos probatorios y también pedir pruebas para sustentar su inocencia. Si ante la evidencia el sospechoso teme ser vencido en el juicio podrá evaluar si admite responsabilidad. En tal caso no tendrá pena alternativa, sino privación de la libertad entre 5 y 8 años. O sea que, en el peor escenario para él, con varias condiciones improbables, el general recibiría una sanción bien inferior a la que estaba pagando quien lo acusa. Cerca de dos mil militares y policías se han acogido a la JEP para el mismo caso de los falsos positivos, muchos de ellos ya condenados por la justicia ordinaria, incluyendo a Rito Alejo del Río, con pena de 25 años y Jairo Humberto Uscátegui con 37. Una de las personas que consulté para indagar sobre el futuro de Montoya ha asesorado a las FF.AA. Anotó que nos demoramos casi un año para convencerlo de que se presentara en la JEP. Buscan que se convierta en el líder político del proceso. Si va a llover mierda que sea él quien lidere la protección de nuestro Ejército Nacional. Años antes de que se volviera dogma que la justicia restaurativa es sustituto idóneo de la penal, publicó testimonios sobre los falsos positivos. Concluía que un centenar de familias lucha para que las</t>
-  </si>
-  <si>
-    <t>que, con motivo de cada elección, vienen por un tiempo a tomar decisiones trascendentales para el cumplimiento de los fines del Estado. Esta discusión interminable tendrá versiones diferentes con el paso del tiempo y las circunstancias propias de cada país. Los equilibrios entre permanencia y transitoriedad en el ejercicio de las funciones serán siempre objeto de precisiones y ajustes, que irán generando nuevos esquemas de atención de las necesidades de todo tipo, y que no pueden terminar en la adjudicación exclusiva, a nadie, del poder en materia administrativa. El arbitraje de esa continua disputa corresponde a la ciudadanía, que se debe manifestar a través del voto, para nutrir el componente político de la administración, y a través de la veeduría ciudadana y el ejercicio de las opciones de control frente a la marcha día a día de una gestión que debe tener como meta y motivación el bien colectivo.</t>
-  </si>
-  <si>
-    <t>chocolate, o el cigarrillo o el café o las cartas o las líneas de las manos. Quiero arrojar mi celular encendido a lo más profundo de un lago para ver cómo se van desconfigurando las palabras, los colores, los muñecos, las recomendaciones y las noticias de última hora, oír cómo se mezclan el estallar de las burbujas con los metálicos acordes de su ring tone, y después, acostumbrarme a la vida sin mensajes urgentes y sin algoritmos. Quiero volver a tener el tiempo que alguna vez tuve, jugar a las escondidas con un amigo imaginario, volver a creerme futbolista o cantante, y aburrirme y buscar después la manera de desaburrirme. Quiero tirarme al pasto, bañarme en los ríos, conversar con los albañiles y regalarle un poema a la profesora de español de la escuela de mi pueblo. Quiero creer de nuevo en el diablo y en un dios, y hacerme amigo de todos los diablos para saber cómo lograron hacer de este mundo un infierno.</t>
-  </si>
-  <si>
-    <t>de la universidad. Esto quizás ayudaría a entender cómo llegó el agua al molino donde anidan las garzas al abrigo de la caña, pero sobre todo sirve para aterrizar en el escenario que nos quieren ocultar con el montaje del Petrovideo. Según el abogado y jurista Ramiro Bejarano, independiente de que Petro sea o no culpable está andando un complot gigantesco para poner a salvo a un fiscal atrapado, al precio que sea y contra todo aquel que se atreva. Ver columna . El nombramiento de un fiscal ad hoc es contentillo para la galería, pues quien resulte elegido de la terna uribista, por supuesto solo se encargará de tres casos y deberá contar con el mismo equipo de investigadores que depende del fiscal general. Vaya bufonada. Ahí misteriosamente los más importantes medios de comunicación evitaron siquiera musitar o sugerir la renuncia del fiscal, que habría sido lo ética y jurídicamente conducente. O como dijo el Groucho Marx colombiano, Adolfo Zableh, en preocupante advertencia : Olvídense de que el fiscal va a renunciar, mucho menos de que va a pagar ante la justicia en caso de que haya cometido un delito. Tiene la bendición del establecimiento y el silencio de la prensa masiva. DE REMATE: Yo le creo a Petro, nunca he visto que haya hecho algo incorrecto o ilegal, exceptuando su militancia en el M19. Pero cuando respondió a las acusaciones por la plata que recibió, le faltó contar con un asesor para momentos de crisis. Ese farragoso video de 40 minutos debió ser editado, recogiendo las siete u ocho explicaciones puntuales que resuelven toda duda. Además, se le vio golpeado, inseguro, sin liderazgo. ¿Cuándo aprenderá la izquierda a comunicar? En eso la derecha le lleva años luz de ventaja. En Twitter: de 40 minutos debió ser editado, recogiendo las siete u ocho explicaciones puntuales que resuelven toda duda. Además, se le vio golpeado, inseguro, sin liderazgo. ¿Cuándo aprenderá la izquierda a comunicar? En eso la derecha le lleva años luz de ventaja. En Twitter:</t>
-  </si>
-  <si>
-    <t>Después del huracán que destruyó Providencia y del dolor de esas imágenes, el país empezó a disolverse como terrón de azúcar. El agua es imparable, las lluvias no cesan. Las imágenes del arroyo en el parque El Virrey, en Bogotá, me hicieron pensar en una extensión urbana del río Magdalena. Desbordamientos, inundaciones. En la Guajira, en el Chocó, en el Catatumbo. Muertos y desaparecidos, torrentes que se llevan el ganado, los carros y de vez en cuando a alguna persona inerme. Es como una maldición bíblica y me pregunto: ¿serán los anuncios preliminares de la llegada del fin del mundo? Entonces decidí inaugurar un cuaderno con el siguiente título: Cosas para hacer en la tarde, antes del fin del mundo. Escribí algunas cosas: Acabar de leer por fin el último tomo de En busca del tiempo perdido, de Proust, que nunca terminé. O también: Irme a vivir para siempre a la India. Alguna vez pensé o anhelé que el fin del mundo me sorprendería en un avión y que, por eso mismo, alcanzaría a disfrutar de una parte del espectáculo desde lo alto. Eso me permitiría alcanzar al menos una vez y a modo de despedida lo sublime, que según la definición de Kant consiste en la contemplación de lo terrible, pero desde un lugar seguro. Luego la realidad del país volvió, terca, a arruinar mis ensoñaciones literarias. Si los aguaceros y tormentas del fenómeno de La Niña están disolviendo a Colombia, cuya tierra firme parece sostenida por raíces de árboles centenarios y huesos de entierros clandestinos, el fenómeno del niño presidente acabará con el resto e incluso vaticino que iremos de niño en niño, pues ya se nos prepara para la inminente candidatura de Tomasito Uribe. Ese grupo de presión económica, creado por ganaderos, empresarios, paramilitares, banqueros e iglesias</t>
-  </si>
-  <si>
-    <t>Si dejamos caer una gota de agua en la mano no podremos predecir con certeza cuál será su camino. La inclinación de la mano, las vellosidades, la temperatura de la sangre, el tamaño de las venas, hasta el más mínimo detalle pueden alterar el curso de esta gota. Y como vivimos en una realidad caótica, estamos expuestos a increíbles variables y alteraciones difíciles de presagiar. Por eso suceden las crisis corporativas, porque el mundo empresarial vive de la misma forma como vivimos las personas: somos todos elementos pequeños en un sistema natural cuyas acciones pueden generar grandes reacciones que nos pueden sobrepasar, dependiendo de las circunstancias y del ambiente. Las crisis son pequeñas monstruosidades nacidas de repente en una atmósfera donde reinaban el equilibrio y la armonía. Pueden salir de su cáscara con dientes muy filudos o pueden ser cándidas e inofensivas; pueden crecer muy rápido, mutar y reproducirse, o pueden morir al instante. Nunca se sabe; nunca lo sabremos. Además, tienen características que los destacan de otros eventos: unicidad, sorpresa y pluriformidad. Causan miedo, pero hay que enfrentarlas y asumirlas con prudencia y estoicismo. Porque lo importante al final sin importar el tamaño de las circunstancias negativas es cómo nos levantaremos el día después de la crisis. Independientemente de las responsabilidades, acciones y omisiones en el caso de Hidroituango, hemos estado enfrentando una crisis nacional que afecta a miles de habitantes de cuatro departamentos y que podría generar estrés al sector eléctrico que le lleva luz a todo el sistema interconectado. A raíz de los eventos del proyecto, EPM ha recibido el respaldo de algunos líderes de opinión, candidatos presidenciales, influenciadores de redes sociales, agremiaciones y políticos. También aparecieron fuertes críticos que buscaron un castigo público y vergonzante para los responsables, que aún desconocemos, mientras las familias que viven</t>
-  </si>
-  <si>
-    <t>meses, en la radio nacional, una mujer de la comunidad raizal explicó cómo el agua no se ha llevado solo las casas, sino también los muertos: Con mucho esfuerzo trabajé yo para hacer esa casa y el mar se la llevó. Vea que me quedé sin nada. Igual con el cementerio. Mi abuelita y mi abuelito no se sabe a dónde quedaron porque el mar se llevó todo eso. Entre tanto, la población espera la continuación de algunas obras de protección costera que se iniciaron a comienzos de 2019 y quedaron a medias debido, según el Distrito, a falta de recursos para continuar. Se me cayó una pared y me tocó salir corriendo con mis hijos para acá, para donde otra hija, y nosotros estamos esperando y esperando a que nos hagan las obras y nada. Pero como dice el dicho: al que no le cae la gota no siente el agua. ¿Hasta cuándo?, denunció otra de las mujeres entrevistadas en medios. Tanto en el Caribe como en el Pacífico, las comunidades en gran mayoría afrodescendientes se resisten sobre todo al desplazamiento hacia las tierras altas, que conduce a un futuro a merced de la caridad, en viviendas improvisadas que no escogieron, y acarrea el fin de las rutinas y las tradiciones de vida. Estos desplazamientos están generando graves cambios en nuestra dinámica cultural. Los niños y pescadores que ahora viven más atrás dicen que extrañan mucho vivir a orillas del océano, resumió Francia Guaitotó. La subida en los niveles del mar, una de las consecuencias más tangibles del calentamiento global, impacta todos los días a las comunidades que viven a menos distancia del nivel medio del mar. Así, numerosos estudios advierten sobre el peligro que se cierne sobre islas, deltas y playas perdidas, cuyas edificaciones están cada vez más</t>
-  </si>
-  <si>
-    <t>suerte que la información privilegiada y el estatus no sean factores que faciliten los modelos de negocios una vez se deja de pertenecer al Estado. Como bien lo demostró el senador Rodrigo Lara, los bonos de agua fueron un pésimo negocio para los municipios involucrados, hasta el punto de que la Nación, vía Findeter, tuvo que asumir el entuerto. El entonces ministro Carrasquilla promovió y contribuyó a configurar un diseño institucional que luego fue un modelo de negocios en el que él fue parte fundamental. Me pregunto, cómo conociendo él la debilidad institucional de los pequeños municipios no estructuró el negocio con requisitos más exigentes en temas de viabilidad técnica de los acueductos y unas condiciones menos onerosas en términos de intereses y pagos. Como intermediario financiero no estaba pensando con interés público. Pero también vale preguntarse cómo fue esa gestión para meter a los municipios en el negocio ¿Quién le reunía los alcaldes en las capitales para echarles el cuento? ¿Por qué nadie ha investigado si es cierto que muchos alcaldes y concejales recibieron comisiones por autorizar la pignoración de los recursos del Sistema General de Participaciones? ¿Quién las habría pagado y contra qué recursos? ¿Qué ha pasado con los alcaldes y concejales de esos 117 municipios? ¿Se han iniciado procesos fiscales para establecer posibles detrimentos patrimoniales? Carrasquilla no cometió ninguna ilegalidad, pero el debate es, si es ético pasar del sector público al privado a participar en un modelo de financiamiento que usted como servidor público ayudó a estructurar. No hay forma de prever la intencionalidad del hecho, pero sí quedan muchas dudas sin resolver para alguien que preside una cartera como la de Hacienda, donde el valor más preciado es la confianza. La Corte Suprema de Justicia debe designar un Fiscal ad hoc que no dependa de estructurar. No hay forma de prever la intencionalidad del hecho, pero sí quedan muchas dudas sin resolver para alguien que preside una cartera como la de Hacienda, donde el valor más preciado es la confianza. La Corte Suprema de Justicia debe designar un Fiscal ad hoc que no dependa de Néstor Humberto Martínez, ahora que se conocen nuevos hechos en la investigación de la Superindustria y Comercio . Esa es la única forma para saber toda la verdad y establecer las responsabilidades a que haya lugar en ese caso emblemático de alta corrupción.</t>
-  </si>
-  <si>
-    <t>asentamientos informales en Barrancabermeja, en los que las agencias y regulaciones públicas contribuyen la producción diaria de marginalidad. Al seguir el agua por todo el país, también es posible identificar las diferentes experiencias del Estado. Por un lado, poner de relieve las respuestas de los gobiernos y poblaciones locales frente a las políticas de descentralización de los ochenta, que a su vez promovieron la participación del sector privado en la provisión de servicios de agua y alcantarillado. Estas respuestas incluyeron, por ejemplo, el surgimiento de nuevas fuerzas y movimientos sociales que resistieron la comercialización y la mercantilización del agua en contextos urbanos y rurales en distritos de riego. Por otro lado, se aprende sobre el agua al investigar las diferentes expectativas y procesos desencadenados por la Ley 142 de 1994. Al tiempo que promovió la participación del sector privado en la prestación de servicios públicos, lo que en ciudades como Santa Marta y Barranquilla significó la venta de las empresas públicas a compañías españolas, esta ley creó la Superintendencia de Servicios Públicos, que se convertiría en una fuente de recursos públicos para que distintas comunidades desafiaran el poder de estas mismas compañías. Finalmente, es a través de estas historias del agua que las experiencias de violencia estatal pueden hacerse visibles. Las experiencias de aquellos que fueron desplazados en el contexto de la guerra y volvieron para ver cómo plantaciones de palma africana se habían chupado las fuentes de agua fresca que antes irrigaban sus tierras. Las de los que pierden diariamente las fuentes de agua subterráneas, cuyos títulos de propiedad son otorgados silenciosamente a mineras e ingenios azucareros. Las de comunidades que tras el desplazamiento forzado llegaron a Buenaventura, a Cúcuta o Soledad para construir una casa, para las que los viajes del rebusque y el endeudamiento económico caracterizan la diariamente las fuentes de agua subterráneas, cuyos títulos de propiedad son otorgados silenciosamente a mineras e ingenios azucareros. Las de comunidades que tras el desplazamiento forzado llegaron a Buenaventura, a Cúcuta o Soledad para construir una casa, para las que los viajes del rebusque y el endeudamiento económico caracterizan la vida una parte de la cotidianidad. Muchos de ellos enfrentan el temor de ser procesados penalmente por fraude si se conectan informalmente al servicio de acueducto.</t>
-  </si>
-  <si>
-    <t>Las encuestas de Guarumo, publicada por EL TIEMPO, y la de Invamer en Semana son muy reveladoras de la paulatina consolidación de las tendencias de opinión frente a la elección presidencial. Aun cuando los punteros, Petro y Duque, quieren dar la sensación de que ya todo está decidido, no se puede presumir que así nos fuimos. En la política, como en el fútbol, las cosas pueden cambiar hasta que no se dé el pitazo final. Pregúntenle a Pékerman. Los electores tienden a votar no por el que más les gusta, sino por el que, en últimas, les parece el menos peor. Además, hay que reconocer que la gente se inclina a apostarle al caballo ganador. Las encuestas se vuelven una bola de nieve que produce un efecto catalítico mediante el cual quienes van arriba actúan como imanes a los que se les suman, a regañadientes incluso, muchos de los electores. La pregunta es si todavía hay espacio para que los demás candidatos, quienes, sumados, podrían ser una opción viable de centro, tienen la lucidez, la generosidad y la disposición para dar ese paso. Las encuestas a la que hacemos referencia son una fotografía, no un hecho cumplido. En ese contexto, y ante la incapacidad observada hasta ahora de los demás candidatos para construir una opción viable de centro, que es lo que verdaderamente quiere el país, la campaña se ha convertido no en una controversia de ideas, sino en la demonización del contrario. El miedo al castrochavismo, alimentado por la oposición contra Santos, y la paz basada en la quimera de que las Farc se iban a tomar el poder llevan a muchos moderados a refugiarse en la derecha. Del otro lado, el temor al autoritarismo y al revanchismo de la extrema derecha asusta a los liberales, a los demócratas,</t>
-  </si>
-  <si>
-    <t>mayor crecimiento económico y esa es la gran apuesta del Gobierno. Hoy Carrasquilla cree en la curva de Laffer, un economista que en los años 80 justificó los recortes tributarios del presidente Ronald Reagan, al afirmar que la baja de las tarifas impositivas siempre da lugar a un aumento del recaudo fiscal. El Nobel Paul Krugman ha rebatido teórica y empíricamente tan contraevidente afirmación, tildándola de economía vudú, más brujería que ciencia social. El argumento principal es que el costo del capital es solo una consideración en la decisión de invertir y que existen muchas más; así, las descargas tributarias de Trump se fueron a la autocompra de acciones de las sociedades en Estados Unidos o en nuestro caso pueden conducir a la fuga de capital. El déficit fiscal de 2018 fue 3,1 del PIB y el MFMP dice que se va a reducir 7 billones, a 2,4 del PIB este año, cuando el faltante generado por la Ley de Financiamiento fue precisamente 7 billones. Los 14 billones saldrán no se sabe de dónde, porque ya estamos a cuatro meses de terminar 2019, el gasto ha debido aumentar vía al Llano, migración venezolana, etc. y las ventas de activos públicos pueden demorar dos años o más. En 2020, más modestamente, el déficit lo reducen al 2,2 del PIB, a punta de crecimiento, pues, como hemos argumentado muchos, la venta de activos no puede aplicarse a reducir el déficit fiscal. Según Sergio Clavijo, el grueso del recorte fiscal va a reducir la formación de capital fijo público carreteras, acueductos, energía que del 2,2 del PIB en 2018 pasará al 1,4 en 2020, ese sí afectando negativamente el crecimiento. El costo fiscal de las deducciones y exenciones de 2018 alcanzó 8 del PIB. Con la piñata de este año será bastante mayor, la formación de capital fijo público carreteras, acueductos, energía que del 2,2 del PIB en 2018 pasará al 1,4 en 2020, ese sí afectando negativamente el crecimiento. El costo fiscal de las deducciones y exenciones de 2018 alcanzó 8 del PIB. Con la piñata de este año será bastante mayor, ya que la sola reducción de la tarifa a empresas vale 0,7 del PIB y faltará contar las gabelas ofrecidas a los sectores particulares de zonas francas, hoteles, restaurantes y un largo etcétera.</t>
-  </si>
-  <si>
-    <t>gran recesión. La tasa de interés de los bancos centrales perdió efectividad para regular el sistema económico. La decisión del Banco de la República, así no se reconozca en forma explícita, es una respuesta a la ineficacia de la política monetaria para reactivar la economía por la vía de la tasa de interés. La baja de la tasa de referencia no evitó que la economía se mantuviera en estancamiento por más de cuatro años. También constituye un reparo la incapacidad de la modalidad de cambio flexible para enfrentar las alteraciones ocasionadas por los productos básicos y la injerencia de los países desarrollados en las relaciones comerciales. En las épocas de alza de los productos básicos se presentan grandes revaluaciones que desplazan los bienes industriales y agrícolas, en tanto que en las épocas de caída se precipitan devaluaciones y déficits en cuenta corriente que frenan la producción y el empleo. Quiérase o no, se regresó a la época en que el tipo de cambio se fijaba dentro del marco de ajustes graduales. El nuevo modelo requiere políticas y prácticas muy distintas a las existentes. El Banco de la República deja de operar como piloto automático y se torna dependiente de los movimientos de divisas y las condiciones fiscales. Su principal función pasa a ser la coordinación con la política fiscal. Lo importante es que al ampliar los instrumentos de control, se incrementa la efectividad de la política macroeconómica para alcanzar el balance interno entre el ingreso nacional y el gasto y se fortalece la flexibilidad para alcanzar el balance de las cuentas externas. Por ahora convendría que el Banco de la República explique las razones que lo llevaron a abandonar la teoría de la autonomía para regular la tasa de interés y cuáles son los elementos de la nueva concepción. En</t>
-  </si>
-  <si>
-    <t>auge del verso libre, está en el olvido. Su adaptación redobla su riesgo al incluir rimas al final de cada verso. Ospina imita el esquema de Shakespeare: el primer verso rima con el tercero, el segundo con el cuarto, el quinto con el séptimo, el sexto con el octavo, el noveno con el decimoprimero, el décimo con el decimosegundo y los dos últimos el uno con el otro. Aquí está un ejemplo: 5 Pero tú de tus ojos haces tu vida escl ava , 6 gastándote, alimentas tu luz solo cont igo , 7 y haciendo la escasez donde todo abund aba , 8 cruel con tu dulce ser, te vuelves tu enem igo . Hasta aquí se han sumado tres decisiones de forma: Ospina vertió los versos yámbicos en alejandrinos; mantuvo la distribución de las estrofas; conservó el esquema de la rima que, por cierto, es propio de Shakespeare. Sin haber entrado en la composición misma, en la elección de palabras, sentidos y efectos que constituyen cualquier traducción, Ospina ya está asumiendo varios riesgos: la rima podría forzar o alterar el sentido; los alejandrinos podrían deteriorar la flexibilidad del pentámetro original; las estrofas podrían perder su orden lógico. Ese es el oficio del traductor: caminar fascinado en los límites del desastre. Para ver los efectos de esas elecciones, habría que desgajar la traducción de Ospina. Por fuerza, se trata de una creación, no sólo de una traslación literal, si eso es posible. Como el traductor es también un creador, y podría apostarse que tiene casi tanta altura como el autor, el texto original cambia pero, a un mismo tiempo, busca mantenerse: la lengua de llegada obliga a la transformación mientras que la obra original impone su aire particular. Quisiera comenzar por el primer cuarteto, que cité más atrás. El</t>
-  </si>
-  <si>
-    <t>día de las elecciones, colocando los jurados electorales de su gusto y cambiando el número votos en el formulario E14. Aquí, según las versiones e investigaciones de la Fundación, no solo se acomodarían jurados sino que se ofrecería el paquete completo. A esto los políticos le llaman el colchón electoral. En los siguientes días a los comicios, estas mismas personas les ofrecerían a los candidatos la compra de registradores adhoc y jurados encargados de vigilar el conteo, para asegurarles la curul mediante el cambiazo en los formularios E14 y E24. Los indicios mostrarían que el valor para reacomodar los votos necesarios para una curul en Cámara de Representantes asciende a mil doscientos millones de pesos, mientras que, para Senado, el costo asciende a los mil ochocientos millones de pesos. De ahí para arriba, si el candidato tiene una diferencia de más de 2 mil votos con el último candidato del partido que alcanzó la curul, el costo ascendería a los 2 mil y 3 mil millones de pesos. Las mismas fuentes indican que habría una red de abogados que tienen acceso a información privilegiada electoral y esperan a los candidatos en los sitios del conteo. En el caso de Bogotá, por ejemplo en Corferias. Estos le dicen al candidato que ellos le llevarán el proceso y le buscarán los votos que le falta y cobran miles de millones. En otros casos estos abogados previamente contratados por otro político distraen a candidatos para que envíen personas a mesas donde no se está cometiendo el fraude. Basados en la sentencia del Consejo de Estado también cabría la posibilidad de la alteración del software o se cambian los tarjetones ya que la seguridad de las bolsas con los votos es terriblemente deficiente. Obsérvese en el siguiente video como los votos se trasladan sin</t>
-  </si>
-  <si>
-    <t>para finalmente beneficiar a todos. Piketty reconoce que esta teoría respondió a un primer y ambicioso esfuerzo estadístico presentado en 1953 cuando arreciaba la guerra fría, pero también lo glosa por cuanto, a pesar de estar consciente del carácter especulativo de su formulación, Kuznets se cuidó de subrayar que estas predicciones tan optimistas también estaban orientadas a mantener a los países en desarrollo dentro de la órbita del mundo libre. Con la obra de Piketty, que los datos anuales de Oxfam Intermon evidencian, ha llegado la hora de colocar a la desigualdad en el centro de las preocupaciones de las ciencias sociales y económicas y de las políticas públicas, pues los extremos de desigualdad que se están registrando y Colombia es un caso emblemático al ser uno de los países más desiguales sobre la tierra no solamente atentan contra la equidad y la eficiencia económica sino contra la democracia. El 60 por ciento de la reducción de la desigualdad y la pobreza se explica por la inversión pública en esas áreas salud, educación y protección social, explica Rosa Cañete Alonso, coordinadora del Programa de Lucha contra la Desigualdad de Oxfam para Latinoamérica y el Caribe ET 27012019. Pero ese gasto público social se hace imposible en los volúmenes necesarios en ausencia de un sistema tributario progresivo que ponga a los excesivamente ricos a pagar su parte. En muchos países del mundo, esos intereses especiales han logrado no solo reducir los gravámenes que deberían pagar, sino eliminar el impuesto a las herencias. Muy pronto empezaremos a ver estudios que muestran que la riqueza en pleno siglo XXI no corresponde al saber sino al linaje, convirtiendo la meritocracia en una heredocracia. Mal augurio para la democracia y para los estímulos al crecimiento económico. Entre más se concentra el poder económico, más se</t>
-  </si>
-  <si>
-    <t>llevan a cabo evaluaciones metódicas y estructuradas en esta área. Al mismo tiempo, cada vez son más los inversionistas que exigen una buena rendición de cuentas por parte de las empresas, en donde los factores ESG representan un principio esencial en su toma de decisiones. El 91 de los inversionistas afirman que, en los últimos 12 meses, el desempeño no financiero ha sido pieza fundamental al momento de tomar sus decisiones de inversión, ya sea de manera frecuente o solo en ocasiones. Y en ese porcentaje, la cantidad de inversionistas que afirman evaluar dicho desempeño de manera frecuente incrementó a 43, en comparación con el 34 que se registró en 2018. Las cifras así lo evidencian, así que es hora de empezar a rediseñar el futuro de las empresas y de las finanzas. En Twitter:</t>
-  </si>
-  <si>
-    <t>del narcomenudeo, sumado a eso, se abonó un resentimiento discriminatorio contra los usuarios de psicoactivos que lesionó el respeto a la diferencia y la sana convivencia. Lo deseable es que el criterio de la Corte ayude a reconstruir y a reglamentar en justicia, los modos de expresión de los consumidores de drogas en el marco del recíproco respeto a las diferencias. En verdad, las inercias sociales han generado necesarias tolerancias entre abstemios y consumidores. Un viernes en Bogotá, se ven compartiendo, pacíficamente, el espacio y el esparcimiento en El Chorro de Quevedo, el Parque de los periodistas, el Parque de la Independencia, el Parque Nacional y el de la 60 que tiene historia y tradición al respecto. Los consumidores se dan mañas para evadir el prohibicionismo punitivo y la policía al acecho de una captura que pueda pagar el indulto, como en el juego: a que te cojo ratón, a que no gato glotón. Maquiavelo aconseja al mandatario: si permites eres débil, debes prohibir para inculcar la obediencia. Aquellos gobernantes para quienes las libertades se oponen a su hegemonía, reaccionan paranoicos ante las expresiones autónomas y las búsquedas de los individuos por fuera de los hábitos comunes, prohíben el matrimonio gay, la adopción de niños por parte de parejas homosexuales, prohíben a los maestros que hablen de política en sus clases... En el caso de las leyes anti drogas ilícitas, la prohibición obedece a una orden del imperio gringo y por más fallidas que sean las prácticas contra el cultivo, la producción, la comercialización y el consumo, se porfía en su aplicación porque en la práctica, la indolente guerra contra las drogas, a la vez que deja destrozos ambientales, guerrera y muerte, también deja ganancias por punta y punta: la aspersión aérea con glifosato es un negociado, es cuantiosa la</t>
-  </si>
-  <si>
-    <t>Este miércoles 27 de marzo, justo cuando se celebra el día mundial del teatro, yo cumplo 60 años de edad. Tal vez por la coincidencia de mi efemérides con el festejo teatral, me siento viviendo el desenlace de una farsa. A partir de hoy, según la ley colombiana, integró el grupo de adultos mayores de la Tercera edad, es decir, que empiezo a ser considerado viejo; aunque no tengo asomos de calvicie, aunque mis canas y mis arrugas sean moderadas, aunque el examen de la próstata avisó que con alimentación adecuada puedo controlar los impases de esa glándula, aunque mi estado físico es aceptable para el promedio, troto, nado, juego fútbol, bailo, todo en la justa proporción de mis fuerzas, nunca he sido deportista. El Estado colombiano y la muchachada callejera ya me están diciendo cucho, en cambio, muchos allegados todavía me dicen Albertico. Los contemporáneos ya me están enviando mensajes con frases de famosos que exaltan y honran la vejez. Pero, la verdad, yo no tengo aprecio exclusivo por una edad determinada, reconozco a viejos venerables pero también a los despreciables, reconozco a jóvenes admirables y también a los insoportables. Con una percepción no pragmática de la existencia, para mi gusto poético, la niñez sería la edad maravillosa, sin obligaciones sociales, plena en el asombro y el goce, con la conciencia totalmente dispuesta a la fantasía. Entre mis referentes de personajes ejemplares, para sus significaciones no fue determinante la edad en que consumaron su existencia: A Simón Bolívar le bastaron 47 años de vida para cumplir su obra, mientras Benjamín Franklin, inventor del Pararayos y político, llegó a viejo porfiando en la unidad de los Estados del norte. Los 34 años de Marylin Monroe fueron suficientes para inmortalizarse cómo ícono femenino, no la resistiríamos como una gringa anciana y</t>
-  </si>
-  <si>
-    <t>la indignación y la tristeza, Gerardo Castrillón Paz, coorganizador del evento, integrante del Consejo Nacional de Paz y Reconciliación, presidente de la Federación de Juntas de Acción Comunal del departamento del Cauca y quien ha sido activista, promotor de derechos humanos, impulsor de la acción contra minas antipersonal y quien actualmente dirige la oficina de asuntos étnicos en la gobernación del Cauca, reaccionó frente a un mensaje vía twitter de la senadora Paloma Valencia, caucana y destacada líder del partido de gobierno. Este fue el intercambio: Felicito al presidente por su decisión de levantar la mesa de negociación y de activar las órdenes de captura de los terroristas. Paloma Valencia L 19 de enero de 2019 Paisana, vengase a vivir al Cauca para que persiva al otro dia de su llegada, la realidad de una determinación de esa naturaleza. Personalmente no lo celebro, lo lamento, se está enrareciendo el camino para obtener una Paz estable y Duradera. No hay que declinar en el intento. Gerardo Castrillon Paz 19 de enero de 2019 Al leer este intercambio, me identifique con la necesidad de persistir en la búsqueda de paz expresada por Gerardo. Frente al dolor, la reacción debe ser persistir en la búsqueda de afianzar los acuerdos firmados con las FARC y construir el fin de la guerra con el ELN. Alegrarse por el cierre de una negociación de paz es felicitar el horror de la muerte que viene. Toda exacerbación de la confrontación ha significado muertes en las FFAA, las guerrillas, pero también en los líderes sociales, de JAC, políticos de nivel local, nacional, eso lo sabemos, ya lo hemos vivido. ¿Cuál es el sentido para que una senadora, dirigente importante del partido de gobierno, madre en proceso de crianza, aplauda el fortalecimiento de un futuro de violencia para las</t>
-  </si>
-  <si>
-    <t>el sello Impedimenta. Era un poema con aires de epopeya heroicocómica, El Levante. Lo que yo hubiera querido y había tratado de escribir durante los tres cuartos de mi vida que he entregado al nadaísmo, ese movimiento hermano del zen y la patafísica. Me dije que si algún día llegaba a conocer a ese monstruo que será nobel, habría alcanzado el tope de mis logros intelectuales. Sentí que era mi descubrimiento personal porque al comentarlo con mis amigos cercanos, no tenían noticia de esa obra totalizante. La sorpresa por estos días fue recibir invitación de la Tertulia Literaria de Gloria Luz Gutiérrez, que, al cumplir 20 años de actividades, nos concedía el privilegio de compartir con Mircea Cartarescu, por cortesía de la embajada rumana. Ni perezoso ni paticortico, abandoné mi amoblado paraíso de Villa de Leyva y me presenté en la Tertulia. Aunque el escritor es 16 años menor que yo, me sentía ante una luminaria interestelar y con el impulso de arrodillarme y besarle la mano que conduce su pluma. Me recorrió la misma emoción que cuando conocí a León de Greiff, a mis 20 años, y a García Márquez, a mis 22, cuando solo había publicado La hojarasca y El coronel... y llegó con su saco de cuadros rojos y verdes a la cafetería El Cisne a preguntarme si había visto a Marta Traba. Quedé deslumbrado con la conversación que sostuvo con Gonzalo Mallarino, hablando él en rumano, con una traductora impecable. Se detuvo a comentar que vivía a la vez en la realidad y en los sueños y que en su literatura, estos se entremezclaban. Que él llevaba una libreta con su diario personal y su diario de sueños, y de allí salía todo. Cuando llegó la hora de los comentarios le expresé que después de haber</t>
-  </si>
-  <si>
-    <t>insania? ¿De qué tamaño es la desconfianza social que hace que un juez no crea en el dictamen del psiquiatra y en el testimonio de un padre? ¿Es que ese juez no está en capacidad de ver la perturbación de un paciente con síntomas tan evidentes? Pero además: ¿qué añade el periodista aclarando que es hijo de un funcionario de la ONU o de un talabartero o de un maestro? ¿Es justo que lo saquen en los medios, escoltado por la Policía, antes de probarle nada? La sociedad sabe poquísimo de la enfermedad mental. No es capaz de comprender un cerebro que ha perdido su ruta, que hace asociaciones incoherentes, que percibe distinto y se extravía. Se burla de los locos y los aísla. Está comprobado que sólo un porcentaje mínimo de enfermos mentales hace daño a otros. La mayoría de los que ejercen alguna violencia, lo hacen sobre sí mismos. Se matan, porque no resisten sus tristes vidas: la depresión, el aislamiento, el insomnio, las voces, las alucinaciones. En artículo reciente en El País , Rosa Montero escribió: los pacientes aquejados por estas dolencias sufren un rechazo social tan feroz que el problema ya no es sólo que tengan que ocultar su condición, sino que lo más importante es evitar que se oculten enteros, es decir, que el ostracismo les encierre en sus casas y les fuerce a una vida de reclusión y aislamiento. Y nos cuenta de una fecha que quizá sea clave para empezar a combatir el estigma: el día del orgullo loco, que el 20 de mayo propondrá darle la vuelta a la tortilla y salir del armario para decir: Sí, tengo esquizofrenia, ¿y qué pasa?. Pero mientras logramos esa conquista, imposible no dolerse de que muchachos como este sean llevados, sin medir el daño, a estigma: el día del orgullo loco, que el 20 de mayo propondrá darle la vuelta a la tortilla y salir del armario para decir: Sí, tengo esquizofrenia, ¿y qué pasa?. Pero mientras logramos esa conquista, imposible no dolerse de que muchachos como este sean llevados, sin medir el daño, a esperar un dictamen en una cárcel repleta de ladrones y asesinos, esos sí perfectamente cuerdos.</t>
-  </si>
-  <si>
-    <t>Una de las grandes virtudes que tiene Cien años de soledad es la de servir como arquetipo de situaciones históricas que se repiten en América Latina porque los mecanismos y las trampas del poder siguen siendo las mismas. Derecha o izquierda. Da lo mismo. Después de que se produce la masacre de los trabajadores bananeros en huelga, que deja tres mil muertos, la versión oficial, mil veces repetida y machacada en todo el país por cuanto medio de divulgación encontró el gobierno a su alcance, terminó por imponerse: no hubo muertos, los trabajadores satisfechos habían vuelto con sus familias. Y mientras tanto, bajo el toque de queda los soldados derribaban puertas a culatazos, sacaban a los sospechosos de sus camas y se los llevaban a un viaje sin regreso. Era todavía la búsqueda y el exterminio de los malhechores, asesinos, incendiarios y revoltosos. Y para quienes preguntaban por sus familiares desaparecidos, la respuesta era: En Macondo no ha pasado nada, ni está pasando ni pasará nunca. Este es un pueblo feliz. A partir del mes de abril de 2018 ocurrió en Nicaragua una masacre ampliamente documentada por los organismos internacionales de derechos humanos, expulsados luego del país, de la que existen innumerables testimonios recogidos en videos y fotografías, y de la cual dieron cuenta los medios de prensa en el mundo. Más de 300 muertos, centenares de heridos, centenares en las cárceles, y más de cien mil exiliados, según la Acnur. Este mes de diciembre, durante un acto de presentación de credenciales, Daniel Ortega ha negado que semejante masacre haya sucedido. En Nicaragua no ha pasado nada, ni está pasando ni pasará nunca. Este es un pueblo feliz. Peor que eso, ocurrió lo contrario. Malhechores, asesinos, incendiarios y revoltosos salieron a las calles para derrocar al Gobierno democrático. Igual que</t>
-  </si>
-  <si>
-    <t>quien tiene su historia y sus motivos; sus motores de reflexión y de beligerancia; de vergüenza, corrupción o convicción. Como un Babel del siglo XXI, se cruzan las lenguas del engaño, el delirio y la sensatez; uno ya sabe a quién le interesa el país y a quién el poder. Hay una jauría de ofensas y mentiras, y mientras tanto, cruza por ahí la memoria encorvada por la muerte vestida de luto y misericordia; o altiva, manipulada por el odio y la venganza. Se enfrentan los resentimientos antagónicos, y mientras intentan vendarnos los ojos, el miedo levanta su andamio. Con distintos lenguajes, formatos y texturas, el Festival nos recuerda que el mundo no se limita a las cuatro paredes que nos rodean; que más allá de nuestras coordenadas, existen otro dolor, otra rabia y otra euforia; más temores, más amantes inconclusos, ecuaciones para el exilio y torrentes de incomprensión. Y por encima de cualquier color en cualquier idioma y con cualquier bandera, que todo aquello que surja y muera inmerso en la violencia, llega al mundo o sale de él, contaminado por el fracaso y el absurdo, bebiendo gota a gota sus propias y letales dosis de soledad. No es por coincidencia que la guerra y sus miserias caminan por muchas de las obras del Festival: es una expresión de la conciencia, que no se resigna a seguir viendo rostros de niños en medio de bombardeos; fragmentos humanos, silencios sordos por la explosión, huérfanos que empuñan armas y muñecas que se rompen antes de llegar al manicomio o al cementerio. Y vuelvo al principio: a la urgencia de reconectarnos con un país sin miedo. Nadie puede obligarnos a sucumbir en la perversión de los extremos; y todavía es tiempo de demostrar que somos más mucho más que un manojo de se rompen antes de llegar al manicomio o al cementerio. Y vuelvo al principio: a la urgencia de reconectarnos con un país sin miedo. Nadie puede obligarnos a sucumbir en la perversión de los extremos; y todavía es tiempo de demostrar que somos más mucho más que un manojo de resignación.</t>
-  </si>
-  <si>
-    <t>Los humanos hemos alterado la composición de la atmósfera, por una combinación de la quema de combustibles fósiles, la deforestación, la concentración de dióxido de carbono en el aire que ha aumentado en un 40 durante los últimos siglos, en tanto que la concentración de metano, un gas invernadero todavía más potente, se ha más que doblado. La ciencia ya tiene las pruebas de estos fenómenos que afectan la vida en el planeta, y sin embargo la educación parece estar aislada de estos hechos contundentes y probados científicamente. En este periodo de amplia movilización ciudadana por la defensa de la educación superior, cabe preguntarse cómo educar a la ciudadanía, en un contexto más amplio, para enfrentar el Antropoceno, la era geológica que ya afecta la salud pública, los ecosistemas en cada rincón del país y delata cambios sustantivos en el comportamiento de especies en cada hemisferio del planeta. En Colombia las respuestas de la academia no se han hecho esperar. Ya existen publicaciones y liderazgos desde las redes temáticas y desde algunos medios de comunicación. La 1a Semana para la Acción Climática se desarrolló en Bogotá justo cuando los estudiantes estaban clamando mejor educación superior en las calles. La acción climática constituye un esfuerzo mancomunado de varias universidades públicas y privadas, de la Agencia Francesa de Desarrollo AFD, la Fundación Alma y la fundación Klimaforum Latinoamérica Network, liderada por Manuel GuzmánHennessey. Esta iniciativa busca también el apoyo del Ministerio de Ambiente para construir a mediano plazo en Colombia, el Diálogo de Talanoa, plataforma facilitadora que trae su nombre internacional desde las Islas Fidji en el Pacífico Sur. El Diálogo busca robustecer las voces de Actores No Estatales alrededor del mundo y particularmente entre el estudiantado, abriéndolo a la responsabilidad climática. Los jóvenes, demostrando una fantástica capacidad de movilización frente al</t>
-  </si>
-  <si>
-    <t>campos donde Dios prodigaba sus milagros se convirtieron en bodegas del mercado, el tiempo se convirtió en un molino industrial, ya no puedes dar un paso sin que algún dueño te cobre por algo, y cada vez más hay un solo dueño de todas las cosas, cuyo poder crece a medida que expulsa y expropia, a medida que saquea y arrasa, a medida que construye y vende, a medida que produce con la misma eficiencia la medicina y la enfermedad. La humanidad tendrá que sacudirse de todo eso antes de que la naturaleza se sacuda de la humanidad como de una plaga mortal. Y para ello bastará comprender que somos nosotros el fundamento de lo que nos oprime, el soporte de lo que nos destruye, el alimento de lo que nos tiraniza. Existe la industria, pero nosotros somos sus consumidores. Existe la técnica, pero nosotros somos su campo de experimentación. Existen los Estados, pero nosotros somos sus tributarios. Existe la corrupta política contemporánea, pero nosotros somos sus electores. Basta saber que la salud depende más del agua pura, de la buena alimentación, de un ambiente sano y de un buen medio afectivo, de un trabajo satisfactorio y de una actividad placentera que de toda la industria farmacéutica, de toda la parafernalia quirúrgica y de todo el leviatán empresarial de los seguros médicos privados, para saber lo que hay que hacer. Basta saber que los alimentos procesados industrialmente son una de las principales fuentes de enfermedad para entender el círculo vicioso de la medicina contemporánea, atrapada en la tela de araña de las farmacéuticas y de los hospitales, donde los médicos son las primeras víctimas del frenesí de las urgencias, del dolor y de la muerte consideradas como culpas profesionales y negligencias. Basta saber que cuanto más representativa sea nuestra democracia,</t>
-  </si>
-  <si>
-    <t>alimentos. Pero, afortunadamente, hay gente buena que quiere ayudar y es a ellos a quienes les estoy recomendando. Ábaco es la Asociación de Bancos de Alimentos de Colombia, miembros de The Global FoodBanking Network. Los bancos contribuyen a reducir el hambre y la desnutrición en el mundo al recibir alimentos excedentarios de comercio, empresas o particulares para su debida distribución entre los más necesitados. Es una organización sin ánimo de lucro que representa a los bancos de alimentos eclesiásticos y civiles que promueve la reducción de pérdidas y desperdicio de alimentos en pro de la seguridad alimentaria y nutricional de la población en situación de vulnerabilidad. Entre el 30 y el 50 de los alimentos producidos en el planeta no son consumidos por seres humanos. En el país, 11 de cada 100 niños entre los 5 y los 12 años tienen desnutrición crónica. ¿No les parece, Iván y Gustavo, que este es el problema número 1 que tienen que enfrentar?</t>
-  </si>
-  <si>
-    <t>de baja altura; la desertificación de las zonas tórridas haría huir a millones de personas hacia las templadas creando en ellas graves conflictos sociales. Hay, sin embargo, razones para un moderado optimismo. Los combustibles fósiles, que son los más contaminantes, deberán convertirse, a la vuelta de un par de décadas, en una fracción minoritaria de la canasta energética del mundo. Los avances en la tecnología para conservar la energía permitirán el rápido auge de las que provienen del viento y el sol. La de origen hídrico, en la que Colombia tiene un potencial enorme, no desaparecerá como consecuencia de sus bajos costos de producción y distribución, de su flexibilidad para guardarla basta retenerla en los embalses, y de que los impactos ambientales que produce son positivos a mediano plazo. El reto, por lo tanto, no es técnico; es político: la adopción de marcos regulatorios que, para ser eficaces, deben adoptarse a escala planetaria. En aquella ocasión hablé también de la crisis de los misiles de 1962 ocurrida en medio de la guerra fría entre Estados Unidos y la Unión Soviética. Su detonante consistió en la instalación, con el consentimiento de Fidel Castro, de misiles nucleares en territorio cubano. Gracias a las habilidades de los diplomáticos de las grandes potencias, la confrontación, que pudo llevar al mundo a una tragedia nuclear, fue resuelta de manera eficaz y perdurable. No obstante, se produjo un efecto colateral negativo: la generalizada creencia de que bastaba la existencia de un cierto equilibrio ofensivo entre los dos países que entonces gozaban de poder nuclear, para conjurar el riesgo de una hecatombe. Son otras las circunstancias actuales. El número de países dotados de esa tecnología ha venido aumentando. Algunos de ellos tienen una larga tradición de enemistad, tales como Irán e Israel, o India y Pakistán; aún</t>
-  </si>
-  <si>
-    <t>vegetarianos y sin duda muy interesados en la sostenibilidad. Cada plato es inspirado en un jardín que, como ellos afirman, es la entrada a una cultura gastronómica ancestral. Sus platos recomendados son el bowl Zen, inspirado en la cocina asiática, y el Islámico, que tiene todos los buenos ingredientes de la cocina árabe. Los letreros de nos veremos pronto parecen empezar a cobrar sentido, y sin duda las puertas de los restaurantes volverán a abrirse con el propósito no solo de generar empleo y aportar a la economía, sino de demostrar su importancia para la conservación de las tradiciones culturales y brindarnos una nueva experiencia gastronómica adaptada a la nueva normalidad, por el momento la reinvención es la única opción.</t>
-  </si>
-  <si>
-    <t>En los primeros tiempos de Roma, se veía como un deber del Estado asegurar que la población fuese debidamente abastecida de grano. Según cuentan los historiadores, en época de Augusto se llegó a repartir trigo el equivalente para hacer un pan de un kilo diario a 320.000 familias, beneficiando a más de 600.000 personas. La ciudad necesitaba en total unas 200.000 toneladas anuales, trigo que procedía de Sicilia, de Cerdeña, del norte de África y sobre todo de Egipto. Denominada la annona, este auxilio era indispensable para la subsistencia diaria y para mantener el orden social. Sin la annona y sin el circo panem et circenses, seguramente la historia del Imperio hubiera sido diferente. El ingreso básico universal IBU siempre ha tenido sus defensores y sus detractores. Los defensores del IBU argumentan que esta medida es una respuesta adecuada a los problemas crecientes de desigualdad y escasez de empleo, y a la disminución de la participación de las rentas salariales en el PIB. También consideran que tendría una gestión sencilla donde se eliminarían los trámites administrativos, disminuyendo los costos por lo que desaparecerían otro tipo de prestaciones, evitando, de paso, la burocracia y los fraudes en los subsidios y apoyos se estima que del 20 al 30 de los afiliados al Sisbén no deberían estarlo. Una ventaja adicional del IBU sería la paulatina erradicación de la pobreza, dado que, debido a este colchón, al tener cubiertas sus necesidades básicas, el bienestar de la población aumentaría. En cuanto a los contras, la existencia del IBU, el tener una renta sin necesidad de hacer nada, podría incentivar un menor esfuerzo por trabajar, cayendo en la trampa de la pobreza. Algunos también podrían argumentar que se configura lo que en economía pública se denomina un free rider , aquel individuo que tiene interés</t>
-  </si>
-  <si>
-    <t>mismos poderes que obligan a los pobres a huir son los que cierran las puertas y alzan los muros. Ahora nos toca repensarlo todo, porque si la aldea no cabe en el universo, el universo no cabe en la aldea. Ahora resulta que las multinacionales no quieren la selva amazónica porque lo que necesitan es un sembrado de soya, las mineras no respetan los páramos porque lo que necesitan es el oro, las petroleras destruyen el agua porque lo que necesitan es petróleo y los políticos no miran a los seres humanos porque necesitan solo los votos. Del mismo modo, ya hay farmacéuticas que no quieren la salud porque necesitan a sus enfermos, y medios que no quieren la verdad porque lo que se vende es la adrenalina. En nuestro continente mucho tiempo vivimos en el desajuste de los relojes; íbamos en vagón de tercera hacia el desarrollo, hasta que el desarrollo se convirtió en esto: petróleo recalentando la atmósfera, sierras eléctricas talando las selvas, glaciares derritiéndose, ciudades asfixiándose, mares creciendo, plásticos inundando la tierra y el mar y hasta el torrente circulatorio. Habría sido útil cobrar conciencia a tiempo de que nuestro mundo no cabía en esas cartillas ni casaba en esos guantes. Algunos pueblos nativos comprendieron primero que la idea de que Dios tiene forma humana despoja al cielo de jaguares y condena a muerte a las iguanas y a los pájaros. Hay que saber que un jaguar no es apenas un animal sino la salud de un ecosistema; que el ser humano, para sobrevivir, tiene que representar la salud del mundo, y saber esas cosas es la democracia. Qué lejano y decadente se ve ya Ernest Hemingway con su sombrerito y su traje caqui demoliendo elefantes. Ahora los jóvenes necesitan todo su amor por el vértigo y</t>
+    <t>3734_0</t>
+  </si>
+  <si>
+    <t>1863_1</t>
+  </si>
+  <si>
+    <t>11824_7</t>
+  </si>
+  <si>
+    <t>6626_2</t>
+  </si>
+  <si>
+    <t>5576_0</t>
+  </si>
+  <si>
+    <t>5649_0</t>
+  </si>
+  <si>
+    <t>13042_4</t>
+  </si>
+  <si>
+    <t>9855_0</t>
+  </si>
+  <si>
+    <t>4553_2</t>
+  </si>
+  <si>
+    <t>2865_1</t>
+  </si>
+  <si>
+    <t>8626_0</t>
+  </si>
+  <si>
+    <t>1493_6</t>
+  </si>
+  <si>
+    <t>8631_1</t>
+  </si>
+  <si>
+    <t>9756_4</t>
+  </si>
+  <si>
+    <t>8003_2</t>
+  </si>
+  <si>
+    <t>7138_3</t>
+  </si>
+  <si>
+    <t>10410_2</t>
+  </si>
+  <si>
+    <t>3038_1</t>
+  </si>
+  <si>
+    <t>8510_1</t>
+  </si>
+  <si>
+    <t>1074_3</t>
+  </si>
+  <si>
+    <t>5041_1</t>
+  </si>
+  <si>
+    <t>2200_1</t>
+  </si>
+  <si>
+    <t>8623_1</t>
+  </si>
+  <si>
+    <t>9916_3</t>
+  </si>
+  <si>
+    <t>4009_2</t>
+  </si>
+  <si>
+    <t>8268_0</t>
+  </si>
+  <si>
+    <t>2249_2</t>
+  </si>
+  <si>
+    <t>12610_0</t>
+  </si>
+  <si>
+    <t>11074_5</t>
+  </si>
+  <si>
+    <t>390_2</t>
+  </si>
+  <si>
+    <t>6714_0</t>
+  </si>
+  <si>
+    <t>6183_1</t>
+  </si>
+  <si>
+    <t>5941_0</t>
+  </si>
+  <si>
+    <t>11226_1</t>
+  </si>
+  <si>
+    <t>1899_0</t>
+  </si>
+  <si>
+    <t>80_1</t>
+  </si>
+  <si>
+    <t>3294_1</t>
+  </si>
+  <si>
+    <t>2626_1</t>
+  </si>
+  <si>
+    <t>9824_4</t>
+  </si>
+  <si>
+    <t>2431_2</t>
+  </si>
+  <si>
+    <t>10396_1</t>
+  </si>
+  <si>
+    <t>8521_6</t>
+  </si>
+  <si>
+    <t>12435_5</t>
+  </si>
+  <si>
+    <t>2719_0</t>
+  </si>
+  <si>
+    <t>7657_2</t>
+  </si>
+  <si>
+    <t>5301_3</t>
+  </si>
+  <si>
+    <t>3956_1</t>
+  </si>
+  <si>
+    <t>13118_6</t>
+  </si>
+  <si>
+    <t>12521_0</t>
+  </si>
+  <si>
+    <t>8809_2</t>
+  </si>
+  <si>
+    <t>3889_3</t>
+  </si>
+  <si>
+    <t>69_1</t>
+  </si>
+  <si>
+    <t>sostenible de millones de compatriotas. Después de décadas de economías cocaleras en estos territorios, 123.000 familias le han dicho sí a la sustitución voluntaria, en un compromiso por dejar atrás esa historia, su historia. Según la entidad validadora del proceso de sustitución, la Oficina de las Naciones Unidas contra la Droga y el Delito UNODC, en su informe número 9, ya 56.655 familias han suscrito compromisos de sustitución, luego de informar que tenían 45.641 hectáreas de cultivos de coca; de estas, 31.315 familias han recibido al menos un primer desembolso en 1.925 veredas, de 38 municipios, en 13 departamentos. En estos territorios, el Sistema Integrado de Monitoreo de Cultivos Ilícitos de Naciones Unidas Simci reportó en su informe de 2017 la existencia de 77.717 hectáreas de coca. Las áreas no declaradas, como está previsto en el acuerdo de paz, son objeto de erradicación por parte de la Fuerza Pública. En</t>
+  </si>
+  <si>
+    <t>políticas públicas, presentamos directamente al Congreso siete proposiciones de protección animal para que sean incluidas en el PND. Son muchos los problemas que hay que atender por la orfandad histórica que han sufrido los animales en Colombia, pero materializar estas acciones sería un gran comienzo. Crear la comisión nacional intersectorial de protección y bienestar animal. Un cuerpo especializado, liderado por MinAmbiente, que defina la política pública nacional y oriente y vigile su implementación. Por ahora, nada de institutos. Implementar un programa de esterilización de gatos y perros en todos los municipios. Atender el 10 por ciento anual de la población de animales con y sin hogar durante los cuatro años del gobierno. Proteger previniendo, sin matanzas ni hacinamientos. Sustituir los vehículos de tracción animal halados por equinos, burros, mulas y asnos en todos los municipios del país; no solo en los de categoría especial y de primera categoría. Jubilar a</t>
+  </si>
+  <si>
+    <t>el mundo y ya en Colombia existe la regulación para ello Res 030 CREG 2018. Hay más de 200 proyectos registrados ante la UPME. Su costo final a usuario por kilovatio hora, sin incluir el sistema de baterías, puede estar entre 250 y 300 pesos por kilovatio puede ser menor si se tienen en cuenta las exenciones tributarias que existen en el actual régimen tributario. Al comparar estos costos con los de estar conectado a la red, la provocación de usuarios con techos grandes y altos consumos de energía establecimientos comerciales, sería la de montar sus sistemas solares y aislarse de la red durante unas horas en el día. En esos momentos, la red sería pagada por los usuarios que quedan conectados, es decir los residenciales con menores consumos y menos área de techo. Entonces, la primera caravana que se aislará de la red no serán los usuarios de menos menos área de techo. Entonces, la primera caravana que se aislará de la red no serán los usuarios de menos recursos, sino los de más, dejando a los otros con mayores costos. Este escenario es tenido en cuenta por la regulación y por dicha razón hay claros límites a este tipo de instalaciones. Desahuciar la red en euforia hacia el sol, contrario de lo que se expresa en el debate político, es algo que perjudica a los usuarios de menos ingresos.</t>
+  </si>
+  <si>
+    <t>del proyecto industrial tendrá que ser examinada a fondo, porque aunque lográramos un 100 de energía limpia, ilimitada y gratuita, igual podría hacer colapsar el mundo un modelo de saqueo irrespetuoso y depredador, que ve en la naturaleza sólo una fría bodega de recursos, en la humanidad un mero rebaño de operadores y consumidores, y en el mundo apenas un escenario desangelado para los designios de una acumulación ciega y sórdida. La idea del desarrollo concebido como mera multiplicación de mercancías y aumento de la rentabilidad parece una variación ya sin poesía del viejo desvelo de los alquimistas por convertir todas las cosas en oro, y contiene en su almendra una alarmante negación de la vida como diversidad, como contención, como profusión y como equilibrio. Porque de todas las cosas que caracterizan al mundo ninguna es más evidente, y a la vez más alarmante para los designios del gran capital,</t>
+  </si>
+  <si>
+    <t>claves de infraestructura. 2 Evitar que nos convirtamos en un importador de petróleo y gas, para lo cual, además de las rondas abiertas por la ANH, resulta indispensable explotar nuestra riqueza de hidrocarburos no convencionales aplicando todas las precauciones ambientales, como bien lo sabe el Gobierno. 3 Identificar sectores exportadores emergentes en los sectores agropecuario, industrial y de servicios incluida la economía naranja, y apoyarlos removiendo cuellos de botella y con regulaciones apropiadas, como se hizo en el gobierno Uribe con los llamados sectores de talla mundial. Las vocaciones regionales convenidas en el Plan de Desarrollo pueden ser muy útiles al respecto. 4 Consolidar la paz cumpliendo los acuerdos no solo con los reinsertados, como se está haciendo, sino también con la estrategia de desarrollo rural y la reforma política convenidas y garantizando la seguridad en los territorios donde antes reinaban las Farc, pero sin falsos positivos ni nada que</t>
+  </si>
+  <si>
+    <t>tuvieran evaluaciones de impacto ambiental, individuales y agregadas, y cumplieran con políticas, acuerdos, normas y el principio de precaución ¿Qué hueco negro en la ley permite que el alcalde de Bogotá cree por decreto Lagos de Torca, una ciudad de 500.000 habitantes en medio de la Sabana? El impacto ambiental acumulado de los proyectos del alcalde en la Sabana y en el país es enorme ¿Quién vigila posibles inexactitudes, omisiones o insuficiencias de los macroproyectos? ¿Quién suma los impactos? ¿Quién vela por el cumplimiento del Acuerdo de París, los Objetivos de Desarrollo Sostenible, la Nueva Agenda Urbana, la Ley 9993, etc., etc.? ¿Por qué la Comisión de Ordenamiento Territorial Nacional no hace nada? ¿Qué hacen la ANLA, la CAR y la Secretaría de Ambiente del Distrito? ¿Qué piensan los concejales que apoyan al alcalde Peñalosa? ¿Qué hacen la Personería y la Procuraduría? En una encuesta reciente el alcalde de Bogotá</t>
+  </si>
+  <si>
+    <t>de la paz completa, poner más muertos, volver a la dinámica de la guerra en una parte importante del territorio colombiano y terminar la gestión de Santos con un fracaso. A esto se le puede agregar darle votos a la extrema derecha y afectar la implementación de lo acordado con las Farc. El presidente ya no tiene popularidad que perder y ese no puede ser su baremo, pero sí le queda oxígeno para la audacia, tanta como la imaginación lo permita. Otras guerras y otros procesos de paz han enseñado que la salida está en ir a contracorriente. Eso implica dejar de ver los actos hacia los elenos como una debilidad, leer al ELN real que existe y NO el que dicen los opinadores, entender que la negociación es de naturaleza política y no militar, echar mano de los amigos de la paz y mirar menos a los enemigos, consultar</t>
+  </si>
+  <si>
+    <t>y oscuras como la noche, hipnotizado con las aguas profundas del lago de Zúrich o las del río turbulento que lo invita a hundirse en él. El alma humana hubiera estado mejor sin ser humana, porque el alma envejece bajo el sol, se derrite, se hunde y combustiona en millones de preguntas que se esparcen sobre el pasado, el presente y el futuro. Alegría : escrito a retazos entre viajes, hoteles, homenajes, conversatorios. El éxito sin precedentes de Ordesa lo lanza a una nueva realidad que jamás había imaginado, como un cohete que de repente se encuentra en un planeta extraño. Nos envuelve como un torbellino. Nos arrastra en su huracán emocional. Vivimos y sentimos sus picos de euforia y desesperación, sus ganas de sumirse en el sueño profundo, de no querer despertar jamás, y la sensación irreal de haber amanecido al milagro de un nuevo día lleno de sol.</t>
+  </si>
+  <si>
+    <t>de Bomba camará . En el mundo de la literatura y la música popular, hay tres títulos bibliográficos que se constituyen en la piedra de toque de esta importante vertiente literaria: Son de máquina de Óscar Collazos, cuyo título es tomado de una canción de Rolando Laserie, y cuyos relatos transcurren en el barrio La Pilota de Buenaventura. El cuento Historia de cantantes del escritor cartagenero Roberto Burgos Cantos y, por supuesto, Bomba camará de Valverde. Allí comienza nuestra literatura escrita en clave musical. Luego vendrá Aire de tango 1973 de Manuel Mejía Vallejo, quien hace un homenaje al tango que se escuchaba en el desaparecido barrio Guayaquil de Medellín. Que viva la música 1977 de Andrés Caicedo, que es un homenaje literario a los Rolling Stones y Richie y Bobby Cruz, y Conciertos del desconcierto 1981 de Magil, donde se narra el primer concierto de rock al aire libre</t>
+  </si>
+  <si>
+    <t>mi calle del alma. Aun, los ruidos que alegran el cielo nocturno de mamá no alcanzan a percibirse. No ha llegado su hora. Ni las estrellas son todavía ese enjambre titilante que de niño me empecinaba en contar, pero que al tiempo se me escurrían por entre los dedos de mis manos cuando creía tenerlas ordenadas. Las estrellas son solo para mirarlas, me repetía, para bautizarlas y contarlas por sus nombres de mujeres mitológicas y dejarlas, hasta el fin de los tiempos, que se consuman en las cavernas sin fondo del cosmos. Con sus ojos de mar, empieza a escudriñar mamá el inmenso mapa de Cocuyos flotantes que caen sobre los patios de mi pueblo repleto de luz, de una luz que no se oxida ni se resiente por el salitre inmemorial que llevan de todos los recovecos del mundo los vientos cantarines del Caribe. Cuando acabe su noche, Jesusita</t>
+  </si>
+  <si>
+    <t>Estrellas, encarnación de aspiraciones amorfas que toma elementos de una y otra tendencia del espectro político, y que se opone al Euro y a la Unión Europea, se reunió en un suburbio de París con Christophe Chalenon y otros líderes de los Chalecos Amarillos. En el encuentro les expresó su apoyo en la lucha contra el gobierno francés, sin reparar en el recurso a la violencia que lleva ya muchas semanas de reedición en la capital y otras ciudades de Francia. Con esa elevada autoestima propia de caciques regionales venidos a más, Di Maio afirmó que el viento de cambio ha cruzado los Alpes, como si sus amigos de la protesta francesa fuesen los continuadores de su movimiento italiano, que desde 2009 proclama el ejercicio del poder ciudadano, en la defensa del ambiente, los derechos sociales y la democracia directa. Sobre las bases anteriores, afirmó que con los Chalecos Amarillos</t>
+  </si>
+  <si>
+    <t>En lugar de llevarme solo a Isis I en ese maravilloso viaje a la inmortalidad, me llevaré también a Keket. Las dos me honrarán y yo me sentiré amado. Pero volvamos a nuestros tiempos. Las sociedades, queramos o no, se están moviendo en mundos religiosos que tienen ciertas exigencias para ganarse el derecho a entrar en el paraíso y adquirir el aura de inmortales. Sin embargo, a la gente le cuesta trabajo desprenderse de riquezas, logros y nombre: Doctor Vladimiro, gracias por elegir nuestro banco. Estamos a su entera disposición para lo que necesite. Es decir que para don Vladimiro el excelso lugar del que hablan las religiones, una vez pasada la prueba de fuego del juicio final, es un placentero territorio donde a todo lo que diga le dicen que sí. Hay otras religiones en las cuales, una vez pasados los requisitos del caso, el futuro occiso tendrá a</t>
+  </si>
+  <si>
+    <t>entre otros animales. Los miasmas lunares resultaron inofensivos. Los espejos, retroreflectores para ser exactos, dejados por las misiones de Apolo 11, 14 y 15 han comprobado la tesis científica que dio origen a la fantasía de Calvino. Esos reflejos de luz que van y vienen nos dicen que la Luna se aleja de la tierra 3,8 centímetros cada año. Tanto que cada vez hay que añadirle un peldaño más a la escalera del señor Qfwfq. Las excursiones de Armstrong y Aldrin fueron distintas a las cotidianas de los personajes de . La primera estadía de los astronautas en la Luna duró 21 horas y 36 minutos, y luego de las caminatas dejó un botín de 21,5 kilos de rocas. Los calvinistas iban por un producto distinto a esa Luna al alcance de la mano: Íbamos a recoger leche con una gran cuchara y un cubo. La leche lunar era muy</t>
+  </si>
+  <si>
+    <t>saca un libro y nos ponemos a charlar de literatura, el secreto mejor guardado de nuestro idilio. En la carátula, Superman sostiene una bandera con la hoz y el martillo de la inexistente Unión Soviética. En el pecho, en vez de la S, otra hoz y otro martillo en escarlata sobre el uniforme azul. La capa, roja como el perverso estandarte. ¿Qué es eso?, me intereso. Una novela que en Colombia llamarían experimental, pero que en realidad es una novelaza o novelota posmoderna, dice Isabel. ¿Supernovela?. Muestra el título: Nuevos juguetes de la Guerra Fría , de Juan Manuel Robles, en Seix Barral Biblioteca Breve, 2015. Ah, yo estuve con Robles en el Hay Festival Medellín, me acuerdo, no sin orgullo. Isabel achina los ojitos: Entonces ya sabes que es una novela con una trama de thriller que te absorbe de principio a fin. Son dos historias a la vez,</t>
+  </si>
+  <si>
+    <t>potencia irascible que truena en las páginas de la Torá? El principito Gabriel Gilinski puede admirar a líderes de derecha, sí, ¿pero tienen que ser los peores, sujetos como Trump, Johnson y Bolsonaro? Puede soñar con corporaciones de medios que facturan miles de millones de dólares al año, ¿pero tienen que ser Fox, la de The Sun y el extinto News of the World , los pasquines más infames de la historia del amarillismo? Uno se hace otras preguntas: si Gilinski quería una revista de ultraderecha, ¿para qué comprar una revista de corte liberal? ¿No era más barato hacer una nueva con María Isabel Rueda, Alejandra Azcárate, José Obdulio, Gurisatti y Yamhure? Y con Plinio Apuleyo Mendoza, si la quería con mucho estilo. ¿La compró solo para quebrarla? ¡De verdad piensa que los que la leíamos por Coronell, Samper Ospina, León Valencia y Antonio Caballero vamos a madrugar ahora a</t>
+  </si>
+  <si>
+    <t>es solo un mecanismo de comunicación, sino también una manera de dejar plasmado en el papel ese conjunto de elementos axiológicos que definen culturalmente a un grupo social en particular. Las normas gramaticales y el lenguaje son el puente que contribuyen a plasmar los conocimientos, los hechos o las perspectivas que alguien tiene de la vida o del mundo. Pero también nos habla de ese diálogo que el escritor, sin importar que hagamos referencia a una columna de opinión, un artículo científico o una extensa obra literaria, ha mantenido, a lo largo de su vida, con otros escritores. Es decir, estos nos dejan ver sus niveles superficiales o profundos de lectura, pero, sobre todo, la riqueza escritural representada en el lenguaje y en eso que el autor de A sangre fría llamó la manera sobre la materia. Las dos réplicas del gerente de Telecaribe publicadas en este mismo espacio a</t>
+  </si>
+  <si>
+    <t>uso de prendas muy ajustadas de minifalda, short o escote muy pronunciado; sugiere llevar ropa discreta pues no hay nada más incómodo que distraer la atención de tus compañeros de clase y profesores. Revive la UPB las pastorales de monseñor Builes, añosas catilinarias dirigidas a la Medellín camandulera, hoy de camándula y Popeye , empeñada en asfixiar la metrópoli que busca mejores aires. Denostaba Builes todavía en 1963 la falda a medio muslo y los descotes vergonzosos. Ante semejante impúdico y escandaloso espectáculo, todos sienten fastidio y vergüenza, tentaciones, pasiones, pensamientos y deseos deshonestos. Condenó el prelado la nueva ola de carne inmunda y horrenda corrupción; la rebelión de la mujer moderna contra lo que Dios dispuso para salvarle el pudor cubriendo sus vergüenzas. Tal como lo hizo con Eva en el paraíso. Respira odio esta normativa sobre el vestir; y sugiere bíblico mandato de venganza contra la mujer, víbora</t>
+  </si>
+  <si>
+    <t>unos cuántos kilómetros, debutaba un símbolo de la tranquilidad, del profesionalismo y de la sabiduría popular y racial, un pequeñogrande hombre que persuade, embelesa y extasía a cuanto hincha se le atraviesa, por su carisma y calidad. Ahh, también por sus excéntricos bailes que invaden el espíritu de quienes tienen dificultad para mover los hombros. Es una mina de oro, el Yerry que nos dío Guachené, en el abatido Cauca. También en tierras cafeteras se disputaban en el mismo fin de semana en el que se despedazaban los futuros conductores del país, los mejores gladiadores de la bicicleta, unos sobre los alargados y planos asfaltos como Fernando Gaviria, al mejor estilo de Céfiro, dios del viento griego, y otros, conquistando las majestuosas montañas para alcanzar el aroma y un sorbo de café, premio sin igual cuando se cruza el portal que hace romper las cuerdas bucales de los mejores narradores</t>
+  </si>
+  <si>
+    <t>una partícula que proviene de un bus es miles de veces mayor a la probabilidad de respirar alguna proveniente de una chimenea industrial. No encuentro argumentos técnicos, políticos ni económicos para justificar que Bogotá se margine de la documentada e irreversible tendencia mundial hacia la movilidad eléctrica. Siendo la nueva licitación de Transmilenio el instrumento más significativo en tal dirección, la carga de la prueba para abstenerse recae en la Administración. Lo que han dicho hasta ahora es cuestionable y no convence. El debate exige una explicación de por qué no tenemos derecho a una ciudad saludable, limpia y moderna.</t>
+  </si>
+  <si>
+    <t>y arropados todo el día, aunque en pueblos cundiboyacenses de tierra caliente la atención al cliente también es mala; si es porque a nadie le importa y no sienten orgullo propio; o porque no les ha explicado que en la buena atención está la receta del éxito y no solo en el queso del relleno de las arepas. Yo, muda, pues más allá de los 5 o 10 minutos de gracia chauvinista que sé que hay que darles a los paisas para que en cualquier tema de conversación puedan destacar algo de su región y criticar lo demás, con especial gusto si es de Bogotá o sus alrededores, debo decir que mi amigo tiene razón. Esa verdad de a puño se confirmaría más adelante. Llegando a Guatavita pinché. Cambiamos el neumático, llegamos al pueblo a pedir datos de un taller, un lugar donde vendieran uno de repuesto. La respuesta fue</t>
+  </si>
+  <si>
+    <t>puras, ecuaciones diofánticas y teoría de números; una transformada lleva su nombre, la transformada de Dyson. Su trabajo posterior se produjo en el campo de la física teórica, la electrodinámica cuántica y en la aplicada. Durante la Segunda Guerra Mundial trabajó en el Ministerio de Defensa del Reino Unido. Como es casi imposible la exploración tripulada fuera del sistema solar empleando combustibles químicos, planteó el uso de la energía nuclear, explosiones controladas fuera de la nave que produzcan ondas de choque en forma tal que la velocidad alcance un 10 o 20 de la velocidad de la luz. Hoy, la velocidad máxima alcanzada es de 20 kms utilizando la gravedad de los planetas para acelerar las naves, es decir, 0,00007 veces la velocidad de la luz. A pesar de ser un entusiasta de la energía nuclear para fines espaciales, fue un opositor de las armas nucleares. The Economist publicó dos un entusiasta de la energía nuclear para fines espaciales, fue un opositor de las armas nucleares. The Economist publicó dos obituarios de estos científicos.</t>
+  </si>
+  <si>
+    <t>española con el beneplácito de la oficialidad realista y del mismísimo Pacificador Morillo. Las posverdades o mentiras de la Gazeta de Santafé eran tan contraevidentes con la realidad que, en lugar de hacerse a una opinión favorable al régimen colonial de reconquista, puso al pueblo de la entonces Nueva Granada hoy Colombia, Venezuela y Ecuador en pie de lucha contra los invasores y de apoyo sin reservas a la causa patriota, aun de aquellos que no eran pocos indiferentes al tipo de gobierno, colonial o republicano, que rigiera sus destinos. Hoy tenemos, y lo hemos tenido hace varios años en varias campañas electorales, a un telegenio maléfico del juego sucio, un tal J. J. Goebels, que con mi dinero y mis recursos, dice él, sin aclarar de dónde saca su dinero y sus recursos, se está ocupando de Petro en Colombia y de López Obrador en México para impedir que</t>
+  </si>
+  <si>
+    <t>misma de sus tejidos. Se inscribió en sus estructuras. Destila de sus muros y verdines. Cuelga sobre el sopor de su vista oceánica y su bahía. Está en los espectros que leyó el gran Joe Arroyo en su melodía sobre una historia cartagenera de liberación. Está en lo que palpita y supura en sus geografías en el esplendor de edificios blancos almidonados que roza contra la desidia de sus terrenos polvorientos y despojados. El contraste abrasivo entre un punto y otro en la misma ciudad. Toda Cartagena de Indias contiene en sí misma la llaga de su virulencia racial. De allí que ciertas iconografías que se han instalado en su paisaje visual puedan suscitar malestar en quien las mira. En la medida en que Cartagena de Indias se ha elevado como enclave de casamientos a nivel global, una escena se ha hecho frecuente en sus postales festivas: la comitiva de</t>
+  </si>
+  <si>
+    <t>metaarchipiélago sin centro ni límites. Esas ideas corresponden al escritor cubano Antonio Benítez Rojo, quien verbalizó con habilidad magnífica algo que nunca se ha desprendido de mí, cazadora furtiva que soy a la hora comprender y discernir el temperamento de mi propia subjetividad y lugar de origen el Caribe. Esa lectura permite entender entonces al Caribe no sólo como un sitio meramente geográfico sino como un cualidad que se codifica en su capacidad de derramamiento, de desborde, de supersincretismo. Como algo que no se restringe a la ubicación geográfica, sino como algo que reta en sí mismo a lo estático, lo preciso. Es evidente que para una relectura del Caribe hay que visitar las fuentes elusivas de donde manaron los variadísimos elementos que contribuyeron a la formación de su cultura. Este viaje imprevisto nos tienta porque, en cuanto logramos identificar por separado los distintos elementos de alguna manifestación supersincrética que</t>
+  </si>
+  <si>
+    <t>comunidades. Desde la Colonia han violado los ríos: Los españoles tenían minas de oro, sobre todo en la cordillera Occidental, la que mira al mar Pacífico. Ahí siempre ha habido mucho oro, miles de toneladas de oro se han sacado de los ríos y quebradas que llevan el agua al océano. A los esclavos negros nunca se les pagaba por su trabajo, solo se les alimentaba para que no se murieran, y cada uno, según su fuerza y salud, valía, dice un fragmento de Cartas a Antonia. Es pertinente, hoy y siempre, el libro del sociólogo y periodista de saco rojo y tenis Converse. Lo es, entre muchas cosas, porque nos recuerda lo infinitamente indolentes que hemos sido con nuestros ríos y las comunidades que viven de ellos, aunque, por fortuna, siempre aparecen ciudadanos salvadores. Esta vez, ellos están en Florencia, Caquetá, y su propósito es lograr la declaración como</t>
+  </si>
+  <si>
+    <t>América para los americanos dejó claro que, del río Bravo para abajo, Latinoamérica carga con el destino de ser el escudo protector de los intereses comerciales de los Estados Unidos. Circulando en esa órbita nos han pasado ya dos siglos. Muchos presidentes han gobernado aquí y allá, pero las relaciones bilaterales de Colombia con los Estados se pueden resumir en un rango que va de la sumisión a la genuflexión, sin pasar jamás por la desobediencia. Y en esta historia común, a la potencia nunca le ha faltado un enemigo en contra del cual alinearnos. Si en el siglo pasado fue el comunismo, en este el que amenaza los intereses de Estados Unidos en su patio trasero se llama China. El gigante asiático está poniendo el más estratégico mojón en estas tierras por la vía de oxigenar a Maduro a cambio de petróleo. En una década, en transacciones rastreables, China</t>
+  </si>
+  <si>
+    <t>y los humanos proporciona a los segundos invaluables destrezas cognitivas, que emplean para concebir variados ordenamientos del mundo y ello se refleja en sus formas de organización social y territorial. Contrario a lo que podría pensarse, el mar está siempre a nuestro lado, pues las conexiones e interacciones con este no son exclusivas de los habitantes del litoral. Quienes habitan el interior tienen sus propias representaciones de los océanos y mares, que se manifiestan en las elaboraciones pictóricas que adornan una biblioteca en una remota ciudad o en un caracol que guarda el sonido del mar detrás de la puerta de una cabaña en la cordillera. Dolorosamente, también estas conexiones con ríos contaminados y con grandes centros poblados del interior del continente se reflejan en los espacios haliéuticos. ¿Debe, por tanto, el pequeño municipio de Puerto Colombia, u otros que podrían ser afectados, asumir en soledad la responsabilidad de limpiar</t>
+  </si>
+  <si>
+    <t>kilómetros cuadrados de superficie, se mueve dentro de la escala media de las corrientes receptivas del planeta, pero no es un destino caracterizado por las oleadas del turismo de masas. Recibe el 4 de las llegadas aéreas internacionales y el 1,7 de los ingresos de la industria por este concepto. En 2016 fue el refugio de 24,5 millones de viajeros del exterior y a sus arcas entró una jugosa tajada de US8.000 millones. Visa, que reina en esta república que tiene entre sus 146 millones de habitantes un alto nivel de bancarización y generalizado uso de tarjetas de crédito, proyecta para la temporada un aumento del 10 en el ingreso de turistas y un incremento en el gasto individual por encima del 31 con respecto al visitante de época normal logrado cuatro años atrás en las húmedas pero soleadas tierras cariocas. Tradicionalmente entre junio y julio se movilizan por Rusia</t>
+  </si>
+  <si>
+    <t>la isla, 62 mujeres, concedieron asistencia médica en sitios lejanos del país, barrios periféricos de grandes ciudades, aldeas indígenas y municipios ubicados en el interior de Brasil, lugares adonde los médicos brasileños históricamente se negaban a ir y la ausencia del Estado era una triste realidad. Se estima que en cinco años ellos atendieron a 113 millones de pacientes y 700 municipios tuvieron por primera vez un médico, todos ellos provenientes de Cuba. La diplomacia médica cubana representa la entrada de millones de dólares e incrementa su presencia y su poder en el mundo, sin embargo no deja de suscitar complejas discusiones. Según algunos analistas, Cuba alquila sus médicos, otros opinan que los esclaviza y muchos afirman que presta servicios solidarios, pero en palabras de uno de los médicos: Nadie sale de la isla engañado. Con el retiro de Cuba del Programa Más Médicos, Brasil tendrá que sustituir rápidamente a</t>
+  </si>
+  <si>
+    <t>de esta batalla, son los médicos, que a diario se enfrentan con el temor del contagio y aun así se levantan para ir al frente y librar la batalla con el enemigo. Desafortunadamente, ni siquiera los discípulos de Esculapio tienen la mínima garantía de seguridad, económica o de salud, tanto para ellos como para sus familias. La abogada Andrea Collazos, representante de la asociación Asociarte Global, entidad de médicos colombianos dedicada a formalizar garantías para su gremio, afirma lo siguiente: Este es el momento de hacer un llamado a gritos al Gobierno Nacional, que después de varios años de pasos errados en la construcción de la Ley 100 de 1993 tiene como consecuencia EPS e IPS quebradas, un deficiente amparo al derecho que tienen las personas a acceder a un sistema de salud eficiente y condiciones laborales precarias para los médicos en Colombia. Los sistemas de salud en el mundo</t>
+  </si>
+  <si>
+    <t>Dosis personal excepción al delito. Reforma constitucional, estupefacientes como asunto de salud pública. Leyes mantienen delito y Corte Constitucional dosis personal. Corte Suprema de Justica considera que no es delito el aprovisionamiento. Código de Policía, porte de droga afecta la actividad económica y prevé su destrucción. Cúmulo de errores. Propuesta de decreto parece innecesaria. La Ley 30 de 1986 estableció la dosis personal como una excepción al delito de porte de drogas ilícitas, que fue declarada exequible por sentencia de la Corte Constitucional, con ponencia de Carlos Gaviria Díaz, que se refirió al libre desarrollo de la personalidad. En 2009 se reformó la Constitución, para disponer que porte y consumo de estupefacientes está prohibido, salvo prescripción médica. La ley establecería tratamientos preventivos o rehabilitadores. La Corte Constitucional declaró exequible la reforma, en el entendido que la drogadicción se trataba de un asunto de salud pública, que no sería aplicable a</t>
+  </si>
+  <si>
+    <t>cannábicas, mientras que otros acceden a la sustancia a través de ciertas farmacias autorizadas para vender una marihuana producida estatalmente. Todo eso sometido a reglamentaciones estrictas para evitar abusos, como la venta a menores de edad. La puesta en marcha de esta política no ha sido fácil, pero su funcionamiento ha permitido disipar la mayor parte de los temores de quienes se opusieron a esa audaz medida. Además, la política ha tenido efectos benéficos para los usuarios, que ya no tienen que acudir a redes de distribución criminales, no son discriminados y reciben una sustancia de calidad controlada. Esto explica que el apoyo ciudadano a esta política esté creciendo. Obviamente el esquema uruguayo dista de ser perfecto, por lo que es probable que, a medida que se hagan seguimientos más precisos, sea necesario introducirle ajustes. Pero Uruguay está mostrando que es posible una política frente a la marihuana más racional</t>
+  </si>
+  <si>
+    <t>Hace 100 años se implantaban las primeras prohibiciones mundiales frente a las drogas hachís, opiáceos, cocaína en la llamada Sociedad de Naciones. El fin de la Primera Guerra dejaba espacio para nuevas preocupaciones y los Estados Unidos asumían un liderazgo para prohibir el suministro de drogas con fines de consumo abusivo. Se abría un espacio para los lucrativos negocios del narcotráfico. Las grandes farmacéuticas se encargaron de inaugurar rutas y mercados y ponerle una cara menos fiera al comercio. Una familia distinguida de Basilea, en Suiza, está en los orígenes de las grandes riquezas y las tristes persecuciones que han llegado a simbolizar el carrusel de la guerra contra las drogas. Inspirado en un idealismo que, como diría Paul Valéry, es además una especie de resentimiento. En 1894, Fritz Hoffmann, el hijo díscolo de un comerciante de Basilea, se casó con Adle La Roche, heredera de otra casa comercial en</t>
+  </si>
+  <si>
+    <t>investigada y judicializada por la policía judicial de Ocaña. Aprovecha la situación para recordar que la Policía de Norte de Santander pide a las madres no realizar estas prácticas e invita a la ciudadanía a delatar a mujeres que incurran en ellas. Se reitera de esta forma que la comunidad debe denunciar este tipo de hechos marcando a la línea única de emergencias. Según información de la Defensoría del Pueblo, los tres hospitales públicos de Ocaña se niegan a practicar cualquier tipo de terminación del embarazo incluso en los escenarios previstos por la ley y entregan a mujeres y adolescentes sospechosas de aborto a la policía judicial. Además del Emiro Quintero, están el Hospital de San Antonio y el Hospital de la Torcoroma. Este último hace homenaje, con su nombre, a la Virgen de Torcoroma, que según cuenta la leyenda apareció en una montaña del municipio en el año 1711.</t>
+  </si>
+  <si>
+    <t>bastante conservadora: no al porte de dosis mínima, no al aborto, no a la adopción de niños por parejas del mismo sexo y un empate en la fumigación. La imagen del doctor Uribe no ha vuelto a las cotas positivas que lo han acompañado por largo rato. Pero la mala imagen sí ha caído y mejorado en igual proporción su favorabilidad. Al calcar esta gráfica con la imagen de la Corte Suprema, hay una armonía indiscutible. Y perversa. Cada uno ha rebajado su desfavorabilidad en igual proporción. Ambos sacan ventaja aunque se mantienen en la esfera negativa. En el largo plazo, pierde el país. En estos seis meses la imagen negativa de Petro ha crecido. ¿Qué pensará? La democracia es disenso. Pero aquí lo que vemos es la presencia creciente de fallas geológicas en nuestra organización estatal y social. El primer acuerdo sobre lo fundamental es el acuerdo para el de fallas geológicas en nuestra organización estatal y social. El primer acuerdo sobre lo fundamental es el acuerdo para el desacuerdo. Un desacuerdo que preserve lo esencial. Coda.: Nuevamente ataca el dolor por la muerte de Chucho Bejarano. Qué desperdicio. Buena la entrevista de Francia Márquez. Se necesitan más mujeres.</t>
+  </si>
+  <si>
+    <t>país con el que nos medimos. ¡Nada pequeños! El ciclismo es nuestro. Quizá como el fútbol para argentinos y brasileños o el atletismo para jamaiquinos. Si uno compara ciclismo y fútbol, debiera admitir que en este último son muchas más las desilusiones, lo que refuerza la mentalidad de país derrotado. Mis vecinos querían ver la carrera, pero solo a partir de las 12 lo lograban por ESPN Internacional. ¡Qué tiene el fútbol que, aun mediocres como somos, nos clavan una tercera parte de las noticias para decirnos que James hizo un pase gol! La otra noticia es aún más diciente: ¡Falcao y James cambiaron de corte de pelo, vaya belleza! El ciclismo sí que retrata a Colombia. Nuestra geografía, nuestras destartaladas carreteras; las montañas de Antioquia y Boyacá, que son la base del poderío. La diferencia entre Rigo, Mijitos... huevones..., y Nairo, silente, es la misma que entre paisas y</t>
+  </si>
+  <si>
+    <t>trasero y ya es tiempo de que le dé su lugar, si de verdad quiere tener una influencia fuerte en la región. La autoridad la estaba perdiendo cuando casi la totalidad del mapa en América Latina estaba hacia la izquierda. Para poder lograr tener una influencia positiva, tiene que invertir en la región, de lo contrario China seguirá haciéndolo y Estados Unidos perderá la menguada influencia que le queda. Trump está ejerciendo presión sobre los productos importados de China, pero eso no necesariamente es suficiente para triunfar en las elecciones. Si su resultado es muy apretado, la democracia más vieja del mundo se enfrentará a una situación muy difícil. A primera vista un triunfo de Trump sería ideal, pero a largo plazo si gana Biden sería mejor para el mundo y para la tierra. y para la tierra.</t>
+  </si>
+  <si>
+    <t>Cada vez que aterrizaba en Rionegro no veía la hora de salir del aeropuerto para buscar un buen chicharrón con arepa en la carretera que lleva a Medellín. Este recorrido, que para muchos solía ser tedioso, para mí era todo disfrute, pues a medida que uno recorría un espectáculo de naturaleza poco a poco se iba adentrando en una de las ciudades de mayor desarrollo y calidad de vida del país. La vía por Las Palmas, llena de viveros, flores y restaurantes, no es solo un paseo de camino a la Capital de la Montaña, sino también un plan perfecto para disfrutar en familia los fines de semana, para una tarde con amigos luego de la jornada de trabajo, o para una escapada con colegas en medio de un congreso o cualquier evento que los lleve a Medallo. Y ahora, con el nuevo Túnel de Oriente, este paseo tiene un</t>
+  </si>
+  <si>
+    <t>Todos los días salimos a la calle. Todos los días caminamos tranquilos, yendo hacia el trabajo o dirigiéndonos hacia la parada del bus, o estirando la mano para tomar un taxi, o abriendo la puerta del carro en los afanes de llegar a tiempo a alguna parte. Todos los días salimos a hacer nuestras cosas, a vivir nuestras vidas y curiosamente, en las prisas y los aspavientos de la vida cotidiana, siempre sacamos algunos instantes para levantar los ojos al firmamento. Es como si quisiéramos ver qué presagios nos trae el cielo, como si en el cielo se pudiera leer todo lo que pasa o todo los que nos va a ocurrir. Por lo general, la atmósfera está limpia o puede traer consigo alguna que otra nube que nos habla de la proximidad de las lluvias. En ese momento podemos llegar a pensar que todo está bien, que los días</t>
+  </si>
+  <si>
+    <t>Diciembre es un tiempo de verano en Bogotá y sus municipios vecinos. Son días en que los capitalinos se calzan las gafas de sol y tiran a un rincón la sombrilla. Cuando era niño, eran los días perfectos para remontar el río Teusacá, saltando de piedra en piedra, chapoteando en sus hondos y persiguiendo truchas, que las había en esos días no tan lejanos. Ahora, los días veraniegos me traen la angustia de cuándo el agua se acabará. Y es que este año ha sido de intenso verano; si tuvimos tres semanas de lluvias en el segundo semestre fue mucho, y en La Calera, donde nace el agua de reserva para Bogotá, paradójicamente sus habitantes sufrimos por la carencia del recurso. Es una paradoja que parece ser lógica en nuestro modelo de desarrollo. En Chocó, la región donde más días llueve al año en el mundo, la gente vive sin</t>
+  </si>
+  <si>
+    <t>Estas noches ha llovido tanto que toda el agua no podría caber en un verso de César Vallejo. Es un golpeteo constante sobre las ventanas que me mantiene en vigilia: el sonido se siente cercano y al fondo los truenos alumbran el cielo. A veces solo escucho el estruendo ronco sin luz y no importa aclarar la mirada para buscar del otro lado, porque todo está oscuro. Desde hace días las noches son así en la ciudad: un ta ta, clap clap, plap plap, que suena dispar en las ventanas de la casa, como si un coro de agua nos recordara los tiempos que estamos viviendo. Entonces no basta abrir los ojos para saber que estoy despierto, ni hacer vanos intentos para dormir de nuevo: contar las gotas o tratar de ubicar el punto exacto en que caen es un esfuerzo inútil, porque nada sirve para recuperar el sueño perdido.</t>
+  </si>
+  <si>
+    <t>examen. Los investigadores recogieron la información sobre la temperatura día a día en cada colegio y datos sobre si contaban con aire acondicionado o no. Adicionalmente, el estudio incorporó otras características medioambientales y socioeconómicas que podrían afectar el desempeño de los bachilleres. Con ese arsenal estadístico, encuentran que haber estado enfrentados a días escolares más calurosos el año anterior al examen redujo su desempeño. Los autores concluyen que el calor reduce la productividad del tiempo de instrucción en el aula: un aumento promedio de 1 F más o menos medio C, para el rango de temperaturas relevante para el estudio en días escolares reduce el aprendizaje en 1 . La buena noticia es que los efectos desaparecen si la institución analizada tiene aire acondicionado. También encuentran que los estudiantes pertenecientes a minorías o de bajos ingresos resultan más afectados. Sospecho que en Colombia debe pasar algo similar: los estudiantes de a minorías o de bajos ingresos resultan más afectados. Sospecho que en Colombia debe pasar algo similar: los estudiantes de ingresos altos seguramente asisten a colegios mejor climatizados. Podemos estar perpetuando nuestras brechas sociales mediante un canal insospechado y que empeorará con el cambio climático. Pero, a diferencia de otras causas de las brechas que son difíciles de romper, esta sí tiene una cura simple. Heat and Learning. Joshua Goodman, Michael Hurwitz, Jisung Park, and Jonathan Smith; NBER Working Paper N. 24639, 2018.</t>
+  </si>
+  <si>
+    <t>una tormenta, los pajaritos se esconden, pero las águilas vuelan más alto. En el tintero. Las ironías de la vida. 1 Mientras el presidente Duque instalaba la cumbre de inversión extranjera más importante del país, el senador Petro solicitaba al Parlamento Europeo suspender el acuerdo comercial entre Colombia y la Unión Europea. 2 Mientras empresarios del país comienzan a reactivar sus negocios por la reapertura del comercio, los indígenas preparan una minga para paralizar la economía del país. 3 Mientras la Fiscalía, la Procuraduría y la mayoría de los colombianos exigíamos la libertad del expresidente Álvaro Uribe, la JEP mantiene en el Congreso a los asesinos de Álvaro Gómez Hurtado. ¿Dónde están la fuerza pública y la justicia de este país? Consultor en acceso a crédito de fomento agropecuario.</t>
+  </si>
+  <si>
+    <t>líder, especie de mesías y redentor de su pueblo para liberarlo de las garras del mal. Ahí no hay espacio para la reflexión, solo para la emoción. Al futuro se llegaría como por encanto, un futuro que se pinta con los tonos más amables, con los cuales es difícil no estar de acuerdo; el problema es que ni los unos ni los otros, especialmente Petro, nos dicen cómo y cuándo vamos a llegar a la tierra prometida y, cual Moisés en el monte Sinaí, simplemente nos la señalan en un horizonte brumoso pero, tal vez por eso mismo, atractivo. Los que crecientemente proponen votar en blanco en dos semanas lo hacen porque no creen en la bondad y factibilidad de las dos propuestas presidenciales y consideran que más que ganar unas elecciones se trata de mirar más allá de la elección para ponerse en la tarea seria e inaplazable de unas elecciones se trata de mirar más allá de la elección para ponerse en la tarea seria e inaplazable de construir un camino cierto a un futuro posible, no simplemente imaginado, que depende del trabajo y compromiso continuado de todos o al menos de muchos, y no de la generosidad o visión de un caudillo iluminado. De los profetas y salvadores debemos proteger a nuestra deficiente democracia, para transformarla y no destruirla.</t>
+  </si>
+  <si>
+    <t>Empiezo esta nota acompañado por el adagio del Concierto para piano en la mayor n. 23 de Mozart. En el insomnio de anoche desde que hay peste me despierto a las tres con una sensación de angustia que solo se disipa con una hora de lectura leí pedazos de un libro sobre el silencio, del violonchelista Mario Brunello. Curioso un músico hablando del silencio, pero, como me dijo Gonzalo Ospina, el concertino de la Filarmónica de Medellín, sin silencio no hay música. Esto es verdad, sin duda, pero también es verdad que si lo único que hay es silencio, la música deja de existir. Una tristeza más que se añade a esta epidemia es que la música, la música en vivo, con los músicos y el público presentes en una sala, se ha vuelto un imposible en estos meses de aislamiento. Tenemos, claro está, las grabaciones, y yo mismo en</t>
+  </si>
+  <si>
+    <t>que su esposa pasó años buscando sus restos y que sus verdugos no le precisaban el lugar donde lo habían enterrado. Quizá no sabe que el profesor Atilio lideraba colegios satélites que permitían que niños de toda la región asistieran a clases. Versiones a Justicia y Paz de Salvatore Mancuso y Juan Manuel Borré han revelado que bajaron al profesor de su moto cuando volvía a casa después de un partido de sóftbol, lo golpearon, lo llevaron a un sector llamado El Totumo, lo torturaron y lo mataron. No saben si su cuerpo fue arrojado a una fosa común o lo echaron al río. Así que no se necesita adoctrinamiento, senador Uribe, para que una escuela tenga consciencia de lo importante que es educar para la paz y la democracia. Mucho menos cuando esa misma escuela ha vivido en su piel las crueldades de la guerra. No son unos niños</t>
+  </si>
+  <si>
+    <t>Pese a las evidencias y a las tragedias domésticas que ha suscitado su declive, los periódicos no han registrado aún la extinción paulatina de una antigua especie literaria: la escritora que lee por el mero gusto de leer. Mientras una lectora de asueto tiene el derecho bacanal de divertirse con su lectura, sin asumir ningún deber con su autora e incluso con el poder de olvidar lo leído una vez cierra el libro, la escritora, por prurito profesional, puede disfrutar siempre y cuando descubra, al final o en el medio, de qué se constituye su gozo. Cuando el libro es un somnífero, la lectora común puede desecharlo, apilarlo o convertirlo en papel para envolver regalos; en cambio, aun en el caso frecuente de los libros deplorables, la escritora siente un apuro por comprender por qué su mecanismo carraspea como el motor tartamudo de un camión en subida. Por desgracia, las</t>
+  </si>
+  <si>
+    <t>Cualquier semejanza con hechos ocurridos o posibles, o con personas e instituciones, es mera coincidencia COMPARTIR Asumo que todos recordamos las fábulas de Rafael Pombo. Solo mencionar algunas suscita nostalgia por la infancia remota y por los hijos que crecieron: El gato con botas, La pobre viejecita y Rin rin renacuajo quien, como recordarán, salió de su casa esta mañana muy tieso y muy majo. Es un género muy antiguo, que asigna a los animales virtudes y defectos que no son suyos sino humanos. Su creación se atribuye a Esopo, quien vivió en el siglo VI a. C. De las fábulas que he leído me fascina la colección de Kalila y Dimna, publicada en sánscrito por primera vez al comienzo de nuestra era; hay una bella edición reciente de Acantilado. Del siglo pasado, recomiendo Rebelión en la Granja de George Orwell para apreciar los abusos que caracterizan a los sistemas</t>
+  </si>
+  <si>
+    <t>cortinas de sus 1.500 habitaciones en aquel verano apestado y el césped crecía sin ley en los fastuosos jardines. Aunque la idea de patrimonio colectivo tal como la entendemos ahora es una construcción posterior y no está presente en los textos, estos pasajes representan una invitación a pensar las afectaciones sobre el patrimonio en tiempos de epidemias y pandemias. Sabemos que a raíz del COVID19 muchos museos y centros culturales de todo el mundo han construido recorridos virtuales para que la gente pueda acceder a colecciones del patrimonio artístico. Además, han tratado de generar espacios de interacción con el público que van desde la muestra en redes sociales de pinturas y esculturas en un estilo desenfadado, hasta invitaciones para que la gente se anime y envíe representaciones hechas en la cotidianidad de sus casas de situaciones de pinturas y fotografías reconocidas. Por supuesto, son estrategias para el confinamiento, pero los</t>
+  </si>
+  <si>
+    <t>Y él parece entender por dónde va el agua al molino: Creamos caos. Más que caos responde ella. Guerra dice Frank. Miedo agrega Claire. Miedo. Algo brutal completa Frank. Devastador. Podemos usar el miedo. Yes, we can remata Francis. Al día siguiente Underwood precipita la ejecución sangrienta en directo para la nación entera de un rehén norteamericano a manos de un grupo yihadista, y él queda al mando soberano de la situación por la vía del shock institucional que acaba de provocar, pero que pareciera culpa del otro bando. La doctrina del shock la viene aplicando desde que ocupó por primera vez la presidencia Álvaro Uribe Vélez, sujeto sub judice hoy investigado y sometido a indagatoria por la Corte Suprema, pero quien, gracias al descomunal poder que ha adquirido, está a punto de torcerle el cuello a la justicia para lograr que la Corte Constitucional decrete segunda instancia en la</t>
+  </si>
+  <si>
+    <t>dichas medidas, más aún cuando se considera que la expectativa de que miembros de la fuerza pública venezolana desertaran en masa no se ha materializado. Ante la inefectividad de las estrategias adoptadas hasta ahora y la renuencia a negociar con un dictador, poco a poco lo impensable se va tornando posible. Dejando de lado el espíritu intervencionista de Rubio y del consejero de seguridad nacional, John Bolton quienes le hablan al oído a Trump sobre Venezuela, sin un hecho determinante que obligue a Washington a iniciar una acción militar directa por ejemplo, la muerte de ciudadanos estadounidenses a manos de actores venezolanos, es improbable que ello ocurra. Sin embargo, la Casa Blanca y la Casa de Nariño han advertido que cualquier amenaza a la soberanía de Colombia o agresión contra Guaidó, respectivamente, obligaría a considerar otros mecanismos. Este lo que es con Colombia o con Guaidó es conmigo que une</t>
+  </si>
+  <si>
+    <t>siglo XXI, esto es a la vuelta de unos pocos años, no solamente se corre el riesgo del descongelamiento del Ártico, sino que se vería afectada la vida cotidiana en diferentes ciudades de todos los continentes, e incluso colapsarían actividades económicas de importancia. De ahí el firme llamado a que todo el mundo se comprometa a no pasar del límite de aumento de la temperatura en un punto y medio por ciento, dentro del mismo período. El desprecio que el extravagante presidente actual de los Estados Unidos ha proclamado por los problemas ambientales ha tenido en esta materia, como en otras, un efecto importante en el contexto de las acciones que a los gobernantes corresponde desarrollar. De manera que no son pocos los que participan de la arrogancia de los que se creen todopoderosos, así esté comprobado que nada pueden hacer contra fenómenos naturales que exceden el poderío de sus</t>
+  </si>
+  <si>
+    <t>a paso, el desarrollo de una epidemia que se convirtió en pandemia y puso al mundo entero patas arriba. Y en un ambiente tan contaminado, en donde el nuevo coronavirus ha infectado en el mundo a tantos millones de personas, ha sido indispensable que la población reciba una información detallada sobre cómo prevenir esa nueva peste, que puede ser letal. No obstante, abundan las personas rebeldes que, sintiéndose muy independientes y muy machas, se empeñan en salir y en hacer lo que les da la gana. Y, contraviniendo las recomendaciones de los médicos y las órdenes de las autoridades, se pasean por las calles como si nada. No tienen en cuenta que con su rebeldía se están exponiendo a contaminarse con un coronavirus que ha invadido casi todos los países del hemisferio, que tiene en cama a varios millones de personas y ha enviado al sepulcro a otros tantos. Con</t>
+  </si>
+  <si>
+    <t>temas, se casara con la idea de la paz a través del diálogo, y de que es preferible una paz injusta, si así considera la pactada con las Farc y la eventual con el ELN, a una guerra que él considere justa, pero que inevitablemente privilegia la muerte, el mayor de los males, sobre la vida, quizá el mayor de los bienes! ¡Quién lo creyera! Probablemente asistiremos en las próximas elecciones presidenciales a una reedición del plebiscito del 2 de octubre de 2016. En ese momento la pregunta fue: ¿Apoya el acuerdo final para la terminación del conflicto y construcción de una paz estable y duradera? El coordinador del Sí fue el expresidente César Gaviria. El Partido Liberal estaba, como seguramente sus bases continúan estándolo, comprometido sin atenuantes con la paz en todas sus expresiones. Como entonces, quizá surjan en esta campaña presidencial mentiras generalizadas en contra del Acuerdo con</t>
+  </si>
+  <si>
+    <t>partido hayan entendido o quieran entender o puedan entender de dónde viene el descontento o que al pobre Duque se le ocurra algo distinto de las exhortaciones babosas a la unidad sin negociar con nadie, la insistencia en que el Gobierno ha hecho lo que no ha hecho y la promesa de que no habrá reformas cuando esas reformas están por venir. Colombia está despertando del largo sueñopesadilla que se llamó el conflicto armado, el presidente eterno y el Acuerdo de Paz. Las guerrillas se acabaron hace tiempo y ahora siguen las protestas normales y legítimas en una democracia tan injusta y excluyente como es la que tenemos. El primer campanazo fue este paro que en realidad fue una marcha en el estilo peculiar de Colombia, mezcla de rebelión, descontento, vandalismo, caminata y fiesta ciudadana. Vendrán otros campanazos. Y tendrá que manejarlos el presidente inepto que elegimos. Escrita el viernes vandalismo, caminata y fiesta ciudadana. Vendrán otros campanazos. Y tendrá que manejarlos el presidente inepto que elegimos. Escrita el viernes a primera hora. Director de la revista digital Razón Pública .</t>
+  </si>
+  <si>
+    <t>Gustavo Petro desafió y pasó por encima de decisiones de los alcaldes de Medellín y Cúcuta, generando cada vez mayor polarización en el ambiente electoral. Cero y van dos ocasiones en las que el exalcalde de Bogotá y precandidato presidencial Gustavo Petro, contradice y desconoce las decisiones de las máximas autoridades locales de importantes ciudades de Colombia. Hace una semana el alcalde de Medellín, Federico Gutiérrez, aplicando la reglamentación vigente para la realización de manifestaciones políticas en la ciudad, trató de impedir que Petro organizara una reunión política sin cumplir el pleno de requisitos necesarios para una concentración superior a 500 personas, que, de acuerdo con las normas locales expedidas desde 2016, debería cumplir los requisitos de seguridad humana, matriz de riesgos tarima y sonido, servicio de logística y plano de evacuación, póliza de responsabilidad civil extracontractual, pago a derechos de autor, y documentación del grupo de aseo y servicios</t>
+  </si>
+  <si>
+    <t>de aquellos que no comparten el gusto por la pirotecnia. Así mismo, existen fuertes contextos educativos para sensibilizar a las personas particulares que se consideran entusiastas de estos productos y que desean celebrar con estos de manera privada. En Colombia la estigmatización moral de la pólvora ha prevenido que estos adelantos se materialicen y han invitado a que la gente siga comprando la misma pirotecnia que compraba hace 30 o 40 años, de manera clandestina. Esta es la pólvora que ataca la Representante Miranda, porque con seguridad es la que recuerda de sus celebraciones familiares, pero es una totalmente alejada de las realidades de la industria a nivel mundial y refleja su desconocimiento. Existe pirotecnia segura, así como alcohol consumido responsablemente y automóviles que han sido regulados en su diseño para reducir los riesgos al conductor. En estas industrias el riesgo asociado a estos productos se manejó elevando niveles de</t>
+  </si>
+  <si>
+    <t>Micrófonos químicamente enervados, cadenas de WhatsApp, trinos ligeros de contenido, fotomontajes, columnas con intereses ocultos, filtración de piezas de expedientes judiciales cuidadosamente editadas, informes periodísticos sin contrastación de fuentes y el activo radiopasillo hacen parte de toda la artillería disponible para acabar con el buen nombre o la reputación de una persona, entidad o funcionario público. No es un tema nuevo, por supuesto. Dicen el texto bíblico que Caín era la mata de la envidia, y desde ahí quedó con el rótulo de ser uno de los primeros fratricidas de la historia. Sócrates fue condenado a muerte por un rumor que circulaba por Atenas que lo señalaba de corromper a los jóvenes y promover deidades diferentes a las que guiaban sus vidas. Desde los tiempos de los griegos hasta nuestros días, el rumor, el chisme le ha ganado la carrera a lo fáctico. Esto ha sido una lucha constante en</t>
+  </si>
+  <si>
+    <t>o valioso los sueños? Excepcionalmente sí, y existen historias de investigadores, escritores y músicos que construyeron sus logros notables sobre sus respectivos desvaríos cuando dormían. El descubrimiento, en 1865, de la estructura molecular del benceno por August Kekule, químico alemán, es quizás el ejemplo más célebre de una inspiración científica surgida durante una siesta. El químico alemán, según su propio relato, soñó que una culebra se comía su propia cola y ello le inspiró la estructura circular de la entonces extraña molécula. Es real que los sueños eventualmente apoyan a los soñadores y pueden sugerir soluciones ingeniosas a sus problemas de turno. Pero los soñadores, importante resaltarlo, tienen que saber muy bien la lógica y la ciencia detrás de sus respectivos proyectos Muy pocos químicos, de cualquier época, comprenderían el mensaje del sueño de la culebra comiéndose su cola Y, muchísimo menos aún, si les tienen miedo a las serpientes. mensaje del sueño de la culebra comiéndose su cola Y, muchísimo menos aún, si les tienen miedo a las serpientes.</t>
+  </si>
+  <si>
+    <t>laboratorios de cocaína, exportadores y comercializadores para terminar, lavado todo, en las impolutas arcas de la banca mundial y nacional. Reafirma la Corte que sólo habrá aspersión si el Gobierno no logra concertación con las comunidades o sustituir cultivos. Pero éste no intenta una acción integral y quiere en cambio repetir la fracasada y costosísima aspersión con glifosato, medio infalible para provocar una crisis humanitaria. Recuerda Romero que en 2005 había en su tierra 3.875 hectáreas de coca; se asperjó sin medida y hoy son 45.000 las hectáreas sembradas. De los 70.000 cultivadores nariñenses, apenas 16.000 reciben ayuda oficial. Ebrio en los soñados efluvios del glifosato, ignora el Gobierno experiencias que, de generalizarse, cortarían por lo sano. En 2013 se destruyeron en Caldas las últimas siembras de coca. El secreto: se pactó la solución con las comunidades, el Estado allegó bienes, servicios y abrió vías; convergieron organizaciones públicas y sociales</t>
+  </si>
+  <si>
+    <t>un hombre químicamente bueno. Dicho lo anterior, albergo serias dudas sobre la imparcialidad y el proceder de la Corte Suprema de Justicia, y muy especialmente sobre el magistrado Barceló, autor principal del auto tan mal redactado como saturado de errores de ortografía y de puntuación. El analista Eduardo Mackenzie comenta: No es sino ver la lógica de lo que Luis Barceló llama abrir investigación en contra del senador Álvaro Uribe Vélez y del representante a la Cámara Álvaro Hernán Prada. Todo el asunto está en eso de abrir investigación en contra. En un sistema democrático la investigación judicial tiene una meta: averiguar y establecer la verdad objetiva. Aquí, en la acción de Barceló, al abrir la investigación, el acusado ya está condenado, su defensa es inútil, pues la investigación es en contra, cuando debería ser una investigación imparcial, sobre unos hechos probados. Hay una regla de oro en estas materias,</t>
+  </si>
+  <si>
+    <t>Para nadie es un secreto que la gasolina es imprescindible no solo para el procesamiento que convierte la coca en cocaína, sino también para que funcionen los laboratorios escondidos en lugares inexpugnables. Allí se requieren plantas eléctricas para alimentar, entre otros, los hornos microondas que deben trabajar permanentemente. Para decirlo de manera simple: si no hay gasolina, no hay cocaína. Por eso la denuncia hecha por Francisco Lourido, el candidato a la Gobernación del Valle, debe ser tenida en cuenta. Sucede que las ventas de gasolina andan disparadas en los departamentos donde se procesa el alcaloide y el Gobierno no ha tomado cartas en el asunto. Las estaciones de gasolina en esos lugares se han multiplicado geométricamente, ante los ojos y oídos de quienes andan persiguiendo a los responsables de este delito. Ejemplos hay muchos: mientras que en el Valle del Cauca con más de 4,7 millones de habitantes existen</t>
+  </si>
+  <si>
+    <t>elaboración, entre la salmuera, el ahumado y la cocción lenta, su método de preparación es quizás el más fiel al americano. Mario Roa, uno de sus dueños y amante de la comida, está convencido de que a Bogotá le hacía falta un pastrami como tienen grandes ciudades como Nueva York y Los Ángeles y no es difícil darle la razón luego de disfrutar de uno de sus sándwiches, con pepinillos, papas o ensalada, por 20 mil pesos. Este lugar tiene una fórmula básica que no tiene pierde, pastrami de pavo o de res y aunque su tamaño parece engañoso es la porción perfecta de 160gr no deja espacio a dudas de su buena preparación e inolvidable sabor. Para hacerle honor a nuestras recetas típicas encontré El Sándwich Taller Cra. 4a 26b34 , un lugar donde se respira costa caribe, desde la música hasta los ingredientes, estos sándwiches son la invención</t>
+  </si>
+  <si>
+    <t>vía fracking dijo que carecía de fundamento Hughes, 2013. Poco después se comprobó que tenía razón. La propia AIE admitió, en 2014, que había evaluado mal el yacimiento no convencional de Monterrey, California. El descache fue de la bicoca del 96 . ¿Está comprobado que los yacimientos no convencionales de San Martín y Puerto Wilches garantizan la seguridad energética que los abanderados del fracking pregonan? ¿Tiene la Upme este dato? ¿O estaremos creando una burbuja, como parece que sucedió en EE. UU.? En 2005 pronosticaban que para 2025 dejarían de depender de las importaciones provenientes de los países de la Opep, pero otro analista, JalifeRhame, descubrió datos deliberadamente abultados y escribió: El modelo financierista prolonga su dolorosa agonía, y ahora parece el turno del fracking JalifeRhame, 2014:91. Ahora bien, es claro que extraer energías vía fracking es más costoso que hacerlo mediante técnicas convencionales. Las inversiones son, por naturaleza, de</t>
+  </si>
+  <si>
+    <t>aquella tierra. Es en este territorio donde se gesta una culinaria, cuya riqueza de sabores y la originalidad de sus preparaciones admiro fanáticamente. Sopas de antología son su suculento caldo de costilla y el caldo de pichón ambos se ofertan para desayunar su exclusivo mute, que es mondongo con garbanzos, ahuyama, arracacha, maíz y papa; sus fríjoles con costilla, preparados con fríjol de Castilla, papa, yuca, guineos verdes, ahuyama, arracacha, zanahoria y cilantro cimarrón; y finalmente su sazonado y reconocido sancocho de rabo de res. Tema especial son sus carnes en cecina, oreadas o ahumadas casi únicas en Colombia, también lo es su sobrebarriga horneada con cerveza y miga de pan; joya de alta cocina es aquel cabrito asado acompañado de aquel legado culinario español llamado pepitoria; y qué decir de la turmada pastel de sobrantes de cocina o de las crocantes empanadas con masa de yuca, los pasteles de</t>
+  </si>
+  <si>
+    <t>de tornarse violenta. Tierra. Hace años recorrí de cabo a rabo el Valle del río Patía. A pie la mayoría de las veces. No vi más que extensas haciendas separadas por alambre de púas en las que pastoreaban lotes de ganado cebú. La mayoría de esas propiedades fueron en el pasado pobladas y cultivadas por cimarrones que huían de las haciendas esclavistas. Con la Ley de Manumisión 1851 los esclavistas se volvieron patrones y los esclavos peones. Los dueños son blancos y los jornaleros negros. Recuerdo que durante una plática un anciano trató de blanco a un mayordomo. Le pregunté que por qué no lo llamaba por el nombre. Lo aprendí de mi abuelo que fue esclavo, contestó. La mayoría negra carece de tierra para trabajar y vive en ranchos de bahareque levantados en las estrechas mangas que dejan las alambradas. Son lugares en los que la vida transcurre como</t>
+  </si>
+  <si>
+    <t>Sobre un suelo que empieza a cuartearse, se esparcen profusamente hojas amarillentas como de un otoño que apenas rozara estos parajes y dejara destellos a su paso. Hojas rojizas de almendros que el viento ni siquiera se molesta en desprender cansadas de vagar entre ramas, la fuerza de su ánima vegetal las deja caer. De suspirar sin esperanzas por un otoño remoto, incapaz de aposentarse entre el verde rotundo del invierno y el pardo marchito de un verano que empieza a rondar por los alares de la casa solariega que aún llevo como un caparazón de amor, de vida, sobre mi vida entera. Un verano tímido, lento y parsimonioso, que poco a poco se va metiendo entre las cosas, hurga en el rústico fogón de cenizas de otro tiempo, en algún tizón que alumbre la memoria de una infancia que nunca acaba de pasar. De un cántico de luz que</t>
+  </si>
+  <si>
+    <t>La humanidad puede dividirse en dos: los que odian el silencio y los que no pueden vivir sin él. Los que lo aman han identificado y medido los lugares más silenciosos de la tierra. El primer lugar lo ocupa la Caldera de Taburiente, una depresión en Canarias, en la isla de Palma, donde los sonidos fluctuantes del área jamás pasan de 12 decibeles un poco más alto que el sonido de la respiración tranquila. El segundo está en la zona más árida del mundo, el corazón del desierto de Atacama en Chile, idéntico a la superficie de Marte, dicen. Cuando no hay vientos, se puede disfrutar allí de un silencio francamente extraterrestre. El tercer lugar es Monteverde en Costa Rica, un parque natural aislado del mundo por círculos concéntricos de árboles de 40 metros de altura y troncos de hasta ocho metros de diámetro y varias toneladas de peso, tapizados</t>
+  </si>
+  <si>
+    <t>campo de batalla ideológico. Descuidar ese flanco era ceder terreno al enemigo, y por eso un personaje como Laureano Gómez dedicó casi más tiempo a la crítica literaria que al debate político en los años 30. Comentó los escritos de León de Greiff, de Darío Samper, de Rafael Maya, de Porfirio Barba Jacob, y con todos ellos peleó, y siempre debido a cuestiones morales que remitían a visiones políticas de la realidad. En la obra de De Greiff, por ejemplo, vio una nociva popularización de la poesía. Sus poemas, al alcance del lustrabotas, del carpintero o del ganapán de esquina, robaban a la poesía la sustancia que hacía de ella una fuerza espiritual capaz de forjar naciones. Casi como Stalin, Laureano creía que el poeta era un herrero del alma. Aunque anacrónicas y derivadas de esa curiosa obsesión grecolatina que sobrevivía en Bogotá mientras el resto del mundo se modernizaba,</t>
+  </si>
+  <si>
+    <t>calor y química mineral, que transformaron la rudimentaria minería de veta usada desde tiempos prehispánicos, en un trabajo de elevados conocimientos que dio lugar a cuantiosas inversiones y a las primeras empresas capitalistas exitosas que operaron en Colombia. Fueron ellos quienes enseñaron a usar el molino de pisones, la pólvora, el fósforo, la nivelación de canales, la construcción de ruedas hidráulicas, la amalgamación con mercurio, el uso de barras de acero para rocas, la fundición industrial, la refinación del oro al fuego, la construcción de hornos y las prácticas de conservación de maquinaria, entre otros aspectos. Ese fue el contexto que permitió el desarrollo, sobre todo en la segunda mitad del siglo XIX, de lo que algunos llamaron la minería científica moderna. El desarrollo de esa minería no puede explicarse sin los impactos de apertura al mundo exterior, en todo sentido, que generó la Independencia. sin los impactos de apertura al mundo exterior, en todo sentido, que generó la Independencia.</t>
+  </si>
+  <si>
+    <t>Macron con los chalecos amarillos en Francia. La Encuesta del CNC muestra que al ciudadano corriente le preocupan más los problemas que tienen que ver con el futuro que con el pasado, sobre todo en lo que este tiene de violento e injusto. Reclaman por una mejor educación y oportunidades y empleo para los jóvenes; contra la corrupción y por la transparencia; por pensiones y condiciones laborales dignas; por una especial atención a la realidad campesina y por una reforma tributaria que genere equidad tributaria y no atropelle a una clase media en proceso de consolidarse y que estuvo bien activa en estos días. Poca mención hacen de los temas que alimentan a la prensa y a muchos analistas y dirigentes políticos: las negociaciones con el ELN, la implementación del Acuerdo de paz, la privatización de empresas estatales, el medio ambiente. Va quedando claro, y tal como se expresó en</t>
+  </si>
+  <si>
+    <t>Hablar hoy en el país de la llamada economía naranja es la manera más segura para escuchar un mal chiste que busca descalificarla sin analizarla, una nefasta práctica que en buena medida se ha impuesto entre nosotros. La idea de esa economía no es nueva en Colombia ni es una invención criolla. Surge en el seno de las llamadas industrias culturales que, gracias a desarrollos tecnológicos, facilitaron y generalizaron la reproducción a escala industrial de mucha de la creación cultural y dieron inicio a la potente industria del entretenimiento que en el mundo mueve billones. Primero fue la palabra escrita, luego fueron las imágenes de la pintura y la fotografía, y ese monstruo magnífico del siglo XX, el cine, y fue la reproducción de la voz, a caballo de los desarrollos fonográficos que no se detienen, y las artes escénicas y de interpretación directa que salieron de las salas de</t>
+  </si>
+  <si>
+    <t>Ganar el poder siempre será apenas el comienzo de la prueba definitiva de cualquier proyecto político. La satisfacción de necesidades básicas de bienestar ciudadano, así como el grado de ejercicio real de libertades fundamentales, terminan por determinar la medida de su éxito, o de su fracaso. La llegada al gobierno de los antiguos combatientes del Frente Patriótico, como se llamó la alianza del ZAPU, Unión del Pueblo Africano de Zimbabwe, de Joshua Nkomo, y el ZANU, Unión Nacional Africana de Zimbabwe, de Robert Mugabe, significó el fin de la Rodesia Británica, para dar paso a un Estado regido por la mayoría negra, y representó un triunfo para los marginados del país y para la causa de la democracia africana. Los acuerdos de Lancaster House, que lord Carrington, entonces canciller británico, condujo con maestría, abrían un enorme campo de esperanza para la realización de un proyecto político de convivencia entre los</t>
+  </si>
+  <si>
+    <t>popular, en especial los congresistas, que hoy son los únicos protagonistas de las decisiones de la mayoría de las colectividades. Sí las listas son cerradas, no es descabellado pensar en una financiación exclusivamente estatal porque serían los partidos quienes harían las campañas y sus directivos quienes deberían responder por el uso de los recursos destinados para esos fines. La financiación estatal, además de facilitar el control del financiamiento político, ofrece un elemento que es central en una democracia: que nadie tenga ventajas electorales por cuenta del dinero, es decir que la competencia sea realmente de las ideas, de las posturas de cada partido frente a los temas de interés de los ciudadanos y de la trayectoria de sus candidatos. De otra parte, es preciso decir que es un avance el hecho de que el proyecto del gobierno proponga que la conformación de las listas deberá acoger los criterios de paridad</t>
+  </si>
+  <si>
+    <t>Con base en la referencia que aparece al final preparé los párrafos a continuación. Elegí esta referencia, porque encuentro numerosas e inquietantes coincidencias entre las razones para las izquierdizaciones de los estadounidenses y de los colombianos. Resulta claro que durante décadas empresas de noticias tales como CNN y The New York Times se han sesgado en favor de la democracia social también conocida como progresismo, o más simple aún, como ideologías de izquierda. Por ejemplo, la gran mayoría de sus periodistas declaran ser demócratas y sus donaciones se dirigen en forma abrumadora hacia estos candidatos. En forma similar, en décadas recientes, no pocas universidades están militando en favor del Partido Demócrata a juzgar por sus afiliaciones y por sus donaciones. Algo más, escriben textos y libros de historia con los cuales influyen en sus colegas, en los profesores y en los colegios de bachillerato. Este adoctrinamiento ideológico que se gesta</t>
+  </si>
+  <si>
+    <t>a un intento, sin duda condenable, pero no tan atípico, por incidir en las decisiones de la Rama Judicial y Legislativa sobre la fumigación con glifosato, la extradición y la JEP, y por castigar a quienes no acatan las órdenes de Washington. Si bien esta indebida intromisión en la política colombiana ha generado un rechazo generalizado, llama la atención la molestia menor que parece haber suscitado la pasividad del gobierno Duque frente a lo que ha descrito como una decisión soberana de Estados Unidos. Le puede interesar: Guerra de testosterona Por más cierto que sea el matoneo diplomático que reviste este episodio de las históricamente estrechas y amistosas relaciones bilaterales, la narrativa de la injerencia yanqui se queda corta al no tener de presente las formas en las que, por simple afinidad o por decisión voluntaria, distintos gobiernos colombianos han tolerado la vulneración de la soberanía y la autonomía nacionales,</t>
+  </si>
+  <si>
+    <t>como muestra de su fortaleza la baja inflación, la solidez del sistema financiero, la confianza de los consumidores, la resiliencia del mercado laboral y la misma política fiscal sustentada en una reforma tributaria que, según el ministro Cárdenas, descartaría cualquier ajuste durante un lustro. Antes de su retiro el ministro dejó el nuevo proyecto de presupuesto nacional debidamente equilibrado. En ese marco una ley de financiamiento resulta, simplemente, innecesaria. De allí surge la otra pregunta: ¿cómo se produce, de repente, un hueco fiscal de 14 billones? La respuesta es fácil: el hueco fue creado por el nuevo ministro. El Gobierno se inventó gastos e inversiones sin el debido respaldo presupuestal. Como lo anota Patricia Lara en su reciente columna de este mismo diario 161118, no hay un hueco fiscal, sino la decisión de acometer nuevos gastos que el Gobierno tasa en esa cifra. Solo que como no hay recursos para</t>
+  </si>
+  <si>
+    <t>Cada vida reproduce la totalidad de la historia humana, aunque no lo verbalicemos ni seamos conscientes. Todos hemos experimentado nuestra propia guerra de Troya, nuestras pestes mortíferas, nuestro descubrimiento de América o la exploración de los polos. También nuestra Revolución francesa y nuestra singular caída de Berlín o de Tenochtitlán, y hemos compuesto nuestras muy personales Canciones de Bilitis. Somos una sola experiencia humana. Lo que nos hace únicos porque somos únicos es el modo en que cada uno interpreta el viejo drama de vivir, esa antigua partitura que en la juventud nos exalta y que, con los años, se vuelve algo insípida, reiterativa. A veces anhelamos salir de ese guion ya visto, pero ¿cómo? Hay días en que somos tan lúgubres, tan lúgubres. Lo no vivido parece estar en la periferia y es cada vez más inalcanzable. ¿Irse, cambiar, ser otro? Escribir es un modo de ponerse frente al</t>
+  </si>
+  <si>
+    <t>genital, el embarazo adolescente, en la mayoría de los casos no deseado, los desórdenes alimenticios fruto de discriminación, y la crueldad mental, que abarca elementos que van desde las limitaciones en el acceso a la educación y el sometimiento a tratos vejatorios. Ante este panorama, que pone en cuestión la calidad de vida que los Estados deberían proveer en condiciones de igualdad, de verdad, a todos los seres humanos, es urgente acometer un compromiso sin fronteras, de encuentro de civilizaciones, que permita pagar la deuda más grande del mundo, de la que son acreedoras las mujeres, que representan al menos la mitad del genero humano.</t>
+  </si>
+  <si>
+    <t>sabiendo mamar y sabiendo andar. Un pez nace y sabe nadar; nosotros no. También nosotros nacemos sabiendo andar con el órgano de caminar en el cerebro, pero nos demoramos un año para volvernos bípedos sin caernos. Antes, al gatear, logramos ser cuadrúpedos. Nacemos sabiendo hablar, o por lo menos con un órgano del lenguaje que empieza pronto a emitir sonidos y que a los tres años estalla en toda su maravillosa amplitud y creatividad: una niña de tres años habla con una gramática perfecta. Nuestro cerebro sabe sin saber que sabe gramática. Conjuga los verbos, hace concordancias de género y número, inventa frases que no ha oído nunca. En ese sentido, platónico, venimos al mundo con una memoria de la vida pasada de la especie: no aprendemos a mamar, a caminar, a hablar: recordamos cómo se habla, pues es algo natural, que viene con nuestro cerebro. A partir de estas</t>
+  </si>
+  <si>
+    <t>lado que no es. Después del virus, la izquierda y la derecha las tengo al revés, y durante 20 días la vida me era indiferente y todo lo que pensaba estaba patas arriba. Lo único bueno es que me estaba muriendo muy tranquila. Casos como el de mi hermana hay por miles, por millones. Pero lo peor es que hay personas que simplemente se acuestan porque se sienten sin ánimos, esperan sin hacer nada, y cuando ya sienten que se están asfixiando, llegan al hospital demasiado tarde. No solo hay consecuencias pulmonares o neurológicas. A algunos enfermos les da miocarditis, y esta inflamación puede ser silenciosa, sin síntomas, lo cual la hace más insidiosa, pues hay atletas que tuvieron COVID, supuestamente están recuperados, y en medio de la práctica de su deporte se desploman. No escribo esto para asustarlos. O, mejor dicho, sí. Sé que estamos hartos de vivir encerrados, su deporte se desploman. No escribo esto para asustarlos. O, mejor dicho, sí. Sé que estamos hartos de vivir encerrados, de no abrazar a nadie, de ponernos máscaras, de tener las manos peladas de tanto lavárnoslas. Pero no es el momento de bajar la guardia. Una vacuna eficaz no está a la vuelta de la esquina, el virus sigue creciendo, y se acerca, y nos cerca: cuidémonos.</t>
+  </si>
+  <si>
+    <t>sexo aséptico. Y es que la humanidad ha sido siempre lasciva pero pacata. Aunque el mundo consume varios gúgoles de terabitexxx por segundo dato de Pornhub, porque en esto solo me fío de las profesionales, la gente denigra de las prostitutas sin reconocer su esforzada función social, la mano que le tienden al tímido y al flácido, al feo y al solitario. La humanidad yacente olvida que si hoy somos más felices bajo techo y sobre el lecho lo debemos por igual a la píldora y a la revolución sexual de los 60 que a la educación del porno por internet. Allí fue donde aprendimos que, como dice Woody, el sexo solo es sucio cuando lo hacemos bien. El Estado debería capacitar a las chicas webcam para que sacien no solo las ansias de los cuerpos sino también la sed espiritual de sus clientes. Así habría una conjunción del putas:</t>
+  </si>
+  <si>
+    <t>de mujeres y niñas que más lo necesitan, por ejemplo: aquellas que viven en zonas rurales y se demoran semanas en llegar a un puesto de salud, las niñas que sufren violaciones sistemáticas desde antes de tener su primera regla y ni siquiera saben que están embarazadas, o las mujeres con embarazos inviables cuyos problemas suelen detectarse en el segundo o tercer trimestre. Otra razón importante es que los estándares internacionales han avanzado para proteger los derechos de las mujeres: por ejemplo, en 2012, en el caso Artavia Murillo contra Costa Rica, la Corte Interamericana de Derechos Humanos aclaró que la protección de la vida desde la concepción no es absoluta y que no puede usarse para restringir desproporcionadamente otros derechos. Y el año pasado, el Comité para la Eliminación de la Discriminación contra la Mujer Cedaw recomendó a Colombia hacer una despenalización más amplia del aborto para eliminar las</t>
+  </si>
+  <si>
+    <t>historia. Apenas nueve meses entre la publicación del código genético del virus y la evidencia estadística sobre seguridad y eficacia de la primera vacuna un proceso que nunca había tardado menos de cinco años. Una tecnología que jamás se había intentado ARN mensajero. Una eficacia superior al 90 , muy por encima de casi todas las vacunas contra enfermedades infecciosas. Millones de vacunascandidatas que se habían fabricado antes de saber su eficacia y que por eso empezaron a aplicarse horas después de su aprobación para uso de emergencia. Pero también en estos días la desigualdad está mostrando su rostro más obsceno: unas vidas humanas valen más que otras y el orden del acceso a las vacunas es el certificado exacto del lugar que ocupa cada uno de nosotros en la pirámide de escala planetaria. Algunas desigualdades se justifican porque una sociedad sensata necesita que existan esas desigualdades: los médicos y</t>
+  </si>
+  <si>
+    <t>una moda, como un sufijo según apunte del fallecido historiador Germán Colmenares. Se buscaba una explicación científica, pero el resultado no cumplió esa meta, en vez de un discurso homogéneo el libro Colombia Violencia y Democracia compiló una serie de ensayos sobre todo tipo de violencias que afectaban a la sociedad colombiana dando una apariencia de igualación de todas ellas. Además, en lo que respecta a la violencia política insistió en la tesis de que la tierra está en la base de los conflictos contemporáneos del país como también las falencias del estado, el carácter excluyente del régimen político, todas las cuales configurarían las llamadas causas objetivas del levantamiento armado. Más aún, Sánchez reitero su tesis según la cual, los colombianos somos propensos a la violencia y el país se ha configurado endémicamente a partir de la violencia, como si se tratase de una enfermedad y todas las situaciones de</t>
+  </si>
+  <si>
+    <t>ciudadana son generalizadas. Segundo, la mayoría de las personas tiene poca confianza en la policía y considera que no hace bien su trabajo. Tercero, el control sobre y la rendición de cuentas de las instituciones policiales son deficientes, aun cuando el uso de la fuerza está regulado. Y cuarto, el nivel cultural de nuestras policías, medido en la duración y profundidad de su formación sobre todo en relación con estrategias no represivas y de desescalamiento de crisis es comparativamente bajo. Para explicar este déficit de legitimidad, algunos analistas sugieren que la forma en que conceptualizamos el policiamiento como bien público condiciona el alcance de cualquier diagnóstico e intento de reforma. Si consideramos que el rol central de la policía se limita a combatir el crimen, estadísticas como las tasas de homicidio e hurto se tornan claves para medir su éxito. Sin embargo, si algo nos muestran muertes injustificables como las</t>
+  </si>
+  <si>
+    <t>Como en todas sus obras, Stanley Kubrick tuvo la ambición de concentrar la humanidad en un hecho y conectar las preguntas metafísicas siempre irresueltas con la intensidad de los colores y las apariciones también metafísicas de un acertijo indescifrable. La última aparición del sol, en los últimos minutos del largometraje, hace el relevo con la imagen de un embrión humano en el espacio mientras retumban los tambores sinfónicos y el ciclo visual cobra una remembranza entera de las búsquedas siempre prolongadas y la incertidumbre. Quedarse mudo y estático después de tanta pirotecnia simbólica y técnica sigue siendo natural ahora, 50 años después de su estreno entre la frialdad de un canon obedecido con mansedumbre. Kubrick llevó a los límites más altos del riesgo su dominio del efectismo, hizo de la atmósfera una nueva versión narrativa, otra posibilidad del juego, otra apertura legal de la creación; una odisea personal en ese atmósfera una nueva versión narrativa, otra posibilidad del juego, otra apertura legal de la creación; una odisea personal en ese vals cinematográfico que fluye evocándolo todo y dinamitándolo todo entre los días iniciales y el futuro.</t>
+  </si>
+  <si>
+    <t>y los hechos? Por supuesto, la distancia podría no existir, ser el espejismo de una mirada sesgada. Este es el tipo de hipótesis que nunca se debe descartar. Pero hay otras explicaciones posibles. En estos casos, una de las mejores maneras de salir de la perplejidad es fijar la atención en los incentivos: cuáles actos y personas premia el Gobierno y cuáles castiga. Allí no solamente se observa realmente dónde están sus apuestas, sino también el tipo de comportamientos que promueve y que podríamos esperar observar en el futuro. Hagamos un pequeño ejercicio de recapitulación para refrescar la memoria. Cuando surgió el escándalo de los falsos positivos redivivos y un general por razones buenas, regulares o malas salió a excusarse frente a la comunidad por el asesinato cruel de un desmovilizado de las Farc, lo primero que sucedió es que ese oficial fue regañado públicamente y después enviado a las</t>
+  </si>
+  <si>
+    <t>pueden existir miles de casos de personas que siendo inocentes han podido ser condenadas a pasar unos buenos años en la cárcel o que se les sigue investigando por acusaciones malintencionadas. Es por esto tan importante una reforma a la justicia que corrija las fallas en el sistema penal acusatorio, obligando a las personas que con sus testimonios participen en los juicios a que aporten pruebas de lo que dicen, bien sea a favor o en contra del acusado, porque con la simple declaración no es suficiente. Es claro que aquí hace falta una valoración uniforme de los testimonios como medio de prueba, mayor capacidad de investigación para corroborar lo dicho por los testigos o para desvirtuar sus afirmaciones, definir estándares de prueba para determinar con exactitud cuando un hecho está probado y un sistema simple y eficaz para incentivar a colaborar con la verdad y la justicia, sancionando a</t>
+  </si>
+  <si>
+    <t>he visto envuelta. Es sorprendente la cercanía de mis experiencias con las experiencias de las mujeres del reportaje y con los relatos de otras mujeres y amigas a través del tiempo. Me pareció por eso que además de ser un valiente esfuerzo de denuncia, el reportaje sirve también como un testimonio formativo para que otras mujeres vean la sutilidad con la que escala el acoso. Normalmente, el acosador nunca tiene cara de acosador y su comportamiento es a veces tan sutil que es casi imposible detectarlo en un inicio. Y, cuando se detecta, es tan ambiguo, que no se puede denunciar de inmediato. Como lo narra una de las denunciantes, de un divertido e inocente baile, el acosador logra en un par de jugadas meterse con ella en un taxi y, tras un beso fallido, tocarle insistentemente la vagina. ¿Cómo lo logra exactamente? Cuando somos adolescentes es común recibir mensajes</t>
+  </si>
+  <si>
+    <t>no es pontificar al respecto y cada caso es tan diferente como complejo de analizar. Sin embargo, sí existen patrones de conducta que nos permiten poner en duda la débil y maleable formación en valores que promueve nuestro sistema educativo; sí hay una serie de normas que no sabemos ni queremos respetar porque no somos conscientes de su importancia para vivir en comunidad. En el caso de los accidentes viales, un solo ejemplo es suficiente: se trata de la confusión que prevalece en nuestra mente en relación con las normas de tránsito. Hoy en día, son muy pocos los que pueden responder al unísono quién lleva la prioridad en un cruce donde no hay una señal de PARE; apenas unos cuantos entienden lo clave que es respetar los límites de velocidad lógicamente cuando éstos han sido colocados con criterio; sólo unos tantos han aprendido que sacar el pase significa aprender</t>
+  </si>
+  <si>
+    <t>en un futuro verano o fenómeno del Niño si no lo manejamos de forma integral? Esta lógica tiene que aplicar en la planeación y desarrollo de cualquier proyecto. Es evidente que necesitamos ser mucho más rigurosos, y construir una visión integral de las cuencas hidrográficas a intervenir. Los diseños económicos tienen que ir mas allá de las ganancias y beneficios a corto plazo y considerar aspectos como los costos por mantenimiento hasta la viabilidad de múltiples proyectos con un clima cambiante. En este momento, solo para la cuenca del río Magdalena, hay alrededor de cien posibles proyectos para nuevas represas. ¿Serán viables tantos proyectos con los extremos climáticos, y teniendo en cuenta los posibles impactos que representan para los sitios de reproducción de decenas de peces migratorios como lo ha advertido TNC? Sin duda, la hidroelectricidad es una oportunidad para el país y una fortaleza que no podemos abandonar como</t>
+  </si>
+  <si>
+    <t>Es media noche y tengo dos ríos atravesando el corazón. Ambos hablan de este país nuestro, bautizado por las balas, armado y desarmado en el afán intermitente de acabar y reconstruir los pedazos de vida que nos han quedado, expectantes, entre el suelo y el cielo. Son dos ríos que deberían ser suficientes para hacernos entender lo funesto que resultaría devolvernos a la guerra, y lo absurdo que ha sido herir los pactos de paz, como si no tuviéramos suficientes cicatrices en la historia, en la verdad y en los abrazos. Dos ríos: Río Muerto, escrito por Ricardo Silva Romero; y el río Atrato, en el que Leyner Palacios y el documental Bojayá, nos llevan a navegar por el más intenso dolor, por la resiliencia, el valor y la ternura. Hoy leí por segunda vez el libro, y vi por segunda vez el documental. Y podría seguir leyendo a Ricardo</t>
+  </si>
+  <si>
+    <t>compuestos por agua un 70,8 y 148940.000 km por tierra un 29,2 . Constituye motivo de honor para el suscrito el que la Tierra sea el tercer planeta en distancia respecto del Sol, del que se encuentra a 149597.872 kilómetros. Estamos en el podio, pues. Y hasta el momento, que se sepa, y desde hace 4.800 millones de años, somos el único lugar habitable entre millones de galaxias en los multiuniversos. Hay cuentas, sin embargo, que no me cuadran en tanta prodigalidad cósmica que me beneficia: yo, como una pieza suelta entre 7.000 millones de habitantes, debería tener, como mínimo asegurado, 85.000 m de tierra, con derecho a aguas saladas y dulces. Siendo realista, dejemos eso en 25.650 m de tierra firme, por aquello de que el planeta es 71 líquido y 29 sólido. Pero no, ni siquiera eso tengo. Y eso que mi derecho hipotético a esos m, yo</t>
+  </si>
+  <si>
+    <t>La voz de los ríos o las montañas, cuando llega a los tribunales a defender sus derechos, pasa inevitablemente por la interpretación que de ellos hagamos los humanos. El reconocimiento de agencia para los ríos, un experimento normativo que promueve un énfasis más biocéntrico en el ejercicio de las responsabilidades humanas respecto al resto del mundo, nos encontramos con un problema fundamental: los ríos dicen cosas, pero hay que saber escucharlos. La forma para llevar el mensaje de los ríos, o por defecto, de las montañas, las plantas o los animales nadie habla de los microorganismos en esos términos, es convertirnos un poco en ellos, asumir su defensa desde la perspectiva, inevitable, de humanizarlos también. En esa mutua conversión sensible y ética se basa la posibilidad de establecer una conversación que no termine siendo religiosa, una en la cual cualquiera que escuche voces en su mente asegure que tiene la</t>
+  </si>
+  <si>
+    <t>cajas de concreto que sirven para orientar el paso del agua. Un tema crítico del proyecto. Según el memorando no tienen medidas ni especificaciones de resistencia. Si esto es cierto, es increíble. Observaciones sobre los planos: carecen de información, carecen de especificaciones, no se articulan con el proceso constructivo, no están respaldados con memorias. Si esto es cierto: es imposible licitar y obtener costos reales de la obra para la adjudicación imparcial. Componente urbanismo, espacio público y accesibilidad. Los comentarios se centran en falta de especificaciones, errores o insuficiencias en el dibujo, problemas en las pendientes y los accesos a garajes de predios, no coincidencia con las cajas de inspección de servicios públicos: todo referido a técnicas de construcción y no a la filosofía del proyecto. Pero, como en todos los puntos anteriores, muestra el informe del subsecretario de Infraestructura cómo hay improvisación y falta de información para proceder a</t>
+  </si>
+  <si>
+    <t>el momento justo. En efecto, un espresso debe disfrutarse al instante porque gran parte del placer está en la espuma. Si se la deja reposar, se deshace más rápido de lo que canta un gallo, transformándose en dispersas manchas adheridas a la pared del pocillo. Nada más ácido y salino que un espresso reposado. En cambio, un espresso bien hecho se muestra cremoso, corpulento y aromático. Y pese a su menudo tamaño, es energizante, con un menor porcentaje de cafeína que los filtrados. Esto ocurre porque su contacto con el agua no supera los 20 segundos, mientras que los anteriores alcanzan la infusión ideal a los cuatro minutos. El espresso debe beberse negro, lo mismo que el ristretto un espresso más fuerte y más corto, y el lungo, un ejemplar menos encantador, que requiere adicionarle agua caliente para reducir su vigor. Otra desviación del lungo es el americano, más diluido</t>
+  </si>
+  <si>
+    <t>Nada peor que un juicio llevado a cabo sin buen juicio; sin que sea posible ver el fondo del caso, como quien mira desde arriba un depósito de agua limpia. Nada mejor que hacer las cosas de manera tal que ninguna de las partes tenga motivo para salir a reclamar que no se tuvieron en cuenta pruebas que pretendía aportar para evaluar mejor los hechos objeto del litigio. Audiatur et altera pars, decían los romanos. En palabras de hoy: que se escuche por igual a la otra parte. La justicia no es solamente asunto de estrategias y tácticas ante los tribunales, ni de consideraciones o artificios técnicos por parte de éstos para justificar sus decisiones. En el trámite de cada proceso se han de advertir con total claridad los argumentos de las partes, que deben contar con la garantía de que sus pruebas y consideraciones sean conocidas, explicadas y justificadas,</t>
+  </si>
+  <si>
+    <t>a conocer mis íntimas convicciones a través de esta columna, he sostenido sistemáticamente que la política, no solo en Colombia o América Latina sino también en los países más desarrollados, atraviesa grandes dificultades a raíz de la llegada al poder de una cantidad importante de líderes populistas y mentirosos, de derecha y de izquierda, con facilidad de convencer a las masas electorales con discursos cataclísmicos que pretenden vender la idea de que todo es un desastre, que todos los antecesores lo han hecho muy mal y que las soluciones, que por cierto las hay, solo las tienen ellos por ser poseedores de un poder mesiánico que no solo instrumenta la salvación sino que la personifica o individualiza. En ese contexto y con una población cada vez más exigente, pero al mismo tiempo más superficial y egoísta, movida y conmovida por redes sociales con mensajes manipulados y falsos, el elector de</t>
+  </si>
+  <si>
+    <t>En alguno de mis artículos califiqué como exagerada la tributación de Colombia. Pues bien, uno de mis lectores me solicitó con argumentos de fondo algunas explicaciones sobre el tema del título, porque consideraba él que la relación entre los recaudos por impuestos en Colombia y nuestro PIB, relación cercana hoy al 15, le resultaba demasiado baja comparada con las similares de la comunidad internacional. La referencia del párrafo a continuación que aparece entre comillas se puede consultar por Google digitando lo entrecomillado. No sobra advertir las grandes discrepancias en este tema entre las publicaciones en Google, debido a la falta de uniformidad sobre lo que se considera impuesto. En Revenue Statistics 2018. Tax revenue trends in the OECD se definen como impuesto todos los pagos obligatorios para todos los niveles del gobierno, sin esperar beneficios proporcionales derivados del pago sobre: Ingresos, utilidades y ganancias de capital, como impuestos sobre la</t>
+  </si>
+  <si>
+    <t>abismo del siempre, siempre, siempre. Y, por más que se estire hasta las dimensiones abracadabrantes del sinfín, no puede privarnos de la felicidad del eterno retorno de lo efímero, de lo que tiene su gloria en su pasar aparente. Es extraño que debamos pagar el privilegio de vivir con el espanto esencial del ser, que consiste en el sentimiento del deterioro inevitable de todo que lo condena a la caducidad. Ahora han regresado, es la moda de enero, los profetas y los que ponderan los porvenires. Unos, de malos augurios, plagan el futuro de ácidas sombras, cenizas amargas y recelos de cagalástimas; y los de signo positivo propalan noticias de alegrías venideras y anuncian realizaciones que estarían preparándose como pavos en los hornos de la esperanza. Cada año, los tarotistas sacan sus cartas de locos, reinas y ahorcados; los numerólogos sacuden sus ábacos, los astrólogos afilan sus compases, otros desempolvan</t>
+  </si>
+  <si>
+    <t>Un promedio de las cuatro últimas realizadas por Guarumo, Centro Nacional de Consultoría, Invamer y Yanhaas arroja como resultado: Duque 38,2 , Petro 28,6 , Fajardo 13 Vargas Lleras 7,6 .Todas coinciden en que Duque y Petro pasarían a segunda vuelta si las elecciones fueran en el momento de su realización. Fueron elaboradas para diferentes empresas, como Caracol Televisión, R.C.N, Semana, W radio y otros medios. La crítica de los candidatos Petro y Vargas Lleras puede entenderse como una respuesta natural en el fragor de la lucha electoral ante resultados, muy parecidos en todas, que consideran adversos. Pero sería inexplicable el cuestionamiento de su fundamento matemático; su capacidad de representatividad y explicación, por parte de dos ciudadanos que aspiran a convertirse en presidentes. La estadística y el cálculo de probabilidades son utilizados como herramienta de soporte por las diferentes ramas de las ciencias y no solo en el análisis político.</t>
+  </si>
+  <si>
+    <t>el fútbol moderno va mucho más allá del análisis que pueda hacer de los mismos el preparador físico. ¿Cómo hacer para que tanta información se pueda transmitir con facilidad al entrenador, el jugador, el directivo, el hincha o el periodista? En eso estamos. Consideremos el Caldas de Maturana en la Liga Águila 20172. La falta de resultados motivó su salida prematura. Pero más allá de analizar en detalle el juego del Caldas, evaluemos la tendencia en el movimiento del balón. La eterna crítica a Maturana fue el exceso de juego lateral de sus equipos. Siempre buscando posesión, ésta tendía a confundirse con falta de profundidad. La gráfica permite analizar el juego del Once Caldas y compararlo con el resto de los equipos del torneo colombiano. La cancha está dividida en 18 cuadrantes iguales. En cada cuadrante se analiza el tipo de pase que realizó un jugador. Se consideran cuatro opciones:</t>
+  </si>
+  <si>
+    <t>lo sumo hablando del gol de Yepes. La esencia del derecho a protestar está ligada a la existencia de grupos inconformes. Lo que el ministro concibe, yendo al fondo, es la idea de una sociedad unificada y homogénea. Esta noción tiene vieja raigambre. Para no ir lejos en la historia del siglo XX, basta la idea criolla de una sociedad sin fisuras. Allí encontramos a Núñez, Miguel Antonio Caro, Laureano y, claro está, José Obdulio, porque eso del Estado de opinión como mecanismo de gobernanza bebe en la misma fuente. Qué diablos con esas carajadas pluralistas. El pensamiento liberal cree, en cambio, en la sociedad multicultural, en el respeto a las ideas ajenas, en el diálogo incluyente. Abomina el fanatismo y la manipulación mediática que fomenta el populismo de derecha y de izquierda. Un pariente de esta noción es que el tal conflicto interno no existe. Se afirma que aquí</t>
+  </si>
+  <si>
+    <t>intenciones de aparecer atildado porque no lo es y no le cuadra. Urán no sólo se descacha, si se quiere decir, sino que igualmente suelta términos que escandalizan a los timoratos, aquellos especímenes sociales que detrás de su pretendida limpieza vocal esconden pecados que de verdad ofenden la sensibilidad de un país sumido en la pocilga moral que los mismos han creado desde el poder seguramente, Rigoberto hablará de mierdero. Otro encuentro que percibimos en esta simpática explosión verbal del escalador de Urrao tiene una trascendencia enorme, ya que toca a la juventud, en la que cada día se afianza más un modo desbraguetado de expresarse, sin que esta costumbre se traduzca necesariamente en conductas reprobables. Hoy, las chicas comparten con sus compañeros generacionales algunas voces democráticas que antes caracterizaban sólo a los muchachos, en una especie de ampliación del espectro de comunicación que rompe con la diferenciación entre unos</t>
+  </si>
+  <si>
+    <t>sin buscarlo, en la vocera de las atrocidades contra miles de mujeres atrapadas en cuerpos de hombre que la mal llamada sociedad normal masculina repudia, pero que las necesita y les teme. Y los gobiernos guardan silencio ante esos asesinatos anónimos. Camila sonríe en las entrevistas, pero también admite que está llena de rabia por tantas injusticias. Sabe muy bien que ahora la buscan y la aplauden, sabe que está linda, esplendorosa, y que esa gloria no durará para siempre. Está trabajando para tener cómo vivir plenamente y guardar para cuando caiga el telón. Posdata. Las malas, una novelatestimonio que estremece y revela ese universo misterioso lleno de ternura y horrores que se esconde tras los maquillajes y vestimentas provocadoras, donde deambulan mujeres frágiles y vulnerables, feroces e invencibles, unidas contra un mundo hostil que se resiste a reconocer sus derechos y su dignidad. contra un mundo hostil que se resiste a reconocer sus derechos y su dignidad.</t>
+  </si>
+  <si>
+    <t>estigmas por otras versiones del divertimento sin que los bebedores ocasionales fueran tildados de alcohólicos. Aunque lo quieran negar, y aduzcan razones comparativas entre los efectos de cada psicoactivo, la historia es exactamente la misma, y el pulso entre la obstinación y las evidencias tendrá el mismo final y el mismo destino: la legalización y la regulación pública de sus excesos. Mientas tanto, todos los muertos que caigan en la lucha esquizoide contra los suburbios adinerados serán muertos inútiles, cuerpos del absurdo acumulados por la custodia romántica de un paraíso moral sin drogas ilícitas, aunque brinden con las lícitas los resultados de una guerra sin fin. Los peces gordos entregados en los partes positivos de la Policía siempre serán reemplazados por los peones de un juego que tiene el combustible exclusivamente en su demanda. Los consumidores serán siempre los mismos aunque tengan que comprar su dosis en la sombra o</t>
+  </si>
+  <si>
+    <t>y desenmascara a los topos dentro de la comandancia del Circus. Hazlos tragar la soberbia y la hipocresía de sus actos. No dejes piedra sobre piedra del socialimperialismo soviético. Escúpelos, si es preciso. Ay, Smiley, no me dejes. Inspírame. Inspira a los escribidores del mundo entero, ansiosos de tu sabiduría. Enséñanos a escribir como escribía tu amo y señor, David John Moore Cornwell: claro, directo, categórico. Sin filigranas de heterosexuales en apuros ni trucos de tuiteras de medio pelo. No te vayas nunca. Ayúdanos a esquivar los adjetivos y adverbios innecesarios. Guíanos en el combate contra el abominable que galicado. Tú no escribías, es cierto. Pero cuando leo las venturas y desventuras de tu vida en las sombras, siempre termino de rodillas ante la prodigiosa habilidad narrativa de tu padre, Cornwell de Cornualles. George de los Georges, no te vayas nunca, por favor. Ánclate a los anaqueles de mi ya</t>
+  </si>
+  <si>
+    <t>Salvo por una o dos ocasiones de extraña abstracción, Hardy nunca explica sus ironías; si la literatura es un juego para el escritor, bien puede serlo también para el lector. Así ocurre más adelante con Angel Clare, un joven cuyo destino era el sacerdocio. Al rehusar el oficio paternal, Clare, que hasta entonces se educaba en los libros, opta por internarse como aprendiz en una granja en donde se topa con Tess. Es un joven con ansias de intelectual que ahora se ocupa de ordeñar vacas. Años atrás se habían encontrado en un baile, aunque sólo Tess parece recordarlo. En el momento en que ambos coinciden en la granja, sin embargo, las condiciones son casi opuestas: años atrás, Tess era una joven que desconocía casi todo del mundo y ahora, tras una serie de percances y desgracias, ha tensado su carácter. Clare es el destinatario adecuado de su madurez. Comienzan</t>
+  </si>
+  <si>
+    <t>en este coma diabético? Los senadores más inteligentes del Congreso, mejores oradores y odiadores de Néstor Humberto Martínez, organizaron un debate de 9 horas para llevar a la gente a concluir que la autoridad es la mala, y que si no hubiera ocurrido jamás este supuesto entrampamiento, óiganme ustedes, no habría disidencias de las Farc. Las disidencias existen porque existe el narcotráfico. No porque Néstor Humberto Martínez, supuesto enemigo de la paz, se las inventó para desacreditar el proceso. Allá están y, por ahora, allá se quedan. Entre tanto... Resumen de Petro: todo esto no fueron sino unas conversaciones de la DEA con la DEA. Y el pobre cieguito, ahí...</t>
+  </si>
+  <si>
+    <t>Pasan los años y uno comienza a perder la capacidad de riesgo. Poco a poco se toma la mente el miedo a perderlo todo: dinero, prestigio, trabajo, lo que sea. Al comienzo, la vida era un juego; después, las cosas que nos gustaban más se convirtieron en sueños y al quererlos hacer realidad llegaron las responsabilidades. Después llega la hora de trabajar, las deudas, sacar a los hijos adelante. En fin, la vida pasa y la presión aumenta. Ya no es tan divertido. Como hincha del fútbol es lo mismo. Primero era jugar a ser el ídolo del equipo amado en el parque del barrio. En la adolescencia comienzan a doler los clásicos que se pierden por cuenta de las burlas de los crueles seguidores del rival. Yo preferí hacerme el enfermo para no ir al colegio el lunes aquel después del 7 a 3 de Santa Fe a Millos</t>
+  </si>
+  <si>
+    <t>¿pero quién se atreve a decirlo? ¿O será simplemente porque la mayoría de los analistas y columnistas nos dedicamos a manipular palabras yo números, y entonces podemos mantener en este período el grueso de nuestra rutina de trabajo y por consiguiente al menos parte de la estructura de nuestra vida cotidiana? Pero el trabajo manual y también mucho del trabajo de conectar a las personas basta con pensar en los llamados call centers es imposible, o muy difícil, de llevar a cabo a distancia. La cohabitación forzada aun en las condiciones ideales con amor y sopa puede ser difícil para muchos. Con hambre, con miedo, puede resultar dura, incluso insoportable. Después vendrán las buenas almas lamentando la intolerancia de personas asustadas y perdidas cogiéndose a tortazos entre sí Claro, que esto se convierta en un drama de proporciones depende de la duración de la crisis. Pero esta puede ser mucho</t>
+  </si>
+  <si>
+    <t>tanto, están los dueños de los recursos y sus títeres en los Estados nacionales, raspando la olla de lo que queda en la biósfera terrestre muchos ya tienen sus búnkeres de preppers o preparacionistas. Y está también la masa amorfa de los hipnotizados, apegados a sus comodidades inmediatas, sin mayor idea de lo que sucede más allá de sus narices, liderados por personajes como Trump. El mejor de los escenarios posibles sería, desde luego, un cambio gradual hacia la conciencia del entorno y el papel de la especie humana en el planeta muy bien guiados por los paneles de expertos, las inversiones en educación, las reformas agrarias con énfasis en la diversificación de los cultivos, la protección a ultranza del agua, la reconexión espiritual con esta tierra y las economías solidarias, entre otras. Pero el drama es el tiempo, que se agota. 875790 20190813T00:00:5405:00 column 20190813T00:15:0105:00 jrincon1275 none 15:03:22:19:33 14 solidarias, entre otras. Pero el drama es el tiempo, que se agota. 875790 20190813T00:00:5405:00 column 20190813T00:15:0105:00 jrincon1275 none 15:03:22:19:33 14 3688 3702</t>
+  </si>
+  <si>
+    <t>ecológico, equivalente a un cataclismo que hubiera bloqueado el Cauca, algo que seguramente habrá sucedido en el pasado innumerables veces pero nunca con la presencia de gente, que se asentó en sus riberas hace apenas 12.000 o 15.000 años, aprovechando la riqueza de sus planicies de inundación, sus recursos biológicos, el agua y el calor. Al final, en la escala más distante, se ubica el manejo de un ecosistema que entra en una etapa de restablecimiento de su complejidad mediante un proceso sucesional que no conocemos: no hay referentes acerca de la manera ni tiempos en los que un río de tal envergadura retoma su funcionalidad biológica, aunque sí tenemos algo de información del efecto de otras grandes represas en condiciones similares Betania, por ejemplo. La palabra clave para evaluar la capacidad de recuperación del río y las posibilidades de utilizar el conocimiento de las comunidades locales o de la</t>
+  </si>
+  <si>
+    <t>nota de alerta. Las crisis humanitarias se resuelven con humanitarismo, no con balazos. En el pasado miles de colombianos fueron a buscarse la comida en Venezuela porque en el país escaseaba. Ahora son los venezolanos los que tienen problemas. Cuando llegaron los ricos de Venezuela comprando apartamentos y ofreciendo negocios, los mercachifles colombianos se frotaban las manos. Ahora que llegan los pobres ponen el grito en el cielo. ¡Hipócritas! Propaganda: les invito a leer mi libro Descansen Armas de Editorial Icono, lanzado en la penúltima FilBo, un ensayo anecdótico sobre la guerra. Quizá la lectura del libro les haga pensar un poco antes de alistarse para el combate.</t>
+  </si>
+  <si>
+    <t>La forma como algunas comunidades indígenas adelantan el llamado proceso de liberación de la madre tierra está convirtiendo al Norte del Cauca en un territorio hostil. Un grupo indígena está planteando un proceso de afirmación de sus derechos a costa de violar la ley; invadiendo la propiedad privada, bloqueando vías, generando pérdidas económicas, irrespetando a la fuerza pública Y más lamentable, ocasionando irrecuperables pérdidas humanas. Para este grupo indígena la liberación de la madre tierra se traduce en usurpar tierras privadas y hacer posesión de ellas para luego reclamarlas. Lo que no se ha dicho, es que la liberación de la madre tierra para la gran mayoría de los grupos indígenas, se entiende como: cambiar prácticas agrícolas por unas más sostenibles y amigables con la naturaleza, es sembrar comida y no cultivos ilícitos, es proteger los recursos naturales sin renunciar al desarrolloEso es liberación, es proteger la tierra para las</t>
+  </si>
+  <si>
+    <t>su subsistencia depende de los recursos del turismo, actividad que se tomará su tiempo en llegar y recobrar los flujos de años anteriores. San Andrés, Providencia y Santa Catalina, y los demás cayos e islas que conforman el archipiélago, han perdido más de 11.000 millones de pesos durante esta emergencia sanitaria, tienen la ocupación hotelera en ceros y sufren parálisis en la circulación de dinero por falta de servicios y alternativas laborales. Los créditos anunciados por el Gobierno han cobijado a menos del 1 de los empresarios, porque los banqueros como sucede en todo el país se abstienen de otorgarlos, por considerar que el turismo el nuevo petróleo colombiano, según el presidente Duque es un sector de alto riesgo. No son fáciles, pues, los tiempos que se viven en San Andrés, donde no hay huéspedes para los hoteles ni comensales para los restaurantes ni compradores para los locales comerciales. Los</t>
+  </si>
+  <si>
+    <t>ríos agravando así el problema ambiental. O mire a las comunidades de Bolívar que se han visto desplazadas de sus tierras para sembrar palma, un monocultivo responsable de gran cantidad de gases de efecto invernadero y cuyo aceite está presente en gran número de productos ultraprocesados. En esta pesadilla, el reporte recomienda crear políticas e incentivos que promuevan un sistema alimentario donde la producción, el consumo y todos los pasos de la cadena sean más responsables; redireccionar los subsidios de la agricultura extensiva a otras formas más sostenibles; poner etiquetados más claros a los productos ultraprocesados, además de acciones individuales para reducir nuestro consumo de carne y nuestra huella ambiental. Pero crear políticas no es cosa fácil. El informe señala que el sistema alimentario actual está en manos de unas pocas industrias que, con frecuencia, logran hacerse al poder económico y político impidiendo dichos cambios. En Colombia tenemos sobrados ejemplos pocas industrias que, con frecuencia, logran hacerse al poder económico y político impidiendo dichos cambios. En Colombia tenemos sobrados ejemplos de cómo las tácticas de ciertas industrias han terminado por limitar intentos de regulación en favor de la salud o el ambiente. Necesitamos medidas para impedir que estas industrias determinen la política pública y el futuro alimentario del planeta. Lo que está en juego es demasiado importante como para ser decidido solo por el bolsillo de unos pocos.</t>
+  </si>
+  <si>
+    <t>generan su propia energía, mediante paneles solares, con excedentes que son almacenados en baterías gigantescas, que tienen la capacidad de venderlos a las empresas distribuidoras de energía. La información que producen los sensores de cada una de las bicicletas inteligentes o de las casas y edificios que generan energía solar, transmiten las coordenadas de los ciclistas, el consumo de los electrodomésticos y otra infinidad de teras de datos a servidores de la nube de la información, conectando a la gente con bicicletas, calles y casas, en una inmensa comunidad del internet de las cosas, inimaginable hasta hace pocos años. Con la ayuda de la llamada inteligencia artificial, se analiza esa información grande big data para encontrar tendencias, correlaciones, para balancear la oferta y la demanda, maximizar usos y para alertar sobre problemas potenciales. Esta es una verdadera revolución tecnológica y de la información que ya está sucediendo a ritmos vertiginosos</t>
   </si>
   <si>
     <t>Ciencias_ambientales_ingenieria</t>
@@ -825,7 +809,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -835,14 +819,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -885,12 +861,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1195,16 +1170,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="55.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="38.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-    <col min="6" max="6" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1224,623 +1200,621 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="E2">
-        <v>0.30285468697547913</v>
+        <v>0.43999242782592768</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>227</v>
+        <v>126</v>
       </c>
       <c r="D3" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="E3">
-        <v>0.30288761854171747</v>
+        <v>0.46253371238708502</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>188</v>
+        <v>127</v>
       </c>
       <c r="D4" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="E4">
-        <v>0.3028990626335144</v>
+        <v>0.42820209264755249</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>174</v>
+        <v>128</v>
       </c>
       <c r="D5" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E5">
-        <v>0.30338847637176508</v>
+        <v>0.53189879655838013</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="D6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E6">
-        <v>0.30555307865142822</v>
+        <v>0.50138282775878906</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="D7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E7">
+        <v>0.53881597518920898</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" t="s">
+        <v>244</v>
+      </c>
+      <c r="E8">
+        <v>0.43581840395927429</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E9">
+        <v>0.44615110754966741</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" t="s">
+        <v>245</v>
+      </c>
+      <c r="E10">
+        <v>0.4204094409942627</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" t="s">
+        <v>245</v>
+      </c>
+      <c r="E11">
+        <v>0.40539336204528809</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12">
+        <v>0.43449768424034119</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" t="s">
+        <v>245</v>
+      </c>
+      <c r="E13">
+        <v>0.41191554069519037</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" t="s">
+        <v>245</v>
+      </c>
+      <c r="E14">
+        <v>0.5529942512512207</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D15" t="s">
+        <v>245</v>
+      </c>
+      <c r="E15">
+        <v>0.41316458582878107</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" t="s">
         <v>246</v>
       </c>
-      <c r="E7">
-        <v>0.30923807621002197</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="E16">
+        <v>0.41711068153381348</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>2</v>
       </c>
-      <c r="B8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" t="s">
-        <v>212</v>
-      </c>
-      <c r="D8" t="s">
-        <v>256</v>
-      </c>
-      <c r="E8">
-        <v>0.30952203273773188</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" t="s">
-        <v>225</v>
-      </c>
-      <c r="D9" t="s">
-        <v>258</v>
-      </c>
-      <c r="E9">
-        <v>0.31011861562728882</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" t="s">
-        <v>211</v>
-      </c>
-      <c r="D10" t="s">
-        <v>256</v>
-      </c>
-      <c r="E10">
-        <v>0.31055963039398188</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>0</v>
-      </c>
-      <c r="B11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C11" t="s">
-        <v>235</v>
-      </c>
-      <c r="D11" t="s">
-        <v>259</v>
-      </c>
-      <c r="E11">
-        <v>0.31210392713546747</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>1</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>194</v>
-      </c>
-      <c r="D12" t="s">
-        <v>253</v>
-      </c>
-      <c r="E12">
-        <v>0.3129977285861969</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>0</v>
-      </c>
-      <c r="B13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" t="s">
-        <v>223</v>
-      </c>
-      <c r="D13" t="s">
-        <v>258</v>
-      </c>
-      <c r="E13">
-        <v>0.31372508406639099</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>0</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" t="s">
-        <v>164</v>
-      </c>
-      <c r="D14" t="s">
-        <v>249</v>
-      </c>
-      <c r="E14">
-        <v>0.3138694167137146</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>1</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>152</v>
-      </c>
-      <c r="D15" t="s">
-        <v>247</v>
-      </c>
-      <c r="E15">
-        <v>0.31488192081451422</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>4</v>
-      </c>
-      <c r="B16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C16" t="s">
-        <v>215</v>
-      </c>
-      <c r="D16" t="s">
-        <v>256</v>
-      </c>
-      <c r="E16">
-        <v>0.31491321325302118</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>0</v>
-      </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D17" t="s">
         <v>246</v>
       </c>
       <c r="E17">
-        <v>0.31569156050682068</v>
+        <v>0.44951805472373962</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="D18" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E18">
-        <v>0.31609156727790833</v>
+        <v>0.41205739974975591</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>213</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="E19">
-        <v>0.3172646164894104</v>
+        <v>0.42998379468917852</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D20" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E20">
-        <v>0.31784769892692571</v>
+        <v>0.45400810241699219</v>
       </c>
       <c r="F20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E21">
-        <v>0.3181302547454834</v>
+        <v>0.41567906737327581</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="D22" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E22">
-        <v>0.31824862957000732</v>
+        <v>0.51365065574645996</v>
       </c>
       <c r="F22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D23" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E23">
-        <v>0.31878894567489618</v>
+        <v>0.40782058238983149</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
-      <c r="H23" s="2"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D24" t="s">
         <v>247</v>
       </c>
       <c r="E24">
-        <v>0.31889474391937261</v>
+        <v>0.44905239343643188</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D25" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E25">
-        <v>0.32086771726608282</v>
+        <v>0.43663865327835077</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E26">
-        <v>0.32117217779159551</v>
+        <v>0.43974250555038452</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="D27" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E27">
-        <v>0.32132202386856079</v>
+        <v>0.4041208028793335</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>208</v>
+        <v>151</v>
       </c>
       <c r="D28" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="E28">
-        <v>0.32220551371574402</v>
+        <v>0.50240278244018555</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="D29" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E29">
-        <v>0.32376304268836981</v>
+        <v>0.46518519520759583</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>193</v>
+        <v>153</v>
       </c>
       <c r="D30" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E30">
-        <v>0.3252767026424408</v>
+        <v>0.45003560185432429</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D31" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E31">
-        <v>0.32566091418266302</v>
+        <v>0.47337266802787781</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="D32" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E32">
-        <v>0.32715612649917603</v>
+        <v>0.44730022549629211</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1848,19 +1822,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>226</v>
+        <v>156</v>
       </c>
       <c r="D33" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="E33">
-        <v>0.32756343483924871</v>
+        <v>0.43223181366920471</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1871,16 +1845,16 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>231</v>
+        <v>157</v>
       </c>
       <c r="D34" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E34">
-        <v>0.32763266563415527</v>
+        <v>0.40417447686195368</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1888,19 +1862,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="D35" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E35">
-        <v>0.32852053642272949</v>
+        <v>0.42976480722427368</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1908,19 +1882,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="D36" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E36">
-        <v>0.32907006144523621</v>
+        <v>0.40277457237243652</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1928,19 +1902,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="D37" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E37">
-        <v>0.32943156361579901</v>
+        <v>0.44794049859046942</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1948,19 +1922,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="D38" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E38">
-        <v>0.32986998558044428</v>
+        <v>0.45302021503448492</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1968,19 +1942,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="D39" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E39">
-        <v>0.33017921447753912</v>
+        <v>0.41291722655296331</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1988,19 +1962,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>236</v>
+        <v>163</v>
       </c>
       <c r="D40" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="E40">
-        <v>0.33049038052558899</v>
+        <v>0.41848501563072199</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2008,19 +1982,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="D41" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E41">
-        <v>0.33191317319870001</v>
+        <v>0.46362414956092829</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2031,16 +2005,16 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D42" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E42">
-        <v>0.33337926864624018</v>
+        <v>0.4253973662853241</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2048,39 +2022,39 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D43" t="s">
         <v>249</v>
       </c>
       <c r="E43">
-        <v>0.33365905284881592</v>
+        <v>0.50531971454620361</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="D44" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E44">
-        <v>0.3344176709651947</v>
+        <v>0.44197601079940801</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2088,19 +2062,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="D45" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E45">
-        <v>0.33679249882698059</v>
+        <v>0.43562495708465582</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2108,39 +2082,39 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="D46" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E46">
-        <v>0.33836829662322998</v>
+        <v>0.40756577253341669</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>228</v>
+        <v>170</v>
       </c>
       <c r="D47" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E47">
-        <v>0.33931940793991089</v>
+        <v>0.40279790759086609</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -2148,19 +2122,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="D48" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E48">
-        <v>0.33937594294548029</v>
+        <v>0.46315619349479681</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2168,19 +2142,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>224</v>
+        <v>172</v>
       </c>
       <c r="D49" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E49">
-        <v>0.34049424529075623</v>
+        <v>0.47312274575233459</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2188,19 +2162,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="D50" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E50">
-        <v>0.34087282419204712</v>
+        <v>0.40127909183502197</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2211,16 +2185,16 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>233</v>
+        <v>174</v>
       </c>
       <c r="D51" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="E51">
-        <v>0.34117871522903442</v>
+        <v>0.46104267239570618</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2228,19 +2202,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B52" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>232</v>
+        <v>175</v>
       </c>
       <c r="D52" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="E52">
-        <v>0.34125250577926641</v>
+        <v>0.41867074370384222</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2248,39 +2222,39 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="D53" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E53">
-        <v>0.34303241968154907</v>
+        <v>0.56203490495681763</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D54" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E54">
-        <v>0.3463892936706543</v>
+        <v>0.48925957083702087</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2288,19 +2262,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B55" t="s">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="D55" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E55">
-        <v>0.34774243831634521</v>
+        <v>0.41412928700447083</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2308,19 +2282,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="D56" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E56">
-        <v>0.35073792934417719</v>
+        <v>0.4065936803817749</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2328,19 +2302,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="D57" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="E57">
-        <v>0.35236743092536932</v>
+        <v>0.40215909481048578</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2348,19 +2322,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D58" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E58">
-        <v>0.356423020362854</v>
+        <v>0.40184247493743902</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2368,19 +2342,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B59" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>242</v>
+        <v>182</v>
       </c>
       <c r="D59" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="E59">
-        <v>0.35646113753318792</v>
+        <v>0.48330262303352362</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -2388,39 +2362,39 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="D60" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="E60">
-        <v>0.35748207569122309</v>
+        <v>0.47308537364006042</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D61" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E61">
-        <v>0.35787594318389893</v>
+        <v>0.42696177959442139</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -2428,39 +2402,39 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="D62" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E62">
-        <v>0.3587874174118042</v>
+        <v>0.45117861032485962</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="D63" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E63">
-        <v>0.36000293493270868</v>
+        <v>0.43266481161117548</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -2468,19 +2442,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B64" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D64" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E64">
-        <v>0.36344796419143682</v>
+        <v>0.41612717509269709</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2491,36 +2465,36 @@
         <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="D65" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E65">
-        <v>0.36435589194297791</v>
+        <v>0.4172598123550415</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="D66" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="E66">
-        <v>0.36625263094902039</v>
+        <v>0.45297509431838989</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -2531,36 +2505,36 @@
         <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="D67" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E67">
-        <v>0.36714130640029907</v>
+        <v>0.45021158456802368</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="D68" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E68">
-        <v>0.36835569143295288</v>
+        <v>0.50900977849960327</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2568,19 +2542,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="D69" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="E69">
-        <v>0.37140044569969177</v>
+        <v>0.43221721053123469</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -2591,56 +2565,56 @@
         <v>1</v>
       </c>
       <c r="B70" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="D70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E70">
-        <v>0.37142333388328552</v>
+        <v>0.41063153743743902</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="D71" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E71">
-        <v>0.37323826551437378</v>
+        <v>0.48053571581840521</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B72" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="D72" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E72">
-        <v>0.37378004193305969</v>
+        <v>0.46616789698600769</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -2651,16 +2625,16 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="D73" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E73">
-        <v>0.37567681074142462</v>
+        <v>0.43825662136077881</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -2668,19 +2642,19 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D74" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E74">
-        <v>0.37611019611358643</v>
+        <v>0.46027138829231262</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2688,19 +2662,19 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B75" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="D75" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E75">
-        <v>0.37842446565628052</v>
+        <v>0.42180317640304571</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -2708,19 +2682,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="D76" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E76">
-        <v>0.37914210557937622</v>
+        <v>0.41760203242301941</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -2728,19 +2702,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B77" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="D77" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E77">
-        <v>0.38409543037414551</v>
+        <v>0.40824753046035772</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -2748,19 +2722,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B78" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="D78" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="E78">
-        <v>0.38466641306877142</v>
+        <v>0.41642993688583368</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2771,16 +2745,16 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="D79" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E79">
-        <v>0.3874945342540741</v>
+        <v>0.4116491973400116</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -2788,19 +2762,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B80" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="D80" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E80">
-        <v>0.388082355260849</v>
+        <v>0.50876307487487793</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -2808,19 +2782,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B81" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="D81" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E81">
-        <v>0.39499866962432861</v>
+        <v>0.46482911705970759</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -2828,59 +2802,59 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B82" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="D82" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E82">
-        <v>0.396065354347229</v>
+        <v>0.41679781675338751</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B83" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="D83" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E83">
-        <v>0.39902323484420782</v>
+        <v>0.40763267874717712</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B84" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="D84" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E84">
-        <v>0.40012836456298828</v>
+        <v>0.43168851733207703</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -2888,19 +2862,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B85" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="D85" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E85">
-        <v>0.40338101983070368</v>
+        <v>0.45425736904144293</v>
       </c>
       <c r="F85">
         <v>1</v>
@@ -2911,16 +2885,16 @@
         <v>1</v>
       </c>
       <c r="B86" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D86" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E86">
-        <v>0.40373110771179199</v>
+        <v>0.51298803091049194</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -2928,19 +2902,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="D87" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E87">
-        <v>0.4061751663684845</v>
+        <v>0.43567174673080439</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -2948,62 +2922,62 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B88" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>156</v>
+        <v>211</v>
       </c>
       <c r="D88" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="E88">
-        <v>0.40690386295318598</v>
+        <v>0.40702453255653381</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B89" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>169</v>
+        <v>212</v>
       </c>
       <c r="D89" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E89">
-        <v>0.40735501050949102</v>
+        <v>0.46923252940177917</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B90" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>166</v>
+        <v>213</v>
       </c>
       <c r="D90" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="E90">
-        <v>0.40882998704910278</v>
+        <v>0.41908115148544312</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -3011,16 +2985,16 @@
         <v>1</v>
       </c>
       <c r="B91" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D91" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E91">
-        <v>0.40996921062469482</v>
+        <v>0.40424668788909912</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -3028,22 +3002,22 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="D92" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E92">
-        <v>0.41141730546951288</v>
+        <v>0.45938310027122498</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3051,36 +3025,36 @@
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="D93" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E93">
-        <v>0.41274932026863098</v>
+        <v>0.48334640264511108</v>
       </c>
       <c r="F93">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>130</v>
+        <v>217</v>
       </c>
       <c r="D94" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="E94">
-        <v>0.41716641187667852</v>
+        <v>0.41065192222595209</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -3088,19 +3062,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="D95" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E95">
-        <v>0.41907218098640442</v>
+        <v>0.45696890354156489</v>
       </c>
       <c r="F95">
         <v>1</v>
@@ -3111,116 +3085,116 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="D96" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E96">
-        <v>0.42128551006317139</v>
+        <v>0.46000951528549189</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>138</v>
+        <v>220</v>
       </c>
       <c r="D97" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E97">
-        <v>0.43343073129653931</v>
+        <v>0.45503976941108698</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B98" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>154</v>
+        <v>221</v>
       </c>
       <c r="D98" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E98">
-        <v>0.43909537792205811</v>
+        <v>0.40014457702636719</v>
       </c>
       <c r="F98">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D99" t="s">
         <v>257</v>
       </c>
       <c r="E99">
-        <v>0.44207236170768738</v>
+        <v>0.41766142845153809</v>
       </c>
       <c r="F99">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B100" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>163</v>
+        <v>223</v>
       </c>
       <c r="D100" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="E100">
-        <v>0.44289156794548029</v>
+        <v>0.42363575100898743</v>
       </c>
       <c r="F100">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>147</v>
+        <v>224</v>
       </c>
       <c r="D101" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E101">
-        <v>0.45168942213058472</v>
+        <v>0.44689995050430298</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -3228,39 +3202,39 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D102" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E102">
-        <v>0.45438504219055181</v>
+        <v>0.44875320792198181</v>
       </c>
       <c r="F102">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>137</v>
+        <v>226</v>
       </c>
       <c r="D103" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="E103">
-        <v>0.46032357215881348</v>
+        <v>0.47130924463272089</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -3271,56 +3245,56 @@
         <v>1</v>
       </c>
       <c r="B104" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>171</v>
+        <v>227</v>
       </c>
       <c r="D104" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E104">
-        <v>0.46062076091766357</v>
+        <v>0.44987413287162781</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>132</v>
+        <v>228</v>
       </c>
       <c r="D105" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="E105">
-        <v>0.46105465292930597</v>
+        <v>0.40533304214477539</v>
       </c>
       <c r="F105">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B106" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="D106" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E106">
-        <v>0.47672468423843378</v>
+        <v>0.44943851232528692</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -3328,162 +3302,162 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B107" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>143</v>
+        <v>230</v>
       </c>
       <c r="D107" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="E107">
-        <v>0.47949668765068049</v>
+        <v>0.45382058620452881</v>
       </c>
       <c r="F107">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B108" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="D108" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E108">
-        <v>0.48057866096496582</v>
+        <v>0.4658108651638031</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B109" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="D109" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E109">
-        <v>0.48205530643463129</v>
+        <v>0.43964973092079163</v>
       </c>
       <c r="F109">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B110" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D110" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E110">
-        <v>0.48567155003547668</v>
+        <v>0.42659205198287958</v>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B111" t="s">
-        <v>41</v>
+        <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>160</v>
+        <v>234</v>
       </c>
       <c r="D111" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="E111">
-        <v>0.48617047071456909</v>
+        <v>0.40218445658683782</v>
       </c>
       <c r="F111">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D112" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E112">
-        <v>0.49779218435287481</v>
+        <v>0.43326705694198608</v>
       </c>
       <c r="F112">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B113" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="D113" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E113">
-        <v>0.50020062923431396</v>
+        <v>0.42127442359924322</v>
       </c>
       <c r="F113">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B114" t="s">
-        <v>22</v>
+        <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>141</v>
+        <v>237</v>
       </c>
       <c r="D114" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="E114">
-        <v>0.50044900178909302</v>
+        <v>0.42329484224319458</v>
       </c>
       <c r="F114">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
@@ -3491,59 +3465,59 @@
         <v>1</v>
       </c>
       <c r="B115" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>151</v>
+        <v>238</v>
       </c>
       <c r="D115" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="E115">
-        <v>0.50217521190643311</v>
+        <v>0.5398324728012085</v>
       </c>
       <c r="F115">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B116" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="D116" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="E116">
-        <v>0.50781267881393433</v>
+        <v>0.41119906306266779</v>
       </c>
       <c r="F116">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>29</v>
+        <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>148</v>
+        <v>240</v>
       </c>
       <c r="D117" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="E117">
-        <v>0.51549053192138672</v>
+        <v>0.40443113446235662</v>
       </c>
       <c r="F117">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
@@ -3551,39 +3525,39 @@
         <v>2</v>
       </c>
       <c r="B118" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>129</v>
+        <v>241</v>
       </c>
       <c r="D118" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="E118">
-        <v>0.5269666314125061</v>
+        <v>0.44581064581871033</v>
       </c>
       <c r="F118">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B119" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="D119" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E119">
-        <v>0.54201674461364746</v>
+        <v>0.49317476153373718</v>
       </c>
       <c r="F119">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -3591,27 +3565,22 @@
         <v>1</v>
       </c>
       <c r="B120" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="D120" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E120">
-        <v>0.54660415649414063</v>
+        <v>0.46563950181007391</v>
       </c>
       <c r="F120">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F120" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F120">
-      <sortCondition ref="E1:E120"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/results/seleccion_umbral_etiquetado.xlsx
+++ b/data/results/seleccion_umbral_etiquetado.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karen\Documents\HumanidadesDigitales_git\data\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224DF34E-35A4-4093-B9E0-3E7B73F752D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6023252C-B268-4D69-9A23-C4F8E5FFC97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$171</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="363">
   <si>
     <t>chunk_id</t>
   </si>
@@ -40,718 +43,1024 @@
     <t>valido_ciencia</t>
   </si>
   <si>
-    <t>10740_2</t>
-  </si>
-  <si>
-    <t>13523_2</t>
-  </si>
-  <si>
-    <t>12676_3</t>
-  </si>
-  <si>
-    <t>1757_5</t>
-  </si>
-  <si>
-    <t>11591_1</t>
-  </si>
-  <si>
-    <t>897_2</t>
-  </si>
-  <si>
-    <t>12652_1</t>
-  </si>
-  <si>
-    <t>6472_1</t>
-  </si>
-  <si>
-    <t>11508_2</t>
-  </si>
-  <si>
-    <t>7983_1</t>
-  </si>
-  <si>
-    <t>3973_2</t>
-  </si>
-  <si>
-    <t>3290_3</t>
-  </si>
-  <si>
-    <t>5097_3</t>
-  </si>
-  <si>
-    <t>675_1</t>
-  </si>
-  <si>
-    <t>7823_2</t>
-  </si>
-  <si>
-    <t>12496_2</t>
-  </si>
-  <si>
-    <t>627_2</t>
-  </si>
-  <si>
-    <t>12606_3</t>
-  </si>
-  <si>
-    <t>10749_4</t>
-  </si>
-  <si>
-    <t>13314_3</t>
-  </si>
-  <si>
-    <t>7543_3</t>
-  </si>
-  <si>
-    <t>10792_1</t>
+    <t>3329_0</t>
+  </si>
+  <si>
+    <t>9121_2</t>
+  </si>
+  <si>
+    <t>2996_2</t>
+  </si>
+  <si>
+    <t>13298_8</t>
+  </si>
+  <si>
+    <t>1088_3</t>
+  </si>
+  <si>
+    <t>8439_3</t>
+  </si>
+  <si>
+    <t>11851_1</t>
+  </si>
+  <si>
+    <t>9189_0</t>
+  </si>
+  <si>
+    <t>9776_4</t>
+  </si>
+  <si>
+    <t>2822_3</t>
+  </si>
+  <si>
+    <t>11137_2</t>
+  </si>
+  <si>
+    <t>2175_1</t>
+  </si>
+  <si>
+    <t>7793_0</t>
+  </si>
+  <si>
+    <t>9466_1</t>
+  </si>
+  <si>
+    <t>5078_0</t>
+  </si>
+  <si>
+    <t>951_0</t>
+  </si>
+  <si>
+    <t>11772_3</t>
+  </si>
+  <si>
+    <t>5706_1</t>
+  </si>
+  <si>
+    <t>5747_1</t>
+  </si>
+  <si>
+    <t>1836_2</t>
+  </si>
+  <si>
+    <t>4815_4</t>
+  </si>
+  <si>
+    <t>4_2</t>
+  </si>
+  <si>
+    <t>3734_1</t>
+  </si>
+  <si>
+    <t>4822_2</t>
+  </si>
+  <si>
+    <t>3031_2</t>
+  </si>
+  <si>
+    <t>4770_3</t>
+  </si>
+  <si>
+    <t>2036_0</t>
+  </si>
+  <si>
+    <t>11701_1</t>
+  </si>
+  <si>
+    <t>517_0</t>
+  </si>
+  <si>
+    <t>2172_1</t>
+  </si>
+  <si>
+    <t>8615_0</t>
+  </si>
+  <si>
+    <t>2415_0</t>
+  </si>
+  <si>
+    <t>9039_5</t>
+  </si>
+  <si>
+    <t>9039_4</t>
+  </si>
+  <si>
+    <t>13524_1</t>
+  </si>
+  <si>
+    <t>3835_2</t>
   </si>
   <si>
     <t>8896_3</t>
   </si>
   <si>
-    <t>9734_1</t>
-  </si>
-  <si>
-    <t>9121_1</t>
-  </si>
-  <si>
-    <t>13422_0</t>
-  </si>
-  <si>
-    <t>4712_2</t>
-  </si>
-  <si>
-    <t>1802_2</t>
-  </si>
-  <si>
-    <t>2824_2</t>
-  </si>
-  <si>
-    <t>7395_2</t>
-  </si>
-  <si>
-    <t>13045_0</t>
-  </si>
-  <si>
-    <t>2753_1</t>
-  </si>
-  <si>
-    <t>4319_0</t>
-  </si>
-  <si>
-    <t>883_3</t>
-  </si>
-  <si>
-    <t>9751_3</t>
-  </si>
-  <si>
-    <t>11919_1</t>
-  </si>
-  <si>
-    <t>9907_3</t>
-  </si>
-  <si>
-    <t>6352_0</t>
-  </si>
-  <si>
-    <t>3833_0</t>
-  </si>
-  <si>
-    <t>10419_0</t>
-  </si>
-  <si>
-    <t>6211_0</t>
-  </si>
-  <si>
-    <t>3626_2</t>
-  </si>
-  <si>
-    <t>9684_3</t>
-  </si>
-  <si>
-    <t>1730_2</t>
-  </si>
-  <si>
-    <t>8012_0</t>
-  </si>
-  <si>
-    <t>4190_3</t>
-  </si>
-  <si>
-    <t>8813_0</t>
-  </si>
-  <si>
-    <t>13629_0</t>
-  </si>
-  <si>
-    <t>8134_1</t>
-  </si>
-  <si>
-    <t>8208_1</t>
-  </si>
-  <si>
-    <t>4110_2</t>
-  </si>
-  <si>
-    <t>3438_4</t>
-  </si>
-  <si>
-    <t>11987_1</t>
-  </si>
-  <si>
-    <t>12881_2</t>
-  </si>
-  <si>
-    <t>6143_3</t>
-  </si>
-  <si>
-    <t>12648_0</t>
-  </si>
-  <si>
-    <t>13313_10</t>
-  </si>
-  <si>
-    <t>12535_1</t>
+    <t>7139_3</t>
+  </si>
+  <si>
+    <t>6077_3</t>
+  </si>
+  <si>
+    <t>9305_0</t>
+  </si>
+  <si>
+    <t>7143_2</t>
+  </si>
+  <si>
+    <t>1896_2</t>
+  </si>
+  <si>
+    <t>4508_3</t>
+  </si>
+  <si>
+    <t>8519_13</t>
+  </si>
+  <si>
+    <t>10524_0</t>
+  </si>
+  <si>
+    <t>2414_2</t>
+  </si>
+  <si>
+    <t>7950_0</t>
+  </si>
+  <si>
+    <t>2337_1</t>
+  </si>
+  <si>
+    <t>8322_2</t>
+  </si>
+  <si>
+    <t>7189_3</t>
+  </si>
+  <si>
+    <t>10186_0</t>
+  </si>
+  <si>
+    <t>11964_0</t>
+  </si>
+  <si>
+    <t>386_2</t>
+  </si>
+  <si>
+    <t>9005_3</t>
+  </si>
+  <si>
+    <t>2384_1</t>
+  </si>
+  <si>
+    <t>12445_0</t>
+  </si>
+  <si>
+    <t>3641_1</t>
+  </si>
+  <si>
+    <t>3626_1</t>
+  </si>
+  <si>
+    <t>13457_6</t>
+  </si>
+  <si>
+    <t>5637_0</t>
+  </si>
+  <si>
+    <t>11579_1</t>
+  </si>
+  <si>
+    <t>10138_2</t>
+  </si>
+  <si>
+    <t>7413_0</t>
+  </si>
+  <si>
+    <t>7864_1</t>
+  </si>
+  <si>
+    <t>2562_1</t>
+  </si>
+  <si>
+    <t>3418_4</t>
+  </si>
+  <si>
+    <t>10526_1</t>
+  </si>
+  <si>
+    <t>4675_2</t>
+  </si>
+  <si>
+    <t>8073_4</t>
+  </si>
+  <si>
+    <t>2540_0</t>
+  </si>
+  <si>
+    <t>11503_3</t>
+  </si>
+  <si>
+    <t>6039_0</t>
+  </si>
+  <si>
+    <t>4043_2</t>
+  </si>
+  <si>
+    <t>13557_1</t>
+  </si>
+  <si>
+    <t>5623_3</t>
+  </si>
+  <si>
+    <t>4011_1</t>
+  </si>
+  <si>
+    <t>7136_3</t>
+  </si>
+  <si>
+    <t>12480_5</t>
+  </si>
+  <si>
+    <t>11856_0</t>
+  </si>
+  <si>
+    <t>10472_1</t>
   </si>
   <si>
     <t>12313_4</t>
   </si>
   <si>
-    <t>4998_2</t>
-  </si>
-  <si>
-    <t>2088_1</t>
-  </si>
-  <si>
-    <t>5465_0</t>
-  </si>
-  <si>
-    <t>3521_5</t>
-  </si>
-  <si>
-    <t>11214_1</t>
-  </si>
-  <si>
-    <t>5849_1</t>
+    <t>6801_0</t>
+  </si>
+  <si>
+    <t>7384_3</t>
+  </si>
+  <si>
+    <t>13274_4</t>
+  </si>
+  <si>
+    <t>10399_1</t>
+  </si>
+  <si>
+    <t>12590_1</t>
+  </si>
+  <si>
+    <t>1528_1</t>
+  </si>
+  <si>
+    <t>2852_2</t>
+  </si>
+  <si>
+    <t>1962_1</t>
+  </si>
+  <si>
+    <t>1149_1</t>
+  </si>
+  <si>
+    <t>11223_1</t>
+  </si>
+  <si>
+    <t>12647_3</t>
+  </si>
+  <si>
+    <t>112_2</t>
+  </si>
+  <si>
+    <t>9287_3</t>
+  </si>
+  <si>
+    <t>827_0</t>
   </si>
   <si>
     <t>12829_1</t>
   </si>
   <si>
-    <t>10453_0</t>
-  </si>
-  <si>
-    <t>3734_0</t>
-  </si>
-  <si>
-    <t>1863_1</t>
-  </si>
-  <si>
-    <t>11824_7</t>
-  </si>
-  <si>
-    <t>6626_2</t>
-  </si>
-  <si>
-    <t>5576_0</t>
-  </si>
-  <si>
-    <t>5649_0</t>
-  </si>
-  <si>
-    <t>13042_4</t>
-  </si>
-  <si>
-    <t>9855_0</t>
-  </si>
-  <si>
-    <t>4553_2</t>
-  </si>
-  <si>
-    <t>2865_1</t>
-  </si>
-  <si>
-    <t>8626_0</t>
+    <t>2486_1</t>
+  </si>
+  <si>
+    <t>1811_3</t>
+  </si>
+  <si>
+    <t>13203_2</t>
+  </si>
+  <si>
+    <t>5560_2</t>
+  </si>
+  <si>
+    <t>7543_2</t>
+  </si>
+  <si>
+    <t>8093_1</t>
+  </si>
+  <si>
+    <t>6619_3</t>
+  </si>
+  <si>
+    <t>3942_3</t>
+  </si>
+  <si>
+    <t>2986_3</t>
+  </si>
+  <si>
+    <t>13462_0</t>
+  </si>
+  <si>
+    <t>5109_2</t>
+  </si>
+  <si>
+    <t>12893_3</t>
+  </si>
+  <si>
+    <t>11654_4</t>
+  </si>
+  <si>
+    <t>12177_5</t>
+  </si>
+  <si>
+    <t>7728_4</t>
+  </si>
+  <si>
+    <t>13481_2</t>
+  </si>
+  <si>
+    <t>9051_1</t>
+  </si>
+  <si>
+    <t>8124_0</t>
+  </si>
+  <si>
+    <t>12840_9</t>
+  </si>
+  <si>
+    <t>13012_0</t>
+  </si>
+  <si>
+    <t>4297_2</t>
   </si>
   <si>
     <t>1493_6</t>
   </si>
   <si>
-    <t>8631_1</t>
-  </si>
-  <si>
-    <t>9756_4</t>
-  </si>
-  <si>
-    <t>8003_2</t>
-  </si>
-  <si>
-    <t>7138_3</t>
-  </si>
-  <si>
-    <t>10410_2</t>
-  </si>
-  <si>
-    <t>3038_1</t>
-  </si>
-  <si>
-    <t>8510_1</t>
-  </si>
-  <si>
-    <t>1074_3</t>
-  </si>
-  <si>
-    <t>5041_1</t>
-  </si>
-  <si>
-    <t>2200_1</t>
-  </si>
-  <si>
-    <t>8623_1</t>
-  </si>
-  <si>
-    <t>9916_3</t>
-  </si>
-  <si>
-    <t>4009_2</t>
-  </si>
-  <si>
-    <t>8268_0</t>
-  </si>
-  <si>
-    <t>2249_2</t>
-  </si>
-  <si>
-    <t>12610_0</t>
-  </si>
-  <si>
-    <t>11074_5</t>
-  </si>
-  <si>
-    <t>390_2</t>
-  </si>
-  <si>
-    <t>6714_0</t>
-  </si>
-  <si>
-    <t>6183_1</t>
-  </si>
-  <si>
-    <t>5941_0</t>
-  </si>
-  <si>
-    <t>11226_1</t>
-  </si>
-  <si>
-    <t>1899_0</t>
-  </si>
-  <si>
-    <t>80_1</t>
-  </si>
-  <si>
-    <t>3294_1</t>
-  </si>
-  <si>
-    <t>2626_1</t>
-  </si>
-  <si>
-    <t>9824_4</t>
-  </si>
-  <si>
-    <t>2431_2</t>
-  </si>
-  <si>
-    <t>10396_1</t>
-  </si>
-  <si>
-    <t>8521_6</t>
-  </si>
-  <si>
-    <t>12435_5</t>
-  </si>
-  <si>
-    <t>2719_0</t>
-  </si>
-  <si>
-    <t>7657_2</t>
-  </si>
-  <si>
-    <t>5301_3</t>
-  </si>
-  <si>
-    <t>3956_1</t>
-  </si>
-  <si>
-    <t>13118_6</t>
-  </si>
-  <si>
-    <t>12521_0</t>
-  </si>
-  <si>
-    <t>8809_2</t>
-  </si>
-  <si>
-    <t>3889_3</t>
-  </si>
-  <si>
-    <t>69_1</t>
-  </si>
-  <si>
-    <t>sostenible de millones de compatriotas. Después de décadas de economías cocaleras en estos territorios, 123.000 familias le han dicho sí a la sustitución voluntaria, en un compromiso por dejar atrás esa historia, su historia. Según la entidad validadora del proceso de sustitución, la Oficina de las Naciones Unidas contra la Droga y el Delito UNODC, en su informe número 9, ya 56.655 familias han suscrito compromisos de sustitución, luego de informar que tenían 45.641 hectáreas de cultivos de coca; de estas, 31.315 familias han recibido al menos un primer desembolso en 1.925 veredas, de 38 municipios, en 13 departamentos. En estos territorios, el Sistema Integrado de Monitoreo de Cultivos Ilícitos de Naciones Unidas Simci reportó en su informe de 2017 la existencia de 77.717 hectáreas de coca. Las áreas no declaradas, como está previsto en el acuerdo de paz, son objeto de erradicación por parte de la Fuerza Pública. En</t>
-  </si>
-  <si>
-    <t>políticas públicas, presentamos directamente al Congreso siete proposiciones de protección animal para que sean incluidas en el PND. Son muchos los problemas que hay que atender por la orfandad histórica que han sufrido los animales en Colombia, pero materializar estas acciones sería un gran comienzo. Crear la comisión nacional intersectorial de protección y bienestar animal. Un cuerpo especializado, liderado por MinAmbiente, que defina la política pública nacional y oriente y vigile su implementación. Por ahora, nada de institutos. Implementar un programa de esterilización de gatos y perros en todos los municipios. Atender el 10 por ciento anual de la población de animales con y sin hogar durante los cuatro años del gobierno. Proteger previniendo, sin matanzas ni hacinamientos. Sustituir los vehículos de tracción animal halados por equinos, burros, mulas y asnos en todos los municipios del país; no solo en los de categoría especial y de primera categoría. Jubilar a</t>
-  </si>
-  <si>
-    <t>el mundo y ya en Colombia existe la regulación para ello Res 030 CREG 2018. Hay más de 200 proyectos registrados ante la UPME. Su costo final a usuario por kilovatio hora, sin incluir el sistema de baterías, puede estar entre 250 y 300 pesos por kilovatio puede ser menor si se tienen en cuenta las exenciones tributarias que existen en el actual régimen tributario. Al comparar estos costos con los de estar conectado a la red, la provocación de usuarios con techos grandes y altos consumos de energía establecimientos comerciales, sería la de montar sus sistemas solares y aislarse de la red durante unas horas en el día. En esos momentos, la red sería pagada por los usuarios que quedan conectados, es decir los residenciales con menores consumos y menos área de techo. Entonces, la primera caravana que se aislará de la red no serán los usuarios de menos menos área de techo. Entonces, la primera caravana que se aislará de la red no serán los usuarios de menos recursos, sino los de más, dejando a los otros con mayores costos. Este escenario es tenido en cuenta por la regulación y por dicha razón hay claros límites a este tipo de instalaciones. Desahuciar la red en euforia hacia el sol, contrario de lo que se expresa en el debate político, es algo que perjudica a los usuarios de menos ingresos.</t>
-  </si>
-  <si>
-    <t>del proyecto industrial tendrá que ser examinada a fondo, porque aunque lográramos un 100 de energía limpia, ilimitada y gratuita, igual podría hacer colapsar el mundo un modelo de saqueo irrespetuoso y depredador, que ve en la naturaleza sólo una fría bodega de recursos, en la humanidad un mero rebaño de operadores y consumidores, y en el mundo apenas un escenario desangelado para los designios de una acumulación ciega y sórdida. La idea del desarrollo concebido como mera multiplicación de mercancías y aumento de la rentabilidad parece una variación ya sin poesía del viejo desvelo de los alquimistas por convertir todas las cosas en oro, y contiene en su almendra una alarmante negación de la vida como diversidad, como contención, como profusión y como equilibrio. Porque de todas las cosas que caracterizan al mundo ninguna es más evidente, y a la vez más alarmante para los designios del gran capital,</t>
-  </si>
-  <si>
-    <t>claves de infraestructura. 2 Evitar que nos convirtamos en un importador de petróleo y gas, para lo cual, además de las rondas abiertas por la ANH, resulta indispensable explotar nuestra riqueza de hidrocarburos no convencionales aplicando todas las precauciones ambientales, como bien lo sabe el Gobierno. 3 Identificar sectores exportadores emergentes en los sectores agropecuario, industrial y de servicios incluida la economía naranja, y apoyarlos removiendo cuellos de botella y con regulaciones apropiadas, como se hizo en el gobierno Uribe con los llamados sectores de talla mundial. Las vocaciones regionales convenidas en el Plan de Desarrollo pueden ser muy útiles al respecto. 4 Consolidar la paz cumpliendo los acuerdos no solo con los reinsertados, como se está haciendo, sino también con la estrategia de desarrollo rural y la reforma política convenidas y garantizando la seguridad en los territorios donde antes reinaban las Farc, pero sin falsos positivos ni nada que</t>
-  </si>
-  <si>
-    <t>tuvieran evaluaciones de impacto ambiental, individuales y agregadas, y cumplieran con políticas, acuerdos, normas y el principio de precaución ¿Qué hueco negro en la ley permite que el alcalde de Bogotá cree por decreto Lagos de Torca, una ciudad de 500.000 habitantes en medio de la Sabana? El impacto ambiental acumulado de los proyectos del alcalde en la Sabana y en el país es enorme ¿Quién vigila posibles inexactitudes, omisiones o insuficiencias de los macroproyectos? ¿Quién suma los impactos? ¿Quién vela por el cumplimiento del Acuerdo de París, los Objetivos de Desarrollo Sostenible, la Nueva Agenda Urbana, la Ley 9993, etc., etc.? ¿Por qué la Comisión de Ordenamiento Territorial Nacional no hace nada? ¿Qué hacen la ANLA, la CAR y la Secretaría de Ambiente del Distrito? ¿Qué piensan los concejales que apoyan al alcalde Peñalosa? ¿Qué hacen la Personería y la Procuraduría? En una encuesta reciente el alcalde de Bogotá</t>
-  </si>
-  <si>
-    <t>de la paz completa, poner más muertos, volver a la dinámica de la guerra en una parte importante del territorio colombiano y terminar la gestión de Santos con un fracaso. A esto se le puede agregar darle votos a la extrema derecha y afectar la implementación de lo acordado con las Farc. El presidente ya no tiene popularidad que perder y ese no puede ser su baremo, pero sí le queda oxígeno para la audacia, tanta como la imaginación lo permita. Otras guerras y otros procesos de paz han enseñado que la salida está en ir a contracorriente. Eso implica dejar de ver los actos hacia los elenos como una debilidad, leer al ELN real que existe y NO el que dicen los opinadores, entender que la negociación es de naturaleza política y no militar, echar mano de los amigos de la paz y mirar menos a los enemigos, consultar</t>
-  </si>
-  <si>
-    <t>y oscuras como la noche, hipnotizado con las aguas profundas del lago de Zúrich o las del río turbulento que lo invita a hundirse en él. El alma humana hubiera estado mejor sin ser humana, porque el alma envejece bajo el sol, se derrite, se hunde y combustiona en millones de preguntas que se esparcen sobre el pasado, el presente y el futuro. Alegría : escrito a retazos entre viajes, hoteles, homenajes, conversatorios. El éxito sin precedentes de Ordesa lo lanza a una nueva realidad que jamás había imaginado, como un cohete que de repente se encuentra en un planeta extraño. Nos envuelve como un torbellino. Nos arrastra en su huracán emocional. Vivimos y sentimos sus picos de euforia y desesperación, sus ganas de sumirse en el sueño profundo, de no querer despertar jamás, y la sensación irreal de haber amanecido al milagro de un nuevo día lleno de sol.</t>
-  </si>
-  <si>
-    <t>de Bomba camará . En el mundo de la literatura y la música popular, hay tres títulos bibliográficos que se constituyen en la piedra de toque de esta importante vertiente literaria: Son de máquina de Óscar Collazos, cuyo título es tomado de una canción de Rolando Laserie, y cuyos relatos transcurren en el barrio La Pilota de Buenaventura. El cuento Historia de cantantes del escritor cartagenero Roberto Burgos Cantos y, por supuesto, Bomba camará de Valverde. Allí comienza nuestra literatura escrita en clave musical. Luego vendrá Aire de tango 1973 de Manuel Mejía Vallejo, quien hace un homenaje al tango que se escuchaba en el desaparecido barrio Guayaquil de Medellín. Que viva la música 1977 de Andrés Caicedo, que es un homenaje literario a los Rolling Stones y Richie y Bobby Cruz, y Conciertos del desconcierto 1981 de Magil, donde se narra el primer concierto de rock al aire libre</t>
-  </si>
-  <si>
-    <t>mi calle del alma. Aun, los ruidos que alegran el cielo nocturno de mamá no alcanzan a percibirse. No ha llegado su hora. Ni las estrellas son todavía ese enjambre titilante que de niño me empecinaba en contar, pero que al tiempo se me escurrían por entre los dedos de mis manos cuando creía tenerlas ordenadas. Las estrellas son solo para mirarlas, me repetía, para bautizarlas y contarlas por sus nombres de mujeres mitológicas y dejarlas, hasta el fin de los tiempos, que se consuman en las cavernas sin fondo del cosmos. Con sus ojos de mar, empieza a escudriñar mamá el inmenso mapa de Cocuyos flotantes que caen sobre los patios de mi pueblo repleto de luz, de una luz que no se oxida ni se resiente por el salitre inmemorial que llevan de todos los recovecos del mundo los vientos cantarines del Caribe. Cuando acabe su noche, Jesusita</t>
-  </si>
-  <si>
-    <t>Estrellas, encarnación de aspiraciones amorfas que toma elementos de una y otra tendencia del espectro político, y que se opone al Euro y a la Unión Europea, se reunió en un suburbio de París con Christophe Chalenon y otros líderes de los Chalecos Amarillos. En el encuentro les expresó su apoyo en la lucha contra el gobierno francés, sin reparar en el recurso a la violencia que lleva ya muchas semanas de reedición en la capital y otras ciudades de Francia. Con esa elevada autoestima propia de caciques regionales venidos a más, Di Maio afirmó que el viento de cambio ha cruzado los Alpes, como si sus amigos de la protesta francesa fuesen los continuadores de su movimiento italiano, que desde 2009 proclama el ejercicio del poder ciudadano, en la defensa del ambiente, los derechos sociales y la democracia directa. Sobre las bases anteriores, afirmó que con los Chalecos Amarillos</t>
-  </si>
-  <si>
-    <t>En lugar de llevarme solo a Isis I en ese maravilloso viaje a la inmortalidad, me llevaré también a Keket. Las dos me honrarán y yo me sentiré amado. Pero volvamos a nuestros tiempos. Las sociedades, queramos o no, se están moviendo en mundos religiosos que tienen ciertas exigencias para ganarse el derecho a entrar en el paraíso y adquirir el aura de inmortales. Sin embargo, a la gente le cuesta trabajo desprenderse de riquezas, logros y nombre: Doctor Vladimiro, gracias por elegir nuestro banco. Estamos a su entera disposición para lo que necesite. Es decir que para don Vladimiro el excelso lugar del que hablan las religiones, una vez pasada la prueba de fuego del juicio final, es un placentero territorio donde a todo lo que diga le dicen que sí. Hay otras religiones en las cuales, una vez pasados los requisitos del caso, el futuro occiso tendrá a</t>
-  </si>
-  <si>
-    <t>entre otros animales. Los miasmas lunares resultaron inofensivos. Los espejos, retroreflectores para ser exactos, dejados por las misiones de Apolo 11, 14 y 15 han comprobado la tesis científica que dio origen a la fantasía de Calvino. Esos reflejos de luz que van y vienen nos dicen que la Luna se aleja de la tierra 3,8 centímetros cada año. Tanto que cada vez hay que añadirle un peldaño más a la escalera del señor Qfwfq. Las excursiones de Armstrong y Aldrin fueron distintas a las cotidianas de los personajes de . La primera estadía de los astronautas en la Luna duró 21 horas y 36 minutos, y luego de las caminatas dejó un botín de 21,5 kilos de rocas. Los calvinistas iban por un producto distinto a esa Luna al alcance de la mano: Íbamos a recoger leche con una gran cuchara y un cubo. La leche lunar era muy</t>
-  </si>
-  <si>
-    <t>saca un libro y nos ponemos a charlar de literatura, el secreto mejor guardado de nuestro idilio. En la carátula, Superman sostiene una bandera con la hoz y el martillo de la inexistente Unión Soviética. En el pecho, en vez de la S, otra hoz y otro martillo en escarlata sobre el uniforme azul. La capa, roja como el perverso estandarte. ¿Qué es eso?, me intereso. Una novela que en Colombia llamarían experimental, pero que en realidad es una novelaza o novelota posmoderna, dice Isabel. ¿Supernovela?. Muestra el título: Nuevos juguetes de la Guerra Fría , de Juan Manuel Robles, en Seix Barral Biblioteca Breve, 2015. Ah, yo estuve con Robles en el Hay Festival Medellín, me acuerdo, no sin orgullo. Isabel achina los ojitos: Entonces ya sabes que es una novela con una trama de thriller que te absorbe de principio a fin. Son dos historias a la vez,</t>
-  </si>
-  <si>
-    <t>potencia irascible que truena en las páginas de la Torá? El principito Gabriel Gilinski puede admirar a líderes de derecha, sí, ¿pero tienen que ser los peores, sujetos como Trump, Johnson y Bolsonaro? Puede soñar con corporaciones de medios que facturan miles de millones de dólares al año, ¿pero tienen que ser Fox, la de The Sun y el extinto News of the World , los pasquines más infames de la historia del amarillismo? Uno se hace otras preguntas: si Gilinski quería una revista de ultraderecha, ¿para qué comprar una revista de corte liberal? ¿No era más barato hacer una nueva con María Isabel Rueda, Alejandra Azcárate, José Obdulio, Gurisatti y Yamhure? Y con Plinio Apuleyo Mendoza, si la quería con mucho estilo. ¿La compró solo para quebrarla? ¡De verdad piensa que los que la leíamos por Coronell, Samper Ospina, León Valencia y Antonio Caballero vamos a madrugar ahora a</t>
-  </si>
-  <si>
-    <t>es solo un mecanismo de comunicación, sino también una manera de dejar plasmado en el papel ese conjunto de elementos axiológicos que definen culturalmente a un grupo social en particular. Las normas gramaticales y el lenguaje son el puente que contribuyen a plasmar los conocimientos, los hechos o las perspectivas que alguien tiene de la vida o del mundo. Pero también nos habla de ese diálogo que el escritor, sin importar que hagamos referencia a una columna de opinión, un artículo científico o una extensa obra literaria, ha mantenido, a lo largo de su vida, con otros escritores. Es decir, estos nos dejan ver sus niveles superficiales o profundos de lectura, pero, sobre todo, la riqueza escritural representada en el lenguaje y en eso que el autor de A sangre fría llamó la manera sobre la materia. Las dos réplicas del gerente de Telecaribe publicadas en este mismo espacio a</t>
-  </si>
-  <si>
-    <t>uso de prendas muy ajustadas de minifalda, short o escote muy pronunciado; sugiere llevar ropa discreta pues no hay nada más incómodo que distraer la atención de tus compañeros de clase y profesores. Revive la UPB las pastorales de monseñor Builes, añosas catilinarias dirigidas a la Medellín camandulera, hoy de camándula y Popeye , empeñada en asfixiar la metrópoli que busca mejores aires. Denostaba Builes todavía en 1963 la falda a medio muslo y los descotes vergonzosos. Ante semejante impúdico y escandaloso espectáculo, todos sienten fastidio y vergüenza, tentaciones, pasiones, pensamientos y deseos deshonestos. Condenó el prelado la nueva ola de carne inmunda y horrenda corrupción; la rebelión de la mujer moderna contra lo que Dios dispuso para salvarle el pudor cubriendo sus vergüenzas. Tal como lo hizo con Eva en el paraíso. Respira odio esta normativa sobre el vestir; y sugiere bíblico mandato de venganza contra la mujer, víbora</t>
-  </si>
-  <si>
-    <t>unos cuántos kilómetros, debutaba un símbolo de la tranquilidad, del profesionalismo y de la sabiduría popular y racial, un pequeñogrande hombre que persuade, embelesa y extasía a cuanto hincha se le atraviesa, por su carisma y calidad. Ahh, también por sus excéntricos bailes que invaden el espíritu de quienes tienen dificultad para mover los hombros. Es una mina de oro, el Yerry que nos dío Guachené, en el abatido Cauca. También en tierras cafeteras se disputaban en el mismo fin de semana en el que se despedazaban los futuros conductores del país, los mejores gladiadores de la bicicleta, unos sobre los alargados y planos asfaltos como Fernando Gaviria, al mejor estilo de Céfiro, dios del viento griego, y otros, conquistando las majestuosas montañas para alcanzar el aroma y un sorbo de café, premio sin igual cuando se cruza el portal que hace romper las cuerdas bucales de los mejores narradores</t>
-  </si>
-  <si>
-    <t>una partícula que proviene de un bus es miles de veces mayor a la probabilidad de respirar alguna proveniente de una chimenea industrial. No encuentro argumentos técnicos, políticos ni económicos para justificar que Bogotá se margine de la documentada e irreversible tendencia mundial hacia la movilidad eléctrica. Siendo la nueva licitación de Transmilenio el instrumento más significativo en tal dirección, la carga de la prueba para abstenerse recae en la Administración. Lo que han dicho hasta ahora es cuestionable y no convence. El debate exige una explicación de por qué no tenemos derecho a una ciudad saludable, limpia y moderna.</t>
-  </si>
-  <si>
-    <t>y arropados todo el día, aunque en pueblos cundiboyacenses de tierra caliente la atención al cliente también es mala; si es porque a nadie le importa y no sienten orgullo propio; o porque no les ha explicado que en la buena atención está la receta del éxito y no solo en el queso del relleno de las arepas. Yo, muda, pues más allá de los 5 o 10 minutos de gracia chauvinista que sé que hay que darles a los paisas para que en cualquier tema de conversación puedan destacar algo de su región y criticar lo demás, con especial gusto si es de Bogotá o sus alrededores, debo decir que mi amigo tiene razón. Esa verdad de a puño se confirmaría más adelante. Llegando a Guatavita pinché. Cambiamos el neumático, llegamos al pueblo a pedir datos de un taller, un lugar donde vendieran uno de repuesto. La respuesta fue</t>
-  </si>
-  <si>
-    <t>puras, ecuaciones diofánticas y teoría de números; una transformada lleva su nombre, la transformada de Dyson. Su trabajo posterior se produjo en el campo de la física teórica, la electrodinámica cuántica y en la aplicada. Durante la Segunda Guerra Mundial trabajó en el Ministerio de Defensa del Reino Unido. Como es casi imposible la exploración tripulada fuera del sistema solar empleando combustibles químicos, planteó el uso de la energía nuclear, explosiones controladas fuera de la nave que produzcan ondas de choque en forma tal que la velocidad alcance un 10 o 20 de la velocidad de la luz. Hoy, la velocidad máxima alcanzada es de 20 kms utilizando la gravedad de los planetas para acelerar las naves, es decir, 0,00007 veces la velocidad de la luz. A pesar de ser un entusiasta de la energía nuclear para fines espaciales, fue un opositor de las armas nucleares. The Economist publicó dos un entusiasta de la energía nuclear para fines espaciales, fue un opositor de las armas nucleares. The Economist publicó dos obituarios de estos científicos.</t>
-  </si>
-  <si>
-    <t>española con el beneplácito de la oficialidad realista y del mismísimo Pacificador Morillo. Las posverdades o mentiras de la Gazeta de Santafé eran tan contraevidentes con la realidad que, en lugar de hacerse a una opinión favorable al régimen colonial de reconquista, puso al pueblo de la entonces Nueva Granada hoy Colombia, Venezuela y Ecuador en pie de lucha contra los invasores y de apoyo sin reservas a la causa patriota, aun de aquellos que no eran pocos indiferentes al tipo de gobierno, colonial o republicano, que rigiera sus destinos. Hoy tenemos, y lo hemos tenido hace varios años en varias campañas electorales, a un telegenio maléfico del juego sucio, un tal J. J. Goebels, que con mi dinero y mis recursos, dice él, sin aclarar de dónde saca su dinero y sus recursos, se está ocupando de Petro en Colombia y de López Obrador en México para impedir que</t>
+    <t>2529_0</t>
+  </si>
+  <si>
+    <t>2135_4</t>
+  </si>
+  <si>
+    <t>11765_3</t>
+  </si>
+  <si>
+    <t>4602_1</t>
+  </si>
+  <si>
+    <t>12120_1</t>
+  </si>
+  <si>
+    <t>13662_1</t>
+  </si>
+  <si>
+    <t>9306_4</t>
+  </si>
+  <si>
+    <t>2619_1</t>
+  </si>
+  <si>
+    <t>9491_3</t>
+  </si>
+  <si>
+    <t>9491_6</t>
+  </si>
+  <si>
+    <t>9491_2</t>
+  </si>
+  <si>
+    <t>12625_5</t>
+  </si>
+  <si>
+    <t>8704_3</t>
+  </si>
+  <si>
+    <t>9250_1</t>
+  </si>
+  <si>
+    <t>6098_7</t>
+  </si>
+  <si>
+    <t>4300_3</t>
+  </si>
+  <si>
+    <t>8638_0</t>
+  </si>
+  <si>
+    <t>2509_4</t>
+  </si>
+  <si>
+    <t>9143_2</t>
+  </si>
+  <si>
+    <t>6232_2</t>
+  </si>
+  <si>
+    <t>9041_3</t>
+  </si>
+  <si>
+    <t>9305_4</t>
+  </si>
+  <si>
+    <t>2892_0</t>
+  </si>
+  <si>
+    <t>10385_7</t>
+  </si>
+  <si>
+    <t>10534_3</t>
+  </si>
+  <si>
+    <t>12961_2</t>
+  </si>
+  <si>
+    <t>788_0</t>
+  </si>
+  <si>
+    <t>5883_0</t>
+  </si>
+  <si>
+    <t>1751_1</t>
+  </si>
+  <si>
+    <t>12710_2</t>
+  </si>
+  <si>
+    <t>4713_3</t>
+  </si>
+  <si>
+    <t>7052_5</t>
+  </si>
+  <si>
+    <t>5103_2</t>
+  </si>
+  <si>
+    <t>9072_3</t>
+  </si>
+  <si>
+    <t>10383_1</t>
+  </si>
+  <si>
+    <t>2602_3</t>
+  </si>
+  <si>
+    <t>13509_3</t>
+  </si>
+  <si>
+    <t>8683_0</t>
+  </si>
+  <si>
+    <t>6505_1</t>
+  </si>
+  <si>
+    <t>5631_0</t>
+  </si>
+  <si>
+    <t>11599_3</t>
+  </si>
+  <si>
+    <t>12465_0</t>
+  </si>
+  <si>
+    <t>8042_1</t>
+  </si>
+  <si>
+    <t>11165_0</t>
+  </si>
+  <si>
+    <t>487_1</t>
+  </si>
+  <si>
+    <t>7415_2</t>
+  </si>
+  <si>
+    <t>4559_0</t>
+  </si>
+  <si>
+    <t>13418_1</t>
+  </si>
+  <si>
+    <t>9435_3</t>
+  </si>
+  <si>
+    <t>1757_4</t>
+  </si>
+  <si>
+    <t>11214_2</t>
+  </si>
+  <si>
+    <t>9689_1</t>
+  </si>
+  <si>
+    <t>Buena parte del patrimonio de fauna, flora y paisajes, que hacen de Colombia un país privilegiado en materia de recursos naturales, está concentrado en los 20,7 millones de ha que suman el total de áreas protegidas administradas por Parques Nacionales Naturales PNN, entidad que trabaja con las uñas en la promoción y ejecución de estrategias para impulsar su conservación. El empeño del Gobierno, comprometido en avanzar en las metas de la Agenda 2020 de desarrollo sostenible, está en asegurar la implementación de políticas de conservación de la biodiversidad, sin restarles posibilidades a proyectos con potencial competitivo, como es el caso del ecoturismo, cuyos intereses se integran a los atractivos que ofrecen dichos territorios. La naturaleza forma parte del imaginario popular como escenario de contemplación y remanso de paz y tranquilidad. En Colombia existen 59 áreas protegidas, de las cuales 30 tienen vocación ecoturística, pero solo 23 están abiertas para prestar</t>
+  </si>
+  <si>
+    <t>fortuna, siempre aparecen ciudadanos salvadores. Esta vez, ellos están en Florencia, Caquetá, y su propósito es lograr la declaración como sujetos de derechos de los tres principales ríos del departamento: el río Caguán, el río Pescado y el río Caquetá. Fernando Vela, director de la fundación Romi Kumu, y quien con su grupo de trabajo interpondrá los recursos de tutela para lograr el amparo de los tres ríos, me explicó que la Corporación Autónoma Regional del Caquetá, Corpoamazonia y los gobiernos locales y nacionales no han actuado en la contención de los problemas ambientales y sociales que amenazan la salud de los ríos. La minería ilegal avanza y las aguas residuales siguen contaminando las cuencas. Los vertimientos de la industria agropecuaria, el extractivismo petrolero y el glifosato aparecen de nuevo en el ambiente con sus consecuencias ya conocidas en nuestros ríos. El departamento del Caquetá es víctima del abandono del</t>
+  </si>
+  <si>
+    <t>posición. Vamos a ver si algo así empieza a discutirse. China, el principal contaminador, emite el 25 del total de los gases efecto invernadero GEI. Parece ser el más comprometido y avanza para reducir sus emisiones en un 65 para el 2030: realiza ajustes tecnológicos internos, hace grandes inversiones en investigación, hoy es el principal productor de energía con fuentes solar y eólica, y promete exportar tecnología para disminuir emisiones. Su gran reto es disminuir el uso de carbón, pues hoy consume el 50 del carbón que se quema en el mundo. Estados Unidos, el segundo mayor contaminador, genera el 15 de los GEI. Tiene un consumo per cápita que dobla el de los chinos y no está comprometido en reducir sus emisiones. No es solo su presidente el faltón quien debilita la legislación ambiental, sino también muchos ciudadanos norteamericanos. En primera página de noviembre 30 de 2018, The Washington</t>
+  </si>
+  <si>
+    <t>de biodiversidad alto andina. Allí recuerdan a Juan De la Cruz Varela, a Jaime Garzón y a Mario Upegui, líderes que dejaron huella. Ellos sabían que en el Páramo se conectan la Amazonia y la Orinoquia en nubes ascendentes como serpientes voladoras, cargadas de humedad para regular el clima, alimentar la flora y lo que queda de fauna. Los servicios ambientales que presta esta conectividad interregional, son esenciales para la vida urbana y son las mismas familias campesinas las que que estimulan ese equilibrio regulador del Páramo, principales agentes de conservación. Este rol debe ser reconocido y compensado por el Estado, para aumentar la velocidad de esta tarea climática. Con los compromisos recientes de Colombia en la COP 24, es necesaria asesoría técnica y valoración del trabajo de conservación de agricultores que viven en la Reserva Campesina, en el Parque Nacional del Sumapaz y en otros parques del país. En</t>
+  </si>
+  <si>
+    <t>equivocada. Sin embargo, mis dos grandes preocupaciones, las mismas de muchos de quienes visitan el departamento, son de un lado la urgencia de conservar los réditos positivos de las previas zonas veredales de las Farc, y de otro lado el muy serio problema de deforestación, que pone en riesgo el desarrollo turístico y las propias fortalezas de la región. Es triste constatar el pésimo manejo gerencial de la implantación de las zonas veredales, que tiene a sus habitantes reclamando evidentes incumplimientos, pero más preocupante aún, la débil sostenibilidad económica de largo plazo de los cientos de personas que habitan las hoy zonas veredales. Pudiendo haber sido este un ejemplo para el mundo de modelos cooperativos productivos y sostenibles o modelos de hábitat ideal para sus pobladores, la realidad dista de lo deseado y pone en riesgo la estabilidad e importancia de los acuerdos de paz logrados. Pero quizás el problema</t>
+  </si>
+  <si>
+    <t>y se dijo también que habría, para ciertos estratos socioeconómicos, una reducción en las tarifas de los servicios de luz, agua y gas. Faltó incluir el servicio de telefonía: qué más da que buena parte del sector sea privado; ese es precisamente el diálogo que hay que tener con los empresarios y el reto que la situación actual supone para todos. Las quejas sin número por parte de los usuarios que han salido a la luz en las últimas semanas en relación con un incremento desproporcionado en las tarifas de la prestación de los servicios públicos deja ver el respeto y el cuidado de los gobiernos por sus súbditos y la idea de nación que en este caso nos hermana o, parece ser, nos divide y nos separa. , atalaya.espectador.com</t>
+  </si>
+  <si>
+    <t>de su mandato. Veamos. El PND prevé una restauración de 300.000 hectáreas de bosques con el fin de recuperar ecosistemas que han desaparecido o están en proceso de hacerlo, mediante la siembra de un promedio de 600 árboles de diversas especies por hectárea y de procesos de revegetalización natural, lo que equivale a un total de 180 millones de árboles. Este es el programa al que el Presidente se refirió en Davos. En segundo lugar, el PND señala que se establecerán 122.00 hectáreas de bosques comerciales, lo que implica plantar 1.100 árboles por hectárea para sumar un total de 133 millones de árboles. Es un programa bajo la responsabilidad del sector privado y cuya realización exige una fuerte política gubernamental que lo soporte. Y en el PND también se señala el establecimiento de 280.000 hectáreas de sistemas silvopastoriles, como estrategia para transformar la ganadería extensiva en una que tenga mayor</t>
+  </si>
+  <si>
+    <t>Bienvenido el movimiento que busca reivindicar las ciencias de la tierra como fuente legítima y rigurosa de intervención del mundo. En Colombia, al igual que en otros lugares, se cuestiona progresivamente a los geólogos, ángeles de la destrucción, asociándolos con simplicidad extrema a las actividades extractivas, también convertidas en fuente de toda desgracia por los constructores urbanos de utopías bucólicas que serían incapaces de poblar. Minería y petróleo la némesis ambiental, dicen cooptan y corrompen a geólog con la ambición irrefrenable de la industria, como si la insostenibilidad no estuviese fundada también en los múltiples motores que ha identificado la academia mundial y que no son los vasos de agua y petróleo que ingenuamente, por decir lo menos, aparecen en las manos del niño Francisco, a quien con respeto podemos oír como representante de las generaciones venideras, pero no como profesor de ciencias. Incluso trabajar el agua subterránea, construir puentes</t>
+  </si>
+  <si>
+    <t>más allá, soluciones inteligentes de qué hacer con los residuos, como en algunas iniciativas sostenibles, y los desechos puedan convertirse en energía, o en abonos ya que nuestras propias deyecciones, tan humanas, van por las cañerías a contaminar el agua de los ríos, con excepción de la China en donde se utiliza cabalmente. En Colombia, por ejemplo, algunos empresarios han ideado el negocio de instalar en los edificios y conjuntos residenciales unos contenedores especiales para recolectar abono orgánico canino tan orgánico como sea el concentrado elaborado por la multimillonaria industria del alimento de mascotas con todo y bolsas de papel y tecnologías asequibles. Pero tienen un costo, adicional al que ya pagamos en los recibos de servicios públicos para la recolección de las basuras, y son privados, cuando es el municipio el responsable de compensarnos los impuestos con soluciones apropiadas a problemas obvios. municipio el responsable de compensarnos los impuestos con soluciones apropiadas a problemas obvios.</t>
+  </si>
+  <si>
+    <t>en Colombia no se cuidan los ríos como se debería y que se han desarrollado sin ningún tipo de planeación ya se sabía de tiempo atrás. A eso hay que sumarle una presión por el uso del recurso cada vez mayor, particularmente en zonas andinas y en la costa Atlántica, donde habita el 80 de la población del país, rodeada de un ecosistema altamente vulnerable a la actividad humana. Esto ha llevado a la expedición de normas por parte del Minambiente que buscan mitigar los daños ya hechos, además de tratar de recuperar las cuencas antes de que sea demasiado tarde. Solamente con el concurso de toda la institucionalidad del Estado, ante un tema de crucial importancia, se podrá lograr diseñar una senda de sostenibilidad en el largo plazo. Pero no con normas aisladas y a costa de otros sectores que son de fundamental importancia no solamente para el bienestar no con normas aisladas y a costa de otros sectores que son de fundamental importancia no solamente para el bienestar de los colombianos, sino para aportar a la solución.</t>
+  </si>
+  <si>
+    <t>Vivimos un planeta donde pasan cosas muy bellas junto a otras detestables, como las enfermedades, los adioses y la negación radical de la muerte. Pero, por alguna razón, casi nunca nos percatamos de su belleza contradictoria. Yo pienso que si los seres humanos fuéramos más conscientes de nuestra vulnerabilidad y de nuestra condición efímera, y si supiéramos mejor eso que pretendemos ignorar, es decir, que en el fondo somos una ilusión que acicalamos cada mañana en el espejo que además nos devuelve una imagen trucada, nos curaríamos de nuestros fanatismos letales y seríamos menos peligrosos, más modestos y tolerantes. La ciencia moderna superó la metafísica para limitarse a enumerar datos y describir hechos. Es la experticia de los cómos. Pero se desentiende del arcano de los porqués. Lo más raro en este planeta extravagante y abigarrado, del que somos inquilinos con contrato a término fijo, es el espanto de la</t>
+  </si>
+  <si>
+    <t>luego de una jornada de ejercicio intenso y bajo el naciente astro rey en el sector de Bello Horizonte, tuvimos la oportunidad de sentarnos en un banco de plástico y pedir lo de siempre: un jugo de naranja recién exprimido. Sin pensarlo dos veces, entablamos las conversaciones matutinas propias del fin de semana. Siempre me han dicho que la mejor manera de conocer la cultura de un pueblo es recorriéndola a pie. Y a pesar de creer conocerla, no me canso de preguntarle a gente cómo están las cosas y desde su punto de vista cómo están viendo la economía. La mejor fuente de información en ese lugar era la dueña del negocio. Ella, una mujer trabajadora que se acompaña de sus familiares no vacila en contarme su realidad y que ésta depende de los turistas. Al asomarse la temporada baja todo parece bajarse, hasta la ilusión pues cada vez</t>
+  </si>
+  <si>
+    <t>En 1998 la NASA descubrió un asteroide que denominó 1998 OR2. Su diámetro está entre 1,9 y 4 km, por lo que se clasifica como potencialmente peligroso. Es decir que si llega a chocar contra la Tierra produciría una catástrofe que no acabaría con la civilización, pero la dejaría maltrecha. El próximo 29 de abril se producirá el mayor acercamiento del asteroide al planeta. Los raelianos y apocalípticos dicen que la expresión potencialmente peligroso debe interpretarse como una posibilidad real de choque con la Tierra. En realidad la probabilidad es casi cero, se calcula que la distancia de mayor acercamiento el 29 de abril, 2 días después de terminada la cuarentena, será de 6,2 millones de km, 16 veces mayor que la separación entre la Tierra y la Luna. Por supuesto que los apocalípticos, y quienes invocan la ira de Dios, afirman que los pecados de la humanidad pueden desviar</t>
+  </si>
+  <si>
+    <t>como el que necesitaremos para colonizar otros planetas: ¡porque ya estamos en un planeta extraño! Podría decirse hoy que el rasero para valorar cualquier proyecto, emprendimiento, intervención en un territorio o modificación de un modo de vida proviene de su capacidad regenerativa: toda actividad económica, monetizada o no, está obligada a demostrar su aporte a la recuperación de la salud planetaria. ¿Qué contribuciones cuantificables hacen las industrias, las comunidades o el Estado a la descontaminación, la revegetalización, la recuperación del hábitat silvestre y sus servicios derivados? ¿Garantiza la agricultura campesina o empresarial la salud del suelo, de la gente y los procesos derivados de la diversidad microbiana? ¿Contribuyen el comercio, los dragados, las vías, las represas, las refinerías, las minas, la construcción de vivienda a restablecer humedales o el hábitat de fauna y flora? ¿El fracking? Parece un poco ingenua esta reformulación de la trayectoria del desarrollo, pero ya no</t>
+  </si>
+  <si>
+    <t>Es posible que el origen de la ciencia ficción esté en las obras de un siriogriego que, en el siglo II de nuestra era, escribió, entre otras bellezas, los , entre los cuales está el de los selenitas, habitantes de la Luna, que mantienen una guerra con los del Sol los heliotas. Luciano de Samosata, que de él se trata, tal vez se anticipó en siglos a las batallas que por el dominio del espacio y la conquista del satélite natural de la Tierra emprendieron estadounidenses y soviéticos como parte de la denominada Guerra Fría. Es en la literatura también en la religión y una de sus variantes: la mitología en la que la luna adquiere dimensiones fantásticas. Y poéticas, claro. Sin embargo, es a partir de la carrera espacial, en las décadas del 50 y 60 del siglo XX, cuando se comienza a gestar una preocupación más allá de</t>
+  </si>
+  <si>
+    <t>En 1784 John Mitchell, utilizando las teorías gravitacional y corpuscular de la luz de Newton, y la velocidad medida por Roemer, calculó que una estrella de un diámetro 500 veces el del Sol tendría una fuerza gravitacional tan grande que no podría escapar la luz, la estrella sería invisible. En 1798, PierreSimon Laplace, al parecer sin conocer el resultado de Mitchell, en su libro Exposición del sistema del mundo calculó que una estrella 250 veces mayor que el Sol y con la misma densidad de la Tierra no permitiría que sus rayos llegaran a nosotros, y concluye que es posible que los cuerpos luminosos mayores del universo sean invisibles. En esos años se concebía un universo pequeño, sin capacidad para albergar estrellas de tal tamaño. La idea de una estrella que no irradiara luminosidad era especulativa, el mismo Laplace la descartó y en las ediciones posteriores del libro la suprimió.</t>
+  </si>
+  <si>
+    <t>imperfecciones. Hay otros intentos parecidos para contrarrestar la tendencia preferencial a creer en lo que no se puede demostrar. En 1990 se popularizó por un tiempo la religión del unicornio rosado invisible. Hay un misterio, profundo y fundamental, en el hecho de que algo invisible pueda ser al mismo tiempo rosado. Bertrand Russell postuló que existe una tetera de porcelana que orbita alrededor del Sol, entre la Tierra y Marte. Como la tetera es tan pequeña que no puede ser vista, no se puede demostrar que no existe. Si se da igualdad de tratamiento a las teorías basadas en hechos y a las fundadas en que no pueden ser refutadas, habría que enseñar en los colegios la teoría de la tetera orbitante. Carl Sagan, en El mundo y sus demonios, trata de convencernos de que tiene un dragón preso en su garaje. Solo que el dragón no tiene peso, flota,</t>
+  </si>
+  <si>
+    <t>de Canarias. Para poder percibir los poquísimos fotones o partículas de luz que nos llegan del pasado rayos de remotas explosiones que ocurrieron hace miles de millones de años, cuando el Sol y la Tierra no se habían formado todavía es necesario tener la atmósfera más serena y transparente posible, y mucha oscuridad. Por eso el alumbrado público en la isla de La Palma es muy tenue, casi inexistente, y la noche se parece de verdad a la noche, que cuanto más oscura es, más noche parece. Estando en La Palma me di cuenta de algo en lo que nunca había pensado: las islas no están aisladas; lo que de verdad nos aísla son las montañas. Cristóbal Colón, se nos enseña, salió de Huelva el 3 de agosto de 1492. Si lo estudiamos bien, en realidad salió por última vez de un territorio español el 6 de septiembre, y concretamente</t>
+  </si>
+  <si>
+    <t>entre conocer el Millennium Falcon , un simulador maravilloso de la preparación para ser parte del equipo de pilotos de la nave espacial, y disfrutar de un día normal en una galaxia muy muy lejana cerca de la princesa Leía, Chewbacca arreglando su avión o los troopers vigilando la zona. Cada detalle es impecable, no hay un solo momento donde uno pueda dejar de soñar que a la vuelta de la esquina estarán R2D2 con Luke Skywalker esperándonos. Y creo firmemente que la oportunidad de conocer Batuu Un planeta remoto, cubierto con bosques y montañas, localizado en el borde exterior de los territorios de la galaxia de La guerra de las galaxias , siendo el puesto de avanzada justo antes del Espacio Salvaje, según explicó Erin Glover, del equipo de comunicaciones de Disney, en agosto de 2015 cuando se anunció la construcción de esta experiencia no solo nos alegró el</t>
+  </si>
+  <si>
+    <t>Con la agudeza, el buen humor y la exactitud de siempre, Le Carré se embarca en una aventura hiperriesgosa: mostrar la cara oculta de la luna del espionaje. Basándose en hechos y personajes de su primer best seller The Spy Who Came in from the Cold El espía que surgió del frío , 1963, se pone a esculcar en lo no visto y no escrito de la novela a lo negra espalda del tiempo, como hace Javier Marías para revelarnos secretos y misterios del pasado heroico de la Guerra Fría, ya olvidado y estigmatizado ad nauseam por los millennials . Poco a poco, con ladina destreza, vamos descubriendo la madeja de la vida de dos antiguos, célebres y entrañables espías cornwellianos: Georges Smiley y Peter Guillam. Smiley, gordiflón, miope e inteligente, encarna la perseverancia y la honestidad de los mejores guerreros del Circus contra el Centro de Moscú, comandado por</t>
+  </si>
+  <si>
+    <t>a velocidades que indican más cercanía o lejanía, en proporciones espaciales perfectas. Las abejas disponen en la parte superior de la cabeza de un trío de ocelos capaces de detectar la polarización de la radiación UV emitida por el sol, y gracias a esto se pueden orientar incluso en un cielo nublado. Estoy leyendo un libro precioso: , de Maurice Maeterlinck, bellamente editado por Taller de Edición Rocca. En él aprendo más asuntos asombrosos sobre las abejas y me alegro cada día más de convivir con ellas. Así como hay millones de abejas enseñando matemáticas y produciendo miel, debería haber millones de obreros humanos sembrando árboles y flores, y algunos puñados de matemáticos y científicos desentrañando sus cálculos y descifrando el dialecto de su danza.</t>
+  </si>
+  <si>
+    <t>máquinas, y exigir tiempos para el descanso y la reflexión. Los Tres Ochos de los mártires de Chicago, y de otros mártires y héroes en otras coordenadas, racionalizó los turnos laborales. El tiempo de lo sagrado, de la ritual, de los mitos y las ceremonias deíficas, el tiempo litúrgico, es, ¡claro!, distinto al de la profana producción. La modernidad tiene, entre sus distinciones, la de convertir al sujeto en una distribución temporal, distinta a la del bíblico Eclesiastés. Cuando el trabajo no permite pensar, ni abre compuertas hacia la crítica y a la formulación de juicios, entonces es parte de una enajenación. Cuando alguien y, como dicen físicos, poetas y filósofos, todos estamos hechos de tiempo distingue con propiedad el antes, el después y el todavía, se acerca a una suerte de dominio de la temporalidad, de la conciencia de ser. Ha conquistado la gracia de vivir. A lo León</t>
+  </si>
+  <si>
+    <t>árboles de 40 metros de altura y troncos de hasta ocho metros de diámetro y varias toneladas de peso, tapizados con cortinas de helechos prehistóricos que absorben casi por completo cualquier vibración del aire. Si usted busca algo más silente, lo puede encontrar en los laboratorios Orfield en Minnesota, donde crearon un engendro que no se le ocurrió ni a Ray Bradbury, la cámara anecoica. Es un sistema cerrado de absorción de sonido, hecho de acero y fibra de vidrio y revestido interiormente con una superficie de tabiques piramidales resortados semejante a los panales de huevos de los estudios pobres que absorbe hasta un 99 de los ruidos del recinto. Es la mejor aproximación lograda hasta ahora al grado cero del sonido. Un lugar endemoniado donde no existe la reverberación. La cámara de antisonido. El uso no controlado de estas cámaras es peligroso porque, explican los neurólogos, la carencia total</t>
+  </si>
+  <si>
+    <t>cuanto esta tiene de transformadora y revolucionaria, como vamos a convenir la convivencia y ese recién alcanzado clima de unidad nacional que es la convivencia pacífica, extrañada por más de medio siglo de la faz de la nación como derecho natural. Y menos constriñendo y supeditando la paz, razón política superior y su logro necesidad de Estado porque convoca el país nacional en todos sus matices, a las sectas, movimientos, partidos, liderazgos y centros de poder más reaccionarios que registre nuestra historia, cuyo horizonte inmóvil de política y nación apenas si alcanza y confunde con el de sus tradiciones, usos y costumbres. Revocar las Cortes, derogar la JEP, extraditar a Santrich, marcha uribista contra las cortes, entre otras prescripciones de un breviario apócrifo, no es la medicina para una crisis institucional que no existe; que se han inventado los usufructuarios y promotores ideológicos del Estado de opinión para sustentar sus</t>
+  </si>
+  <si>
+    <t>puede escribir sobre cosas que uno ha llevado largo tiempo en la cabeza y en el corazón. Nadie puede decir, digamos, voy a investigar esta noche sobre partículas de altas energías porque tengo que hacer un ensayo físico mañana. No. Como diría san Agustín, no es bueno investigar pero es bueno haber investigado. Un buen ensayista tiene que saberlo todo sobre su materia, incluso qué es lo que los lectores saben por ejemplo, que Montaigne es el padre, para no andar repitiendo vejeces. El ensayo exige primicias y, algo que olvidan muchos, tensión. Sin tensión, la reflexión resulta flácida, enciclopédica. Académica, en el sentido tedioso del adjetivo. Pedirle rigor es un contrasentido porque el ensayo es eso, una prueba, un ejercicio, no una monografía. Es un boceto, no un óleo. Una cometa, no un ladrillo. No sentencia, especula. No repta a punta de penosos silogismos: vuela. La erudición, que es</t>
+  </si>
+  <si>
+    <t>pausas, todo es barullo. La música es inseparable del ritmo, una sucesión de sonidos separados con intervalos cortos de silencios simétricos. El cine es una alternación de fotogramas y pantallas en blanco, invisibles por el fenómeno de la persistencia de las imágenes en la retina. Entre plato y plato, el lava sus papilas con pan, vino o cítricos frapeados. El perfumista lava sus mucosas aspirando café finamente molido. El fotógrafo encuadra, es decir, privilegia un fragmento del mundo y silencia el resto. Escribir es tachar. Y pausar. El doble espacio, las comas y los puntos son pausas, silencios. La literatura es un mensaje encriptado cuyo sentido oscila entre lo que el autor dice y lo que el lector adivina. Hemingway la imaginó como un iceberg: el texto, la parte visible, está sostenido sobre una masa invisible de sucesos implícitos. Los pitagóricos amaban el silencio, túnel que llevaba a la trascendencia está sostenido sobre una masa invisible de sucesos implícitos. Los pitagóricos amaban el silencio, túnel que llevaba a la trascendencia metafísica. Antes de ser admitido en la secta, el aspirante debía pasar largas pruebas de silencio para alcanzar el magisterio de la palabra exacta sin ruidos, decimos hoy. Al principio fue el verbo, dicen las Escrituras. Falso, al principio fue el silencio, y así será el final.</t>
+  </si>
+  <si>
+    <t>Corea, Zona desmilitarizada DMZ. La ola de calor que azota esta parte del mundo no da tregua tampoco, en esta quizás la última frontera de la guerra fría. El mercurio marca 37 grados. Establecida al final de la guerra de Corea, la DMZ es una de esas creaciones del ser humano perfectas para películas de ciencia ficción. Dos kilómetros a lado y lado del paralelo 38, frontera natural entre las dos Coreas, una nación dividida por los avatares de la historia, legado que ni el final de la guerra fría logró deshacer. Las otras dos naciones que quedaron divididas al final de la segunda guerra mundial; Vietnam y Alemania ya borraron de su geografía esa frontera artificial impuesta por los de afuera; la primera reunificada bajo la dominación del norte comunista, la segunda absorbida por la poderosa República Federal. En la península coreana se escenificó el mayor capítulo caliente de</t>
+  </si>
+  <si>
+    <t>la puerta a la intuición, la facultad de comprender sin necesidad de razonar. Todos alguna vez hemos reconocido nuestra capacidad intuitiva cuando, en relámpagos de lucidez, llegamos a conclusiones inesperadas e irrefutables. De forma similar a los koans, muchos de los dogmas cristianos están por encima del raciocinio convencional. Cuando durante la oración evocamos los misterios de la religión, ¿estamos declarando nuestra fe ilimitada? ¿O, más bien, estamos utilizando koans con la intención escondida de trascender la lógica corriente? Tomemos del credo cristiano algunos ejemplos de potenciales koans occidentales: Creo en Jesucristo, nacido del Padre antes de todos los siglos Engendrado, no creado, para nuestra salvación Espero la resurrección de los muertos.... ¿No nos sacan estos enunciados de la forma estándar de pensar? Comparemos las frases anteriores con dos koans, el ya citado y otro más, también muy reconocido en la escuela Rinzai: Dos manos cuando aplauden generan un sonido,</t>
+  </si>
+  <si>
+    <t>Al lado de las competencias de los Juegos Olímpicos de PyeongChang, que se desarrollan bajo el frío extremo del invierno coreano, tiene lugar, en los mismos escenarios, un proceso político de alta temperatura, ante la publicitada presencia de delegados de alto rango del gobierno norcoreano de Pyongyang. A la manera de los juegos antiguos, cuando las ciudades helénicas suspendían hostilidades para competir en los campos apacibles de Olympía, bajo la premisa de la búsqueda de armonía entre el cuerpo y el espíritu, las competencias de nuestra era pueden ser propicias para que los más caracterizados contradictores políticos aprovechen cada oportunidad olímpica para el encuentro y el diálogo. Después de todo, o mejor antes que todo, además de la competencia deportiva honesta, bajo reglas claras y comunes, el espíritu del olimpismo implica esencialmente un esfuerzo en favor del respeto, el entendimiento entre las naciones, y la paz. Por lo tanto no</t>
+  </si>
+  <si>
+    <t>a los físicos que manejan esas pequeñeces. Lo mencioné para demostrar lo que dije de la inexistencia física del mediodía y de la medianoche; porque tan pronto se llega a una de ellas se está saliendo también porque el tiempo no se detiene. Como todas las horas están referidas al meridiem se encuentra dificultad cuando el inicio o la terminación es la media noche, Ese instante, si es terminal, pudiera incluirse entre los posts meridiem y, si es inicial, en los antes meridiem . Eso dificultaría el nombre único, por lo que mejor se habla de la media noche y el texto dirá si la media noche es inicial o terminal. De la academia uno a uno de los homenajeados desfiló ante los demás estudiantes, familias, docentes e invitados al evento, para ser enaltecidos en alguna de las siguientes categorías. Al parecer, el escritor consideró que la expresión uno a evento, para ser enaltecidos en alguna de las siguientes categorías. Al parecer, el escritor consideró que la expresión uno a uno fuera singular; la confundió con ...cada uno de los homenajeados desfiló y por eso la concordancia la puso en singular, pero cuando aparece el participio enaltecidos. Imposible volverlo singular; así la expresión sustantiva uno a uno es plural: uno a uno los homenajeados desfilaron para ser enaltecidos en alguna de las siguientes categorías. Sobra, entonces la palabra que. Si estoy equivocado con estas suposiciones, agradeceré las observaciones.</t>
+  </si>
+  <si>
+    <t>El Estadonación continúa como eje de la división geográfica mundial, luego de estancamientos y fracasos de integraciones regionales. Su principal avance fue la Unión Europea y el Grupo Andino lo fue en nuestro entorno, aunque fracasó. Así mismo, el modelo de democracia liberal es el mejor, aunque con variantes: complejas, como en Estados Unidos, y sencillas, en países de la región. Los Estados tienen mayor o menor fortaleza política, al igual que las formaciones nacionales, en parte por las complejidades geográficas. Colombia es uno de los países con mayor complejidad geográfica, lo que afecta su formación nacional y estatal. Sin embargo, los efectos negativos al respecto tienen que ver más con factores políticos. Desde los inicios de su modernización capitalista, finalizada la Segunda Guerra Mundial, el Estado ha sido incapaz de ocupar de manera legítima territorios dispersos en más de la mitad de su extensión. También hay departamentos, como Antioquia,</t>
+  </si>
+  <si>
+    <t>Sito en la parte central de la región Caribe, norte de Colombia, entre el río Cauca y el mar Caribe, Sucre, aunque es el departamento de Colombia en el que brilla más el sol, presenta un cuadro de pobreza por encima de la media nacional que contrasta con su luminosidad y fulgor. Igual que calcinante es el contraste que se observa entre su precario desempeño económico y social y el potencial de sus abundantes factores de producción, tierras, ganados, recursos hídricos, energéticos, capital humano, hoy limitados en su productividad, uso, transformación y generación de demanda, empleo y riqueza, imprescindibles para coadyuvar de manera efectiva y expedita a reducir las agudas disparidades de orden social y humano que sitian e inmovilizan su desarrollo. A la vez que las de crecimiento y desarrollo económico integral, a partir de la implementación de un modelo económico local que, teniendo como base los factores de</t>
+  </si>
+  <si>
+    <t>la costa europea. La antigua idea francesa de entender al África, o al menos el Magreb, como su domaine réservée, tiene cada vez menos posibilidades de convertirse en realidad. Y ello es así porque el escenario africano se ha convertido, otra vez, en una especie de territorio de ambiciones, animada por una especie de fiebre del oro. En las acciones de búsqueda de fortuna propias de esa fiebre participan todas las potencias de nuestro tiempo, salvo claro está los Estados Unidos, que bajo Trump no muestran interés por el continente negro. China, Rusia y otros, tienen sus ojos puestos en las oportunidades de fortalecer su presencia en países africanos. China, por supuesto, resulta ser la más decidida y dinámica, conforme a propósitos claros, en su búsqueda por consolidar una presencia fuerte en el continente africano, al punto que el Presidente Macron, rememorando los tradicionales designios franceses y europeos respecto del</t>
+  </si>
+  <si>
+    <t>no lo es. Por eso han existido, y sobreviven, enfoques distintos, según se trate de Egipto o el Magreb, que cubren la costa sur del Mediterráneo, o de los países subsaharianos, que a su vez admiten agrupaciones según relación cultural derivada de los antiguos pactos coloniales, o afinidades políticas o institucionales que facilitan procesos de cooperación. Trabajar con África y no hacia África, parece ser el lema de una nueva actitud de parte de los antiguos explotadores y luego más o menos benefactores de un continente que ahora no necesita padrinos sino socios. Continente que, además, en su expresión mediterránea, tiene bien puestas unas cuántas basas en Europa continental, como lo puede atestiguar el paisaje contemporáneo de Marsella, para citar solo un ejemplo, que resulta una nítida prolongación africana en la costa europea. La antigua idea francesa de entender al África, o al menos el Magreb, como su domaine réservée,</t>
+  </si>
+  <si>
+    <t>en la primaria, cuando dibujaba con colores las venas azules que se desprendían de las montañas para unirse, curvas y meandros adelante, a las líneas azules más gordas, que eran en mi mapa el Magdalena, el Cauca, el Caquetá, el Atrato, el Meta, el Patía. Cuando terminaba la tarea de geografía de los ríos y las cuencas de Colombia, mi país era como el cuerpo humano en la cartelera de ciencias, lleno de venas que transportan líquido vital a todo el organismo. Somos un país tremendamente privilegiado, decía Gustavo, porque nuestras grandes cuencas están alimentadas por ríos que nacen y mueren en el país. Esto significa que, en términos administrativos y políticos, afectar o proteger nuestros ríos nos incumbe exclusivamente a nosotros mismos, a los colombianos. Por ejemplo, no tenemos los problemas del Nilo que atraviesa 10 países, o el Amazonas que rueda por 9, de manera que cualquier política</t>
+  </si>
+  <si>
+    <t>Pacífico en la superficie se encuentra 0,7 C sobre el promedio de tiempos normales, aumento que se considera elevado. En diciembre promediaba 1,0 C. Los fenómenos de El Niño promedio los llaman El Niño 3.4 y en ellos la temperatura se eleva 0,5 C. En las profundidades del océano ecuatorial en el centro y este, costas de Colombia, las temperaturas también están por encima del promedio. Pero los vientos bajos y altos, los que soplan del mar hacia nuestro litoral Pacífico se encuentran en niveles cercanos al promedio. Esta parece ser la única buena noticia. La organización World Meteorological Organization WMO comentó en su último informe, hace pocos días: La actualización más reciente de las temperaturas en la superficie del océano Pacifico, tanto al este como en su centro, permanecen desde octubre en los niveles bajos característicos de un El Niño débil, lo que predice un evento que se inicie desde octubre en los niveles bajos característicos de un El Niño débil, lo que predice un evento que se inicie en diciembre y que termine en marzo con el 90 de probabilidad y con el 60 de que termine en junio. Coinciden con la NOAA.</t>
   </si>
   <si>
     <t>misma de sus tejidos. Se inscribió en sus estructuras. Destila de sus muros y verdines. Cuelga sobre el sopor de su vista oceánica y su bahía. Está en los espectros que leyó el gran Joe Arroyo en su melodía sobre una historia cartagenera de liberación. Está en lo que palpita y supura en sus geografías en el esplendor de edificios blancos almidonados que roza contra la desidia de sus terrenos polvorientos y despojados. El contraste abrasivo entre un punto y otro en la misma ciudad. Toda Cartagena de Indias contiene en sí misma la llaga de su virulencia racial. De allí que ciertas iconografías que se han instalado en su paisaje visual puedan suscitar malestar en quien las mira. En la medida en que Cartagena de Indias se ha elevado como enclave de casamientos a nivel global, una escena se ha hecho frecuente en sus postales festivas: la comitiva de</t>
   </si>
   <si>
-    <t>metaarchipiélago sin centro ni límites. Esas ideas corresponden al escritor cubano Antonio Benítez Rojo, quien verbalizó con habilidad magnífica algo que nunca se ha desprendido de mí, cazadora furtiva que soy a la hora comprender y discernir el temperamento de mi propia subjetividad y lugar de origen el Caribe. Esa lectura permite entender entonces al Caribe no sólo como un sitio meramente geográfico sino como un cualidad que se codifica en su capacidad de derramamiento, de desborde, de supersincretismo. Como algo que no se restringe a la ubicación geográfica, sino como algo que reta en sí mismo a lo estático, lo preciso. Es evidente que para una relectura del Caribe hay que visitar las fuentes elusivas de donde manaron los variadísimos elementos que contribuyeron a la formación de su cultura. Este viaje imprevisto nos tienta porque, en cuanto logramos identificar por separado los distintos elementos de alguna manifestación supersincrética que</t>
-  </si>
-  <si>
-    <t>comunidades. Desde la Colonia han violado los ríos: Los españoles tenían minas de oro, sobre todo en la cordillera Occidental, la que mira al mar Pacífico. Ahí siempre ha habido mucho oro, miles de toneladas de oro se han sacado de los ríos y quebradas que llevan el agua al océano. A los esclavos negros nunca se les pagaba por su trabajo, solo se les alimentaba para que no se murieran, y cada uno, según su fuerza y salud, valía, dice un fragmento de Cartas a Antonia. Es pertinente, hoy y siempre, el libro del sociólogo y periodista de saco rojo y tenis Converse. Lo es, entre muchas cosas, porque nos recuerda lo infinitamente indolentes que hemos sido con nuestros ríos y las comunidades que viven de ellos, aunque, por fortuna, siempre aparecen ciudadanos salvadores. Esta vez, ellos están en Florencia, Caquetá, y su propósito es lograr la declaración como</t>
-  </si>
-  <si>
-    <t>América para los americanos dejó claro que, del río Bravo para abajo, Latinoamérica carga con el destino de ser el escudo protector de los intereses comerciales de los Estados Unidos. Circulando en esa órbita nos han pasado ya dos siglos. Muchos presidentes han gobernado aquí y allá, pero las relaciones bilaterales de Colombia con los Estados se pueden resumir en un rango que va de la sumisión a la genuflexión, sin pasar jamás por la desobediencia. Y en esta historia común, a la potencia nunca le ha faltado un enemigo en contra del cual alinearnos. Si en el siglo pasado fue el comunismo, en este el que amenaza los intereses de Estados Unidos en su patio trasero se llama China. El gigante asiático está poniendo el más estratégico mojón en estas tierras por la vía de oxigenar a Maduro a cambio de petróleo. En una década, en transacciones rastreables, China</t>
-  </si>
-  <si>
-    <t>y los humanos proporciona a los segundos invaluables destrezas cognitivas, que emplean para concebir variados ordenamientos del mundo y ello se refleja en sus formas de organización social y territorial. Contrario a lo que podría pensarse, el mar está siempre a nuestro lado, pues las conexiones e interacciones con este no son exclusivas de los habitantes del litoral. Quienes habitan el interior tienen sus propias representaciones de los océanos y mares, que se manifiestan en las elaboraciones pictóricas que adornan una biblioteca en una remota ciudad o en un caracol que guarda el sonido del mar detrás de la puerta de una cabaña en la cordillera. Dolorosamente, también estas conexiones con ríos contaminados y con grandes centros poblados del interior del continente se reflejan en los espacios haliéuticos. ¿Debe, por tanto, el pequeño municipio de Puerto Colombia, u otros que podrían ser afectados, asumir en soledad la responsabilidad de limpiar</t>
-  </si>
-  <si>
-    <t>kilómetros cuadrados de superficie, se mueve dentro de la escala media de las corrientes receptivas del planeta, pero no es un destino caracterizado por las oleadas del turismo de masas. Recibe el 4 de las llegadas aéreas internacionales y el 1,7 de los ingresos de la industria por este concepto. En 2016 fue el refugio de 24,5 millones de viajeros del exterior y a sus arcas entró una jugosa tajada de US8.000 millones. Visa, que reina en esta república que tiene entre sus 146 millones de habitantes un alto nivel de bancarización y generalizado uso de tarjetas de crédito, proyecta para la temporada un aumento del 10 en el ingreso de turistas y un incremento en el gasto individual por encima del 31 con respecto al visitante de época normal logrado cuatro años atrás en las húmedas pero soleadas tierras cariocas. Tradicionalmente entre junio y julio se movilizan por Rusia</t>
-  </si>
-  <si>
-    <t>la isla, 62 mujeres, concedieron asistencia médica en sitios lejanos del país, barrios periféricos de grandes ciudades, aldeas indígenas y municipios ubicados en el interior de Brasil, lugares adonde los médicos brasileños históricamente se negaban a ir y la ausencia del Estado era una triste realidad. Se estima que en cinco años ellos atendieron a 113 millones de pacientes y 700 municipios tuvieron por primera vez un médico, todos ellos provenientes de Cuba. La diplomacia médica cubana representa la entrada de millones de dólares e incrementa su presencia y su poder en el mundo, sin embargo no deja de suscitar complejas discusiones. Según algunos analistas, Cuba alquila sus médicos, otros opinan que los esclaviza y muchos afirman que presta servicios solidarios, pero en palabras de uno de los médicos: Nadie sale de la isla engañado. Con el retiro de Cuba del Programa Más Médicos, Brasil tendrá que sustituir rápidamente a</t>
-  </si>
-  <si>
-    <t>de esta batalla, son los médicos, que a diario se enfrentan con el temor del contagio y aun así se levantan para ir al frente y librar la batalla con el enemigo. Desafortunadamente, ni siquiera los discípulos de Esculapio tienen la mínima garantía de seguridad, económica o de salud, tanto para ellos como para sus familias. La abogada Andrea Collazos, representante de la asociación Asociarte Global, entidad de médicos colombianos dedicada a formalizar garantías para su gremio, afirma lo siguiente: Este es el momento de hacer un llamado a gritos al Gobierno Nacional, que después de varios años de pasos errados en la construcción de la Ley 100 de 1993 tiene como consecuencia EPS e IPS quebradas, un deficiente amparo al derecho que tienen las personas a acceder a un sistema de salud eficiente y condiciones laborales precarias para los médicos en Colombia. Los sistemas de salud en el mundo</t>
-  </si>
-  <si>
-    <t>Dosis personal excepción al delito. Reforma constitucional, estupefacientes como asunto de salud pública. Leyes mantienen delito y Corte Constitucional dosis personal. Corte Suprema de Justica considera que no es delito el aprovisionamiento. Código de Policía, porte de droga afecta la actividad económica y prevé su destrucción. Cúmulo de errores. Propuesta de decreto parece innecesaria. La Ley 30 de 1986 estableció la dosis personal como una excepción al delito de porte de drogas ilícitas, que fue declarada exequible por sentencia de la Corte Constitucional, con ponencia de Carlos Gaviria Díaz, que se refirió al libre desarrollo de la personalidad. En 2009 se reformó la Constitución, para disponer que porte y consumo de estupefacientes está prohibido, salvo prescripción médica. La ley establecería tratamientos preventivos o rehabilitadores. La Corte Constitucional declaró exequible la reforma, en el entendido que la drogadicción se trataba de un asunto de salud pública, que no sería aplicable a</t>
-  </si>
-  <si>
-    <t>cannábicas, mientras que otros acceden a la sustancia a través de ciertas farmacias autorizadas para vender una marihuana producida estatalmente. Todo eso sometido a reglamentaciones estrictas para evitar abusos, como la venta a menores de edad. La puesta en marcha de esta política no ha sido fácil, pero su funcionamiento ha permitido disipar la mayor parte de los temores de quienes se opusieron a esa audaz medida. Además, la política ha tenido efectos benéficos para los usuarios, que ya no tienen que acudir a redes de distribución criminales, no son discriminados y reciben una sustancia de calidad controlada. Esto explica que el apoyo ciudadano a esta política esté creciendo. Obviamente el esquema uruguayo dista de ser perfecto, por lo que es probable que, a medida que se hagan seguimientos más precisos, sea necesario introducirle ajustes. Pero Uruguay está mostrando que es posible una política frente a la marihuana más racional</t>
-  </si>
-  <si>
-    <t>Hace 100 años se implantaban las primeras prohibiciones mundiales frente a las drogas hachís, opiáceos, cocaína en la llamada Sociedad de Naciones. El fin de la Primera Guerra dejaba espacio para nuevas preocupaciones y los Estados Unidos asumían un liderazgo para prohibir el suministro de drogas con fines de consumo abusivo. Se abría un espacio para los lucrativos negocios del narcotráfico. Las grandes farmacéuticas se encargaron de inaugurar rutas y mercados y ponerle una cara menos fiera al comercio. Una familia distinguida de Basilea, en Suiza, está en los orígenes de las grandes riquezas y las tristes persecuciones que han llegado a simbolizar el carrusel de la guerra contra las drogas. Inspirado en un idealismo que, como diría Paul Valéry, es además una especie de resentimiento. En 1894, Fritz Hoffmann, el hijo díscolo de un comerciante de Basilea, se casó con Adle La Roche, heredera de otra casa comercial en</t>
-  </si>
-  <si>
-    <t>investigada y judicializada por la policía judicial de Ocaña. Aprovecha la situación para recordar que la Policía de Norte de Santander pide a las madres no realizar estas prácticas e invita a la ciudadanía a delatar a mujeres que incurran en ellas. Se reitera de esta forma que la comunidad debe denunciar este tipo de hechos marcando a la línea única de emergencias. Según información de la Defensoría del Pueblo, los tres hospitales públicos de Ocaña se niegan a practicar cualquier tipo de terminación del embarazo incluso en los escenarios previstos por la ley y entregan a mujeres y adolescentes sospechosas de aborto a la policía judicial. Además del Emiro Quintero, están el Hospital de San Antonio y el Hospital de la Torcoroma. Este último hace homenaje, con su nombre, a la Virgen de Torcoroma, que según cuenta la leyenda apareció en una montaña del municipio en el año 1711.</t>
-  </si>
-  <si>
-    <t>bastante conservadora: no al porte de dosis mínima, no al aborto, no a la adopción de niños por parejas del mismo sexo y un empate en la fumigación. La imagen del doctor Uribe no ha vuelto a las cotas positivas que lo han acompañado por largo rato. Pero la mala imagen sí ha caído y mejorado en igual proporción su favorabilidad. Al calcar esta gráfica con la imagen de la Corte Suprema, hay una armonía indiscutible. Y perversa. Cada uno ha rebajado su desfavorabilidad en igual proporción. Ambos sacan ventaja aunque se mantienen en la esfera negativa. En el largo plazo, pierde el país. En estos seis meses la imagen negativa de Petro ha crecido. ¿Qué pensará? La democracia es disenso. Pero aquí lo que vemos es la presencia creciente de fallas geológicas en nuestra organización estatal y social. El primer acuerdo sobre lo fundamental es el acuerdo para el de fallas geológicas en nuestra organización estatal y social. El primer acuerdo sobre lo fundamental es el acuerdo para el desacuerdo. Un desacuerdo que preserve lo esencial. Coda.: Nuevamente ataca el dolor por la muerte de Chucho Bejarano. Qué desperdicio. Buena la entrevista de Francia Márquez. Se necesitan más mujeres.</t>
-  </si>
-  <si>
-    <t>país con el que nos medimos. ¡Nada pequeños! El ciclismo es nuestro. Quizá como el fútbol para argentinos y brasileños o el atletismo para jamaiquinos. Si uno compara ciclismo y fútbol, debiera admitir que en este último son muchas más las desilusiones, lo que refuerza la mentalidad de país derrotado. Mis vecinos querían ver la carrera, pero solo a partir de las 12 lo lograban por ESPN Internacional. ¡Qué tiene el fútbol que, aun mediocres como somos, nos clavan una tercera parte de las noticias para decirnos que James hizo un pase gol! La otra noticia es aún más diciente: ¡Falcao y James cambiaron de corte de pelo, vaya belleza! El ciclismo sí que retrata a Colombia. Nuestra geografía, nuestras destartaladas carreteras; las montañas de Antioquia y Boyacá, que son la base del poderío. La diferencia entre Rigo, Mijitos... huevones..., y Nairo, silente, es la misma que entre paisas y</t>
-  </si>
-  <si>
-    <t>trasero y ya es tiempo de que le dé su lugar, si de verdad quiere tener una influencia fuerte en la región. La autoridad la estaba perdiendo cuando casi la totalidad del mapa en América Latina estaba hacia la izquierda. Para poder lograr tener una influencia positiva, tiene que invertir en la región, de lo contrario China seguirá haciéndolo y Estados Unidos perderá la menguada influencia que le queda. Trump está ejerciendo presión sobre los productos importados de China, pero eso no necesariamente es suficiente para triunfar en las elecciones. Si su resultado es muy apretado, la democracia más vieja del mundo se enfrentará a una situación muy difícil. A primera vista un triunfo de Trump sería ideal, pero a largo plazo si gana Biden sería mejor para el mundo y para la tierra. y para la tierra.</t>
-  </si>
-  <si>
-    <t>Cada vez que aterrizaba en Rionegro no veía la hora de salir del aeropuerto para buscar un buen chicharrón con arepa en la carretera que lleva a Medellín. Este recorrido, que para muchos solía ser tedioso, para mí era todo disfrute, pues a medida que uno recorría un espectáculo de naturaleza poco a poco se iba adentrando en una de las ciudades de mayor desarrollo y calidad de vida del país. La vía por Las Palmas, llena de viveros, flores y restaurantes, no es solo un paseo de camino a la Capital de la Montaña, sino también un plan perfecto para disfrutar en familia los fines de semana, para una tarde con amigos luego de la jornada de trabajo, o para una escapada con colegas en medio de un congreso o cualquier evento que los lleve a Medallo. Y ahora, con el nuevo Túnel de Oriente, este paseo tiene un</t>
-  </si>
-  <si>
-    <t>Todos los días salimos a la calle. Todos los días caminamos tranquilos, yendo hacia el trabajo o dirigiéndonos hacia la parada del bus, o estirando la mano para tomar un taxi, o abriendo la puerta del carro en los afanes de llegar a tiempo a alguna parte. Todos los días salimos a hacer nuestras cosas, a vivir nuestras vidas y curiosamente, en las prisas y los aspavientos de la vida cotidiana, siempre sacamos algunos instantes para levantar los ojos al firmamento. Es como si quisiéramos ver qué presagios nos trae el cielo, como si en el cielo se pudiera leer todo lo que pasa o todo los que nos va a ocurrir. Por lo general, la atmósfera está limpia o puede traer consigo alguna que otra nube que nos habla de la proximidad de las lluvias. En ese momento podemos llegar a pensar que todo está bien, que los días</t>
-  </si>
-  <si>
-    <t>Diciembre es un tiempo de verano en Bogotá y sus municipios vecinos. Son días en que los capitalinos se calzan las gafas de sol y tiran a un rincón la sombrilla. Cuando era niño, eran los días perfectos para remontar el río Teusacá, saltando de piedra en piedra, chapoteando en sus hondos y persiguiendo truchas, que las había en esos días no tan lejanos. Ahora, los días veraniegos me traen la angustia de cuándo el agua se acabará. Y es que este año ha sido de intenso verano; si tuvimos tres semanas de lluvias en el segundo semestre fue mucho, y en La Calera, donde nace el agua de reserva para Bogotá, paradójicamente sus habitantes sufrimos por la carencia del recurso. Es una paradoja que parece ser lógica en nuestro modelo de desarrollo. En Chocó, la región donde más días llueve al año en el mundo, la gente vive sin</t>
-  </si>
-  <si>
-    <t>Estas noches ha llovido tanto que toda el agua no podría caber en un verso de César Vallejo. Es un golpeteo constante sobre las ventanas que me mantiene en vigilia: el sonido se siente cercano y al fondo los truenos alumbran el cielo. A veces solo escucho el estruendo ronco sin luz y no importa aclarar la mirada para buscar del otro lado, porque todo está oscuro. Desde hace días las noches son así en la ciudad: un ta ta, clap clap, plap plap, que suena dispar en las ventanas de la casa, como si un coro de agua nos recordara los tiempos que estamos viviendo. Entonces no basta abrir los ojos para saber que estoy despierto, ni hacer vanos intentos para dormir de nuevo: contar las gotas o tratar de ubicar el punto exacto en que caen es un esfuerzo inútil, porque nada sirve para recuperar el sueño perdido.</t>
-  </si>
-  <si>
-    <t>examen. Los investigadores recogieron la información sobre la temperatura día a día en cada colegio y datos sobre si contaban con aire acondicionado o no. Adicionalmente, el estudio incorporó otras características medioambientales y socioeconómicas que podrían afectar el desempeño de los bachilleres. Con ese arsenal estadístico, encuentran que haber estado enfrentados a días escolares más calurosos el año anterior al examen redujo su desempeño. Los autores concluyen que el calor reduce la productividad del tiempo de instrucción en el aula: un aumento promedio de 1 F más o menos medio C, para el rango de temperaturas relevante para el estudio en días escolares reduce el aprendizaje en 1 . La buena noticia es que los efectos desaparecen si la institución analizada tiene aire acondicionado. También encuentran que los estudiantes pertenecientes a minorías o de bajos ingresos resultan más afectados. Sospecho que en Colombia debe pasar algo similar: los estudiantes de a minorías o de bajos ingresos resultan más afectados. Sospecho que en Colombia debe pasar algo similar: los estudiantes de ingresos altos seguramente asisten a colegios mejor climatizados. Podemos estar perpetuando nuestras brechas sociales mediante un canal insospechado y que empeorará con el cambio climático. Pero, a diferencia de otras causas de las brechas que son difíciles de romper, esta sí tiene una cura simple. Heat and Learning. Joshua Goodman, Michael Hurwitz, Jisung Park, and Jonathan Smith; NBER Working Paper N. 24639, 2018.</t>
-  </si>
-  <si>
-    <t>una tormenta, los pajaritos se esconden, pero las águilas vuelan más alto. En el tintero. Las ironías de la vida. 1 Mientras el presidente Duque instalaba la cumbre de inversión extranjera más importante del país, el senador Petro solicitaba al Parlamento Europeo suspender el acuerdo comercial entre Colombia y la Unión Europea. 2 Mientras empresarios del país comienzan a reactivar sus negocios por la reapertura del comercio, los indígenas preparan una minga para paralizar la economía del país. 3 Mientras la Fiscalía, la Procuraduría y la mayoría de los colombianos exigíamos la libertad del expresidente Álvaro Uribe, la JEP mantiene en el Congreso a los asesinos de Álvaro Gómez Hurtado. ¿Dónde están la fuerza pública y la justicia de este país? Consultor en acceso a crédito de fomento agropecuario.</t>
-  </si>
-  <si>
-    <t>líder, especie de mesías y redentor de su pueblo para liberarlo de las garras del mal. Ahí no hay espacio para la reflexión, solo para la emoción. Al futuro se llegaría como por encanto, un futuro que se pinta con los tonos más amables, con los cuales es difícil no estar de acuerdo; el problema es que ni los unos ni los otros, especialmente Petro, nos dicen cómo y cuándo vamos a llegar a la tierra prometida y, cual Moisés en el monte Sinaí, simplemente nos la señalan en un horizonte brumoso pero, tal vez por eso mismo, atractivo. Los que crecientemente proponen votar en blanco en dos semanas lo hacen porque no creen en la bondad y factibilidad de las dos propuestas presidenciales y consideran que más que ganar unas elecciones se trata de mirar más allá de la elección para ponerse en la tarea seria e inaplazable de unas elecciones se trata de mirar más allá de la elección para ponerse en la tarea seria e inaplazable de construir un camino cierto a un futuro posible, no simplemente imaginado, que depende del trabajo y compromiso continuado de todos o al menos de muchos, y no de la generosidad o visión de un caudillo iluminado. De los profetas y salvadores debemos proteger a nuestra deficiente democracia, para transformarla y no destruirla.</t>
-  </si>
-  <si>
-    <t>Empiezo esta nota acompañado por el adagio del Concierto para piano en la mayor n. 23 de Mozart. En el insomnio de anoche desde que hay peste me despierto a las tres con una sensación de angustia que solo se disipa con una hora de lectura leí pedazos de un libro sobre el silencio, del violonchelista Mario Brunello. Curioso un músico hablando del silencio, pero, como me dijo Gonzalo Ospina, el concertino de la Filarmónica de Medellín, sin silencio no hay música. Esto es verdad, sin duda, pero también es verdad que si lo único que hay es silencio, la música deja de existir. Una tristeza más que se añade a esta epidemia es que la música, la música en vivo, con los músicos y el público presentes en una sala, se ha vuelto un imposible en estos meses de aislamiento. Tenemos, claro está, las grabaciones, y yo mismo en</t>
-  </si>
-  <si>
-    <t>que su esposa pasó años buscando sus restos y que sus verdugos no le precisaban el lugar donde lo habían enterrado. Quizá no sabe que el profesor Atilio lideraba colegios satélites que permitían que niños de toda la región asistieran a clases. Versiones a Justicia y Paz de Salvatore Mancuso y Juan Manuel Borré han revelado que bajaron al profesor de su moto cuando volvía a casa después de un partido de sóftbol, lo golpearon, lo llevaron a un sector llamado El Totumo, lo torturaron y lo mataron. No saben si su cuerpo fue arrojado a una fosa común o lo echaron al río. Así que no se necesita adoctrinamiento, senador Uribe, para que una escuela tenga consciencia de lo importante que es educar para la paz y la democracia. Mucho menos cuando esa misma escuela ha vivido en su piel las crueldades de la guerra. No son unos niños</t>
-  </si>
-  <si>
-    <t>Pese a las evidencias y a las tragedias domésticas que ha suscitado su declive, los periódicos no han registrado aún la extinción paulatina de una antigua especie literaria: la escritora que lee por el mero gusto de leer. Mientras una lectora de asueto tiene el derecho bacanal de divertirse con su lectura, sin asumir ningún deber con su autora e incluso con el poder de olvidar lo leído una vez cierra el libro, la escritora, por prurito profesional, puede disfrutar siempre y cuando descubra, al final o en el medio, de qué se constituye su gozo. Cuando el libro es un somnífero, la lectora común puede desecharlo, apilarlo o convertirlo en papel para envolver regalos; en cambio, aun en el caso frecuente de los libros deplorables, la escritora siente un apuro por comprender por qué su mecanismo carraspea como el motor tartamudo de un camión en subida. Por desgracia, las</t>
-  </si>
-  <si>
-    <t>Cualquier semejanza con hechos ocurridos o posibles, o con personas e instituciones, es mera coincidencia COMPARTIR Asumo que todos recordamos las fábulas de Rafael Pombo. Solo mencionar algunas suscita nostalgia por la infancia remota y por los hijos que crecieron: El gato con botas, La pobre viejecita y Rin rin renacuajo quien, como recordarán, salió de su casa esta mañana muy tieso y muy majo. Es un género muy antiguo, que asigna a los animales virtudes y defectos que no son suyos sino humanos. Su creación se atribuye a Esopo, quien vivió en el siglo VI a. C. De las fábulas que he leído me fascina la colección de Kalila y Dimna, publicada en sánscrito por primera vez al comienzo de nuestra era; hay una bella edición reciente de Acantilado. Del siglo pasado, recomiendo Rebelión en la Granja de George Orwell para apreciar los abusos que caracterizan a los sistemas</t>
-  </si>
-  <si>
-    <t>cortinas de sus 1.500 habitaciones en aquel verano apestado y el césped crecía sin ley en los fastuosos jardines. Aunque la idea de patrimonio colectivo tal como la entendemos ahora es una construcción posterior y no está presente en los textos, estos pasajes representan una invitación a pensar las afectaciones sobre el patrimonio en tiempos de epidemias y pandemias. Sabemos que a raíz del COVID19 muchos museos y centros culturales de todo el mundo han construido recorridos virtuales para que la gente pueda acceder a colecciones del patrimonio artístico. Además, han tratado de generar espacios de interacción con el público que van desde la muestra en redes sociales de pinturas y esculturas en un estilo desenfadado, hasta invitaciones para que la gente se anime y envíe representaciones hechas en la cotidianidad de sus casas de situaciones de pinturas y fotografías reconocidas. Por supuesto, son estrategias para el confinamiento, pero los</t>
-  </si>
-  <si>
-    <t>Y él parece entender por dónde va el agua al molino: Creamos caos. Más que caos responde ella. Guerra dice Frank. Miedo agrega Claire. Miedo. Algo brutal completa Frank. Devastador. Podemos usar el miedo. Yes, we can remata Francis. Al día siguiente Underwood precipita la ejecución sangrienta en directo para la nación entera de un rehén norteamericano a manos de un grupo yihadista, y él queda al mando soberano de la situación por la vía del shock institucional que acaba de provocar, pero que pareciera culpa del otro bando. La doctrina del shock la viene aplicando desde que ocupó por primera vez la presidencia Álvaro Uribe Vélez, sujeto sub judice hoy investigado y sometido a indagatoria por la Corte Suprema, pero quien, gracias al descomunal poder que ha adquirido, está a punto de torcerle el cuello a la justicia para lograr que la Corte Constitucional decrete segunda instancia en la</t>
-  </si>
-  <si>
-    <t>dichas medidas, más aún cuando se considera que la expectativa de que miembros de la fuerza pública venezolana desertaran en masa no se ha materializado. Ante la inefectividad de las estrategias adoptadas hasta ahora y la renuencia a negociar con un dictador, poco a poco lo impensable se va tornando posible. Dejando de lado el espíritu intervencionista de Rubio y del consejero de seguridad nacional, John Bolton quienes le hablan al oído a Trump sobre Venezuela, sin un hecho determinante que obligue a Washington a iniciar una acción militar directa por ejemplo, la muerte de ciudadanos estadounidenses a manos de actores venezolanos, es improbable que ello ocurra. Sin embargo, la Casa Blanca y la Casa de Nariño han advertido que cualquier amenaza a la soberanía de Colombia o agresión contra Guaidó, respectivamente, obligaría a considerar otros mecanismos. Este lo que es con Colombia o con Guaidó es conmigo que une</t>
-  </si>
-  <si>
-    <t>siglo XXI, esto es a la vuelta de unos pocos años, no solamente se corre el riesgo del descongelamiento del Ártico, sino que se vería afectada la vida cotidiana en diferentes ciudades de todos los continentes, e incluso colapsarían actividades económicas de importancia. De ahí el firme llamado a que todo el mundo se comprometa a no pasar del límite de aumento de la temperatura en un punto y medio por ciento, dentro del mismo período. El desprecio que el extravagante presidente actual de los Estados Unidos ha proclamado por los problemas ambientales ha tenido en esta materia, como en otras, un efecto importante en el contexto de las acciones que a los gobernantes corresponde desarrollar. De manera que no son pocos los que participan de la arrogancia de los que se creen todopoderosos, así esté comprobado que nada pueden hacer contra fenómenos naturales que exceden el poderío de sus</t>
-  </si>
-  <si>
-    <t>a paso, el desarrollo de una epidemia que se convirtió en pandemia y puso al mundo entero patas arriba. Y en un ambiente tan contaminado, en donde el nuevo coronavirus ha infectado en el mundo a tantos millones de personas, ha sido indispensable que la población reciba una información detallada sobre cómo prevenir esa nueva peste, que puede ser letal. No obstante, abundan las personas rebeldes que, sintiéndose muy independientes y muy machas, se empeñan en salir y en hacer lo que les da la gana. Y, contraviniendo las recomendaciones de los médicos y las órdenes de las autoridades, se pasean por las calles como si nada. No tienen en cuenta que con su rebeldía se están exponiendo a contaminarse con un coronavirus que ha invadido casi todos los países del hemisferio, que tiene en cama a varios millones de personas y ha enviado al sepulcro a otros tantos. Con</t>
-  </si>
-  <si>
-    <t>temas, se casara con la idea de la paz a través del diálogo, y de que es preferible una paz injusta, si así considera la pactada con las Farc y la eventual con el ELN, a una guerra que él considere justa, pero que inevitablemente privilegia la muerte, el mayor de los males, sobre la vida, quizá el mayor de los bienes! ¡Quién lo creyera! Probablemente asistiremos en las próximas elecciones presidenciales a una reedición del plebiscito del 2 de octubre de 2016. En ese momento la pregunta fue: ¿Apoya el acuerdo final para la terminación del conflicto y construcción de una paz estable y duradera? El coordinador del Sí fue el expresidente César Gaviria. El Partido Liberal estaba, como seguramente sus bases continúan estándolo, comprometido sin atenuantes con la paz en todas sus expresiones. Como entonces, quizá surjan en esta campaña presidencial mentiras generalizadas en contra del Acuerdo con</t>
-  </si>
-  <si>
-    <t>partido hayan entendido o quieran entender o puedan entender de dónde viene el descontento o que al pobre Duque se le ocurra algo distinto de las exhortaciones babosas a la unidad sin negociar con nadie, la insistencia en que el Gobierno ha hecho lo que no ha hecho y la promesa de que no habrá reformas cuando esas reformas están por venir. Colombia está despertando del largo sueñopesadilla que se llamó el conflicto armado, el presidente eterno y el Acuerdo de Paz. Las guerrillas se acabaron hace tiempo y ahora siguen las protestas normales y legítimas en una democracia tan injusta y excluyente como es la que tenemos. El primer campanazo fue este paro que en realidad fue una marcha en el estilo peculiar de Colombia, mezcla de rebelión, descontento, vandalismo, caminata y fiesta ciudadana. Vendrán otros campanazos. Y tendrá que manejarlos el presidente inepto que elegimos. Escrita el viernes vandalismo, caminata y fiesta ciudadana. Vendrán otros campanazos. Y tendrá que manejarlos el presidente inepto que elegimos. Escrita el viernes a primera hora. Director de la revista digital Razón Pública .</t>
-  </si>
-  <si>
-    <t>Gustavo Petro desafió y pasó por encima de decisiones de los alcaldes de Medellín y Cúcuta, generando cada vez mayor polarización en el ambiente electoral. Cero y van dos ocasiones en las que el exalcalde de Bogotá y precandidato presidencial Gustavo Petro, contradice y desconoce las decisiones de las máximas autoridades locales de importantes ciudades de Colombia. Hace una semana el alcalde de Medellín, Federico Gutiérrez, aplicando la reglamentación vigente para la realización de manifestaciones políticas en la ciudad, trató de impedir que Petro organizara una reunión política sin cumplir el pleno de requisitos necesarios para una concentración superior a 500 personas, que, de acuerdo con las normas locales expedidas desde 2016, debería cumplir los requisitos de seguridad humana, matriz de riesgos tarima y sonido, servicio de logística y plano de evacuación, póliza de responsabilidad civil extracontractual, pago a derechos de autor, y documentación del grupo de aseo y servicios</t>
-  </si>
-  <si>
-    <t>de aquellos que no comparten el gusto por la pirotecnia. Así mismo, existen fuertes contextos educativos para sensibilizar a las personas particulares que se consideran entusiastas de estos productos y que desean celebrar con estos de manera privada. En Colombia la estigmatización moral de la pólvora ha prevenido que estos adelantos se materialicen y han invitado a que la gente siga comprando la misma pirotecnia que compraba hace 30 o 40 años, de manera clandestina. Esta es la pólvora que ataca la Representante Miranda, porque con seguridad es la que recuerda de sus celebraciones familiares, pero es una totalmente alejada de las realidades de la industria a nivel mundial y refleja su desconocimiento. Existe pirotecnia segura, así como alcohol consumido responsablemente y automóviles que han sido regulados en su diseño para reducir los riesgos al conductor. En estas industrias el riesgo asociado a estos productos se manejó elevando niveles de</t>
-  </si>
-  <si>
-    <t>Micrófonos químicamente enervados, cadenas de WhatsApp, trinos ligeros de contenido, fotomontajes, columnas con intereses ocultos, filtración de piezas de expedientes judiciales cuidadosamente editadas, informes periodísticos sin contrastación de fuentes y el activo radiopasillo hacen parte de toda la artillería disponible para acabar con el buen nombre o la reputación de una persona, entidad o funcionario público. No es un tema nuevo, por supuesto. Dicen el texto bíblico que Caín era la mata de la envidia, y desde ahí quedó con el rótulo de ser uno de los primeros fratricidas de la historia. Sócrates fue condenado a muerte por un rumor que circulaba por Atenas que lo señalaba de corromper a los jóvenes y promover deidades diferentes a las que guiaban sus vidas. Desde los tiempos de los griegos hasta nuestros días, el rumor, el chisme le ha ganado la carrera a lo fáctico. Esto ha sido una lucha constante en</t>
+    <t>puertos y muelles, la industria petroquímica, la acuicultura, pesca, agricultura y cárnicos, entre otros recursos y oportunidades que ofrece nuestra franja costera sucreña en el mar Caribe. Nuestro gobernador, conjuntamente con el DNP, los alcaldes de Tolú, Coveñas, San Onofre, Capitanía del Puerto, Comisión Oceanográfica, Ministerio de Ambiente, CarSucre, CarDique, las comunidades nativas afectadas y organizaciones defensoras del ecosistema y la biodiversidad, tienen el reto de emprender con carácter prioritario el Plan de Ordenamiento Territorial y de Desarrollo del Golfo de Morrosquillo, al igual que otros planes y proyectos de intervención integral que coadyuven a contener la amenaza que compromete este rico y variado recurso natural que nos pertenece y beneficia a sucreños y colombianos. De igual manera, a proyectar y poner en marcha un nuevo modelo de desarrollo económico diversificado, altamente productivo y sostenible, cuyo epicentro sea el Golfo de Morrosquillo. Poeta diversificado, altamente productivo y sostenible, cuyo epicentro sea el Golfo de Morrosquillo. Poeta</t>
+  </si>
+  <si>
+    <t>la costa Caribe. Canciones de Torres como La volqueta gozan de amplia acogida. El retroceso de la derecha y el consecuente avance alternativo constituyen un cambio del paisaje político tan protuberante que el presidente de la República no puede ignorar esta nueva realidad; ello normalmente debe conducir a replanteamientos y relevos como lo han indicado varios analistas, entre ellos la colega columnista de este diario Patricia Lara. El presidente Duque, a partir de los resultados electorales, tiene todo el aval para buscar una alianza en el Congreso con la Bancada de la Paz Partido Verde, Liberal, de la U, Polo Democrático, Cambio Radical, Decentes y FARC, y así superar el estancamiento político y sacar adelante sus proyectos Debe oír los mensajes el Eln, con el fin de que deje su empeño en continuar la guerra, entienda que le dan más frutos los caminos democráticos, busque un acuerdo con el Gobierno</t>
+  </si>
+  <si>
+    <t>¿Qué tienen en común San Agustín y Barranquilla? Cuando pensamos en ellos nos parecen dos mundos, dos geografías, dos climas, dos tipos de humanidad; uno encajonado en sus montañas, el otro abierto a la inmensidad del océano; uno contemplando sus jaguares de piedra que custodian el origen y el otro tejiendo las músicas que en este momento baila el planeta. También los gobiernos los pensaron siempre como cosas distintas y casi incompatibles, pero hay algo poderoso y sagrado que los une: el río Magdalena, que tiene en ellos su comienzo y su fin. Algo esencial de Colombia depende del hilo que une esos extremos, y que es uno de los muchos caminos que todos tenemos que recorrer y celebrar. Porque no es solo un río de agua, no es solo el río generoso de peces que llamamos la subienda, es también un hilo de músicas, desde los bambucos y los</t>
+  </si>
+  <si>
+    <t>de diclofenaco, señaló la doctora. En un tercer análisis, hecho en enero de 2020, la UIS consiguió Dololed en otras ciudades. ¿Qué se encontró? Oh sorpresa, ahí está presente el señor diclofenaco en todas las muestras, afirmó la doctora. Estas contundentes afirmaciones de una científica no fueron tomadas en cuenta por el director del Invima, Julio César Aldana Bula, natural de Sahagún. Aldana señaló en un principio que puede tratarse de falsificación de un tercero o producto de una ilegalidad del titular del registro sanitario. Sin necesidad de examinar sus palabras en un laboratorio de cromatografía, es obvio que el director sugería que terceros distintos a Pronabell vendían el Dololed con diclofenaco a espaldas del laboratorio. Esto implicaría que Pronabell jamás se percató de que los falsificadores le quitaron el mercado. Resulta curioso que todas las muestras analizadas por la doctora Stashenko, compradas al azar, contenían diclofenaco. ¿Por qué el</t>
+  </si>
+  <si>
+    <t>de la unidad por capitación, provenientes de los aportes de los afiliados y del presupuesto nacional, en lugar de circunscribir dicha publicidad a campañas de prevención, vacunación e información relacionada con la prestación de servicios de salud. Mientras tanto, Medimás no paga a otras de sus IPS pues, aunque facturan a tiempo, no hace el desembolso efectivo, mermando la caja de hospitales y clínicas mientras jinetea financieramente esos recursos para sacar con qué pagarle al Gobierno el torcido negocio de Cafesalud. Pero sospechosos contratos con empresas de papel y costosos gastos publicitarios para cooptar medios de comunicación también lo hicieron Pacific Rubiales, Odebrecht y Saludcoop durante los dos gobiernos de Uribe y de Santos: en eso son cónyuges sus respectivos candidatos presidenciales. Igualitos.</t>
+  </si>
+  <si>
+    <t>pasa su factura al hospital IPS. La IPS la pasa a la EPS y es allí donde demoran los pagos con las excusas más inverosímiles. ¿Pueden demandar? Claro. ¿Ganarían? Sin duda. ¿Los volverían a contratar? Jamás. Quedarían con un inri imborrable porque pedir justicia tiene ese precio. ¿Por qué mis colegas en los medios no hablan de esto? En el Quindío, por ejemplo, los especialistas tienen otro elemento en su contra: según me informaron varios de ellos, no más de 500 pacientes están afiliados a la salud prepagada, con lo cual, esa atención tampoco compensa lo que dejan de recibir de las EPS. Lo que plantean es que la prestación del servicio de salud no sea tomada como un negocio y que no hagan intermediación financiera para evitar la corrupción. Y que les paguen, porque además así lo exige la resolución 630 del Ministerio de Salud del pasado 13 de Y que les paguen, porque además así lo exige la resolución 630 del Ministerio de Salud del pasado 13 de marzo. Señores del Gobierno, prestadores de salud, colegas: incluyamos en la discusión a los médicos, enfermeras, camilleros y todo aquel que vive del sistema. Su subsistencia depende de eso, y nuestra vida, de muchas formas, también.</t>
+  </si>
+  <si>
+    <t>XXI. México. 1970. pp.180183; 446459. RADKAU, Joachim 2011. Max Weber. La pasión del pensamiento. FCE. México D.F. pp. 168224; 363398; 631717; 865972. ROA, Hernando. Karl Marx y Max Weber. Científicos sociales. Esap. Publicaciones. Bogotá. 1996. pp. 5985. WEBER, Max. Economía y Sociedad. FCE. México. 1969. Tomo I. pp. 170204. Tomo II. pp. 695889. El político y el científico. Alianza Editorial. Madrid. 1970. Ensayos de sociología contemporánea. Martínez Roca. Barcelona. 1972. pp. 1194; 195324. Ensayos sobre metodología sociológica. Amorrortu. Buenos Aires. 1973. pp. 175269. Historia económica general. FCE. México. 1976. pp. 1527; 236253; 285309. The protesthant ethic and the spirit of capitalism. Charles Scribners Sons. New York. 1958. pp. 4779; 155185.</t>
+  </si>
+  <si>
+    <t>Si usted comienza a meditar motivado por los cambios significativos que espera alcanzar en su vida perfecta salud, muchos amigos, más dinero, mejor trabajo, pareja ideal, menos timidez, estaría perdiendo su tiempo Y aumentando la lista de los factores generadores de ansiedad y estrés. La iluminación, el éxtasis y la extinción del ego, entre otros anhelos etéreos, están también entre las metas que tampoco deben perseguirse. La meditación ha de emprenderse despreocupada y desinteresadamente; su práctica continuada desvanecerá, sin que lo notemos, las barreras que impiden la llegada de la armonía a nuestra vida Y, cuando la armonía aparezca de manera espontánea, las transformaciones que nos convienen ocurrirán. Los grandes meditadores de la historia, desde Siddhattha Gotama, iniciador del budismo, pasando por Eihei D?gen, fundador de la escuela S?t? del Zen, hasta Tenzin Gyatso, el décimo cuarto Dalai Lama, han sido monjes o místicos. Para el ciudadano corriente, sin embargo,</t>
+  </si>
+  <si>
+    <t>pobre, con o sin tatuajes. Además de ocuparnos en el debate sobre los tatuajes, los medios se deleitaron entrevistando a padres y madres de familia que lloraban en vivo porque sus hijos son drogadictos. Son testimonios extraños en donde queda la sensación de que las drogas son sustancias mágicas y que una vez los jóvenes entran en contacto con ellas quedan transformados como si los mordiera un vampiro. Por el contrario, está más que comprobado que las adicciones a las drogas ilegales, a las drogas legales como el alcohol o el azúcar, a las apuestas, a la religión tienen que ver con una necesidad de llenar carencias psicoafectivas o materiales. Porque, bien lo dijo Martín Santos: para el marihuanero pobre hay bolillo y cárcel, pero un marihuanero uribista puede alcanzar el éxito profesional y hasta una embajada. ¿Se preocupa el Estado por la salud mental y física de toda la</t>
+  </si>
+  <si>
+    <t>Doctor, si no se va, matamos a su esposa e hijas. Esquela terrorífica escrita en la fachada de un apartamento en Bogotá, tal vez trazada por un émulo de la guerra sucia que se ensañó en Colombia; de una ética capaz de calificar al defenestrado como buen muerto. De la misma que hace 28 años, con la Ley 100, convirtió en negocio vergonzoso la salud; causa, según dicen, de más muertos que el conflicto armado. Matar a un médico, al que expone su vida todos los días por salvar la ajena, es una monstruosidad. Se le mata por disparo de vecino o por negarle protectores biomédicos en su duelo contra el coronavirus. Treinta y cinco organizaciones médicas le escriben al presidente: El Gobierno está vulnerando el derecho a la vida de los trabajadores de la salud al país no le servirá una larga lista de ese personal muerto y sin</t>
+  </si>
+  <si>
+    <t>de estas prácticas él, como ortopedista, tiene que recibir todas las complicaciones de cirugías e implantes mal hechos. Las clínicas de garaje se preocupan por operar, exista o no la necesidad, sacar la plata del seguro y después dejan al paciente sin acompañamiento. Los hospitales que reciben los casos agravados gastan horas y horas lavando heridas y aplicando antibióticos antes de poder intervenir nuevamente. El médico profesional de las clínicas legales debe esperar días para poder intervenir a pacientes infectados que hubieran podido ser operados exitosamente desde un principio. Esto les reduce notablemente las horas de trabajo y el salario, pues muchos médicos cirujanos cobran por hora en sala, que es cada vez menor debido a estas mafias. En otras palabras, tenemos un sistema donde los pacientes se complican, arriesgan su salud y su vida, y los médicos especialistas ven sus jornadas dilatadas por horas y horas de antibióticos mientras</t>
+  </si>
+  <si>
+    <t>heridas de su animal y la frotó en los brazos de su familia. Cuando el rumor de la cura se regó por el pueblo, muchos respondieron con más hostilidad que emoción. Al parecer, les repugnaba la idea de inyectarse material animal. Es más, por mucho tiempo se creyó que ese proceso convertiría a las personas en bestias. La técnica de inoculación, que no surgió en Inglaterra, sino que hacía ya parte del conocimiento del mediano y lejano oriente, había sido acogida por viajeros occidentales, incluida la británica lady Montagu, que ni corta ni perezosa la puso en práctica. Pese a su éxito, la comunidad científica inglesa se burló de ella. Ochenta años más tarde, el científico Edward Jenner logró mejor recepción. Toda esta historia para decir que los procesos de descubrimiento y refinamiento del conocimiento científico son tortuosos no sólo en lo técnico. También lo son en términos de comunicación</t>
+  </si>
+  <si>
+    <t>que se mueren jóvenes, que viven en condiciones insalubres, y que no tienen nada más que vender sino sus cuerpos y su sexualidad intacta. Las posibilidades del novelesco mercado son infinitas: más que la informática, más que la biotecnología, más que la industria y los medios; no existe un sector económico que se le pueda comparar. Las transferencias económicas del centro a la periferia son monumentales. Años antes de la publicación de Plateforme , el premio Nobel de Economía Amartya Sen llamaba la atención sobre enormes desequilibrios demográficos en el Asia. Calculaba un faltante de cerca de 100 millones de mujeres, particularmente crítico en la China y la India, por los sesgos contra las niñas en nutrición y cuidados médicos. Una década después, el mismo Sen anotaba que mientras en la India la situación había mejorado, en la China se había agravado por la política del hijo único y la</t>
+  </si>
+  <si>
+    <t>El cambio climático llegó para quedarse y tiene al Gobierno y al país entero en acuartelamiento de primer grado por el agresivo invierno advertido desde principio de este año por el Servicio Meteorológico de los Estados Unidos NWS, por sus siglas en inglés. El año pasado, la Administración Nacional Oceánica y Atmosférica NOAA nos había advertido sobre una extensa sequía que entraría en noviembre del 2019 hasta abril de este año, y así sucedió, trayendo como consecuencia la caída de la productividad en los sectores agrícola y ganadero del país en el primer semestre de este año, lo cual redujo los ingresos de los empresarios del campo, obligándolos a reestructurar sus créditos bancarios. Claramente, estas situaciones de variabilidad del clima exigen del Gobierno Nacional un cambio en la política de administración del riesgo, comenzando por una reestructuración a fondo del Ideam que mejore el servicio de predicciones y avisos de</t>
+  </si>
+  <si>
+    <t>Los nubarrones iban ocultando el cielo; el viento venía denso, húmedo, lleno de olor de tierra; en las laderas las ráfagas huracanadas rizaban la hierba amarillenta; en las cumbres, el aire apenas movía las copas de los árboles de hojas rojizas. Luego, las faldas de los montes se borraron envueltas en la niebla; el cielo se oscureció más; pasó una bandada de pájaros gritando.... Esta descripción de una tempestad, de Pío Baroja texto que no leía desde la primaria, describe lo que siento en medio de la situación generada por el covid19: es como si uno estuviera esperando una tormenta. Por asuntos de trabajo, me encontraba en Miami cuando se anunció la llegada de Katrina, hace 15 años. Los días previos fueron una sucesión de altibajos emocionales que solo se acentuaban con el paso de las horas. En la zona donde yo me encontraba la evacuación no era obligatoria, lo</t>
+  </si>
+  <si>
+    <t>de una sabiduría campesina, anclada en el conocimiento adquirido de una manera empírica padeciendo el tiempo meteorológico, y destilado por el paso del tiempo, del otro tiempo, el cronológico. Lo que ya no sé es cuánta vigencia seguirán teniendo en estos nuevos tiempos, donde los cultivos en invernadero y el cambio climático pueden desmentir, y de hecho la desmienten, esa tradicional sabiduría del campesino. Pero lo que sí sé es que analizando despacito los refraneros populares, en su vertiente relativa a la meteorología, casi puede afirmarse de manera contundente, comparado con lo que se nos viene encima, que sí, que cualquier tiempo pasado fue mejor. Y lo que también sé es aquello que uno de los más grandes poetas del siglo anterior, el norteamericano Robert Frost, dejó burilado en el bronce inoxidable de un poema que no tiene desperdicio y se titula Hielo y fuego : Algunos dicen que al bronce inoxidable de un poema que no tiene desperdicio y se titula Hielo y fuego : Algunos dicen que al mundo lo acabará el fuego, otros dicen que el hielo. Por lo que he degustado del deseo, estoy con los partidarios del fuego. Pero si tuviera que perecer dos veces, creo saber lo bastante acerca del odio como para decir que en la destrucción también el hielo es poderoso. Y que bastaría.</t>
+  </si>
+  <si>
+    <t>precipicios de otra realidad ajena a la suya, deben saber dónde están y con quién procrean, dónde lo hacen, cómo viven, dónde se esconden, como gozan y sienten placer sin su aprobación y lejos de sus cuerpos que sanan. Ellos, los pastores de un rebaño que ahora consideran nacional, deben saberlo todo para aprobarlo con el libro plenipotenciario y sacrosanto sobre todas las constituciones del mundo, aunque existan cientos de miles de libros sagrados que compiten por la misma oficialidad, y aunque cientos de miles de vidas caigan acribilladas por la brutalidad de sus viejos designios. Subieron al poder por las alianzas desesperadas de una ultraderecha que debe repartir las últimas cuotas de la tradición. Pensarán, tal vez, que la persecución debe acelerarse ahora y antes del fin, para recobrar el paraíso que perdieron cuando el diezmo y las limosnas dejaron de alcanzar para los excesos y los pecados silenciosos el paraíso que perdieron cuando el diezmo y las limosnas dejaron de alcanzar para los excesos y los pecados silenciosos de la exculpación que los devolverá a la gracia de sus ejemplos.</t>
+  </si>
+  <si>
+    <t>clima y del desarraigo, escucharemos todo tipo de explicaciones según el lugar del espectro político desde el que se hable. Lo cierto del caso es que Venezuela, siendo uno de los países más ricos y poseedor de la mayor cantidad de reservas de petróleo del orbe, donde se dan el lujo de adquirir la gasolina más barata que el agua como que con un dólar se pueden comprar 3,5 millones de litros de petróleo, ver , hoy ha reducido su producción en más de 1.500 millones de barriles diarios, no hay medicinas, no hay oferta de alimentos en las cantidades y precios adecuados para sobrevivir. Pero, además de haber matado la gallina de los huevos de oro, el gobierno de ese país se empeñó en adelantar un proyecto de socialismo bolivariano, copiando el modelo castrista, atacando la empresa y la propiedad privada, persiguiendo a empresarios, causando la emigración forzada de</t>
+  </si>
+  <si>
+    <t>Sábado frío, lluvioso y nublado en Bogotá. Es el clima que les privaba a nuestros abuelos, pero los descendientes no hemos podido acostumbrarnos a tanta oscuridad. Dan pocas ganas de salir bajo estas condiciones, pero en este mundo de infinitas alternativas, planes es lo que hay para no aburrirse en la casa. Sobre mi mesa de noche está el maravilloso libro de Melba Escobar Cuando éramos felices pero no lo sabíamos. En la de mi señora, su libro Historias de amor en campos de guerra y el primer tomo de la autobiografía de Barack Obama. En Netflix, The Crown nos hace ojitos para tenernos enchufados todo el fin de semana, y en la cocina nos aguardan 70 canastos de , nuestra tienda de Instagram, para empacar, aunque eso no es lo mío. Prefiero entregarlos. Tengo un don innato para la entrega. Pero no, este sábado nada de eso me llamó</t>
+  </si>
+  <si>
+    <t>una medida del nivel del mar o de la profundidad del hielo en un lugar en el que jamás has estado. Está justo frente a ti. Y aunque los patrones climáticos tienen mucha aleatoriedad, en efecto están cambiando. De eso se trata el cambio climático: cambia el clima. Quería escribir mi última columna de 2018 sobre el clima como una suerte de súplica: en medio de todo lo demás que está pasando, no pierdas de vista la historia más importante del año. Sé que había mucha competencia por ese título, incluyendo a algunos contendientes más evidentes, como el presidente Donald Trump y Robert Mueller. No obstante, nada más tiene la importancia del saldo creciente y los enormes peligros del cambio climático. Me preocupa que nuestros hijos y nietos un día nos pregunten, con amargura, por qué pasamos tanto tiempo distraídos por asuntos menos relevantes. La historia del cambio climático en</t>
+  </si>
+  <si>
+    <t>tan marcadas, escapar del calor vía calendario escolar es una tarea imposible en muchas regiones del país. Pero eso no quiere decir que las altas temperaturas sean inocuas. De hecho, como quedará claro a continuación, ni siquiera la estrategia de los países con estaciones alcanza para aislar a los estudiantes de los efectos adversos de estudiar bajo altas temperaturas. Una reciente investigación se pregunta si las altas temperaturas afectan el aprendizaje de los niños. El estudio analiza el desempeño en pruebas estatales de diez millones de bachilleres en Estados Unidos entre 2001 y 2014. Estos presentaron pruebas estatales al menos dos veces, lo que permite analizar, teniendo en cuenta el desempeño anterior, el efecto que tiene en sus resultados haber estado sometidos a un año caluroso antes de presentar el examen. Los investigadores recogieron la información sobre la temperatura día a día en cada colegio y datos sobre si contaban</t>
+  </si>
+  <si>
+    <t>zonas rurales? Esta pregunta deberá responderse ante la crítica situación social y climática que confirma el Instituto de Hidrología, Meteorología y Estudios Ambientales IDEAM, informando a sectores productivos, a la comunidad y a la opinión pública en general que, debido a las altas temperaturas del aire, fuertes vientos y antecedentes de vegetación seca de los últimos tres meses, en la región Caribe y los Llanos Orientales se vienen presentando incendios forestales que afectan considerablemente estas zonas del país. Aquí añadimos a este reporte oficial meteorológico que los cambios climáticos y los avatares políticos van juntos, acentuando la crisis humanitaria y la incertidumbre. El Sistema de Información Ambiental Territorial de la Amazonia Colombiana SIATAC del Instituto Amazónico de Investigaciones Científicas, SINCHI, reporta diariamente la gravedad de la situación. En épocas de Niño, Se registra un total de 3689 reportes de fuegos, desde las 6:00 AM del 26022019 a las 6:00 AM</t>
+  </si>
+  <si>
+    <t>Los pequeños estados insulares del Caribe son, en su generalidad, auténticos paraísos tropicales, cuya economía tiene fuerte dependencia del turismo, una actividad que en algunos de ellos se interrumpe abruptamente, año tras año, por la acción devastadora de los huracanes. Estos se han vuelto más frecuentes, intensos y erráticos, y los riesgos podrían ir más allá de estremecer sus frágiles sistemas económicos. La amenaza, incluso, acecha la existencia de las propias islas. Los huracanes llamados ciclones o tifones en otras regiones del mundo se forman por la acción del aire cálido y húmedo que se eleva desde los océanos, un fenómeno que en el Atlántico Norte registra una temporada convencional, entre junio y noviembre, en la que se presenta una media de diez tormentas de diferentes magnitudes. Sin embargo, en los últimos cinco años, algunos tornados tropicales se han salido del calendario, entre ellos, Alberto, el año pasado, y Andrea,</t>
+  </si>
+  <si>
+    <t>Caracol Estéreo. Me tocó el tomo sexto, de la LN, y al azar abrí la página, recordando el juego del diccionario de Antonio Caballero, que fue para mí, de lengua madre italiana, un ejercicio de aprendizaje que me sirvió por toda la vida. Sí. Sin esperar más, abrí, y me tocó el adjetivo malo, de la página 268 a la 283, en todas sus acepciones. La primera es Ineficiente, y no podía faltar una cita del Quijote: Afirma que esta muerte es vida, que así se la dé Dios a él y a todos los de su ralea: digo, a la de los malos médicos, que la de los buenos palmas y lauros merecen. Y de Cervantes a García Márquez, el paso es breve: Ese día se metió en el agua por un mal camino y no lo encontraron hasta la mañana siguiente, varado en un recodo luminoso y con</t>
+  </si>
+  <si>
+    <t>el coco del pastel la pondría Eduardo Carranza. En 1971 algunos de sus versos sencillos se convertirían en el himno oficial de San Andrés, Providencia y Santa Catalina. La cosa todavía venía de mucho más atrás. Las islas fueron durante mucho tiempo solo un lugar de contrabando donde cagaban las aves y se exiliaba a los revoltosos de la nación. Después se trató de integrarlas al territorio nacional con un proyecto turístico que ponía, como suele pasar, a la gente en el mismo nivel de exotismo del paisaje; se colocó uno que otro busto por ahí y se bautizaron sitios con los nombres de los héroes de la patria. Pero los vientos también son antiguos. En 1879 Joaquín Esguerra Ortiz publicó el Diccionario geográfico de los Estados Unidos de Colombia y cuando se refirió a Providencia dijo: En dos años continuos ha sido azotada por la calamidad de los huracanes,</t>
+  </si>
+  <si>
+    <t>Colombia padece de varias infecciones ecosistémicas derivadas del contagio global de especies vivas que han migrado al país de manera espontánea o inducida los humanos somos vectores. En algunos casos, esas infecciones se resuelven dentro de los parámetros del sistema inmune propio de la complejidad ecológica, que constantemente está previniendo el ingreso de organismos que no se produjeron dentro de la trayectoria evolutiva propia de cada territorio. Pero, a menudo, esta inmunidad no es suficiente, al menos en tiempos humanos. Hay muchos ejemplos: el caracol africano devora la vegetación nativa y se expande como peste que pone en riesgo decenas de especies nativas que requieren esas plantas para prosperar. La tilapia, enfermedad comercial expandida por acuicultores irresponsables, sigue depredando cuanto encuentra a su paso sin que haya un mínimo de monitoreo, ni un pago de tasas o compensaciones de control de poblaciones indeseables. La acacia negra o el retamo espinoso</t>
+  </si>
+  <si>
+    <t>hablar. Reírse menos. Eso. Todo este catálogo está muy bien. La mayoría de los habitantes de este planeta lo cumplimos... y los que se saltan esta cartilla básica lo más probable es que terminen entubados y asfixiados o contagien a alguien. Esto es un hecho. Mientras los atardeceres estrenan colores, los nevados se muestran impúdicos y altivos, las estrellan iluminan la noche parpadeando, los cielos se ven limpios y la naturaleza respira, nosotros, los reyes, estamos como la calandria, algunos en jaulas de oro, otros en jaulas de zinc, pero toditos quietecitos y sin derecho a pataleo. No valen chequeras ni el manido usted no sabe quién soy yo. Lo que es repudiable es el sensacionalismo de todos los medios de comunicación, sean falsos, inventados o verídicos. Es el morbo infinito de periodistas, locutores, reporteros, fotógrafos... que nos meten el coronavirus envenenado en nuestras casas por los oídos, por los</t>
+  </si>
+  <si>
+    <t>eres del montón. Supéralo. Digamos que esa es una ley de la vida. O una ley de la naturaleza y si se quiere hasta de Dios. Puede que no existan criterios objetivos, universales o eternos de lo que es la belleza, pero de que cada cual tiene una intuición muy personal de lo que le gusta y no le gusta no hay ninguna duda. Todo el que encuentra matices estéticos en el mundo, lo quiera o no, establece diferencias. Esas diferencias no son negativas, no necesariamente. Determinan la personalidad de cada cual: que fulanito vista sólo con prendas de tal color, que zutanito frecuente puntualmente este café y no otro, que menganito prefiera la compañía de tal tipo de personas y no de las demás. En últimas, así no lo expresemos en esos términos, cada uno trata de rodearse de belleza, de su particular forma de entender la belleza y</t>
+  </si>
+  <si>
+    <t>Botero, el Mindefensa que tiene alma de tendero. En esas llegó Alicia Arango como un ventarrón: Bueno niños, se acabó el recreo... Cristo José se va pa su casa y usté Ivancito vaye orine y acuéstese. Ñapa. Educad al niño y no tendréis que votar por el adulto. Ñapita. En la época de Colón los curas decían que la tierra era plana, los científicos decían que era redonda y los terratenientes aseguraban que era de ellos... Payola. El que no conoce la historia está condenado a oírla: de la entrevista con Diana Uribe en el libro Tola y Maruja sin agüeros, en la librería Nacional .</t>
+  </si>
+  <si>
+    <t>humanos para conocer la realidad objetiva, pues casi todo lo que damos por cierto ha sido el resultado de nuestra imaginación. Dicho en forma simple, nos inventamos cosas que no existen o que deseamos que existan y, a base de creer que son verdaderas, terminamos viviendo en ellas y de ellas, aun contra las evidencias que nos proporciona la razón. Religiones, ideologías, doctrinas y hasta estilos de vida saludable responden a la necesidad de encontrar sentido a la vida y de dar orden al caos de la experiencia. La realidad, para la mayoría, es aquello en lo que creen. La política se mueve en este terreno de la realidad imaginada y, por lo tanto, termina revelando lo que la gente quiere creer dentro de un amplio menú de ofertas. Una sociedad madura tendrá, tal vez, dos o tres propuestas alternativas capaces de reforzar aquello que otorga identidad y reconocimiento ante</t>
+  </si>
+  <si>
+    <t>libre. Hay indignación. La gente quiere cárcel, la gente está como en una plaza de toros o en el Circo Romano, que sufran los otros, que paguen, que se pudran. El presidente, maniatado en su inmenso poder, sólo puede gritar: ¡es un mafioso! Yo me apego a un sentimiento de libertad. No entiendo al ser humano en cautiverio, pero ni siquiera a ser vivo alguno. En mi senilidad, al fin sensata, desatrapo insectos del tejido de las arañas, enderezo los cucarrones, y pienso que mis perros, aunque corran por un patio alfombrado de hierba, tienen la casa por cárcel. El gato, que es casi aéreo, va y vuelve de la vecindad, con algún riesgo; lo veo llegar a casa, le abro y da tres vueltas alrededor de mis tobillos, llega a la hora de comida, pero es libre. Y yo también. Escuché de un pacífico excomandante guerrillero que en materia a la hora de comida, pero es libre. Y yo también. Escuché de un pacífico excomandante guerrillero que en materia de delitos sexuales, acaso cometidos por su guerrillerada, ninguno de los que él hubiera tenido noticia, quedó vivo. ¡Qué bárbaro! Vi a con Yamid, delgado, limitado por su condición y por un cierto ahogo de voz. No se salió de casillas y, sin méritos para medir su inteligencia, digo sin reato que sorprenden su talento y su empecinamiento.</t>
+  </si>
+  <si>
+    <t>cambiaría el mundo, ni íbamos a hacer una investigación profunda sobre tigres, pero que durante todo el proceso íbamos a aprender un montón de habilidades para la vida. Estos dos profesores son ejemplos para mí en mi labor diaria. Me llevaron a formarme como persona y a valorar interacciones pequeñas y grandes, y a darme cuenta del significado de una conversación en el momento adecuado. También a soñar en grande y a aprovechar todas las oportunidades que existen para aprender. Los aprendizajes que recibimos de los profesores a diario van mucho más allá de las áreas básicas como matemáticas, ciencias y lenguaje. Los profesores son unos modelos de vida y de cómo expresar valores en acciones. Todos los días hay ejemplos de profesores que dan la milla extra para acompañar a los estudiantes, para buscar que aprendan y para que se vayan formando como ciudadanos de bien. La voluntad y</t>
+  </si>
+  <si>
+    <t>La acrobacia aérea o vuelo acrobático es un deporte internacional que contempla varias categorías de exigencia de acuerdo con la experiencia de los pilotos y el grado de dificultad de las rutinas. La escala empieza desde la elemental, para graduados, y termina en la ilimitada, exclusiva para verdaderos pájaros voladores con alto nivel de pericia y destreza. Sus orígenes se remontan hacia la primavera de los años 90, cuando se formalizó con el primer campeonato del mundo en la ya desaparecida Checoslovaquia . Los campeonatos mundiales se alternan con los europeos y estadounidenses y causan furor por la rigurosidad y precisión de los ejercicios acrobáticos. Pero, sin duda, el evento más competitivo, en donde se combina acrobacia con velocidad, se realiza desde 2003, cuando prendió motores el Red Bull Air Race World Series, espectacular circuito aéreo de tres kilómetros de área, que transformó la actividad en un show vistoso y</t>
+  </si>
+  <si>
+    <t>y sin qué echarle, como se dice, pues andan sin cinco pe, ya que tienen dificultad para la inserción a la vida laboral. Y también para el reencuentro con sus familias. Y muchos padecen estrés traumático. O estrés plomático, pues, por desgracia, los están matando: 114 ex Farc han sido asesinados luego de la firma de la paz. Otros, un 17 por ciento, están en peligro de ser reclutados por las bandas criminales. Y qué decir de los líderes sociales, que también están siendo asesinados. El panorama es gris. Los territorios dejados por las Farc han sido ocupados por las bracrim, llámense Caparrapos, caparrabos, elenos, Pelusos o pelados. Y el campo, presidente Duque, está prácticamente en cuidados intensivos, abandonado, sin cinco pe. Y qué decir de las víctimas del conflicto, que padecieron todas las violencias, incluidas las sexuales. Muchas están solas, con miedos y dolor. Ellas necesitan, senadores y reanimadores que padecieron todas las violencias, incluidas las sexuales. Muchas están solas, con miedos y dolor. Ellas necesitan, senadores y reanimadores de la Farc, JEP, verdad, reparación y justicia. Atención, en todo caso. El episodio del senador José Obdulio, aunque parezca aislado, puede ser un símbolo para que pasemos todos a las salas de reconciliación, para que dejemos la paz en paz. A ver si somos capaces de sacar el país de la sala de urgencias. Usted puede ser el líder, senador Gaviria, se lo digo de corazón abierto.</t>
+  </si>
+  <si>
+    <t>En lugares tan distintos como Colombia, Corea del Sur, Ecuador, España, Francia y Sudáfrica, protestas sociales inicialmente pacíficas han terminado en violencia. Cuando la protesta un derecho sagrado empleado globalmente en las luchas contra la injusticia, el racismo, el mal gobierno, el autoritarismo, la explotación ambiental y la violencia de género, entre otros se torna violenta, frecuentemente es representada como algo peligrosa, confirmando la necesidad de suprimirla. Los actos de vandalismo, saqueo y bloqueo del espacio público que por lo general acompañan la mal llamada radicalización, tienden a reforzar dicho encuadre, invisibilizando de paso las fuentes legítimas de descontento que crecientemente llevan a las personas a protestar. Dejando a un lado el comprobado vínculo entre la represión estatal y la conversión de las manifestaciones pacíficas en violentas, el meollo del asunto está en las palabras con las que la protesta suele ser representada y construida como fenómeno social. En años</t>
+  </si>
+  <si>
+    <t>asunto tapó: la afirmación de Trump sobre la posibilidad de traer a nuestro país tropas estadounidenses para una posible invasión a Venezuela. La insinuación es una grave amenaza a nuestra soberanía y una absurda idea para resolver la crisis del vecino país, y que ni Duque, ni María Juliana reaccionaran en contra de la misma sí nos debería preocupar y convocar a todos los colombianos. Esto nos lleva al punto original. La denominación de primera dama es absurda, tanto que si la pareja fuera hombre no sabríamos como llamarlo, ¿primer caballero? En las anacrónicas monarquías existe el rol de reina madre o príncipe consorte, función remunerada a la que se puede renunciar, como lo hizo el príncipe Felipe, esposo de la reina Isabel II del Reino Unido. Pero la primera dama colombiana no parece poder darse ese lujo. Eso sí, debe renunciar a su carrera o congelarla para dedicarse a</t>
+  </si>
+  <si>
+    <t>desarrollo tecnológico de minas antipersonal, la destrucción de los arsenales, la atención de las víctimas y comprometer la limpieza de las tierras contaminadas en todas los regiones del planeta donde mutilan y asesinan a animales, niños, niñas, jóvenes, miembros de fuerzas armadas, integrantes de grupos de actores armados no estatales, en fin, un arma que mata, hiere y mutila sin discriminación alguna. En Colombia, avanzamos mucho en la superación del problema hasta 2017 luego de años de dolor. 2018 nos alerta de nuevo por un incremento del 300 en el número de víctimas de minas y remanentes explosivos de guerra. de 57 en el 2017, a 178 en el 2018. En 2019 La persistencia del conflicto armado con el ELN al igual que la agresividad de actores armados no estatales como las bandas de Los Caparrapos, el Clan del Golfo, y las disidencias de las Farc incrementan los riesgos para</t>
+  </si>
+  <si>
+    <t>ahogado en barbarie. Que se está llevando a cabo una operación profunda de rearme de las conciencias y de crispación de los ánimos. En el parpadeo que va de un gobierno al siguiente, Colombia pasó de ser ejemplo mundial de conciliación a espanto de viajeros y paranoia permanente de sus ciudadanos. Los libros de historia no omitirán la isla de tres años que vivimos en aire de pacificación. Tampoco dejarán de señalar la ignominia de quienes llegaron a hundir esta isla a cañonazos. Rearmar la guerra es asesinar el cuerpo, quebrar la ilusión es matar el espíritu. ¿Qué es peor, lo primero o lo segundo? email protected</t>
+  </si>
+  <si>
+    <t>que se confabulan para imponer la corrupción, el tráfico ilegal de drogas, el paramilitarismo, la extorción o aglutinar una delincuencia organizada que se aprovecha de la estructura estatal y actúa en contra de las poblaciones más vulnerables en especial víctimas, pobres, desplazados, campesinos, líderes sociales y grupos étnicos. Según el Registro Único de VíctimasRUV hay 8,801.000 personas víctimas del conflicto armado de los cuales solo el 76,54 son sujetos de atención por parte del Estado colombiano. Estos datos estadísticos comprueban que los departamentos con más víctimas los encabeza Antioquia con 26,991, Santander con 7,210 y Meta con 6,080 coincidentemente también son los territorios donde se han presentado las mayores masacres y desapariciones forzadas en las tres últimas décadas. Las cifras muestran que es preciso revisar el daño real y medir el peso social de la violencia y la guerra, porque de cada 10 muertes violentas tres son generadas por el</t>
+  </si>
+  <si>
+    <t>seguros para el comercio marítimo fue en Brujas, en donde el Conde de Flandes autorizó en 1310 el establecimeinto de una Cámara de Seguros por medio de la cual los mercaderes podían asegurar sus bienes expuestos a los peligros del mar pagando un porcentaje estipulado. Una de las ramas más importantes del common law es el derecho de daños. El tort liability, como sistema de responsabilidad personal, exige de jueces y abogados familiaridad con los riesgos y el cálculo probabilístico. En el otro extremo, la antigua Unión Soviética es tal vez el lugar donde con mayor fuerza se rechazó la posibilidad de asegurar la responsabilidad civil. La importancia que el derecho soviético le ha asignado a la culpa como medio para controlar conductas antisociales o dañinas condujo a considerar tal tipo de mecanismo como totalmente inaplicable a una sociedad y un marco legal socialistas. El derecho civil continental, en particular</t>
+  </si>
+  <si>
+    <t>tabla, con 723 muertes por millón de habitantes por covid19 Bélgica registra 1.446 y 168 muertes por millón de habitantes por siniestros viales Irán tiene 580.En 2011, la Asamblea General de las Naciones Unidas declaró el Decenio de Acción de la Seguridad Vial con la meta de estabilizar y empezar a reducir las muertes y heridas graves en el tráfico; no lo logramos. En septiembre pasado, la Asamblea General de Naciones Unidas reiteró su compromiso con la seguridad vial y declaró el Segundo Decenio de Acción, con la meta de reducir las muertes y heridas graves en 50 entre 2021 y 2030. Para lograrlo, la receta es conocida: el enfoque de sistema seguro o Visión Cero, que ya han aplicado con éxito países europeos, Australia y Japón. Este implica diseñar las vías de forma segura para todos los usuarios viales; elevar la competencia de conductores, peatones y ciclistas; controlar los</t>
+  </si>
+  <si>
+    <t>La euforia que se propagó con la caída del Muro de Berlín y el ascenso imparable de la globalización se ha transformado en un sentimiento bastante generalizado de miedo, escepticismo y frustración a lo largo y ancho de la Tierra. En el frente económico, la promesa de un modelo liberal en el que todos los países ganarían mediante un régimen financiero y comercial más abierto y neutral ha sido reemplazada por una avalancha de unilateralismo económico selectivo y discriminatorio. El avance de un mercado global sin barreras que facilitaría el afloramiento de las ventajas competitivas y comparativas inherentes a cada país terminó siendo una quimera. Aunque son palpables las bondades que aportó la liberación económica en materia de bienestar y crecimiento, los ajustes estructurales que conlleva abrirse a la competencia se tradujeron en un malestar social que a la postre les dio un incontenible impulso político al proteccionismo y el</t>
+  </si>
+  <si>
+    <t>cuanto más pasa el tiempo más cruel es el virus porque sus víctimas se van acumulando día a día y en Colombia con unos 200 muertos diarios y 5.000 al mes nos acercamos rápidamente a los 50.000. Cruel sería morirse poco antes de la primera tanda de vacunación. La humanidad convivió siempre con las plagas, pero las generaciones que crecimos rodeadas de medicina científica pensamos que a nosotros no nos tocaría vivir esa experiencia de angustia y miedo. La COVID19 es un aviso benigno de las pestes que podríamos padecer si estas se parecieran a las de la antigüedad. Cuando los europeos llegaron a América hubo tres grandes pestilencias una de viruela y dos de fiebres hemorrágicas que en medio siglo mataron a 90 de cada 100 indígenas. En la Nueva España, donde hubo censos más o menos confiables, los 25 millones de indígenas que había en 1520 se redujeron</t>
   </si>
   <si>
     <t>o valioso los sueños? Excepcionalmente sí, y existen historias de investigadores, escritores y músicos que construyeron sus logros notables sobre sus respectivos desvaríos cuando dormían. El descubrimiento, en 1865, de la estructura molecular del benceno por August Kekule, químico alemán, es quizás el ejemplo más célebre de una inspiración científica surgida durante una siesta. El químico alemán, según su propio relato, soñó que una culebra se comía su propia cola y ello le inspiró la estructura circular de la entonces extraña molécula. Es real que los sueños eventualmente apoyan a los soñadores y pueden sugerir soluciones ingeniosas a sus problemas de turno. Pero los soñadores, importante resaltarlo, tienen que saber muy bien la lógica y la ciencia detrás de sus respectivos proyectos Muy pocos químicos, de cualquier época, comprenderían el mensaje del sueño de la culebra comiéndose su cola Y, muchísimo menos aún, si les tienen miedo a las serpientes. mensaje del sueño de la culebra comiéndose su cola Y, muchísimo menos aún, si les tienen miedo a las serpientes.</t>
   </si>
   <si>
-    <t>laboratorios de cocaína, exportadores y comercializadores para terminar, lavado todo, en las impolutas arcas de la banca mundial y nacional. Reafirma la Corte que sólo habrá aspersión si el Gobierno no logra concertación con las comunidades o sustituir cultivos. Pero éste no intenta una acción integral y quiere en cambio repetir la fracasada y costosísima aspersión con glifosato, medio infalible para provocar una crisis humanitaria. Recuerda Romero que en 2005 había en su tierra 3.875 hectáreas de coca; se asperjó sin medida y hoy son 45.000 las hectáreas sembradas. De los 70.000 cultivadores nariñenses, apenas 16.000 reciben ayuda oficial. Ebrio en los soñados efluvios del glifosato, ignora el Gobierno experiencias que, de generalizarse, cortarían por lo sano. En 2013 se destruyeron en Caldas las últimas siembras de coca. El secreto: se pactó la solución con las comunidades, el Estado allegó bienes, servicios y abrió vías; convergieron organizaciones públicas y sociales</t>
-  </si>
-  <si>
-    <t>un hombre químicamente bueno. Dicho lo anterior, albergo serias dudas sobre la imparcialidad y el proceder de la Corte Suprema de Justicia, y muy especialmente sobre el magistrado Barceló, autor principal del auto tan mal redactado como saturado de errores de ortografía y de puntuación. El analista Eduardo Mackenzie comenta: No es sino ver la lógica de lo que Luis Barceló llama abrir investigación en contra del senador Álvaro Uribe Vélez y del representante a la Cámara Álvaro Hernán Prada. Todo el asunto está en eso de abrir investigación en contra. En un sistema democrático la investigación judicial tiene una meta: averiguar y establecer la verdad objetiva. Aquí, en la acción de Barceló, al abrir la investigación, el acusado ya está condenado, su defensa es inútil, pues la investigación es en contra, cuando debería ser una investigación imparcial, sobre unos hechos probados. Hay una regla de oro en estas materias,</t>
-  </si>
-  <si>
-    <t>Para nadie es un secreto que la gasolina es imprescindible no solo para el procesamiento que convierte la coca en cocaína, sino también para que funcionen los laboratorios escondidos en lugares inexpugnables. Allí se requieren plantas eléctricas para alimentar, entre otros, los hornos microondas que deben trabajar permanentemente. Para decirlo de manera simple: si no hay gasolina, no hay cocaína. Por eso la denuncia hecha por Francisco Lourido, el candidato a la Gobernación del Valle, debe ser tenida en cuenta. Sucede que las ventas de gasolina andan disparadas en los departamentos donde se procesa el alcaloide y el Gobierno no ha tomado cartas en el asunto. Las estaciones de gasolina en esos lugares se han multiplicado geométricamente, ante los ojos y oídos de quienes andan persiguiendo a los responsables de este delito. Ejemplos hay muchos: mientras que en el Valle del Cauca con más de 4,7 millones de habitantes existen</t>
-  </si>
-  <si>
-    <t>elaboración, entre la salmuera, el ahumado y la cocción lenta, su método de preparación es quizás el más fiel al americano. Mario Roa, uno de sus dueños y amante de la comida, está convencido de que a Bogotá le hacía falta un pastrami como tienen grandes ciudades como Nueva York y Los Ángeles y no es difícil darle la razón luego de disfrutar de uno de sus sándwiches, con pepinillos, papas o ensalada, por 20 mil pesos. Este lugar tiene una fórmula básica que no tiene pierde, pastrami de pavo o de res y aunque su tamaño parece engañoso es la porción perfecta de 160gr no deja espacio a dudas de su buena preparación e inolvidable sabor. Para hacerle honor a nuestras recetas típicas encontré El Sándwich Taller Cra. 4a 26b34 , un lugar donde se respira costa caribe, desde la música hasta los ingredientes, estos sándwiches son la invención</t>
-  </si>
-  <si>
-    <t>vía fracking dijo que carecía de fundamento Hughes, 2013. Poco después se comprobó que tenía razón. La propia AIE admitió, en 2014, que había evaluado mal el yacimiento no convencional de Monterrey, California. El descache fue de la bicoca del 96 . ¿Está comprobado que los yacimientos no convencionales de San Martín y Puerto Wilches garantizan la seguridad energética que los abanderados del fracking pregonan? ¿Tiene la Upme este dato? ¿O estaremos creando una burbuja, como parece que sucedió en EE. UU.? En 2005 pronosticaban que para 2025 dejarían de depender de las importaciones provenientes de los países de la Opep, pero otro analista, JalifeRhame, descubrió datos deliberadamente abultados y escribió: El modelo financierista prolonga su dolorosa agonía, y ahora parece el turno del fracking JalifeRhame, 2014:91. Ahora bien, es claro que extraer energías vía fracking es más costoso que hacerlo mediante técnicas convencionales. Las inversiones son, por naturaleza, de</t>
-  </si>
-  <si>
-    <t>aquella tierra. Es en este territorio donde se gesta una culinaria, cuya riqueza de sabores y la originalidad de sus preparaciones admiro fanáticamente. Sopas de antología son su suculento caldo de costilla y el caldo de pichón ambos se ofertan para desayunar su exclusivo mute, que es mondongo con garbanzos, ahuyama, arracacha, maíz y papa; sus fríjoles con costilla, preparados con fríjol de Castilla, papa, yuca, guineos verdes, ahuyama, arracacha, zanahoria y cilantro cimarrón; y finalmente su sazonado y reconocido sancocho de rabo de res. Tema especial son sus carnes en cecina, oreadas o ahumadas casi únicas en Colombia, también lo es su sobrebarriga horneada con cerveza y miga de pan; joya de alta cocina es aquel cabrito asado acompañado de aquel legado culinario español llamado pepitoria; y qué decir de la turmada pastel de sobrantes de cocina o de las crocantes empanadas con masa de yuca, los pasteles de</t>
+    <t>En un laboratorio de Helsinki, la espuma viva de la sopa primordial cuyo fermento bulle en un tonel de aluminio anodizado será luego pasada por rodillos calientes para secarla y producir harina de panqueques finlandeses. Esta nutrición, hija de las penurias del planeta y de la necedad del ecocidio, ha sido creada con técnicas relativamente sencillas y gestada en el agua preñada con bacterias de la madre tierra, manipuladas con rigor científico; la fuente de la energía vital es el hidrógeno extraído de la H mayúscula del agua, en una electrólisis potenciada por energía solar de la que abunda, por ejemplo, en los desiertos. ¿Comida de probeta? ¡No para mí, mil gracias!, diría instintivamente desde lo tropical territorial telúrico. Pero El caviloso George Monbiot, lúcido periodista y naturalista de células sensibles de las que acusan el deterioro de la Tierra, nos da la cachetada de estas nuevas y esgrime argumentos</t>
+  </si>
+  <si>
+    <t>o el humo de la gloria que mezcla perfecto el ron diplomático macerado en hojas de coca, con amargos de chocolate. Estos platos de la revolución, muestran el interés detrás de sus creadores, no solo de transportarlo a usted uno de los momentos más importantes de nuestra historia como país y crear toda una experiencia culinaria a su al rededor; también buscan promover el llamado farm to table, factor diferenciador en sus preparaciones, pues este movimiento social promueve que restaurantes y otros negocios adquieran los productos dentro de su propia comunidad, apoyando a los pequeños productores y asegurando la calidad y frescura de los insumos, ofreciendo finalmente un servicio que da cuenta de un sentido de lugar. La idea clave del concepto FTT se genera en base a una producción sustentable, que de ninguna manera ponga en amenaza el consumo de la población local. Significa generar valor sin destrucción de</t>
+  </si>
+  <si>
+    <t>y el posterior fallecimiento de su hijo, Alejandro Pizano, envenenado con cianuro en circunstancias muy extrañas, sumaron un ingrediente sórdido al coctel molotov que se destapó el 12 de noviembre y que puso patas arriba al establecimiento colombiano. En un año, cuando estemos haciendo el balance del 2019, veremos si el capítulo Pizano se convirtió en el catalizador necesario para llegar a las raíces profundas de la corrupción de Odebrecht o si el letargo volverá. Sin embargo, el controller logró patear el tablero de las instituciones y cambiar el statu quo al que estábamos acostumbrados. En un año veremos si todo eso valió la pena.</t>
+  </si>
+  <si>
+    <t>durante la cocción y probar para identificar qué podría faltar. Sin embargo, mientras casi todo el mundo dice que con la práctica se mejora el desempeño en el oficio de cocinar, debo decir que escribir en ciencias sociales es radicalmente diferente, pues con los años el desempeño no parece avanzar. Diría que investigar o escribir es un proceso de cocinar, pero en la cabeza. Cuando estamos inmersos en alguna investigación que nos apasiona soñamos con el tema, es como si nuestro cerebro tomara la evidencia y la fuera cocinando a fuego lento, muy lento, y vamos avanzando por niveles de comprensión cada vez más complejos e interrelacionados. Son temas sobre los que he estado reflexionando en estos tiempos de encierro y COVID19, en relación con una investigación que estoy adelantando. Y como casualmente es un tema afín al primer trabajo de investigación que publiqué en mi vida, hace 41 años,</t>
+  </si>
+  <si>
+    <t>al persistente uso de carbón en ciertas industrias y peor para los muy menores y muy mayores de edad. Hoy día, hasta las ciudades costeras enfrentan el problema del material particulado en suspensión nada que ver con el CO2, que configura la peor pesadilla para la salud humana y una de las fuentes de aerosoles atmosféricos que confunden todas las predicciones de cambio climático, pues modifican la cantidad de radiación capturada por un territorio dado. En el área metropolitana del Valle de Aburrá, conformada por 10 ciudades, se firmó en días pasados un Pacto por el Aire Limpio en una ceremonia pública en la cual decenas de empresarios, organizaciones de la sociedad civil, ramas de la gestión pública y ciudadanos de a pie se comprometieron con metas y acciones concretas para reducir las emisiones. Bajo la mirada escrutadora de la Procuraduría, el ministro de Ambiente, el gobernador de Antioquia, el</t>
+  </si>
+  <si>
+    <t>de productos químicos, de derivados del acero, del hierro y de metales no ferrosos, de procesamiento de alimentos, de textiles, de muebles y de madera. Y si no es tan rico en lo económico, ¿cómo ha llegado a ser tan rico en lo social?, le pregunto. Los daneses tienen una formación luterana y calvinista y, para ellos, primero está el trabajo; conciben su vida de manera austera, sin grandes lujos; y eso lo combinan con una conciencia y una convicción del cumplimiento del deber y de la honestidad. Por otra parte, en el siglo XX, la socialdemocracia implementó para la población una política de bienestar social. ¿Y cuáles son los valores de esa sociedad?, vuelvo a preguntarle. Primero, la honestidad, responde. Por eso la corrupción es ínfima. Después, la transparencia: cualquiera puede acceder a los archivos públicos. La sencillez: muchos ministros van a su trabajo en bicicleta, y los nietos</t>
+  </si>
+  <si>
+    <t>analizar lo que todavía muchos opinan sobre la imagen. Unos tomaban el ángulo del Esmad lanzando gases y escribían: Violentar a los estudiantes, ataques a la protesta pacífica, policías infiltrados. Otros publicaban fotos de personas tirando piedras o haciendo grafitis y escribían: Delincuentes de la marcha, vandalismo, no es protesta pacífica. Maquiavelo escribió en El príncipe : Las personas, en general, juzgan más con los ojos que con las manos, pues ver es de todos, mientras que tocar es de pocos. Todos ven lo que pareces, pocos tocan lo que eres y esos pocos no se atreverían a enfrentarse a la opinión de muchos. Esto fue en 1500, mucho antes de la fotografía, el Photoshop y la edición.</t>
+  </si>
+  <si>
+    <t>ambiente y más. La madera es cortada, encerada y secada, proceso que requiere muchos expertos, que se multiplican contando a quienes crearon las máquinas que lo hacen posible. Y eso es solo la madera. Para la punta, el grafito es extraído en un país como Sri Lanka por mineros tradicionales con la ayuda de retroexcavadoras, químicos y técnicas que combinan conocimientos de todo el planeta. El grafito se mezcla con arcilla de Mississipi, a la cual se le aplica hidróxido de amonio en un proceso refinado. Ese compuesto después se trata con una mezcla con cera proveniente de México, y sigue. El metal que sostiene el borrador es cobre, que se extrae en Colombia y requiere de complejos procesos de extracción. El borrador es hecho con un ingrediente llamado fatice hecho con un aceite que viene de las Antillas Holandesas y que contiene vulcanizadores y aceleradores como la piedra pómez,</t>
+  </si>
+  <si>
+    <t>trances característicos de la Gran Guerra: el uso masivo por parte de los ejércitos de variados tipos de gases: cloro, fosgeno y el letal gas mostaza, que quemaba la piel de los soldados, protegidos respiratoriamente por las máscaras antigás. El uso de químicos para eliminar al enemigo ha existido desde siempre. Flechas envenenadas, alquitrán ardiente, gases de arsénico, balas con cianuro y otros. Sin embargo, el horror, la muerte masiva y el sufrimiento permanente de los heridos causados por armas químicas de gran poder durante los años de la Primera Guerra, sumados a su discutible valor militar, llevaron a que su uso fuera proscrito por el Protocolo de Ginebra aprobado por la Liga de las Naciones en 1925. Durante la Segunda Guerra Mundial, los estados combatientes cumplieron con el protocolo de no hacer uso de armas químicas en el campo de batalla. Sin embargo, a los gases se les asignó</t>
+  </si>
+  <si>
+    <t>este mineral de azul tan profundo como el cielo de un buen día de sol y que nunca había visto en una playa? ¿Habrá en la zona algún coral, roca marina o concha que por los efectos mismos del mar termine molido y reducido a microscópicas partículas azules que acaban mezclándose con el resto de arena en esa playa? La dolorosa respuesta es que ni coral, ni roca ni concha. Los azulados granitos de arena no son de origen mineral, son de plástico. No fue difícil llegar a esa conclusión porque entre los millones de granitos azules que hay entre la arena también se encuentran decenas de trozos del mismo color más grandes y aplanados, como del tamaño de una moneda. Para el observador desprevenido pueden parecer conchas maltrechas, pero una inspección más cuidadosa revela que las tales conchas no son más que pedazos de plástico que han pasado días,</t>
+  </si>
+  <si>
+    <t>embera y sus cinco grupos, y con quien compartimos sus reivindicaciones por un mejor país ruralurbano. Todos tienen sus portales web y sus posiciones bien explicadas. De estos tiempos de juego preelectoral, con tanta abundancia de ruidos, debates y foros académicos, laicos y religiosos, sobresale el aumento de jóvenes que se han postulado y que serán votantes. Entre estudiantes, campesinas, indígenas, LGBT, se evidencian cambios culturales significativos en la forma de hacer política y en las ganas de cambio en el Congreso. De esta dinámica juvenil y refrescante, algo bueno tiene que resurgir. Se vive esa libertad de opinión para escoger y seleccionar de aquí y de allá, sin señores feudales que ordenen por quién votar, sin etiquetas religiosas, ni colores de partido. Esta nueva dinámica, posterior al acuerdo del Gobierno con las Farc, posibilita escoger con mayor libertad, sin llevar el sello de ser de uno u otro partido,</t>
+  </si>
+  <si>
+    <t>modelo de país. O en el fondo sí, pero en la superficie es llanamente un quejido de dos maneras de sentir. Y hoy en día lo que prima no es la idea sino la exaltación. Hoy gana quien emberraca el sentimiento. Esta inquina se derramó por fuera del recipiente de la política y contaminó la vida cotidiana. Se introdujo en las sabanas, aguó el desayuno, sembró discordia bajo el mismo techo. El extremismo se infiltró en el seno de lo que antiguamente constituía la clase alta y la baja. Media familia se fue con un bando, otra media con el otro. Fue el infierno. Hoy nos cogemos las sienes para procurar un remedio. ¿Cómo es posible que semejante belleza de territorio, que daría pescado, ñame y ron para todos, no sea un patio de recreo donde cada cual produzca, duerma, baile, cree y sueñe sin miedo al aguacero de balas?</t>
+  </si>
+  <si>
+    <t>Geológico Colombiano, el nivel de actividad se situó en amarillo frente a un incremento importante de la actividad sísmica volcanotectónica. Hace 35 años, la presencia de las fumarolas, la salida de azufre del volcán y la irrupción de columnas de ceniza oscura fueron las manifestaciones anteriores a la erupción, hecho sucedido en horas de la noche del 13 de noviembre de 1985, que hizo desaparecer a Armero y llorar a toda la nación. En la nota final de su novela, escribe Álvarez Gardeazábal: De Armero no queda para el mundo sino el recuerdo de una niña que trataron de salvar por horas enteras de los escombros inundados de su casa. Por ello esta novela, quizás, no sea toda la historia de lo que pasó en Armero, pero sí resulta muy cercana a la verdad de lo que a diario ha venido sucediendo en Colombia, donde los sordos hace mucho rato cercana a la verdad de lo que a diario ha venido sucediendo en Colombia, donde los sordos hace mucho rato que ya no hablan. escritor.com</t>
+  </si>
+  <si>
+    <t>No hay nada que despierte más la indignación de analistas nacionales y extranjeros que la discutible concentración de la propiedad de la tierra en Colombia. Las cifras que se barajan dicen que el 70 de las tierras están en manos del 12 de los propietarios. La culpa, reza el mito urbano, casi siempre es de acaparadores que violentamente se apoderaron de la tierra. Lo que casi nadie tiene en cuenta es que, dada su compleja topografía, las características de la tierra en el país son marcadamente heterogéneas; y gran parte no toda de la concentración de la tierra tiene una razón de fondo: las diferencias en productividad. El suroriente colombiano, que incluye la Orinoquia y comprende seis departamentos, tiene 12 millones de hectáreas casi todas planas disponibles para la agricultura y la ganadería. En el resto del país hay otros 28 millones de ha. muchas de ellas en loma aprovechables</t>
   </si>
   <si>
     <t>de tornarse violenta. Tierra. Hace años recorrí de cabo a rabo el Valle del río Patía. A pie la mayoría de las veces. No vi más que extensas haciendas separadas por alambre de púas en las que pastoreaban lotes de ganado cebú. La mayoría de esas propiedades fueron en el pasado pobladas y cultivadas por cimarrones que huían de las haciendas esclavistas. Con la Ley de Manumisión 1851 los esclavistas se volvieron patrones y los esclavos peones. Los dueños son blancos y los jornaleros negros. Recuerdo que durante una plática un anciano trató de blanco a un mayordomo. Le pregunté que por qué no lo llamaba por el nombre. Lo aprendí de mi abuelo que fue esclavo, contestó. La mayoría negra carece de tierra para trabajar y vive en ranchos de bahareque levantados en las estrechas mangas que dejan las alambradas. Son lugares en los que la vida transcurre como</t>
   </si>
   <si>
-    <t>Sobre un suelo que empieza a cuartearse, se esparcen profusamente hojas amarillentas como de un otoño que apenas rozara estos parajes y dejara destellos a su paso. Hojas rojizas de almendros que el viento ni siquiera se molesta en desprender cansadas de vagar entre ramas, la fuerza de su ánima vegetal las deja caer. De suspirar sin esperanzas por un otoño remoto, incapaz de aposentarse entre el verde rotundo del invierno y el pardo marchito de un verano que empieza a rondar por los alares de la casa solariega que aún llevo como un caparazón de amor, de vida, sobre mi vida entera. Un verano tímido, lento y parsimonioso, que poco a poco se va metiendo entre las cosas, hurga en el rústico fogón de cenizas de otro tiempo, en algún tizón que alumbre la memoria de una infancia que nunca acaba de pasar. De un cántico de luz que</t>
-  </si>
-  <si>
-    <t>La humanidad puede dividirse en dos: los que odian el silencio y los que no pueden vivir sin él. Los que lo aman han identificado y medido los lugares más silenciosos de la tierra. El primer lugar lo ocupa la Caldera de Taburiente, una depresión en Canarias, en la isla de Palma, donde los sonidos fluctuantes del área jamás pasan de 12 decibeles un poco más alto que el sonido de la respiración tranquila. El segundo está en la zona más árida del mundo, el corazón del desierto de Atacama en Chile, idéntico a la superficie de Marte, dicen. Cuando no hay vientos, se puede disfrutar allí de un silencio francamente extraterrestre. El tercer lugar es Monteverde en Costa Rica, un parque natural aislado del mundo por círculos concéntricos de árboles de 40 metros de altura y troncos de hasta ocho metros de diámetro y varias toneladas de peso, tapizados</t>
-  </si>
-  <si>
-    <t>campo de batalla ideológico. Descuidar ese flanco era ceder terreno al enemigo, y por eso un personaje como Laureano Gómez dedicó casi más tiempo a la crítica literaria que al debate político en los años 30. Comentó los escritos de León de Greiff, de Darío Samper, de Rafael Maya, de Porfirio Barba Jacob, y con todos ellos peleó, y siempre debido a cuestiones morales que remitían a visiones políticas de la realidad. En la obra de De Greiff, por ejemplo, vio una nociva popularización de la poesía. Sus poemas, al alcance del lustrabotas, del carpintero o del ganapán de esquina, robaban a la poesía la sustancia que hacía de ella una fuerza espiritual capaz de forjar naciones. Casi como Stalin, Laureano creía que el poeta era un herrero del alma. Aunque anacrónicas y derivadas de esa curiosa obsesión grecolatina que sobrevivía en Bogotá mientras el resto del mundo se modernizaba,</t>
-  </si>
-  <si>
-    <t>calor y química mineral, que transformaron la rudimentaria minería de veta usada desde tiempos prehispánicos, en un trabajo de elevados conocimientos que dio lugar a cuantiosas inversiones y a las primeras empresas capitalistas exitosas que operaron en Colombia. Fueron ellos quienes enseñaron a usar el molino de pisones, la pólvora, el fósforo, la nivelación de canales, la construcción de ruedas hidráulicas, la amalgamación con mercurio, el uso de barras de acero para rocas, la fundición industrial, la refinación del oro al fuego, la construcción de hornos y las prácticas de conservación de maquinaria, entre otros aspectos. Ese fue el contexto que permitió el desarrollo, sobre todo en la segunda mitad del siglo XIX, de lo que algunos llamaron la minería científica moderna. El desarrollo de esa minería no puede explicarse sin los impactos de apertura al mundo exterior, en todo sentido, que generó la Independencia. sin los impactos de apertura al mundo exterior, en todo sentido, que generó la Independencia.</t>
-  </si>
-  <si>
-    <t>Macron con los chalecos amarillos en Francia. La Encuesta del CNC muestra que al ciudadano corriente le preocupan más los problemas que tienen que ver con el futuro que con el pasado, sobre todo en lo que este tiene de violento e injusto. Reclaman por una mejor educación y oportunidades y empleo para los jóvenes; contra la corrupción y por la transparencia; por pensiones y condiciones laborales dignas; por una especial atención a la realidad campesina y por una reforma tributaria que genere equidad tributaria y no atropelle a una clase media en proceso de consolidarse y que estuvo bien activa en estos días. Poca mención hacen de los temas que alimentan a la prensa y a muchos analistas y dirigentes políticos: las negociaciones con el ELN, la implementación del Acuerdo de paz, la privatización de empresas estatales, el medio ambiente. Va quedando claro, y tal como se expresó en</t>
-  </si>
-  <si>
-    <t>Hablar hoy en el país de la llamada economía naranja es la manera más segura para escuchar un mal chiste que busca descalificarla sin analizarla, una nefasta práctica que en buena medida se ha impuesto entre nosotros. La idea de esa economía no es nueva en Colombia ni es una invención criolla. Surge en el seno de las llamadas industrias culturales que, gracias a desarrollos tecnológicos, facilitaron y generalizaron la reproducción a escala industrial de mucha de la creación cultural y dieron inicio a la potente industria del entretenimiento que en el mundo mueve billones. Primero fue la palabra escrita, luego fueron las imágenes de la pintura y la fotografía, y ese monstruo magnífico del siglo XX, el cine, y fue la reproducción de la voz, a caballo de los desarrollos fonográficos que no se detienen, y las artes escénicas y de interpretación directa que salieron de las salas de</t>
-  </si>
-  <si>
-    <t>Ganar el poder siempre será apenas el comienzo de la prueba definitiva de cualquier proyecto político. La satisfacción de necesidades básicas de bienestar ciudadano, así como el grado de ejercicio real de libertades fundamentales, terminan por determinar la medida de su éxito, o de su fracaso. La llegada al gobierno de los antiguos combatientes del Frente Patriótico, como se llamó la alianza del ZAPU, Unión del Pueblo Africano de Zimbabwe, de Joshua Nkomo, y el ZANU, Unión Nacional Africana de Zimbabwe, de Robert Mugabe, significó el fin de la Rodesia Británica, para dar paso a un Estado regido por la mayoría negra, y representó un triunfo para los marginados del país y para la causa de la democracia africana. Los acuerdos de Lancaster House, que lord Carrington, entonces canciller británico, condujo con maestría, abrían un enorme campo de esperanza para la realización de un proyecto político de convivencia entre los</t>
-  </si>
-  <si>
-    <t>popular, en especial los congresistas, que hoy son los únicos protagonistas de las decisiones de la mayoría de las colectividades. Sí las listas son cerradas, no es descabellado pensar en una financiación exclusivamente estatal porque serían los partidos quienes harían las campañas y sus directivos quienes deberían responder por el uso de los recursos destinados para esos fines. La financiación estatal, además de facilitar el control del financiamiento político, ofrece un elemento que es central en una democracia: que nadie tenga ventajas electorales por cuenta del dinero, es decir que la competencia sea realmente de las ideas, de las posturas de cada partido frente a los temas de interés de los ciudadanos y de la trayectoria de sus candidatos. De otra parte, es preciso decir que es un avance el hecho de que el proyecto del gobierno proponga que la conformación de las listas deberá acoger los criterios de paridad</t>
-  </si>
-  <si>
-    <t>Con base en la referencia que aparece al final preparé los párrafos a continuación. Elegí esta referencia, porque encuentro numerosas e inquietantes coincidencias entre las razones para las izquierdizaciones de los estadounidenses y de los colombianos. Resulta claro que durante décadas empresas de noticias tales como CNN y The New York Times se han sesgado en favor de la democracia social también conocida como progresismo, o más simple aún, como ideologías de izquierda. Por ejemplo, la gran mayoría de sus periodistas declaran ser demócratas y sus donaciones se dirigen en forma abrumadora hacia estos candidatos. En forma similar, en décadas recientes, no pocas universidades están militando en favor del Partido Demócrata a juzgar por sus afiliaciones y por sus donaciones. Algo más, escriben textos y libros de historia con los cuales influyen en sus colegas, en los profesores y en los colegios de bachillerato. Este adoctrinamiento ideológico que se gesta</t>
-  </si>
-  <si>
-    <t>a un intento, sin duda condenable, pero no tan atípico, por incidir en las decisiones de la Rama Judicial y Legislativa sobre la fumigación con glifosato, la extradición y la JEP, y por castigar a quienes no acatan las órdenes de Washington. Si bien esta indebida intromisión en la política colombiana ha generado un rechazo generalizado, llama la atención la molestia menor que parece haber suscitado la pasividad del gobierno Duque frente a lo que ha descrito como una decisión soberana de Estados Unidos. Le puede interesar: Guerra de testosterona Por más cierto que sea el matoneo diplomático que reviste este episodio de las históricamente estrechas y amistosas relaciones bilaterales, la narrativa de la injerencia yanqui se queda corta al no tener de presente las formas en las que, por simple afinidad o por decisión voluntaria, distintos gobiernos colombianos han tolerado la vulneración de la soberanía y la autonomía nacionales,</t>
-  </si>
-  <si>
-    <t>como muestra de su fortaleza la baja inflación, la solidez del sistema financiero, la confianza de los consumidores, la resiliencia del mercado laboral y la misma política fiscal sustentada en una reforma tributaria que, según el ministro Cárdenas, descartaría cualquier ajuste durante un lustro. Antes de su retiro el ministro dejó el nuevo proyecto de presupuesto nacional debidamente equilibrado. En ese marco una ley de financiamiento resulta, simplemente, innecesaria. De allí surge la otra pregunta: ¿cómo se produce, de repente, un hueco fiscal de 14 billones? La respuesta es fácil: el hueco fue creado por el nuevo ministro. El Gobierno se inventó gastos e inversiones sin el debido respaldo presupuestal. Como lo anota Patricia Lara en su reciente columna de este mismo diario 161118, no hay un hueco fiscal, sino la decisión de acometer nuevos gastos que el Gobierno tasa en esa cifra. Solo que como no hay recursos para</t>
-  </si>
-  <si>
-    <t>Cada vida reproduce la totalidad de la historia humana, aunque no lo verbalicemos ni seamos conscientes. Todos hemos experimentado nuestra propia guerra de Troya, nuestras pestes mortíferas, nuestro descubrimiento de América o la exploración de los polos. También nuestra Revolución francesa y nuestra singular caída de Berlín o de Tenochtitlán, y hemos compuesto nuestras muy personales Canciones de Bilitis. Somos una sola experiencia humana. Lo que nos hace únicos porque somos únicos es el modo en que cada uno interpreta el viejo drama de vivir, esa antigua partitura que en la juventud nos exalta y que, con los años, se vuelve algo insípida, reiterativa. A veces anhelamos salir de ese guion ya visto, pero ¿cómo? Hay días en que somos tan lúgubres, tan lúgubres. Lo no vivido parece estar en la periferia y es cada vez más inalcanzable. ¿Irse, cambiar, ser otro? Escribir es un modo de ponerse frente al</t>
+    <t>valorados por encima de las tierras y la maquinaria, para Gates la tierra seguirá siendo lo más importante. Según Gates, la información será cada vez más accesible y su valor radicará en saber qué hacer con ella y no simplemente en tenerla. Por el contrario, el valor de la tierra en el mundo, que está ya en los diez billones de habitantes, seguirá siempre en subida así solo se quede en engorde. Que uno de los magnates de los computadores, y por lo mismo de la información, diga que la tierra seguirá siendo valiosísima no se debe tomar a la ligera. Menos en Colombia, donde la titulación de las tierras se sigue banalizando e ignorando. Esta semana se retomó la discusión sobre el proyecto de restitución de tierras que propone María Fernanda Cabal. La propuesta del Centro Democrático quiere volver a la segunda instancia en los juicios y poner la</t>
+  </si>
+  <si>
+    <t>su algarabía de tierra caliente, los únicos gritos que se escuchaban en la ciudad eran los que venían los domingos del estadio y los de los vendedores ambulantes del centro. Pero ahí estaban casi todos 15 años después, salieron de las piedras, bajaron de la copas de los árboles y llegaron de todas partes del país para cumplir una cita muchas veces postergada. Los que no pudieron estar enviaron videos con poemas propios y prestados, otros mandaron canciones y anécdotas, y la presencia de los ausentes estaba en la brisa que esa noche fue más fresca que de costumbre. Nadie quería dejar de cantar, porque el silencio suele tender trampas en la memoria, con preguntas que no tienen respuesta o, lo que es más doloroso aún, con las posibles versiones que muchos han construido con el paso del tiempo: ¿Cómo habrán sido sus últimas horas de vida? ¿Cuáles fueron sus</t>
+  </si>
+  <si>
+    <t>sabemos hoy, son relatos explicativos que tienen como propósito dar razones sobre un hecho, o conjunto de hechos, de naturaleza, aparentemente, inexplicable. Por lo tanto, la erupción de un volcán, el movimiento de las placas tectónica o la devastación producida por un tsunami tenía, por lo general, una explicación de naturaleza divina. Los mitos, pues, han sido relatos que han buscado llenar un vacío de carácter científico. Han sido utilizados como herramientas de control social, pero también como unificación del pensamiento de un grupo en un momento histórico determinado. El mito de que los reyes eran seres con cierto halo divino sigue inserto en la mente de algunos pueblos, así como la creencia de que las religiones son el camino que nos conducirá a Dios. La llegada de nuevas generaciones sepulta algunos mitos, pero les da vida a otros. Dudo de que a esta altura de la historia y los</t>
+  </si>
+  <si>
+    <t>ocupados y transformados fueron los que contenían los mejores suelos: valles interandinos del Cauca y Magdalena, y suelos de origen volcánico en las cordilleras. Las zonas PDET presentan múltiples retos. El modelo ganadero predominante y socialmente apropiado no es viable. Hay que buscar alternativas productivas novedosas y sostenibles relacionadas con ecoturismo, turismo cultural, bioeconomía, café con sombra biodiversa, cacao y caucho en bosque, ganadería en sistemas silvopastoriles, maderables y frutas tropicales, entre otras. Algo de esto ya se está haciendo, pero falta aumentar su escala. En esta búsqueda, la ZAP propuesta por el Centro de Estudios para la Paz Cespaz, por solicitud y en coordinación con el Ministerio de Ambiente, reconoce la capacidad y el conocimiento de las comunidades para imaginar y ordenar su territorio. La ZAP parte de que no hay áreas de conservación vs. áreas de producción, sino áreas donde predomina la conservación y se incluyen procesos productivos,</t>
+  </si>
+  <si>
+    <t>ingeniosos cálculos, así como la formulación de los modelos, se convirtieron en la labor del grupo de Katherine. Las trayectorias más críticas correspondían al reingreso de las naves a la atmósfera terrestre. Un acercamiento en un ángulo muy pequeño, con respecto a la vertical, podía incendiar la cápsula al regreso, y un ángulo mayor podía enviarla nuevamente a una órbita. A diferencia de muchos de los matemáticos de la NASA que habían olvidado la geometría analítica y la euclidiana, el grupo de Katherine era fuerte en estas elementales áreas y eso les permitía acercarse en forma más intuitiva al cálculo de las trayectorias. La película Talentos ocultos está basada en el trabajo del equipo de Katherine. Por su parte, Freeman Dyson, físico, matemático, humanista, científico, político, trabajó inicialmente en matemáticas puras, ecuaciones diofánticas y teoría de números; una transformada lleva su nombre, la transformada de Dyson. Su trabajo posterior se</t>
+  </si>
+  <si>
+    <t>proyectar, en principio, los organismos de gobierno, comenzando por los de carácter multilateral. El escenario es complicado. Cuando pensábamos que la agenda mundial en 2020 estaría signada por las elecciones en Estados Unidos, llegó el coronavirus que, por el contrario, puede definir ahora el resultado de unas elecciones en las que el virus se ha convertido en un importante referente de campaña. Hacen parte de ella, también, el devenir de la guerra comercial con China y las sospechas sobre una conducta poco solidaria y ética del gobierno chino al informar lo ocurrido. ¿Están fundadas en suposiciones o en el interés de la campaña Trump? En cualquier caso, se trata de un hecho político que terminará de alterar la coyuntura internacional generando más incertidumbre. Cuando menos hasta noviembre, tendremos temores de una guerra comercial transformada en una de coronavirus. Pocos recuerdan ahora que, para evitar la escalada de un conflicto desde</t>
+  </si>
+  <si>
+    <t>construir la nuestra. Incluso, podría pensarse en un trabajo conjunto entre las secretarías de cultura y educación, para que esta colección haga parte de los planes lectores de las instituciones educativas de la ciudad. Así, por ejemplo, se podría trabajar con los más pequeños las obras de Triunfo Arciniegas, uno de los escritores de literatura infantil más importantes del país. En bachillerato, cuando se enseñan los distintos tipos de escritura, se leería a los poetas Gaitán Durán, Cote Lamus, Saúl Gómez o Ana María Vega Rangel; textos periodísticos con Miguel Méndez Camacho o Renson Said Sepúlveda; ensayo a través de la prolífica obra de Antonio Donadio y, cuento y novela con Carlos Perozzo y Manuel Valdivieso. Estas obras son desconocidas por los cucuteños y no hacen parte del currículo escolar. Ahí, hay una oportunidad interesante para que la nueva administración acompañe esa transformación social propuesta en campaña, con la comprensión Ahí, hay una oportunidad interesante para que la nueva administración acompañe esa transformación social propuesta en campaña, con la comprensión profunda de aquello que han escrito los autores de la región. No se trata de crear un sistema educativo en el que solo se enseñe poesía, como soñaba Ugolugo Rangel, uno de los protagonistas de Hasta el sol de los venados , sino de crear un vínculo estético y sensible con Cúcuta, para que la transformación social también consolide una identidad local.</t>
+  </si>
+  <si>
+    <t>solución al tema. La tercera línea es vincular la evaluación docente con los resultados de la enseñanza, fundamental para el propósito nacional de mejorar la calidad de la educación pública. Fecode aspira a un único estatuto docente, con el interés de quedarse con las condiciones de ascenso del Decreto 2277 de 1979, sin evaluación, y las remuneraciones más altas del Decreto 1278 de 2002, cosa que se comería cualquier financiación sin ayudar a elevar la calidad. En el actual sistema de evaluación no importa si los niños han aprendido o no. Y nuestra educación pública se ha ido poblando de instituciones donde los estudiantes celebran los paros docentes y las asambleas asociadas porque no tendrán que ir a aburrirse al colegio, mientras madres y padres de familia se preocupan sobre todo porque no tendrán guardería ni alimentación escolar para sus hijos. Incluso en el aula se dan acuerdos entre docentes</t>
+  </si>
+  <si>
+    <t>de las anteriores opciones muestra un escenario preocupante: o las investigaciones las siguen adelantando quienes hasta ahora lo hacen pese a que no se puede garantizar su independencia frente al fiscal general, o se le entregan al fiscal ad hoc para que las comience de nuevo, o se crea una Fiscalía paralela que las asuma. En semejante coyuntura, ¿para qué sirve la figura del fiscal ad hoc ? Para solucionarle a Martínez un problema que solo él creó con sus conflictos de intereses y, de esa manera, permitirle continuar en su cargo. Todo este enredo tiene una salida jurídica mucho más simple: la renuncia del fiscal general. No se debe sacrificar la institucionalidad para ayudarle a un funcionario a resolver una dificultad personal; son sus intereses particulares los que deben ceder ante el riesgo de que por ellos se deshonre la institución que preside. ceder ante el riesgo de que por ellos se deshonre la institución que preside.</t>
+  </si>
+  <si>
+    <t>En torno al número de hectáreas pedidas unas organizaciones dan unos números, otras las descartan y dan nuevos datos, estas discusiones que no son nuevas se dan, en parte, por el acceso amplio a la información que se tiene derivado de las imágenes satelitales, en otros casos, por las denominadas fake news o noticias falsas, muchas de las cuales corren sin control. Lo fundamental está en la buena medición y el monitoreo de las variables ambientales que se realicen sobre este tema crucial, pues este es el cimiento para definir políticas públicas con soluciones que permitan controlar la deforestación. La cifra oficial que cada año publica el Instituto de Meteorología y Estudios Ambientales Ideam es suficientemente buena. Eso no quiere decir que no se tenga espacio para mejorías. Una de ellas tiene que ver con aspectos metodológicos para darle espacio a variables como bosques naturales manejados bajo planes de ordenación,</t>
+  </si>
+  <si>
+    <t>Por eso bien se dice que la economía depende de las personas. Es ahí donde debe analizarse no solo la cantidad de personas en el mercado objetivo sino el comportamiento de las mismas. Acá es donde debe analizarse una segmentación del mercado en donde se tenga claro a la generación a la que se quiere impactar. Si ese análisis queda bien hecho seguramente los ingresos fluirán y tendremos buenos resultados. Recordemos que poner las ventas en el centro de la estrategia es una de las claves de los negocios exitosos. Pero como no hay mal que dure cien años ni cuerpo que lo resista, los negocios no pueden ser pensados para el presente próximo sino para que perdure. Estoy convencido que cuanto más se ha fallado, más y mejores posibilidades tendremos de no volver a equivocarnos. Por eso el pasado en los negocios es importante, no solo por la historia</t>
+  </si>
+  <si>
+    <t>del Estado, los trámites, los controles y la descoordinación de las agencias oficiales. Así las cosas, la acción estatal resulta ineficiente, tardía y en ocasiones contraproducente. El Estado se convierte en un obstáculo para el ciudadano, un requirente de requisitos, certificados y papeles. Y qué decir de la politización, que pretende colocar la máquina estatal al servicio de las coyunturas partidista y electorales, cuando no se convierte en el acusador y perseguidor de sus opositores. Por último, el Estado es víctima de la corrupción, el desfalco y de las organizaciones criminales del narcotráfico, que minan sus decisiones e inhiben sus acciones, cuando no es presa de saqueos. Sí, el Estado es débil y por ende presa de los más disimiles intereses. En esta coyuntura de las negociaciones de paz, podría decirse que las Farc se aprovecharon de su debilidad, no solo para pactar amnistías, indultos y justicia de transición, sino</t>
+  </si>
+  <si>
+    <t>solo con el VAR sino también con instituciones políticas y con sistemas de gobierno, con ideologías, con modelos económicos, con teorías: que su éxito depende del que los use, no de su presunto y fallido valor universal. Las recetas se acomodan al paciente; lo que en un cuerpo es salvación, en otro es maldición. Y la naturaleza de cada quien, obvio, lo determina todo. En la Copa América, por ejemplo, el VAR le ha añadido caos y confusión al juego. Antes que aclarar las situaciones, las oscurece más. Como si su misión fuera, según parece, anular los aciertos y promover las equivocaciones. Todo dentro de la solemnidad, la farsa, el absurdo y el ridículo. Y hay quienes creen que es el VAR lo que está mal. ¿Están seguros? Volvamos a ver la jugada. ver la jugada.</t>
+  </si>
+  <si>
+    <t>suelen agarrar de ciertas expresiones de promoción del proyecto, como que sería un negocio entre privados como si fuera una manera de facilitar un mayor enriquecimiento de la banca privada. Como quiera que se dé la opción de avaluar tanto en moneda legal como en UVR, es mejor dejar el concepto de moneda legal constante, es decir, actualizando dicho valor con el IPC del Dane. En lo posible limitar los actores al hogar primigenio de la pareja o el que por razones de fuerza mayor se haya convertido en hogar unipersonal, con el fin de evitar los problemas derivados de la propiedad repartida, por cuanto tampoco aquí se cumpliría plenamente el objetivo de que la renta vitalicia la perciba plenamente el adulto mayor al que se quiere beneficiar. Es decir, que al concepto de propiedad repartida se le trate de la misma forma restringida que el de la propiedad familiar que al concepto de propiedad repartida se le trate de la misma forma restringida que el de la propiedad familiar inembargable. Finalmente, lo más importante, y lo ha reiterado el ministro Malagón, se trata de una negociación voluntaria con procedimientos transparentes, que tiene la posibilidad de mejorarle la vida a un potencial inmenso de personas que el proyecto estima en un millón ochocientas mil.</t>
+  </si>
+  <si>
+    <t>Y sin que haya a quién quejarse. ¿O sí? He traído a colación la muerte de Buda para hacer hincapié en que todo lo referente a una posible vida después de la vida es un tema que sigue envuelto en el misterio. Ahora bien, con la inhumación o entierro se asume un pequeño riesgo: que el cuerpo caiga en un estado de catalepsia mediante el cual cesen las funciones vitales y lo den por muerto y le hagan la velación y lo lloren y luego lo entierren, para despertar horas después atrapado en un ataúd y vivir la más aterradora de las pesadillas. ¿Cuánto tiempo podría soportar alguien encerrado en un ataúd entre el momento en que recupera la conciencia hasta el instante en que muere de nuevo? Depende de la cantidad de oxígeno en el lugar donde despierta, pues mientras menos posea, más breve será su tormento. Sin descartar</t>
+  </si>
+  <si>
+    <t>y estigmas. Todas las mujeres del planeta, durante 3 a 5 días de cada mes y en promedio durante 35 años, sangramos por la vagina. Así ha sucedido desde antes que el ser humano fuera Homo sapiens. Pero en todas las culturas de todas las épocas, la menstruación es un tabú. Las normas y suposiciones que establecen qué puede y qué no puede hacer una mujer en su luna no han sido jamás dictadas por mujeres. No bañarse, no hacer ejercicio, no comer determinados alimentos, no tener sexo, no participar de actividades sociales o no batir los dulces en el fogón, son apenas asomos de los misterios con los que se envuelve a las mujeres y su extraña condición ovular. El otro día escuche decir, en Bogotá, que no hay que cortarse el pelo con mujeres sino con hombres, porque si están con la menstruación, se lo dañan. Un simple</t>
+  </si>
+  <si>
+    <t>es entender que el enemigo está libre, armado y acechando para metérsele en el cuerpo al que le dé tiro. En esto el coronavirus sigue la lógica de la naturaleza, pues sus presas son los individuos con un organismo biológico debilitado por la desnutrición, edad o preexistencia de enfermedades que han afectado o afectan su sistema respiratorio o de defensas. O bien porque viven en un entorno, en un organismo social igualmente debilitado, que no solo no les ofrece protección a sus cuerpos, sino que antes bien los hace vulnerables al ataque por el hacinamiento, por la falta de aire y espacio, de agua y en general de condiciones sanitarias mínimas, por una mala alimentación y aun grados diversos de desnutrición, y para rematar una tensión alta por la incertidumbre de una supervivencia económica amenazada. Ahora bien, el camino no es huirle al bicho sino entender su comportamiento y adaptar</t>
+  </si>
+  <si>
+    <t>Soy de los que cree en los razonamientos de Morgan y Bachofen, acerca de la existencia de un periodo de la humanidad, la sociedad matriarcal , en el cual la mujer era preponderante y se constituía en el núcleo articulador de la familia y de la organización social en su conjunto, de la política y la economía, de la moral, la religión y la administración de justicia, entre otros de sus liderazgos. Fueron ellas, las mujeres, quienes, al igual que a los hijos, alumbraron el mundo en sus albores, organizándolo, orientándolo y conduciéndolo por la senda de su crecimiento y desarrollo, hasta cuando el derrocamiento del derecho materno, como consecuencia del aumento de la riqueza y del cambio de genero de vida, dio paso al dominio del padre y a su supremacía en la dirección de la familia y el hogar. Desde entonces, con la gran derrota histórica del sexo</t>
+  </si>
+  <si>
+    <t>sobrevivirá, asumir la muerte o secuelas permanentes en la salud después de terminar el embarazo o llevar a término un embarazo resultado de un hecho traumático como lo es el ser forzada sexualmente. Dado que estas situaciones pueden aparecer en cualquier momento en el embarazo, este modelo no tiene plazos o límites de semanas: puede solicitarse la interrupción del embarazo cuando la situación aparece. De hecho muchas de las malformaciones que son incompatibles con la vida solamente pueden descubrirse después de las veinte semanas de gestación. Las complicaciones para la salud de la madre también pueden aparecer muy tarde. Lo más importante, sin embargo, es que el principio tras el modelo es que la mujer no tiene por qué soportarlo y por tanto el remedio o reparación mínimo que se le ofrece es poder salir de esta situación. Si se suman las trabas y barreras en el sistema, más razones</t>
+  </si>
+  <si>
+    <t>Leyendo el maravilloso libro de Biología de Hongos que gentilmente me regaló Silvia Restrepo, hoy vicerrectora de Investigaciones y coautora del texto con otras cuatro expertas Ediciones Uniandes, 2012, pensé en los humanos como los hongos de los sistemas electrónicos de sílice, operando de manera equivalente a estos organismos que introdujeron la innovación bioquímica dentro del reino de lo orgánico hace millones de años. Al fin y al cabo, en la etapa evolutiva que estamos viviendo apenas se está organizando esta relación fundante con el universo de los ordenadores y de ella dependerá la capacidad de retener dentro de ellos los rasgos críticos del nivel de organización humana. Las redes de hifas, los hilos infinitos que conectan el mundo del reino Fungi entre sí y con el resto de vida en todo el planeta establecieron un convenio con las algas fotosintéticas para unir la potencia de la disolución mineral fueron</t>
+  </si>
+  <si>
+    <t>humanos y que nos separan de la vivencia mística del Dios que habita en el silencio íntimo; en el asombro de lo indecible; más allá del lenguaje, más allá de las lenguas; más allá de nuestra limitada percepción de lo luminoso que nos constituye y nos rodea. Vivimos también dentro de sistemas políticos y jurídicos, en órdenes económicos legitimados en la palabra, según teorías, paradigmas, modelos construidos en el lenguaje. Está también dentro de nuestra naturaleza ignorar ese origen y creer que son naturales los mundos que creamos, aferrándonos dogmáticamente a una u otra práctica o creencia. Hasta mediados del siglo XX se creyó que en el campo de la teoría social había de un lado los postulados de una ciencia única e infalible y del otro las posiciones ideológicas del libre examen. Hasta que el vuelco total en la concepción del conocimiento puso en tela de juicio esos pretendidos</t>
   </si>
   <si>
     <t>genital, el embarazo adolescente, en la mayoría de los casos no deseado, los desórdenes alimenticios fruto de discriminación, y la crueldad mental, que abarca elementos que van desde las limitaciones en el acceso a la educación y el sometimiento a tratos vejatorios. Ante este panorama, que pone en cuestión la calidad de vida que los Estados deberían proveer en condiciones de igualdad, de verdad, a todos los seres humanos, es urgente acometer un compromiso sin fronteras, de encuentro de civilizaciones, que permita pagar la deuda más grande del mundo, de la que son acreedoras las mujeres, que representan al menos la mitad del genero humano.</t>
   </si>
   <si>
-    <t>sabiendo mamar y sabiendo andar. Un pez nace y sabe nadar; nosotros no. También nosotros nacemos sabiendo andar con el órgano de caminar en el cerebro, pero nos demoramos un año para volvernos bípedos sin caernos. Antes, al gatear, logramos ser cuadrúpedos. Nacemos sabiendo hablar, o por lo menos con un órgano del lenguaje que empieza pronto a emitir sonidos y que a los tres años estalla en toda su maravillosa amplitud y creatividad: una niña de tres años habla con una gramática perfecta. Nuestro cerebro sabe sin saber que sabe gramática. Conjuga los verbos, hace concordancias de género y número, inventa frases que no ha oído nunca. En ese sentido, platónico, venimos al mundo con una memoria de la vida pasada de la especie: no aprendemos a mamar, a caminar, a hablar: recordamos cómo se habla, pues es algo natural, que viene con nuestro cerebro. A partir de estas</t>
-  </si>
-  <si>
-    <t>lado que no es. Después del virus, la izquierda y la derecha las tengo al revés, y durante 20 días la vida me era indiferente y todo lo que pensaba estaba patas arriba. Lo único bueno es que me estaba muriendo muy tranquila. Casos como el de mi hermana hay por miles, por millones. Pero lo peor es que hay personas que simplemente se acuestan porque se sienten sin ánimos, esperan sin hacer nada, y cuando ya sienten que se están asfixiando, llegan al hospital demasiado tarde. No solo hay consecuencias pulmonares o neurológicas. A algunos enfermos les da miocarditis, y esta inflamación puede ser silenciosa, sin síntomas, lo cual la hace más insidiosa, pues hay atletas que tuvieron COVID, supuestamente están recuperados, y en medio de la práctica de su deporte se desploman. No escribo esto para asustarlos. O, mejor dicho, sí. Sé que estamos hartos de vivir encerrados, su deporte se desploman. No escribo esto para asustarlos. O, mejor dicho, sí. Sé que estamos hartos de vivir encerrados, de no abrazar a nadie, de ponernos máscaras, de tener las manos peladas de tanto lavárnoslas. Pero no es el momento de bajar la guardia. Una vacuna eficaz no está a la vuelta de la esquina, el virus sigue creciendo, y se acerca, y nos cerca: cuidémonos.</t>
-  </si>
-  <si>
-    <t>sexo aséptico. Y es que la humanidad ha sido siempre lasciva pero pacata. Aunque el mundo consume varios gúgoles de terabitexxx por segundo dato de Pornhub, porque en esto solo me fío de las profesionales, la gente denigra de las prostitutas sin reconocer su esforzada función social, la mano que le tienden al tímido y al flácido, al feo y al solitario. La humanidad yacente olvida que si hoy somos más felices bajo techo y sobre el lecho lo debemos por igual a la píldora y a la revolución sexual de los 60 que a la educación del porno por internet. Allí fue donde aprendimos que, como dice Woody, el sexo solo es sucio cuando lo hacemos bien. El Estado debería capacitar a las chicas webcam para que sacien no solo las ansias de los cuerpos sino también la sed espiritual de sus clientes. Así habría una conjunción del putas:</t>
-  </si>
-  <si>
-    <t>de mujeres y niñas que más lo necesitan, por ejemplo: aquellas que viven en zonas rurales y se demoran semanas en llegar a un puesto de salud, las niñas que sufren violaciones sistemáticas desde antes de tener su primera regla y ni siquiera saben que están embarazadas, o las mujeres con embarazos inviables cuyos problemas suelen detectarse en el segundo o tercer trimestre. Otra razón importante es que los estándares internacionales han avanzado para proteger los derechos de las mujeres: por ejemplo, en 2012, en el caso Artavia Murillo contra Costa Rica, la Corte Interamericana de Derechos Humanos aclaró que la protección de la vida desde la concepción no es absoluta y que no puede usarse para restringir desproporcionadamente otros derechos. Y el año pasado, el Comité para la Eliminación de la Discriminación contra la Mujer Cedaw recomendó a Colombia hacer una despenalización más amplia del aborto para eliminar las</t>
-  </si>
-  <si>
-    <t>historia. Apenas nueve meses entre la publicación del código genético del virus y la evidencia estadística sobre seguridad y eficacia de la primera vacuna un proceso que nunca había tardado menos de cinco años. Una tecnología que jamás se había intentado ARN mensajero. Una eficacia superior al 90 , muy por encima de casi todas las vacunas contra enfermedades infecciosas. Millones de vacunascandidatas que se habían fabricado antes de saber su eficacia y que por eso empezaron a aplicarse horas después de su aprobación para uso de emergencia. Pero también en estos días la desigualdad está mostrando su rostro más obsceno: unas vidas humanas valen más que otras y el orden del acceso a las vacunas es el certificado exacto del lugar que ocupa cada uno de nosotros en la pirámide de escala planetaria. Algunas desigualdades se justifican porque una sociedad sensata necesita que existan esas desigualdades: los médicos y</t>
-  </si>
-  <si>
-    <t>una moda, como un sufijo según apunte del fallecido historiador Germán Colmenares. Se buscaba una explicación científica, pero el resultado no cumplió esa meta, en vez de un discurso homogéneo el libro Colombia Violencia y Democracia compiló una serie de ensayos sobre todo tipo de violencias que afectaban a la sociedad colombiana dando una apariencia de igualación de todas ellas. Además, en lo que respecta a la violencia política insistió en la tesis de que la tierra está en la base de los conflictos contemporáneos del país como también las falencias del estado, el carácter excluyente del régimen político, todas las cuales configurarían las llamadas causas objetivas del levantamiento armado. Más aún, Sánchez reitero su tesis según la cual, los colombianos somos propensos a la violencia y el país se ha configurado endémicamente a partir de la violencia, como si se tratase de una enfermedad y todas las situaciones de</t>
-  </si>
-  <si>
-    <t>ciudadana son generalizadas. Segundo, la mayoría de las personas tiene poca confianza en la policía y considera que no hace bien su trabajo. Tercero, el control sobre y la rendición de cuentas de las instituciones policiales son deficientes, aun cuando el uso de la fuerza está regulado. Y cuarto, el nivel cultural de nuestras policías, medido en la duración y profundidad de su formación sobre todo en relación con estrategias no represivas y de desescalamiento de crisis es comparativamente bajo. Para explicar este déficit de legitimidad, algunos analistas sugieren que la forma en que conceptualizamos el policiamiento como bien público condiciona el alcance de cualquier diagnóstico e intento de reforma. Si consideramos que el rol central de la policía se limita a combatir el crimen, estadísticas como las tasas de homicidio e hurto se tornan claves para medir su éxito. Sin embargo, si algo nos muestran muertes injustificables como las</t>
-  </si>
-  <si>
-    <t>Como en todas sus obras, Stanley Kubrick tuvo la ambición de concentrar la humanidad en un hecho y conectar las preguntas metafísicas siempre irresueltas con la intensidad de los colores y las apariciones también metafísicas de un acertijo indescifrable. La última aparición del sol, en los últimos minutos del largometraje, hace el relevo con la imagen de un embrión humano en el espacio mientras retumban los tambores sinfónicos y el ciclo visual cobra una remembranza entera de las búsquedas siempre prolongadas y la incertidumbre. Quedarse mudo y estático después de tanta pirotecnia simbólica y técnica sigue siendo natural ahora, 50 años después de su estreno entre la frialdad de un canon obedecido con mansedumbre. Kubrick llevó a los límites más altos del riesgo su dominio del efectismo, hizo de la atmósfera una nueva versión narrativa, otra posibilidad del juego, otra apertura legal de la creación; una odisea personal en ese atmósfera una nueva versión narrativa, otra posibilidad del juego, otra apertura legal de la creación; una odisea personal en ese vals cinematográfico que fluye evocándolo todo y dinamitándolo todo entre los días iniciales y el futuro.</t>
-  </si>
-  <si>
-    <t>y los hechos? Por supuesto, la distancia podría no existir, ser el espejismo de una mirada sesgada. Este es el tipo de hipótesis que nunca se debe descartar. Pero hay otras explicaciones posibles. En estos casos, una de las mejores maneras de salir de la perplejidad es fijar la atención en los incentivos: cuáles actos y personas premia el Gobierno y cuáles castiga. Allí no solamente se observa realmente dónde están sus apuestas, sino también el tipo de comportamientos que promueve y que podríamos esperar observar en el futuro. Hagamos un pequeño ejercicio de recapitulación para refrescar la memoria. Cuando surgió el escándalo de los falsos positivos redivivos y un general por razones buenas, regulares o malas salió a excusarse frente a la comunidad por el asesinato cruel de un desmovilizado de las Farc, lo primero que sucedió es que ese oficial fue regañado públicamente y después enviado a las</t>
-  </si>
-  <si>
-    <t>pueden existir miles de casos de personas que siendo inocentes han podido ser condenadas a pasar unos buenos años en la cárcel o que se les sigue investigando por acusaciones malintencionadas. Es por esto tan importante una reforma a la justicia que corrija las fallas en el sistema penal acusatorio, obligando a las personas que con sus testimonios participen en los juicios a que aporten pruebas de lo que dicen, bien sea a favor o en contra del acusado, porque con la simple declaración no es suficiente. Es claro que aquí hace falta una valoración uniforme de los testimonios como medio de prueba, mayor capacidad de investigación para corroborar lo dicho por los testigos o para desvirtuar sus afirmaciones, definir estándares de prueba para determinar con exactitud cuando un hecho está probado y un sistema simple y eficaz para incentivar a colaborar con la verdad y la justicia, sancionando a</t>
-  </si>
-  <si>
-    <t>he visto envuelta. Es sorprendente la cercanía de mis experiencias con las experiencias de las mujeres del reportaje y con los relatos de otras mujeres y amigas a través del tiempo. Me pareció por eso que además de ser un valiente esfuerzo de denuncia, el reportaje sirve también como un testimonio formativo para que otras mujeres vean la sutilidad con la que escala el acoso. Normalmente, el acosador nunca tiene cara de acosador y su comportamiento es a veces tan sutil que es casi imposible detectarlo en un inicio. Y, cuando se detecta, es tan ambiguo, que no se puede denunciar de inmediato. Como lo narra una de las denunciantes, de un divertido e inocente baile, el acosador logra en un par de jugadas meterse con ella en un taxi y, tras un beso fallido, tocarle insistentemente la vagina. ¿Cómo lo logra exactamente? Cuando somos adolescentes es común recibir mensajes</t>
-  </si>
-  <si>
-    <t>no es pontificar al respecto y cada caso es tan diferente como complejo de analizar. Sin embargo, sí existen patrones de conducta que nos permiten poner en duda la débil y maleable formación en valores que promueve nuestro sistema educativo; sí hay una serie de normas que no sabemos ni queremos respetar porque no somos conscientes de su importancia para vivir en comunidad. En el caso de los accidentes viales, un solo ejemplo es suficiente: se trata de la confusión que prevalece en nuestra mente en relación con las normas de tránsito. Hoy en día, son muy pocos los que pueden responder al unísono quién lleva la prioridad en un cruce donde no hay una señal de PARE; apenas unos cuantos entienden lo clave que es respetar los límites de velocidad lógicamente cuando éstos han sido colocados con criterio; sólo unos tantos han aprendido que sacar el pase significa aprender</t>
-  </si>
-  <si>
-    <t>en un futuro verano o fenómeno del Niño si no lo manejamos de forma integral? Esta lógica tiene que aplicar en la planeación y desarrollo de cualquier proyecto. Es evidente que necesitamos ser mucho más rigurosos, y construir una visión integral de las cuencas hidrográficas a intervenir. Los diseños económicos tienen que ir mas allá de las ganancias y beneficios a corto plazo y considerar aspectos como los costos por mantenimiento hasta la viabilidad de múltiples proyectos con un clima cambiante. En este momento, solo para la cuenca del río Magdalena, hay alrededor de cien posibles proyectos para nuevas represas. ¿Serán viables tantos proyectos con los extremos climáticos, y teniendo en cuenta los posibles impactos que representan para los sitios de reproducción de decenas de peces migratorios como lo ha advertido TNC? Sin duda, la hidroelectricidad es una oportunidad para el país y una fortaleza que no podemos abandonar como</t>
-  </si>
-  <si>
-    <t>Es media noche y tengo dos ríos atravesando el corazón. Ambos hablan de este país nuestro, bautizado por las balas, armado y desarmado en el afán intermitente de acabar y reconstruir los pedazos de vida que nos han quedado, expectantes, entre el suelo y el cielo. Son dos ríos que deberían ser suficientes para hacernos entender lo funesto que resultaría devolvernos a la guerra, y lo absurdo que ha sido herir los pactos de paz, como si no tuviéramos suficientes cicatrices en la historia, en la verdad y en los abrazos. Dos ríos: Río Muerto, escrito por Ricardo Silva Romero; y el río Atrato, en el que Leyner Palacios y el documental Bojayá, nos llevan a navegar por el más intenso dolor, por la resiliencia, el valor y la ternura. Hoy leí por segunda vez el libro, y vi por segunda vez el documental. Y podría seguir leyendo a Ricardo</t>
-  </si>
-  <si>
-    <t>compuestos por agua un 70,8 y 148940.000 km por tierra un 29,2 . Constituye motivo de honor para el suscrito el que la Tierra sea el tercer planeta en distancia respecto del Sol, del que se encuentra a 149597.872 kilómetros. Estamos en el podio, pues. Y hasta el momento, que se sepa, y desde hace 4.800 millones de años, somos el único lugar habitable entre millones de galaxias en los multiuniversos. Hay cuentas, sin embargo, que no me cuadran en tanta prodigalidad cósmica que me beneficia: yo, como una pieza suelta entre 7.000 millones de habitantes, debería tener, como mínimo asegurado, 85.000 m de tierra, con derecho a aguas saladas y dulces. Siendo realista, dejemos eso en 25.650 m de tierra firme, por aquello de que el planeta es 71 líquido y 29 sólido. Pero no, ni siquiera eso tengo. Y eso que mi derecho hipotético a esos m, yo</t>
-  </si>
-  <si>
-    <t>La voz de los ríos o las montañas, cuando llega a los tribunales a defender sus derechos, pasa inevitablemente por la interpretación que de ellos hagamos los humanos. El reconocimiento de agencia para los ríos, un experimento normativo que promueve un énfasis más biocéntrico en el ejercicio de las responsabilidades humanas respecto al resto del mundo, nos encontramos con un problema fundamental: los ríos dicen cosas, pero hay que saber escucharlos. La forma para llevar el mensaje de los ríos, o por defecto, de las montañas, las plantas o los animales nadie habla de los microorganismos en esos términos, es convertirnos un poco en ellos, asumir su defensa desde la perspectiva, inevitable, de humanizarlos también. En esa mutua conversión sensible y ética se basa la posibilidad de establecer una conversación que no termine siendo religiosa, una en la cual cualquiera que escuche voces en su mente asegure que tiene la</t>
-  </si>
-  <si>
-    <t>cajas de concreto que sirven para orientar el paso del agua. Un tema crítico del proyecto. Según el memorando no tienen medidas ni especificaciones de resistencia. Si esto es cierto, es increíble. Observaciones sobre los planos: carecen de información, carecen de especificaciones, no se articulan con el proceso constructivo, no están respaldados con memorias. Si esto es cierto: es imposible licitar y obtener costos reales de la obra para la adjudicación imparcial. Componente urbanismo, espacio público y accesibilidad. Los comentarios se centran en falta de especificaciones, errores o insuficiencias en el dibujo, problemas en las pendientes y los accesos a garajes de predios, no coincidencia con las cajas de inspección de servicios públicos: todo referido a técnicas de construcción y no a la filosofía del proyecto. Pero, como en todos los puntos anteriores, muestra el informe del subsecretario de Infraestructura cómo hay improvisación y falta de información para proceder a</t>
-  </si>
-  <si>
-    <t>el momento justo. En efecto, un espresso debe disfrutarse al instante porque gran parte del placer está en la espuma. Si se la deja reposar, se deshace más rápido de lo que canta un gallo, transformándose en dispersas manchas adheridas a la pared del pocillo. Nada más ácido y salino que un espresso reposado. En cambio, un espresso bien hecho se muestra cremoso, corpulento y aromático. Y pese a su menudo tamaño, es energizante, con un menor porcentaje de cafeína que los filtrados. Esto ocurre porque su contacto con el agua no supera los 20 segundos, mientras que los anteriores alcanzan la infusión ideal a los cuatro minutos. El espresso debe beberse negro, lo mismo que el ristretto un espresso más fuerte y más corto, y el lungo, un ejemplar menos encantador, que requiere adicionarle agua caliente para reducir su vigor. Otra desviación del lungo es el americano, más diluido</t>
-  </si>
-  <si>
-    <t>Nada peor que un juicio llevado a cabo sin buen juicio; sin que sea posible ver el fondo del caso, como quien mira desde arriba un depósito de agua limpia. Nada mejor que hacer las cosas de manera tal que ninguna de las partes tenga motivo para salir a reclamar que no se tuvieron en cuenta pruebas que pretendía aportar para evaluar mejor los hechos objeto del litigio. Audiatur et altera pars, decían los romanos. En palabras de hoy: que se escuche por igual a la otra parte. La justicia no es solamente asunto de estrategias y tácticas ante los tribunales, ni de consideraciones o artificios técnicos por parte de éstos para justificar sus decisiones. En el trámite de cada proceso se han de advertir con total claridad los argumentos de las partes, que deben contar con la garantía de que sus pruebas y consideraciones sean conocidas, explicadas y justificadas,</t>
-  </si>
-  <si>
-    <t>a conocer mis íntimas convicciones a través de esta columna, he sostenido sistemáticamente que la política, no solo en Colombia o América Latina sino también en los países más desarrollados, atraviesa grandes dificultades a raíz de la llegada al poder de una cantidad importante de líderes populistas y mentirosos, de derecha y de izquierda, con facilidad de convencer a las masas electorales con discursos cataclísmicos que pretenden vender la idea de que todo es un desastre, que todos los antecesores lo han hecho muy mal y que las soluciones, que por cierto las hay, solo las tienen ellos por ser poseedores de un poder mesiánico que no solo instrumenta la salvación sino que la personifica o individualiza. En ese contexto y con una población cada vez más exigente, pero al mismo tiempo más superficial y egoísta, movida y conmovida por redes sociales con mensajes manipulados y falsos, el elector de</t>
-  </si>
-  <si>
-    <t>En alguno de mis artículos califiqué como exagerada la tributación de Colombia. Pues bien, uno de mis lectores me solicitó con argumentos de fondo algunas explicaciones sobre el tema del título, porque consideraba él que la relación entre los recaudos por impuestos en Colombia y nuestro PIB, relación cercana hoy al 15, le resultaba demasiado baja comparada con las similares de la comunidad internacional. La referencia del párrafo a continuación que aparece entre comillas se puede consultar por Google digitando lo entrecomillado. No sobra advertir las grandes discrepancias en este tema entre las publicaciones en Google, debido a la falta de uniformidad sobre lo que se considera impuesto. En Revenue Statistics 2018. Tax revenue trends in the OECD se definen como impuesto todos los pagos obligatorios para todos los niveles del gobierno, sin esperar beneficios proporcionales derivados del pago sobre: Ingresos, utilidades y ganancias de capital, como impuestos sobre la</t>
-  </si>
-  <si>
-    <t>abismo del siempre, siempre, siempre. Y, por más que se estire hasta las dimensiones abracadabrantes del sinfín, no puede privarnos de la felicidad del eterno retorno de lo efímero, de lo que tiene su gloria en su pasar aparente. Es extraño que debamos pagar el privilegio de vivir con el espanto esencial del ser, que consiste en el sentimiento del deterioro inevitable de todo que lo condena a la caducidad. Ahora han regresado, es la moda de enero, los profetas y los que ponderan los porvenires. Unos, de malos augurios, plagan el futuro de ácidas sombras, cenizas amargas y recelos de cagalástimas; y los de signo positivo propalan noticias de alegrías venideras y anuncian realizaciones que estarían preparándose como pavos en los hornos de la esperanza. Cada año, los tarotistas sacan sus cartas de locos, reinas y ahorcados; los numerólogos sacuden sus ábacos, los astrólogos afilan sus compases, otros desempolvan</t>
-  </si>
-  <si>
-    <t>Un promedio de las cuatro últimas realizadas por Guarumo, Centro Nacional de Consultoría, Invamer y Yanhaas arroja como resultado: Duque 38,2 , Petro 28,6 , Fajardo 13 Vargas Lleras 7,6 .Todas coinciden en que Duque y Petro pasarían a segunda vuelta si las elecciones fueran en el momento de su realización. Fueron elaboradas para diferentes empresas, como Caracol Televisión, R.C.N, Semana, W radio y otros medios. La crítica de los candidatos Petro y Vargas Lleras puede entenderse como una respuesta natural en el fragor de la lucha electoral ante resultados, muy parecidos en todas, que consideran adversos. Pero sería inexplicable el cuestionamiento de su fundamento matemático; su capacidad de representatividad y explicación, por parte de dos ciudadanos que aspiran a convertirse en presidentes. La estadística y el cálculo de probabilidades son utilizados como herramienta de soporte por las diferentes ramas de las ciencias y no solo en el análisis político.</t>
-  </si>
-  <si>
-    <t>el fútbol moderno va mucho más allá del análisis que pueda hacer de los mismos el preparador físico. ¿Cómo hacer para que tanta información se pueda transmitir con facilidad al entrenador, el jugador, el directivo, el hincha o el periodista? En eso estamos. Consideremos el Caldas de Maturana en la Liga Águila 20172. La falta de resultados motivó su salida prematura. Pero más allá de analizar en detalle el juego del Caldas, evaluemos la tendencia en el movimiento del balón. La eterna crítica a Maturana fue el exceso de juego lateral de sus equipos. Siempre buscando posesión, ésta tendía a confundirse con falta de profundidad. La gráfica permite analizar el juego del Once Caldas y compararlo con el resto de los equipos del torneo colombiano. La cancha está dividida en 18 cuadrantes iguales. En cada cuadrante se analiza el tipo de pase que realizó un jugador. Se consideran cuatro opciones:</t>
-  </si>
-  <si>
-    <t>lo sumo hablando del gol de Yepes. La esencia del derecho a protestar está ligada a la existencia de grupos inconformes. Lo que el ministro concibe, yendo al fondo, es la idea de una sociedad unificada y homogénea. Esta noción tiene vieja raigambre. Para no ir lejos en la historia del siglo XX, basta la idea criolla de una sociedad sin fisuras. Allí encontramos a Núñez, Miguel Antonio Caro, Laureano y, claro está, José Obdulio, porque eso del Estado de opinión como mecanismo de gobernanza bebe en la misma fuente. Qué diablos con esas carajadas pluralistas. El pensamiento liberal cree, en cambio, en la sociedad multicultural, en el respeto a las ideas ajenas, en el diálogo incluyente. Abomina el fanatismo y la manipulación mediática que fomenta el populismo de derecha y de izquierda. Un pariente de esta noción es que el tal conflicto interno no existe. Se afirma que aquí</t>
-  </si>
-  <si>
-    <t>intenciones de aparecer atildado porque no lo es y no le cuadra. Urán no sólo se descacha, si se quiere decir, sino que igualmente suelta términos que escandalizan a los timoratos, aquellos especímenes sociales que detrás de su pretendida limpieza vocal esconden pecados que de verdad ofenden la sensibilidad de un país sumido en la pocilga moral que los mismos han creado desde el poder seguramente, Rigoberto hablará de mierdero. Otro encuentro que percibimos en esta simpática explosión verbal del escalador de Urrao tiene una trascendencia enorme, ya que toca a la juventud, en la que cada día se afianza más un modo desbraguetado de expresarse, sin que esta costumbre se traduzca necesariamente en conductas reprobables. Hoy, las chicas comparten con sus compañeros generacionales algunas voces democráticas que antes caracterizaban sólo a los muchachos, en una especie de ampliación del espectro de comunicación que rompe con la diferenciación entre unos</t>
-  </si>
-  <si>
-    <t>sin buscarlo, en la vocera de las atrocidades contra miles de mujeres atrapadas en cuerpos de hombre que la mal llamada sociedad normal masculina repudia, pero que las necesita y les teme. Y los gobiernos guardan silencio ante esos asesinatos anónimos. Camila sonríe en las entrevistas, pero también admite que está llena de rabia por tantas injusticias. Sabe muy bien que ahora la buscan y la aplauden, sabe que está linda, esplendorosa, y que esa gloria no durará para siempre. Está trabajando para tener cómo vivir plenamente y guardar para cuando caiga el telón. Posdata. Las malas, una novelatestimonio que estremece y revela ese universo misterioso lleno de ternura y horrores que se esconde tras los maquillajes y vestimentas provocadoras, donde deambulan mujeres frágiles y vulnerables, feroces e invencibles, unidas contra un mundo hostil que se resiste a reconocer sus derechos y su dignidad. contra un mundo hostil que se resiste a reconocer sus derechos y su dignidad.</t>
-  </si>
-  <si>
-    <t>estigmas por otras versiones del divertimento sin que los bebedores ocasionales fueran tildados de alcohólicos. Aunque lo quieran negar, y aduzcan razones comparativas entre los efectos de cada psicoactivo, la historia es exactamente la misma, y el pulso entre la obstinación y las evidencias tendrá el mismo final y el mismo destino: la legalización y la regulación pública de sus excesos. Mientas tanto, todos los muertos que caigan en la lucha esquizoide contra los suburbios adinerados serán muertos inútiles, cuerpos del absurdo acumulados por la custodia romántica de un paraíso moral sin drogas ilícitas, aunque brinden con las lícitas los resultados de una guerra sin fin. Los peces gordos entregados en los partes positivos de la Policía siempre serán reemplazados por los peones de un juego que tiene el combustible exclusivamente en su demanda. Los consumidores serán siempre los mismos aunque tengan que comprar su dosis en la sombra o</t>
-  </si>
-  <si>
-    <t>y desenmascara a los topos dentro de la comandancia del Circus. Hazlos tragar la soberbia y la hipocresía de sus actos. No dejes piedra sobre piedra del socialimperialismo soviético. Escúpelos, si es preciso. Ay, Smiley, no me dejes. Inspírame. Inspira a los escribidores del mundo entero, ansiosos de tu sabiduría. Enséñanos a escribir como escribía tu amo y señor, David John Moore Cornwell: claro, directo, categórico. Sin filigranas de heterosexuales en apuros ni trucos de tuiteras de medio pelo. No te vayas nunca. Ayúdanos a esquivar los adjetivos y adverbios innecesarios. Guíanos en el combate contra el abominable que galicado. Tú no escribías, es cierto. Pero cuando leo las venturas y desventuras de tu vida en las sombras, siempre termino de rodillas ante la prodigiosa habilidad narrativa de tu padre, Cornwell de Cornualles. George de los Georges, no te vayas nunca, por favor. Ánclate a los anaqueles de mi ya</t>
-  </si>
-  <si>
-    <t>Salvo por una o dos ocasiones de extraña abstracción, Hardy nunca explica sus ironías; si la literatura es un juego para el escritor, bien puede serlo también para el lector. Así ocurre más adelante con Angel Clare, un joven cuyo destino era el sacerdocio. Al rehusar el oficio paternal, Clare, que hasta entonces se educaba en los libros, opta por internarse como aprendiz en una granja en donde se topa con Tess. Es un joven con ansias de intelectual que ahora se ocupa de ordeñar vacas. Años atrás se habían encontrado en un baile, aunque sólo Tess parece recordarlo. En el momento en que ambos coinciden en la granja, sin embargo, las condiciones son casi opuestas: años atrás, Tess era una joven que desconocía casi todo del mundo y ahora, tras una serie de percances y desgracias, ha tensado su carácter. Clare es el destinatario adecuado de su madurez. Comienzan</t>
-  </si>
-  <si>
-    <t>en este coma diabético? Los senadores más inteligentes del Congreso, mejores oradores y odiadores de Néstor Humberto Martínez, organizaron un debate de 9 horas para llevar a la gente a concluir que la autoridad es la mala, y que si no hubiera ocurrido jamás este supuesto entrampamiento, óiganme ustedes, no habría disidencias de las Farc. Las disidencias existen porque existe el narcotráfico. No porque Néstor Humberto Martínez, supuesto enemigo de la paz, se las inventó para desacreditar el proceso. Allá están y, por ahora, allá se quedan. Entre tanto... Resumen de Petro: todo esto no fueron sino unas conversaciones de la DEA con la DEA. Y el pobre cieguito, ahí...</t>
-  </si>
-  <si>
-    <t>Pasan los años y uno comienza a perder la capacidad de riesgo. Poco a poco se toma la mente el miedo a perderlo todo: dinero, prestigio, trabajo, lo que sea. Al comienzo, la vida era un juego; después, las cosas que nos gustaban más se convirtieron en sueños y al quererlos hacer realidad llegaron las responsabilidades. Después llega la hora de trabajar, las deudas, sacar a los hijos adelante. En fin, la vida pasa y la presión aumenta. Ya no es tan divertido. Como hincha del fútbol es lo mismo. Primero era jugar a ser el ídolo del equipo amado en el parque del barrio. En la adolescencia comienzan a doler los clásicos que se pierden por cuenta de las burlas de los crueles seguidores del rival. Yo preferí hacerme el enfermo para no ir al colegio el lunes aquel después del 7 a 3 de Santa Fe a Millos</t>
-  </si>
-  <si>
-    <t>¿pero quién se atreve a decirlo? ¿O será simplemente porque la mayoría de los analistas y columnistas nos dedicamos a manipular palabras yo números, y entonces podemos mantener en este período el grueso de nuestra rutina de trabajo y por consiguiente al menos parte de la estructura de nuestra vida cotidiana? Pero el trabajo manual y también mucho del trabajo de conectar a las personas basta con pensar en los llamados call centers es imposible, o muy difícil, de llevar a cabo a distancia. La cohabitación forzada aun en las condiciones ideales con amor y sopa puede ser difícil para muchos. Con hambre, con miedo, puede resultar dura, incluso insoportable. Después vendrán las buenas almas lamentando la intolerancia de personas asustadas y perdidas cogiéndose a tortazos entre sí Claro, que esto se convierta en un drama de proporciones depende de la duración de la crisis. Pero esta puede ser mucho</t>
-  </si>
-  <si>
-    <t>tanto, están los dueños de los recursos y sus títeres en los Estados nacionales, raspando la olla de lo que queda en la biósfera terrestre muchos ya tienen sus búnkeres de preppers o preparacionistas. Y está también la masa amorfa de los hipnotizados, apegados a sus comodidades inmediatas, sin mayor idea de lo que sucede más allá de sus narices, liderados por personajes como Trump. El mejor de los escenarios posibles sería, desde luego, un cambio gradual hacia la conciencia del entorno y el papel de la especie humana en el planeta muy bien guiados por los paneles de expertos, las inversiones en educación, las reformas agrarias con énfasis en la diversificación de los cultivos, la protección a ultranza del agua, la reconexión espiritual con esta tierra y las economías solidarias, entre otras. Pero el drama es el tiempo, que se agota. 875790 20190813T00:00:5405:00 column 20190813T00:15:0105:00 jrincon1275 none 15:03:22:19:33 14 solidarias, entre otras. Pero el drama es el tiempo, que se agota. 875790 20190813T00:00:5405:00 column 20190813T00:15:0105:00 jrincon1275 none 15:03:22:19:33 14 3688 3702</t>
-  </si>
-  <si>
-    <t>ecológico, equivalente a un cataclismo que hubiera bloqueado el Cauca, algo que seguramente habrá sucedido en el pasado innumerables veces pero nunca con la presencia de gente, que se asentó en sus riberas hace apenas 12.000 o 15.000 años, aprovechando la riqueza de sus planicies de inundación, sus recursos biológicos, el agua y el calor. Al final, en la escala más distante, se ubica el manejo de un ecosistema que entra en una etapa de restablecimiento de su complejidad mediante un proceso sucesional que no conocemos: no hay referentes acerca de la manera ni tiempos en los que un río de tal envergadura retoma su funcionalidad biológica, aunque sí tenemos algo de información del efecto de otras grandes represas en condiciones similares Betania, por ejemplo. La palabra clave para evaluar la capacidad de recuperación del río y las posibilidades de utilizar el conocimiento de las comunidades locales o de la</t>
-  </si>
-  <si>
-    <t>nota de alerta. Las crisis humanitarias se resuelven con humanitarismo, no con balazos. En el pasado miles de colombianos fueron a buscarse la comida en Venezuela porque en el país escaseaba. Ahora son los venezolanos los que tienen problemas. Cuando llegaron los ricos de Venezuela comprando apartamentos y ofreciendo negocios, los mercachifles colombianos se frotaban las manos. Ahora que llegan los pobres ponen el grito en el cielo. ¡Hipócritas! Propaganda: les invito a leer mi libro Descansen Armas de Editorial Icono, lanzado en la penúltima FilBo, un ensayo anecdótico sobre la guerra. Quizá la lectura del libro les haga pensar un poco antes de alistarse para el combate.</t>
-  </si>
-  <si>
-    <t>La forma como algunas comunidades indígenas adelantan el llamado proceso de liberación de la madre tierra está convirtiendo al Norte del Cauca en un territorio hostil. Un grupo indígena está planteando un proceso de afirmación de sus derechos a costa de violar la ley; invadiendo la propiedad privada, bloqueando vías, generando pérdidas económicas, irrespetando a la fuerza pública Y más lamentable, ocasionando irrecuperables pérdidas humanas. Para este grupo indígena la liberación de la madre tierra se traduce en usurpar tierras privadas y hacer posesión de ellas para luego reclamarlas. Lo que no se ha dicho, es que la liberación de la madre tierra para la gran mayoría de los grupos indígenas, se entiende como: cambiar prácticas agrícolas por unas más sostenibles y amigables con la naturaleza, es sembrar comida y no cultivos ilícitos, es proteger los recursos naturales sin renunciar al desarrolloEso es liberación, es proteger la tierra para las</t>
-  </si>
-  <si>
-    <t>su subsistencia depende de los recursos del turismo, actividad que se tomará su tiempo en llegar y recobrar los flujos de años anteriores. San Andrés, Providencia y Santa Catalina, y los demás cayos e islas que conforman el archipiélago, han perdido más de 11.000 millones de pesos durante esta emergencia sanitaria, tienen la ocupación hotelera en ceros y sufren parálisis en la circulación de dinero por falta de servicios y alternativas laborales. Los créditos anunciados por el Gobierno han cobijado a menos del 1 de los empresarios, porque los banqueros como sucede en todo el país se abstienen de otorgarlos, por considerar que el turismo el nuevo petróleo colombiano, según el presidente Duque es un sector de alto riesgo. No son fáciles, pues, los tiempos que se viven en San Andrés, donde no hay huéspedes para los hoteles ni comensales para los restaurantes ni compradores para los locales comerciales. Los</t>
-  </si>
-  <si>
-    <t>ríos agravando así el problema ambiental. O mire a las comunidades de Bolívar que se han visto desplazadas de sus tierras para sembrar palma, un monocultivo responsable de gran cantidad de gases de efecto invernadero y cuyo aceite está presente en gran número de productos ultraprocesados. En esta pesadilla, el reporte recomienda crear políticas e incentivos que promuevan un sistema alimentario donde la producción, el consumo y todos los pasos de la cadena sean más responsables; redireccionar los subsidios de la agricultura extensiva a otras formas más sostenibles; poner etiquetados más claros a los productos ultraprocesados, además de acciones individuales para reducir nuestro consumo de carne y nuestra huella ambiental. Pero crear políticas no es cosa fácil. El informe señala que el sistema alimentario actual está en manos de unas pocas industrias que, con frecuencia, logran hacerse al poder económico y político impidiendo dichos cambios. En Colombia tenemos sobrados ejemplos pocas industrias que, con frecuencia, logran hacerse al poder económico y político impidiendo dichos cambios. En Colombia tenemos sobrados ejemplos de cómo las tácticas de ciertas industrias han terminado por limitar intentos de regulación en favor de la salud o el ambiente. Necesitamos medidas para impedir que estas industrias determinen la política pública y el futuro alimentario del planeta. Lo que está en juego es demasiado importante como para ser decidido solo por el bolsillo de unos pocos.</t>
-  </si>
-  <si>
-    <t>generan su propia energía, mediante paneles solares, con excedentes que son almacenados en baterías gigantescas, que tienen la capacidad de venderlos a las empresas distribuidoras de energía. La información que producen los sensores de cada una de las bicicletas inteligentes o de las casas y edificios que generan energía solar, transmiten las coordenadas de los ciclistas, el consumo de los electrodomésticos y otra infinidad de teras de datos a servidores de la nube de la información, conectando a la gente con bicicletas, calles y casas, en una inmensa comunidad del internet de las cosas, inimaginable hasta hace pocos años. Con la ayuda de la llamada inteligencia artificial, se analiza esa información grande big data para encontrar tendencias, correlaciones, para balancear la oferta y la demanda, maximizar usos y para alertar sobre problemas potenciales. Esta es una verdadera revolución tecnológica y de la información que ya está sucediendo a ritmos vertiginosos</t>
+    <t>Entiendo que para algunos lectores este artículo puede no ser de su interés, lo que es parte de la indiferencia de las personas que se vive cuando se tiene un cuerpo que no está al ciento por ciento. Para quienes no saben, Cirec quiere decir Centro Integral de Rehabilitación de Colombia. Hace diez años sufrí un accidente cardiovascular, el cual vino de un momento a otro y cambió para siempre mi manera de ver y enfrentar la vida. Mi trabajo cambió, me separé, la movilidad se vio afectada, el día a día naturalmente cambió. Pertenecí a la junta directiva de Cirec, fundación sin ánimo de lucro, siendo mi idea involucrarme más allá de ver resultados. Tuve la fortuna de ir con Cirec a Anapoima el último día de una capacitación y entrega de sillas de ruedas. Este evento cambió mi manera de ver la vida, pues en ese lugar había</t>
+  </si>
+  <si>
+    <t>de fetos y embriones, a los que les atribuyen hasta ambiciones profesionales, como ocurrió con el feto ingeniero, se desarmaron a punta de humor, a punta de memes, y hoy suenan anacrónicos y ridículos. Incluso si la ley se vota en contra, el cambio social que produjo la ola verde feminista es irreversible; la liberalización del aborto en Argentina y ojalá en toda la región es cuestión de tiempo. Afortunadamente, esa ola verde feminista se está expandiendo por toda América Latina y el Caribe una de las regiones más restrictivas del mundo en materia de derechos sexuales y reproductivos y la lucha por la despenalización del aborto está sumando a las latinoamericanas más jóvenes, quienes hoy están incursionando en la creación de sus propios movimientos feministas locales. El acceso a un aborto seguro nunca ha sido ni será un problema de moral, es un problema de salud pública y de un aborto seguro nunca ha sido ni será un problema de moral, es un problema de salud pública y de clase, y esto es cada vez más evidente para más mujeres, niñas y adolescentes que hoy no tienen miedo de decir en voz alta, en las calles, en sus redes: ¡el embarazo será deseado o no será!</t>
+  </si>
+  <si>
+    <t>proceso, las repeticiones del mismo argumento y el énfasis en su defensa generan corrimiento hacia una posición más extrema. Las dudas de Sunstein incluyen a los grandes cuerpos legislativos. Realmente sería interesante que algún buen politólogo hiciera un trabajo de investigación sobre cuántas posiciones cambian en el Congreso de la República como resultado de los argumentos durante la deliberación. Mi predicción sería que muy pocos, si es que alguno. Cambian posiciones por ofertas, por alianzas, hasta por mermelada. ¿Pero hay casos reales en que una bancada haya convencido a otra con argumentos? Tal vez se podría ahorrar tiempo y esfuerzo. El asunto, por supuesto, es cómo no ser esclavo de esa ley y sacar ventaja del poder según dicen los filósofos que tienen la discusión y el debate. Sunstein propone la fragmentación de la discusión en muchos grupos heterogéneamente conformados. A mí me parece más importante la etapa previa a la fragmentación de la discusión en muchos grupos heterogéneamente conformados. A mí me parece más importante la etapa previa a la adopción de las posiciones iniciales. Los maestros deben exponer posiciones diversas y estimular decisiones individuales y autónomas en sus educandos. Eso podría sacarnos del callejón sin salida; de otra forma, seguiremos escogiendo solo aquellos hechos que confirman nuestras opiniones previas, y la gritería será ensordecedora.</t>
+  </si>
+  <si>
+    <t>acceso para observar, hacer entrevistas, revisar, elaborar prototipos y pruebas in situ. Definitivamente una imagen vale más que mil palabras. La primera fotografía es del plácido entorno, con vista panorámica sobre Bogotá, donde se conciben ideas geniales para arreglar problemas nacionales. Al bajar al mundo real se ve un camión con los bultos de expedientes que llegan desde todo el país y que nadie volverá a mirar. Dentro de la sede de la CC se aprecia el gigantesco espacio en donde estudiantes de derecho en pasantía, necesariamente de Bogotá y probablemente de Uniandes y otras facultades de élite, hacen una selección de las tutelas que serán revisadas por la CC. Ahí se alcanza a sospechar cómo llegan las modas intelectuales del exterior a la jurisprudencia y por qué muchos debates se centran en las preocupaciones intensas de unas cuantas mentes brillantes, que convencen a los medios y a la opinión</t>
+  </si>
+  <si>
+    <t>humano en el pasado, lo que los franceses llaman problemática. Este cuestionario nace de sus propias experiencias: la época en que ha vivido, los lugares que ha recorrido, las personas que lo han marcado, las artes que lo han conmovido y los libros que ha leído, no solo de historia, sino también de filosofía, literatura, ciencias sociales en general, divulgación científica, etc. Tan pronto tiene listo un cuestionario inicial, el historiador hace el balance de lo que se ha escrito sobre el asunto que quiere abordar para diagnosticar qué se sabe al respecto y qué no, y así poder afinar sus preguntas. A continuación, busca respuestas en documentos, no solo escritos, de la época y el lugar que le interesan. Este paso puede calificarse de cronófago: son cientos o tal vez miles de horas las que debe pasar en bibliotecas y archivos, así como en museos o en lugares y</t>
+  </si>
+  <si>
+    <t>manera que, si la fiabilidad de las pruebas es cuestionable, es decir, carece de peso, las razones que se expongan serán tan débiles como las bases de un edificio construido sobre un terreno de arenas movedizas. En este sentido, la crítica camina siempre sobre los hechos, y en argumentación los cuestionamientos no radican en los hechos mismos, sino en la mirada o interpretaciones que se tienen de estos. Cuando lo anterior no se cumple, entonces es como si se caminara por el borde de una cornisa, exponiéndose, de esta manera, a una posible caída. En el periodismo, la verificación de las fuentes es el equivalente a la fiabilidad de las premisas en los procedimientos argumentativos. Esta verificación permite al periodista y al medio para el cual trabaja la confiabilidad que se traducirá en credibilidad, y la credibilidad es la razón de ser del periodismo. La imagen de Juan Gossaín llorando</t>
+  </si>
+  <si>
+    <t>que el ICFES implementó hace unos años buscaba precisamente dar este tipo de retroalimentación formativa y gratuita a los estudiantes del país. Es una lástima que el ICFES la haya retirado. La reflexión sobre la evaluación se debe enfocar en su principal objetivo: identificar el nivel de aprendizaje de cada estudiante. Con esto en mente, existen muchas herramientas que podemos usar, que nos dan una idea de dónde están nuestros estudiantes para apoyarlos de la mejor manera. Es evidente que durante este periodo va a haber pérdidas en el aprendizaje. Para todos es fundamental poder hacer un diagnóstico real de en qué está cada estudiante y sus respectivos grupos. Después, debemos hacer un análisis como sistema educativo de cuáles son las mejores formas de apoyar a los estudiantes en su nivelación a medida que vayamos recuperando los espacios presenciales de aprendizaje. nivelación a medida que vayamos recuperando los espacios presenciales de aprendizaje.</t>
+  </si>
+  <si>
+    <t>cine, entre otras formas del arte, han sido legitimadores sociales de este tipo de relaciones que durante tanto tiempo se habían asumido como naturales, sin considerar el factor de verticalidad, de poder, que media en ellas. Las investigaciones periodísticas sobre acosadores como Bill OReilly quien además recibió el respaldo inicial de Donald Trump o Harvey Weinstein y el movimiento MeToo han sido campanazos sobre la naturalización de un delito en el entorno laboral entre adultos. La multiplicación de casos judiciales obliga a una reflexión que no juicio instantáneo, sin investigación previa sobre los protocolos para denunciar. Los entornos educativos en Colombia requieren una mirada desde perspectivas como las que proponen MeToo y NoEsHoraDeCallar. Los manuales de convivencia suelen contener algunas normas sobre la relación estudianteprofesor. Los niveles de aceptación o rechazo van desde la prohibición absoluta de relaciones sentimentales hasta su autorización cuando ambos ya no comparten aula. Otros ignoran</t>
+  </si>
+  <si>
+    <t>de formación de los maestros, en tanto los resultados evidenciados en las pruebas Saber Pro de 2019, por estudiantes de carreras pertenecientes a ciencias de la educación sacaron un puntaje global por debajo del promedio nacional. Sin embargo, afirmaciones como estas, lejos de ayudar a superar las dificultades del sistema educativo y a subsanar las brechas existentes de un escenario a otro, globalizan los contextos e impiden abordar el tema desde sus múltiples aristas, pues la generalización, impide analizar y atender las necesidades propias de los procesos educativos y programas de formación de maestros en las regiones, y puede sesgar la toma de medidas gubernamentales y de políticas de calidad sobre los programas de formación de maestros, que lejos de contribuir a derribar las dificultades, las agudice; como ya ocurrió en 2016 con la expedición del decreto 2041 que obligaba a los programas de licenciatura a estar acreditados so pena</t>
+  </si>
+  <si>
+    <t>los contenidos analíticos de sus espacios académicos. No se trata de establecer simples comparaciones, se trata de identificar elementos que permitan el mejoramiento de los procesos de aprendizaje, en función de las competencias genéricas que se evalúan allí, pero también de las competencias específicas, directamente relacionadas con el quehacer de los futuros maestros del país. Un análisis que proponemos a la Universidad Javeriana y a quienes se enfocan en estos resultados de las pruebas Saber es la mirada profunda a los contextos, los procesos, los niveles de formación de quienes se agrupan en el área de las ciencias de la educación. Que se analicen los resultados de acuerdo a estas necesarias distinciones. Un comparativo muy interesante lo ha planteado incluso el mismo Icfes, realizando un ejercicio de estimación de valor agregado de las instituciones de educación superior universitaria, analizando los resultados de las pruebas Saber 11 y los resultados de</t>
+  </si>
+  <si>
+    <t>atender las demandas impuestas por los modelos de medición. En esa medida, la evaluación es utilizada como una herramienta cuantitativa para censar y categorizar los conocimientos y habilidades desarrolladas, durante los procesos de formación en cada nivel, alejándose de su característica y posibilidad formativa. Es ese el escenario en el que incursionan las pruebas Saber 11 y Saber Pro como instrumentos de medición y categorización de la educación colombiana. Recientemente el Laboratorio de Economía de la Educación de la Universidad Javeriana LEE publicó un informe, a su vez divulgado por El Tiempo, sobre los resultados de las pruebas de Estado de estudiantes de educación superior del área de ciencias de la educación. En dicho informe sugieren que uno de los principales problemas del sistema educativo estaría relacionado con el proceso de formación de los maestros, en tanto los resultados evidenciados en las pruebas Saber Pro de 2019, por estudiantes de</t>
+  </si>
+  <si>
+    <t>Ni justicia, ni responsabilidad, ni hechos comprobados. Las revelaciones y las grabaciones solo buscan crear, reforzar, alinear opiniones, puntos de vista simplistas y crean otra polarización entre los que creen a María Andrea víctima o culpable. Ahí están los audios y las historias, disponibles para que el que quiera refuerce su punto de vista si era una niña buena o si tenía doble vida. Todo disponible en los grandes colectores de opinión instintiva, de brutalidad y resentimiento que llegan a ser las redes sociales, para que la gente afirme lo que quiera sin análisis, sin responsabilidad, sin contexto. En ese panorama de opciones binarias se van quedando en la oscuridad, los temas importantes. El comandante de la Policía de Bogotá Hoover Penilla debería explicar, por ejemplo, por qué no hay acciones contundentes contra los falsos clubes y otros espacios destinados a la droga y los excesos, que pululan en diferentes</t>
+  </si>
+  <si>
+    <t>suministro. Sin embargo, la crisis que legó la ruptura del mentado tubo debilitó a comunidades ya de por sí muy vulnerables. Comunidades que sabían además que esto iba a pasar tarde o temprano debido al mal servicio que, sin ninguna consecuencia económica o sanción social, presta Hidropacífico. Esto pues, aunque desde los días del paro sabemos de la mediocridad con que esta empresa presta el servicio de agua a esta población, nadie increpa a sus dos o tres accionistas. Estos saldrán invictos de esta crisis, que tal vez tendrá secuelas sobre el número de contagiados en la ciudad. Quizá lo peor es que nadie en el Gobierno central parece entender la importancia de volver a una empresa pública. Esto, porque tecnócratas en Bogotá afirman que las dos décadas sin suficiente agua obedecen únicamente a mala suerte con el operador privado y que con uno nuevo amanecerán las soluciones. Pero las agua obedecen únicamente a mala suerte con el operador privado y que con uno nuevo amanecerán las soluciones. Pero las organizaciones fuertes que dejó el paro saben que esto no es cierto. Saben que nadie en el sector privado encontrará rentable prestar un buen servicio para todos. Saben también que, con la asesoría adecuada, ellos mismos pueden reconstruir sus acueductos, repensar su empresa pública y cuidar sus ríos.</t>
+  </si>
+  <si>
+    <t>área semiurbana invadida en algunas partes por viviendas, clubes y universidades. Luego está el tramo que va desde Puente la Virgen Cota hasta Alicachín Muña, una ronda desde hace muchos años invadida, donde se han rellenado los reguladores naturales y sobre ellos se ha construido. En este tramo la CAR adelantó, con recursos del Banco Mundial y contrapartida de los bogotanos, proveniente del impuesto predial, el proyecto Plan de adecuación hidráulica y recuperación ambiental del río Bogotá, para evitar que se repitan las inundaciones y el desastre social del 2011. Su diseño se basó en detallados estudios técnicos y desde la construcción de esos enormes jarillones el canal de drenaje está cumpliendo su cometido: proteger de inundaciones a la población ribereña que hace años invadió la ronda del río. Si viviéramos en Dinamarca y no en Cundinamarca, se hubiese evitado que tanta gente construyera su vivienda en la ronda del</t>
+  </si>
+  <si>
+    <t>de servicio del corredor de agua de Suez. Además de significar un incremento importante en los ingresos por la prestación del servicio, la nueva obra ha sido muestra de eficiencia y de la capacidad que puede tener un Estado para emprender proyectos de infraestructura de grandes proporciones. Obras cuyo aprovechamiento conlleva beneficios de dimensión nacional e internacional. Inversiones de prestigio, capaces de convocar el entusiasmo colectivo y fortalecer el sentido de pertenencia, además de elevar el ánimo de diferentes sectores sociales que se pueden sentir identificados con un mismo propósito. Siempre sobre la base de una premisa que debería ser válida en todas partes, que no es otra que la del potencial ilimitado de acometer proyectos de grandes proporciones, y de verdadera utilidad común. Cuando existe un liderazgo idóneo, claro está. está.</t>
+  </si>
+  <si>
+    <t>el municipio distribuye sus aguas de manera desigual, haya lluvia o sequía con aguas potables en algunos barrios e intermitencias y problemas con aguas servidas en otros. Esto es quizá de esperarse en una de las siete ciudades más desiguales del país, en que conviven grandes desarrollos inmobiliarios y hoteleros con una de las mayores incidencias de pobreza extrema en Colombia la quinta más alta después de Quibdó, Riohacha, Popayán y Valledupar. Como la Empresa de Servicios Públicos se prepara para prestar el servicio, el alcalde Rafael Martínez hizo un viaje a Israel con el fin de conocer más detalles sobre el funcionamiento de las plantas desalinizadoras, una nueva alternativa para resolver el problema histórico de abastecimiento del preciado líquido. Martínez dijo que su recorrido por Israel inspiraría a la ciudad a resolver el problema del agua. Pero, como lo ha demostrado el cercano caso de San Andrés, en condiciones</t>
+  </si>
+  <si>
+    <t>En una investigación sobre agua en barrios de Tijuana, México, un grupo de académicos encontró que, pese a la reciente construcción de redes nuevas que llevaban agua potable de manera continua a sus casas, las familias continuaban cosechando y almacenando aguas de lluvia. Las tinajas permanecían en los patios a la espera de aguaceros, tal y como en los días previos a la inauguración de la nueva tubería. Las mujeres usaban el suministro de agua potable pocas veces y preferían el agua lluvia para hacer funcionar los baños, lavar y regar las matas. Seguían, además, comprando agua comercial en bolsa o embotellada para cocinar y tomar. En un contexto de total desconfianza en el Estado, las mujeres preferían no depender de los servicios públicos, sino seguir limpiando los barriles de almacenamiento de agua e hirviendo el agua que allí se recoge. A estas rutinas les llaman nuestro propio sistema de</t>
+  </si>
+  <si>
+    <t>unas condiciones para el desembolso del préstamo en cuotas, dependiendo del progreso del proyecto. Funcionarios insinuaron cierta mala fe por parte del Banco Mundial, que entregó millonarias sumas sin monitorear el proyecto. Todas estas anécdotas reposan en la caja de la historia nacional: debates sobre cómo llevar agua a los barrios en ausencia de fondos. Cómo conseguir préstamos y usarlos con cuidado. Cómo extender redes, forzando la solidaridad entre clases sociales. Reposa también el conocimiento, basado en la experiencia, de que los desembolsos sin condiciones fomentan la corrupción y el despilfarro. En los bonos del agua del ministro Carrasquilla, que tienen desastrosas consecuencias en la cotidianidad de tantos municipios, podemos ver distintos factores combinados. El uso de fondos para el agua en campañas políticas y el robo desaforado de políticos profesionales; la falta de capacidad institucional de los municipios, la mala fe de quienes diseñaron el préstamo sin condiciones para profesionales; la falta de capacidad institucional de los municipios, la mala fe de quienes diseñaron el préstamo sin condiciones para la finalización de las obras. Pero sobre todo, y a diferencia del legado de los veinte, los bonos del agua apuntan a la falta de imaginación a la hora de diseñar políticas públicas. A cierta pereza de los tecnócratas. A la desidia de lo público.</t>
+  </si>
+  <si>
+    <t>suministra eficientemente nada menos que agua abundante y potable, electricidad sin cortes, telefonía fija y móvil, televisión, internet, ni esta gran compañía propiedad del municipio la podía manejar el alcalde como si fuera su finca. Si el gran proyecto de Hidroituango, una megaobra de generación de energía limpia, hubiera salido bien, este matrimonio estaría ahora en perfecta armonía. Ya se estarían recogiendo los primeros dividendos de un esfuerzo multimillonario en lo técnico, lo financiero, lo humano. Lo que menos quería EPM, o los empresarios de Antioquia, o los alcaldes de turno, o los ciudadanos, era que Hidroituango presentara las enormes fallas que presentó. ¿Y a qué se debieron esas fallas? No fue por ahorrar cemento o hierro, y favorecer a algún cacao, como dicen los paranoicos. No fue porque calcularan mal la resistencia de la roca. No fue porque asignaran a dedo el constructor, el diseñador o el interventor. Fue</t>
+  </si>
+  <si>
+    <t>venta y distribución que facturaba para 44 mil consumidores, cuyo consumomes ascendía en promedio a 500 millones de pesos, sin incluir la utilizada para fabricar hielo y envasar agua que, según la investigación, era el objeto social de la fachada utilizada. Que se roben los presupuestos públicos apropiados para construir acueductos, escuelas, vías, desarrollar proyectos productivos en las zonas rurales, sembrar ñame, cacao, aguacate, malanga, es de uso corriente, oficial y legal en Colombia, y de manera muy particular por estos pagos del Caribe, al igual que lo es la conformación de carteles, fundaciones, asociaciones, para robarse la plata de la salud en gobernaciones y alcaldías, vía enfermedades mentales, hemofilia, epilepsia, síndrome de Down, entre otras dolamas objeto del fraude, pero que se constituyan empresas para robarse el agua, venderla y distribuirla legalmente en una ciudad como Santa Marta, sí que constituye una innovación de última generación de estos delincuentes</t>
+  </si>
+  <si>
+    <t>destino. Muchos lo consideran como el Río más hermoso del mundo, por sus aguas transparentes que dejan ver sus algas verdes, moradas, azules, rojas y amarillas; pero muy especialmente, porque en sus suelos se entrecruzan mil colores. Es un río tan pequeño que los lugareños llaman caño, pero que expertos viajeros como Andrés Hurtado, lo consideran el lugar más hermoso del planeta. También participé de otra excursión con estudiantes en Ciudad Perdida, un antiguo poblado Tairona, que estuvo escondido varios siglos y que fue descubierto accidentalmente por guaqueros en 1973. Para poder llegar a la cima después de tres días de caminata, debemos recorrer un largo camino en el que llueve 25 horas al día y atravesamos varias veces el mismo río. Aun así, la tranquilidad y magia que se respira, ameritan el esfuerzo. Las excursiones virtuales están siendo pensadas para cultivar esperanza y cohesionar los grupos. Un grupo de</t>
+  </si>
+  <si>
+    <t>formar los ríos enormes, y Colombia tiene la mitad de los páramos de este planeta, pero nosotros hemos tenido la audacia y la insensatez de poner el destino de la nación en manos de gentes que venden los páramos y destrozan los ríos. Solo por la salud de los ríos podemos saber cómo está funcionando esa fábrica de agua. Del mismo modo las palabras nos dicen cómo está la conciencia de una comunidad, los relatos nos muestran si sigue viva la memoria, las canciones revelan si todavía amamos y cuidamos el mundo. Cuántas historias, de La Jagua al Quimbo, de Pitalito a Neiva, de Natagaima a Purificación, de Girardot a Ambalema, de Honda a La Dorada: caminos, fundaciones, cultivos, desastres; historias de los panches bajo el azote de Añasco y Belalcázar; historias de los herboristas de Mutis y sus pintores de plantas; el paso de las canoas de Humboldt cargadas</t>
+  </si>
+  <si>
+    <t>Volvamos la vista al pasado reciente. Escojamos por ejemplo el año 2000. Algunos de los estudiantes que hoy marchan exigiendo más recursos para la educación superior no habían nacido, otros gateaban y los mayores daban sus primeros pasos. En ese entonces nuestro gobierno destinaba a la educación superior el 0.7 del PIB y atendía al 39 de los matriculados el resto estaba en instituciones privadas. Los datos más recientes muestran que el gasto escaló a más de 1 del PIB y ahora atiende al 52 de los matriculados: saltos significativos. ¿De qué se quejan? Mantengamos la vista en ese año inicial: los estudiantes matriculados en programas de educación superior públicos y privados no llegaban a 400.000; ahora bordean los dos millones. Al mirar este enorme incremento en la población matriculada, el esfuerzo estatal, que ponía en duda la justificación de las quejas, ya no luce tan significativo. Otras dos cifras</t>
+  </si>
+  <si>
+    <t>alebresten, señores, no se pretenden categorías monolíticas aquí, pero sí arrojar luz y foco sobre asuntos estructurales, arraigados, visibles, y sobre todo, relatar lo que muchas mujeres viven. Se habla del varón heterosexual socializado también, por supuesto, dentro de las turbiedades del catolicismo. Qué puede esperarse de un sistema de creencias que concibe a una madre virgen como gran modelo para emulación femenina. Las mujeres tienen que parecerse a ese molde ficticio. Así nace, en cierto modo, esa disociación. La tipificación. La mujer que se desea hace posible los deleites de la carne; más la esposa, la madre de los hijos, no debe participar en ese tipo de mundanidades, debe en cambio ser correcta, prístina. Querría enunciarlo con un adagio que circula y nos es conocido, ese deseo varonil de que una mujer sea una dama en la calle y una puta en la cama. Ese deseo que, según he</t>
+  </si>
+  <si>
+    <t>reconocimiento social, todos somos lagartos o debemos serlo. La sociedad ha crecido en tamaño, en heterogeneidad y en densidad. Los miembros de las viejas clases que eran la flor y nata de la sociedad ya no lo son si no lo pueden demostrar. Hoy se ha llenado de parvenus o advenedizos, es decir, aquellos de origen desconocido que han adquirido poder, riqueza y fama. Pero, como no se sabe de dónde vienen, tienen que demostrar su excelencia, que no necesariamente es la inteligencia o la sabiduría, sino la posesión material, la riqueza y la situación de poder. Y todos, sin excepción, porque los miembros de las viejas clases altas se mezclan con los de las nuevas, tienen que mostrar su condición. Todos tienen que ser lagartos. Y lo son a través de los carros de alta gama, los guardaespaldas, los viajes al exterior, las casas o apartamentos suntuosos, las fincas</t>
+  </si>
+  <si>
+    <t>también contrarresta lo que dicen Lafaurie y Cabal. Los responsables del despojo en porcentajes según sentencias judiciales son los siguientes: Paramilitares: 55 Combates: 24 Combates entre guerrillas y Estado o entre guerrillas y paramilitares. En ningún caso, de las más de 3.700 sentencias, se observan combates entre Estado y paramilitares, pareciera que no los combatían. Guerrillas: 13 Grupos Armados no definidos: 7 Estado: 1 Así las cosas, según sentencias judiciales los mayores despojadores, de lejos, fueron los grupos paramilitares y no las guerrillas. Además se destaca que el Estado combatía las guerrillas, lo cual es normal, pero no los paramilitares, lo cual es anormal, es un Estado de derecho. El tercer dato es que de las más de 6.000.000 de hectáreas despojadas apenas se ha restituido 237.679, ni siquiera el 10 por ciento. Falta aún mucho. Ahora bien, antes de entrar al análisis quiero citar lo que dicen el señor</t>
+  </si>
+  <si>
+    <t>Políticos y encuestadores se parecen en que ninguno admite haber perdido una elección o haber fallado en un pronóstico. Los ejemplos abundan en todas las jornadas electorales hasta en la última, pues todos los políticos, inclusive quienes perdieron estruendosamente, han salido a reclamar el triunfo, mientras ninguno de los encuestadores que inflamaron el ambiente con sus cifras erradas ha tenido el arrojo de poner la cara y pedir al menos excusas. Como todos los liberales, tenía esperanza en que el expresidente César Gaviria llevaría el partido a puerto seguro y exitoso. Su prestigio y carisma permitían acariciar esa ilusión, pero no; condujo una desastrosa campaña electoral en la que solo se le vio cuando le reclamó al Gobierno participación en la torta burocrática. Adicionalmente, propició una lista al Senado encabezada por un amigo suyo que sólo se representa a sí mismo y avaló listas para la Cámara con candidatos sombríos.</t>
+  </si>
+  <si>
+    <t>Más allá de las cifras macroeconómicas y las discusiones de coyuntura, hay varias preguntas sobre el rumbo de la economía en el largo plazo que comienzan a ser debatidas por los economistas. Entre ellas se pueden mencionar el futuro de la producción de petróleo y los ingresos externos bajo escenarios de incorporación o rechazo de nuevas tecnologías de extracción del crudo; la reducción de la demanda de combustibles fósiles ante la entrada de vehículos eléctricos y la salida de algunas plantas térmicas en las próximas décadas; el impacto sobre el mercado de trabajo de la inteligencia artificial y robótica; la trayectoria del déficit de la balanza de pagos, y el volumen y la composición de la canasta de las exportaciones no tradicionales en los años por venir. Con respecto a este último tema, el Banco de la República acaba de publicar un importante libro que recoge una serie de trabajos</t>
+  </si>
+  <si>
+    <t>las posibilidades de un futuro imaginado ha sido el más usado por economistas y opinadores en los paneles de radio y televisión durante los meses previos a una primera vuelta que parecía revelar claramente los dos rostros de la contienda final. Y sigue siendo el argumento principal a pocos días de la jornada electoral definitiva. Lo usan con la sacralidad que inspira la inquebrantable solidez de la economía tradicional, esa maraña de nubes que solo puede sustentarse en la especulación y en la predicción poética del comportamiento de las bolsas. Pero lo absurdo de esta paranoia unificada alrededor de un misterio político no ha sucedido solo por la banalidad de las discusiones, enfocadas todas al antecedente guerrillero del candidato sin preguntarse si el perfil de esa guerrilla fue nacionalista o anarquista o marxistaleninista o proChina o independentista o de nacionalismo negro o ultracatólico, dando por hecho que la palabra y</t>
+  </si>
+  <si>
+    <t>improbable, en toda asamblea de copropietarios hay un contador siempre listo a preguntar si los libros se llevan atendiendo la norma internacional aunque no es obligatorio para las copropiedades. Los asistentes se acomodan en las Rimax. ¿Y esos 220.000 de papelería y taxis, por qué?. Baldado de sospecha. La administradora responde que toca voltear por el problema del restaurante que pusieron al lado, ir a la curaduría para ver usos del suelo; las fotocopias corresponden a los informes de estados financieros que ustedes pidieron en papel. Y en esa capacidad de digresión al infinito que tenemos los colombianos, otra señora interrumpe para manifestar su gran molestia por el tamaño de la letra del informe, que le impide leer y comentar adecuadamente, marcando así otro punto que nos une como colombianos: el derecho al inciso. Un propietario abogado se mete por esa rendija para anotar los errores en la redacción de</t>
+  </si>
+  <si>
+    <t>su crecimiento, será necesario traducir el peso demográfico en poder electoral. Demográfica y culturalmente las estadísticas de los latinos son significativas: de 1990 a 2017 el crecimiento de los hispanos ha sido superior al de otras etnias o culturas. Los hispanos en 25 años han aumentado sus números en un 160 en EE. UU., creciendo un 6,36 anual de media, mientras que los blancos de origen noreuropeo solo crecen a un 1,2 anual. Algunas previsiones dicen que para 2050 la población hispana de Estados Unidos podría rebasar a la población de México, convirtiéndose en el país con el mayor número de hispanoparlantes del mundo. Pretender llegar a la Presidencia de EE. UU. sin contar con el voto hispano, más que una quimera, es una verdadera estupidez. Tanto Trump como Biden lo saben. Sanders también. . Según informes de prensa, YouTube piensa remover todo tipo de videos y canales que promuevan lo saben. Sanders también. . Según informes de prensa, YouTube piensa remover todo tipo de videos y canales que promuevan el fascismo. Asume uno que también vayan a remover aquellos videos y canales que promueven el comunismo, un fascismo que se proclama antifascista.</t>
+  </si>
+  <si>
+    <t>justo ejemplo de lo que escasea en los medios colombianos y que en cambio en los estadounidenses, como la Critic At Large de The New Yorker , parece un animal frecuente. Ambos valoran una obra, de manera explícita o implícita, pero se desplazan después hacia terrenos incluso ajenos a esa obra para encontrar otras respuestas, otros rumbos, como el ensayo que escribe V. S. Naipaul sobre la perspectiva literaria discutiendo sobre Salambó de Flaubert y luego sobre Los comentarios de Julio César. Más allá de las obras y del autor, en ocasiones el interés del crítico es absorbido por el tema, el método o los contrastes. Aunque parezca una añoranza inútil del pasado, un pasado donde en los diarios que llegan a un público general se abrían debates literarios, en realidad se trata de un reclamo por lo básico. La crítica hace parte del periodismo diario y la cultura no</t>
+  </si>
+  <si>
+    <t>el indeseable pero necesario precio de la victoria. Algo similar ocurre en la guerra contra las drogas. La Organización Mundial de la Salud dice que el glifosato es probablemente cancerígeno, la Unión Europea prorrogó su licencia solo hasta el 2022 y Francia lo prohibirá a partir del 2021; en Estados Unidos son ya varias las condenas a Monsanto, el mismo fabricante del tenebroso agente naranja usado en Vietnam, no solo porque el glifosato causó cáncer a personas que utilizaron productos que lo contenían, sino porque el fabricante hizo todo lo posible por ocultar sus efectos nocivos; cerca de 13.000 procesos más esperan su turno ante la justicia norteamericana por hechos similares. Nuestra Corte Constitucional no se ha limitado a prohibir su aspersión en parques naturales, comunidades indígenas y territorios ancestrales, sino que ha dicho que su uso debe estar precedido de evidencia objetiva y concluyente que demuestre ausencia de daño</t>
+  </si>
+  <si>
+    <t>últimos años y todos los que han estado cerca de él parecen estar maldecidos. Es posible que con un poco de suerte estemos viendo la caída de un pseudorey que desde el comienzo nos hizo creer que la única solución contra la violencia era más violencia. Leo las noticias sobre A. Uribe y pienso en Guillermo Cano, Jaime Pardo Leal, Bernardo Jaramillo Ossa, Álvaro Gómez, Rodrigo Lara Bonilla, Luis Carlos Galán, Andrés Escobar y todos esos líderes sociales que han intentado construir un mejor país. Por ellos y ellas necesitamos que la justicia no tenga miedo y no se deje amedrentar de los que no sólo han conseguido el poder a punta de bala y de prácticas corruptas, sin importar si son de derecha o de izquierda, sino que además han sido incapaces de construir un poquito de paz. Colombia ha sufrido mucho como para seguir soportando tantas tristezas y</t>
+  </si>
+  <si>
+    <t>de la propiedad privada. No obstante haber quedado vaciada de contenido, la nomenclatura subsiste. Resulta paradójico incluso preocupante que algo sin enjundia divida a la sociedad en forma tan aguda como delirante. No es la razón, ni siquiera los intereses, son las pasiones. Algunos analistas, atados al ideologismo, se atreven a sugerir que la izquierda privilegia la igualdad sobre la libertad y la derecha proclama lo contrario. ¿Pero la libertad para qué, o la igualdad ante quién? Ese es un marco facilista: ¿serían de derecha quienes privilegian la libertad religiosa o la libertad económica, por ejemplo? ¿Serían de izquierda quienes proclaman la igualdad ante la ley o la igualdad de oportunidades? Más allá de esas preguntas, la confusión subsiste: si usted mira con tolerancia a los miembros de la comunidad LGBT, por ejemplo, entonces es de izquierda. Si los condena o rechaza de plano, usted es de derecha. En este</t>
+  </si>
+  <si>
+    <t>sin las cuales la democracia es una ficción y la máxima hobbesiana se hace también realidad en la arena económica. Ambas circunstancias llevan a que en la vida del país se imponga un sentimiento que es de simple supervivencia y no de pertenencia a un cuerpo social que reconoce y potencia los derechos a la vida y la dignidad de las personas. La solidaridad, que debe ser el pegante de la vida social, se reduce a su dimensión horizontal entre quienes comparten las mismas privaciones y amenazas; al ámbito de las relaciones familiares ampliadas, de los compadres, de los vecinos de barrio o de vereda. Mientras tanto, las dirigencias del país, así en plural, pasan a 30.000 pies de altura por encima de la brega diaria de una inmensa mayoría que no da el brazo a partir, a espaldas de unos dirigentes entregados a unas peleas que a nadie interesan</t>
+  </si>
+  <si>
+    <t>obsesión de las Farc, de su aparato de propaganda nacional e internacional y de los movimientos que los apoyan, en labrar y señalar distancias con los métodos y procedimientos de los paramilitares y en su afán por vestir la historia de la guerrilla con un tinte político. Definir y consagrar esa separación fue uno de los ejes estratégicos de sus negociaciones en La Habana y los delegados del Gobierno les compraron el proyecto, casi completo. De ahí surgieron las espinas: narcotráfico como delito conexo, justicia a la medida, garantías de impunidad para delitos atroces, lasitud en la entrega de bienes y reparación a las víctimas, etc. La extensa lista de imposiciones y maniobras que han realizado los amigos del proyecto y los abogados de las Farc para forzar un acuerdo a su conveniencia e insertarlo en la Constitución y la ley, dividió, polarizó y sigue enfrentando rabiosamente a los colombianos.</t>
+  </si>
+  <si>
+    <t>Con vergüenza, amor, con odio, con miedo, así se escribe poesía en el país que odia a las mujeres, dice el poeta mexicano Alejandro Merino, reflexionando sobre cómo es posible que haya mujeres que gozan del amor, mientras que otras sufren las consecuencias del maltrato, de la opresión y de la violencia. Este gran interrogante no es común en muchos hombres. La violación salvaje de la niña embera de 13 años ocurrida en los días pasados reactivó discusiones y charlas entre hombres y mujeres, entre si el caso era más pedofílico que otra cosa, si debía considerarse abuso o violación, si realmente valía la pena hacer tanto alarde si los niños, en mayoría estadística, eran mucho más propensos a ser víctimas de la pedofilia que las niñas. Las violaciones y feminicidios siempre reactivan esas viejas y desvencijadas posiciones masculinas: A los hombres también nos matan, a los hombres también nos</t>
+  </si>
+  <si>
+    <t>lo que sucede cuando se impone la doctrina de que ciertos sectores pueden y deben estar por encima de la ley. Y que hay otros no cobijados por ella. Pero esa es la doctrina oficial del Centro Democrático: desde las palomas hasta los duques. Es, en buena medida, lo que los mantiene unidos. Si la sociedad colombiana acompaña a Duque en su funesta omisión, estará declarando tácitamente que se merece que le ocurran estas y otras desgracias mayores. Normalizar estas cosas es girar un cheque en blanco a buena cuenta del horror un horror que puede explotar después en la cara de cada uno de nosotros. Me recuerdo mucho pues fue tal vez el primer libro serio de historia que leí en mi vida que, al final de sus Apuntamientos para la historia , el general José María Obando les responde a quienes lo acusaban de haber contribuido a destruir</t>
+  </si>
+  <si>
+    <t>La elasticidad moral que muchos tienen como norma de vida da para todo, inclusive para que quienes la estiran o encogen según lo requieran, se paren ante sus auditorios a pronunciar discursos de indignación por los escándalos de corrupción y, simultáneamente, sean corruptos en su vida cotidiana y corrompan a otros con actos que no merecen la menor autocensura porque, practicados por ellos, sus familiares, sus amigos o sus aliados, quedan cubiertos con un manto de santidad: una especie de varita mágica que convierte lo feo en bonito, lo malo en bueno y lo inadmisible, en indispensable para conseguir el fin que justifica cualquier medio. Sí, se trata de la elasticidad moral que funciona de manera similar al fenómeno económico de acuerdo con el cual una variable modifica su ser, si otra variable también lo hace. Uno de los descubrimientos del presidente Duque, estrella de su gabinete por su inteligencia,</t>
+  </si>
+  <si>
+    <t>cuando la cura es él y solo él. Peligroso espejismo vende el expresidente Uribe: un sofisticado populismo que exacerba pasiones sobre razones. El Estado de opinión no está diseñado para entenderse del todo con la democracia. Es un eufemismo para permitir a una élite modificar las reglas supremas, con diseño sobre medidas a sus necesidades e intereses, asegurándoles a los ciudadanos que han sido ellos los sastres. El Estado de opinión es la manera como la derecha se permite alentar una revolución sin untarse de izquierda. Es ese estadio delirante en que la horda, tea en mano, arrasa con la ley y el orden, clamando su defensa. Es fácil abrir las puertas del infierno, lo difícil es cerrarlas. Grima. De Claudia Palacios tengo la mejor opinión. No me sumé a la exaltación de redes acosándola por los planteamientos de su columna Paren de parir, sobre los hijos de refugiados venezolanos la exaltación de redes acosándola por los planteamientos de su columna Paren de parir, sobre los hijos de refugiados venezolanos nacidos en Colombia. Pero con enorme tristeza digo que al texto le sobró frialdad y le faltó humanidad. Bienvenido el debate sobre el control de la natalidad. Pero, tratándose de poblaciones vulnerables, las lógicas terminan pasando del escenario de las ideas al de la insensibilidad.</t>
+  </si>
+  <si>
+    <t>Según el Diccionario de la Real Academia Española, la palabra catarsis se usa para referirse al efecto purificador que causa una tragedia o experiencia vital profunda suscitando la compasión. Fue así como el sábado, mientras leía sumida en la intensidad del dolor narrado por Helena Urán en su libro Mi vida y el Palacio, la palabra vino a mi mente. Pensaba que un texto donde una contemporánea narra en primera persona lo que significó para ella y su familia haber perdido a su padre magistrado en la toma del Palacio de Justicia, cuando la autora apenas tenía diez años, tiene una textura afectiva muy distinta a tantos otros escritos sobre el mismo tema. De la mano de Helena, entiendo que esta tragedia es un horror que va mucho más allá de cifras, informes o posturas ideológicas. Siento más que entiendo, desde un plano emocional, el que me permite relacionarme con</t>
+  </si>
+  <si>
+    <t>el cambio del aceite de ballena al querosene siglo XIX, era el momento de pasar del petróleo al viento y el sol como fuentes de energía. En 2014 los Rockefeller anunciaron que uno de los fondos de la familia vendería sus inversiones en combustibles fósiles para reinvertirlas en energía limpia. No eran los únicos. El anuncio reforzaba la iniciativa llamada Global DivestInvest, que surgió de movimientos universitarios que cuestionaron la inversión de recursos de las universidades en el sector de hidrocarburos y que hoy es una gran red de más de 800 organizaciones y miles de inversionistas privados que han sacado sus inversiones de la industria de energía fósil para invertir en soluciones respetuosas del ambiente, acelerando la transición hacia una economía sin emisiones de carbono. Millones de dólares han cambiado su propósito de inversión. Así, en 2016, la familia Rockefeller retiró sus acciones de Exxon Mobil Corp. argumentando que</t>
+  </si>
+  <si>
+    <t>El futuro de la movilidad es multimodal e integrado. Cuando se usen vehículos, deben ser de tamaño correcto, compartidos y de cero emisiones. Este es el preámbulo de los diez principios de movilidad compartida para ciudades amables, una iniciativa de múltiples organizaciones que trabajan por la sostenibilidad urbana alrededor del mundo. El principio 6 busca que el transporte público y las flotas de uso compartido contribuyan a acelerar la transición a vehículos de cero emisiones, a partir de fuentes de energía renovables para maximizar beneficios climáticos y de calidad del aire. En este marco, los buses eléctricos juegan un papel esencial. Aún con desarrollo de redes de metro, tranvía, cables y trenes de cercanías eléctricos, los buses seguirán siendo una parte importante en la conectividad urbana multimodal e integrada. La tecnología de buses eléctricos está disponible hace décadas, con trolebuses que requieren suministro eléctrico continuo a través de catenarias. Recientemente</t>
+  </si>
+  <si>
+    <t>habitante es de 3.700 calorías. A continuación, el modelo se enfoca en las calorías de origen vegetal carbohidratos, vegetales, frutas y aceites vegetales y aquellas de origen animal res, cerdo, aves y pescado. En el campo de las proteínas vegetales, el consumo de carbohidratos se reduce a medida que aumenta el ingreso per cápita, mientras que el consumo de proteínas de aceite vegetal aumenta. El consumo de carbohidratos varía de forma importante, siendo el trigo la mayor fuente de proteína en un país como Rusia; y el arroz en Asia. El modelo del Dr. Fry lo que señala, aparte del crecimiento en la demanda por biocombustibles, es un importante aumento del consumo de calorías de origen animal, especialmente pescado, pollo y cerdo. Para el experto, las grandes oportunidades de crecimiento global en los próximos 20 años están es en el maíz, la soya y la palma, tres productos en los</t>
+  </si>
+  <si>
+    <t>a la posteridad. Los estamos consumiendo a una velocidad tal, que nuestros descendientes se quedarán sin recursos de ese tipo. El petróleo está compuesto por moléculas tan complicadas, que es criminal quemarlas. Eso es lo que hacemos con los motores de combustión interna. Hay que buscar combustibles alternativos; de hecho, ya los hay. El hidrógeno es el elemento más común en el universo. En la tierra se encuentra combinado con el oxígeno, como en el agua. Se puede hacer electrólisis de agua usando por ejemplo la energía solar y extraer el hidrógeno del aire utilizándolo como combustión. Eso ya lo hace la firma Mercedes Benz en Alemania. No contaminan el ambiente, no consumen un recurso no renovable que es una de las fuentes de energía del futuro. En cuanto a energía eléctrica, habrá que terminar totalmente con las usinas térmicas y finalmente también con las nucleares, porque éstas generan no</t>
+  </si>
+  <si>
+    <t>La potencial desaparición de un millón de especies vivas de la Tierra fue el mensaje más simple con el que los medios recibieron el documento final de la evaluación del estado de la biodiversidad global elaborado por expertos centenares de la Ipbes plataforma global intergubernamental de biodiversidad, equivalente del IPCC. Si bien es una figura contundente, su importancia radica en el análisis de las causas y consecuencias que la rodean, pues es indispensable entender el contexto histórico de las transformaciones generadas por los seres humanos en el planeta y las trayectorias del cambio, para que quienes estén en capacidad de incidir positivamente en ellas lo hagan. La evaluación contiene un reporte de varios volúmenes que solo será publicado en inglés en unos pocos meses, pero una síntesis y sus principales hallazgos fueron liberados como resultado de una intensa semana de negociaciones en la sede de la Unesco: no es fácil</t>
+  </si>
+  <si>
+    <t>crecimiento como Colombia cada vez demanda más energía e Hidruituango eventualmente va a entrar a aportar al sistema nacional de generación con beneficio para todos. Diversos grupos, y por distintas razones, exageraron y dramatizaron lo que pasó con la reducción del caudal del río Cauca. Claro que hay un daño ambiental causado por cambios de este tipo, pero la naturaleza se adapta y reacciona rápidamente tanto en función del cambio como en su forma de recuperarse una vez pasa la crisis. Hay muchos ejemplos de cambios drásticos y abruptos en ecosistemas los cuales no son causados por el hombre y de la misma manera son ejemplos de la resiliencia de las especies animales. Muchas sequías, inundaciones y diezmas de especies son parte del ciclo natural de las estaciones y de la naturaleza. El río Cauca no es una excepción dentro de la naturaleza. Lo grave de esta crisis, es cómo</t>
+  </si>
+  <si>
+    <t>2040 será menos del 10 de la canasta global de generación eléctrica. Y esa demanda va a estar concentrada casi de manera exclusiva es en los países asiáticos, economías que ya de por sí producen cerca de 60 veces más carbón que Colombia. Asumir que vamos a seguir vendiendo carbón en Asia, a precios remunerativos, no es realista. Pero al final del día no son las consideraciones ambientales las que van a decidir si el negocio del carbón térmico es viable, sino las realidades económicas. España se ha desenganchado totalmente del carbón no por orden gubernamental, sino porque ya no es rentable generar electricidad con este mineral. Seguir explotando el carbón simplemente porque tenemos reservas es tan insensato como el que algunos balleneros de New Bedford hubieran seguido cazando cetáceos porque en el mar todavía seguían nadando. Ni el Gobierno ni los contribuyentes tenemos un papel que cumplir en un porque en el mar todavía seguían nadando. Ni el Gobierno ni los contribuyentes tenemos un papel que cumplir en un sector en serios riesgos de desaparecer. No es, como se sugiere, que algunos queramos darle un entierro de tercera al carbón. Cuando están en juego 130.000 empleos directos, irresponsable es el no señalar el riesgo de la desaparición del sector y la necesidad de empezar desde ya conversaciones que contemplen esta posibilidad.</t>
+  </si>
+  <si>
+    <t>edad de los combustibles fósiles, que ya comienza su sustitución por energía solar y eólica, que esa energía ilimitada en el futuro será gratuita, que está comenzando la tercera revolución industrial basada en las energías sostenibles y las consecuencias de internet como la economía colaborativa, que el 90 de los automóviles va a desaparecer y que la inmensa mayoría de los que queden serán eléctricos y sin conductor, que llegó la edad de las reforestaciones masivas y de la energía limpia, que ya Copenhague quiere convertirse en la ciudad más verde del mundo. Paradójicamente nada resulta más favorable para la expansión de los bosques que la sobreabundancia de dióxido de carbono en la atmósfera, de modo que lo que hoy se requiere es inteligencia y voluntad. Pero la manera misma del proyecto industrial tendrá que ser examinada a fondo, porque aunque lográramos un 100 de energía limpia, ilimitada y gratuita,</t>
+  </si>
+  <si>
+    <t>claro que extraer energías vía fracking es más costoso que hacerlo mediante técnicas convencionales. Las inversiones son, por naturaleza, de muy largo plazo. Las que empiecen antes de 2020 no se abandonarán antes de 2030, cuando el país deberá empezar una estrategia de descarbonización según su compromiso de Colombia en el Acuerdo de París. Comprometer el país a la dolorosa agonía de los combustibles fósiles vía fracking sería una actuación en contra de los compromisos internacionales adquiridos por Colombia. Sugiero tener en cuenta el principio Keystone K. C. Golden, 2013, según el cual si queremos resolver la crisis del cambio global, en lugar de empeorarla formulando políticas favorables a la extracción ilimitada de combustibles fósiles, debemos dejar de empeorarla.</t>
+  </si>
+  <si>
+    <t>el último mapa del hambre, 821millones de personas, más de 1 de cada 9 habitantes del planeta, no tienen suficiente para comer. A pesar de que se produce suficiente comida para alimentar a todas las personas del mundo, todos los días 690 millones se acuestan con hambre y una de cada tres padece de desnutrición.150 millones de niños menores de 5 años sufren de problemas de crecimiento por no consumir los nutrientes necesarios. Una de cada tres mujeres en edad reproductiva padece de anemia. Es de conocimiento de una buena parte de dirigentes del mundo,que el cambio climático y las crisis económicas son las principales causas del hambre. Sin embargo, en 2020 la pandemia del Covid 19, los incendios y las sequías ocurridas en varias partes del mundo, han ampliado considerablemente el mapa del hambre, sobre todo en países como la República Democrática del Congo, Nigeria, Sudán del Sur y</t>
   </si>
   <si>
     <t>Ciencias_ambientales_ingenieria</t>
@@ -1170,11 +1479,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F171"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="3" max="3" width="51.33203125" customWidth="1"/>
     <col min="4" max="4" width="38.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
@@ -1205,36 +1515,36 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>276</v>
       </c>
       <c r="D2" t="s">
-        <v>244</v>
+        <v>356</v>
       </c>
       <c r="E2">
-        <v>0.43999242782592768</v>
+        <v>0.51064568758010864</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>283</v>
       </c>
       <c r="D3" t="s">
-        <v>244</v>
+        <v>356</v>
       </c>
       <c r="E3">
-        <v>0.46253371238708502</v>
+        <v>0.50503098964691162</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1242,39 +1552,39 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>281</v>
       </c>
       <c r="D4" t="s">
-        <v>244</v>
+        <v>356</v>
       </c>
       <c r="E4">
-        <v>0.42820209264755249</v>
+        <v>0.49721622467041021</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>284</v>
       </c>
       <c r="D5" t="s">
-        <v>244</v>
+        <v>356</v>
       </c>
       <c r="E5">
-        <v>0.53189879655838013</v>
+        <v>0.4854891300201416</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1285,16 +1595,16 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
+        <v>277</v>
       </c>
       <c r="D6" t="s">
-        <v>244</v>
+        <v>356</v>
       </c>
       <c r="E6">
-        <v>0.50138282775878906</v>
+        <v>0.47632744908332819</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1302,19 +1612,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>280</v>
       </c>
       <c r="D7" t="s">
-        <v>244</v>
+        <v>356</v>
       </c>
       <c r="E7">
-        <v>0.53881597518920898</v>
+        <v>0.47612309455871582</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1322,39 +1632,39 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>131</v>
+        <v>279</v>
       </c>
       <c r="D8" t="s">
-        <v>244</v>
+        <v>356</v>
       </c>
       <c r="E8">
-        <v>0.43581840395927429</v>
+        <v>0.46224826574325562</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>132</v>
+        <v>278</v>
       </c>
       <c r="D9" t="s">
-        <v>245</v>
+        <v>356</v>
       </c>
       <c r="E9">
-        <v>0.44615110754966741</v>
+        <v>0.4621238112449646</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1362,19 +1672,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>133</v>
+        <v>285</v>
       </c>
       <c r="D10" t="s">
-        <v>245</v>
+        <v>356</v>
       </c>
       <c r="E10">
-        <v>0.4204094409942627</v>
+        <v>0.4620099663734436</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1382,19 +1692,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="C11" t="s">
-        <v>134</v>
+        <v>282</v>
       </c>
       <c r="D11" t="s">
-        <v>245</v>
+        <v>356</v>
       </c>
       <c r="E11">
-        <v>0.40539336204528809</v>
+        <v>0.43137913942337042</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1402,19 +1712,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>293</v>
       </c>
       <c r="D12" t="s">
-        <v>245</v>
+        <v>357</v>
       </c>
       <c r="E12">
-        <v>0.43449768424034119</v>
+        <v>0.50876307487487793</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1422,39 +1732,39 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>121</v>
       </c>
       <c r="C13" t="s">
-        <v>136</v>
+        <v>291</v>
       </c>
       <c r="D13" t="s">
-        <v>245</v>
+        <v>357</v>
       </c>
       <c r="E13">
-        <v>0.41191554069519037</v>
+        <v>0.50417077541351318</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>122</v>
       </c>
       <c r="C14" t="s">
-        <v>137</v>
+        <v>292</v>
       </c>
       <c r="D14" t="s">
-        <v>245</v>
+        <v>357</v>
       </c>
       <c r="E14">
-        <v>0.5529942512512207</v>
+        <v>0.49723291397094732</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1465,36 +1775,36 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>138</v>
+        <v>288</v>
       </c>
       <c r="D15" t="s">
-        <v>245</v>
+        <v>357</v>
       </c>
       <c r="E15">
-        <v>0.41316458582878107</v>
+        <v>0.48386642336845398</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>139</v>
+        <v>286</v>
       </c>
       <c r="D16" t="s">
-        <v>246</v>
+        <v>357</v>
       </c>
       <c r="E16">
-        <v>0.41711068153381348</v>
+        <v>0.46397626399993902</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1502,19 +1812,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>290</v>
       </c>
       <c r="D17" t="s">
-        <v>246</v>
+        <v>357</v>
       </c>
       <c r="E17">
-        <v>0.44951805472373962</v>
+        <v>0.4636630117893219</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1525,16 +1835,16 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="C18" t="s">
-        <v>141</v>
+        <v>287</v>
       </c>
       <c r="D18" t="s">
-        <v>246</v>
+        <v>357</v>
       </c>
       <c r="E18">
-        <v>0.41205739974975591</v>
+        <v>0.46337363123893738</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1542,19 +1852,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>142</v>
+        <v>289</v>
       </c>
       <c r="D19" t="s">
-        <v>246</v>
+        <v>357</v>
       </c>
       <c r="E19">
-        <v>0.42998379468917852</v>
+        <v>0.45406705141067499</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1565,36 +1875,36 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="C20" t="s">
-        <v>143</v>
+        <v>295</v>
       </c>
       <c r="D20" t="s">
-        <v>246</v>
+        <v>357</v>
       </c>
       <c r="E20">
-        <v>0.45400810241699219</v>
+        <v>0.43654978275299072</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>144</v>
+        <v>294</v>
       </c>
       <c r="D21" t="s">
-        <v>246</v>
+        <v>357</v>
       </c>
       <c r="E21">
-        <v>0.41567906737327581</v>
+        <v>0.43627861142158508</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1602,19 +1912,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="C22" t="s">
-        <v>145</v>
+        <v>304</v>
       </c>
       <c r="D22" t="s">
-        <v>246</v>
+        <v>358</v>
       </c>
       <c r="E22">
-        <v>0.51365065574645996</v>
+        <v>0.54590564966201782</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1625,16 +1935,16 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>127</v>
       </c>
       <c r="C23" t="s">
-        <v>146</v>
+        <v>297</v>
       </c>
       <c r="D23" t="s">
-        <v>247</v>
+        <v>358</v>
       </c>
       <c r="E23">
-        <v>0.40782058238983149</v>
+        <v>0.52551215887069702</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1642,22 +1952,22 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="C24" t="s">
-        <v>147</v>
+        <v>298</v>
       </c>
       <c r="D24" t="s">
-        <v>247</v>
+        <v>358</v>
       </c>
       <c r="E24">
-        <v>0.44905239343643188</v>
+        <v>0.48539537191390991</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1665,16 +1975,16 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="C25" t="s">
-        <v>148</v>
+        <v>299</v>
       </c>
       <c r="D25" t="s">
-        <v>247</v>
+        <v>358</v>
       </c>
       <c r="E25">
-        <v>0.43663865327835077</v>
+        <v>0.47581207752227778</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1682,39 +1992,39 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="C26" t="s">
-        <v>149</v>
+        <v>303</v>
       </c>
       <c r="D26" t="s">
-        <v>247</v>
+        <v>358</v>
       </c>
       <c r="E26">
-        <v>0.43974250555038452</v>
+        <v>0.47441071271896362</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="C27" t="s">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="D27" t="s">
-        <v>247</v>
+        <v>358</v>
       </c>
       <c r="E27">
-        <v>0.4041208028793335</v>
+        <v>0.46835750341415411</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1722,19 +2032,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s">
-        <v>151</v>
+        <v>296</v>
       </c>
       <c r="D28" t="s">
-        <v>247</v>
+        <v>358</v>
       </c>
       <c r="E28">
-        <v>0.50240278244018555</v>
+        <v>0.46727514266967768</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1742,19 +2052,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s">
-        <v>152</v>
+        <v>305</v>
       </c>
       <c r="D29" t="s">
-        <v>247</v>
+        <v>358</v>
       </c>
       <c r="E29">
-        <v>0.46518519520759583</v>
+        <v>0.4592459499835968</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1762,39 +2072,39 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="C30" t="s">
-        <v>153</v>
+        <v>302</v>
       </c>
       <c r="D30" t="s">
-        <v>248</v>
+        <v>358</v>
       </c>
       <c r="E30">
-        <v>0.45003560185432429</v>
+        <v>0.45258885622024542</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="C31" t="s">
-        <v>154</v>
+        <v>300</v>
       </c>
       <c r="D31" t="s">
-        <v>248</v>
+        <v>358</v>
       </c>
       <c r="E31">
-        <v>0.47337266802787781</v>
+        <v>0.43600952625274658</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1805,76 +2115,76 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="C32" t="s">
-        <v>155</v>
+        <v>310</v>
       </c>
       <c r="D32" t="s">
-        <v>248</v>
+        <v>359</v>
       </c>
       <c r="E32">
-        <v>0.44730022549629211</v>
+        <v>0.57568401098251343</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="C33" t="s">
-        <v>156</v>
+        <v>309</v>
       </c>
       <c r="D33" t="s">
-        <v>248</v>
+        <v>359</v>
       </c>
       <c r="E33">
-        <v>0.43223181366920471</v>
+        <v>0.5070343017578125</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="C34" t="s">
-        <v>157</v>
+        <v>312</v>
       </c>
       <c r="D34" t="s">
-        <v>248</v>
+        <v>359</v>
       </c>
       <c r="E34">
-        <v>0.40417447686195368</v>
+        <v>0.50607031583786011</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>141</v>
       </c>
       <c r="C35" t="s">
-        <v>158</v>
+        <v>311</v>
       </c>
       <c r="D35" t="s">
-        <v>248</v>
+        <v>359</v>
       </c>
       <c r="E35">
-        <v>0.42976480722427368</v>
+        <v>0.49717199802398682</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1885,16 +2195,16 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>136</v>
       </c>
       <c r="C36" t="s">
-        <v>159</v>
+        <v>306</v>
       </c>
       <c r="D36" t="s">
-        <v>248</v>
+        <v>359</v>
       </c>
       <c r="E36">
-        <v>0.40277457237243652</v>
+        <v>0.47465848922729492</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1902,19 +2212,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="C37" t="s">
-        <v>160</v>
+        <v>308</v>
       </c>
       <c r="D37" t="s">
-        <v>249</v>
+        <v>359</v>
       </c>
       <c r="E37">
-        <v>0.44794049859046942</v>
+        <v>0.47148236632347112</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1922,19 +2232,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
-        <v>161</v>
+        <v>307</v>
       </c>
       <c r="D38" t="s">
-        <v>249</v>
+        <v>359</v>
       </c>
       <c r="E38">
-        <v>0.45302021503448492</v>
+        <v>0.46406179666519171</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1942,19 +2252,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="C39" t="s">
-        <v>162</v>
+        <v>313</v>
       </c>
       <c r="D39" t="s">
-        <v>249</v>
+        <v>359</v>
       </c>
       <c r="E39">
-        <v>0.41291722655296331</v>
+        <v>0.4421924352645874</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1962,19 +2272,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="C40" t="s">
-        <v>163</v>
+        <v>314</v>
       </c>
       <c r="D40" t="s">
-        <v>249</v>
+        <v>359</v>
       </c>
       <c r="E40">
-        <v>0.41848501563072199</v>
+        <v>0.43886324763298029</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1982,19 +2292,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="C41" t="s">
-        <v>164</v>
+        <v>315</v>
       </c>
       <c r="D41" t="s">
-        <v>249</v>
+        <v>359</v>
       </c>
       <c r="E41">
-        <v>0.46362414956092829</v>
+        <v>0.43679291009902949</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2005,56 +2315,56 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>151</v>
       </c>
       <c r="C42" t="s">
-        <v>165</v>
+        <v>321</v>
       </c>
       <c r="D42" t="s">
-        <v>249</v>
+        <v>360</v>
       </c>
       <c r="E42">
-        <v>0.4253973662853241</v>
+        <v>0.49737265706062322</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>152</v>
       </c>
       <c r="C43" t="s">
-        <v>166</v>
+        <v>322</v>
       </c>
       <c r="D43" t="s">
-        <v>249</v>
+        <v>360</v>
       </c>
       <c r="E43">
-        <v>0.50531971454620361</v>
+        <v>0.45366477966308588</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>147</v>
       </c>
       <c r="C44" t="s">
-        <v>167</v>
+        <v>317</v>
       </c>
       <c r="D44" t="s">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="E44">
-        <v>0.44197601079940801</v>
+        <v>0.44635388255119318</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2062,19 +2372,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>155</v>
       </c>
       <c r="C45" t="s">
-        <v>168</v>
+        <v>325</v>
       </c>
       <c r="D45" t="s">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="E45">
-        <v>0.43562495708465582</v>
+        <v>0.44432294368743902</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2082,19 +2392,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="C46" t="s">
-        <v>169</v>
+        <v>323</v>
       </c>
       <c r="D46" t="s">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="E46">
-        <v>0.40756577253341669</v>
+        <v>0.44131883978843689</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2105,16 +2415,16 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="C47" t="s">
-        <v>170</v>
+        <v>324</v>
       </c>
       <c r="D47" t="s">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="E47">
-        <v>0.40279790759086609</v>
+        <v>0.43594783544540411</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -2125,16 +2435,16 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="C48" t="s">
-        <v>171</v>
+        <v>316</v>
       </c>
       <c r="D48" t="s">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="E48">
-        <v>0.46315619349479681</v>
+        <v>0.43519952893257141</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2142,19 +2452,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="C49" t="s">
-        <v>172</v>
+        <v>318</v>
       </c>
       <c r="D49" t="s">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="E49">
-        <v>0.47312274575233459</v>
+        <v>0.43420374393463129</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2162,19 +2472,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="C50" t="s">
-        <v>173</v>
+        <v>319</v>
       </c>
       <c r="D50" t="s">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="E50">
-        <v>0.40127909183502197</v>
+        <v>0.43294763565063482</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2182,19 +2492,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="C51" t="s">
-        <v>174</v>
+        <v>320</v>
       </c>
       <c r="D51" t="s">
-        <v>251</v>
+        <v>360</v>
       </c>
       <c r="E51">
-        <v>0.46104267239570618</v>
+        <v>0.43257206678390497</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2205,56 +2515,56 @@
         <v>2</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="C52" t="s">
-        <v>175</v>
+        <v>326</v>
       </c>
       <c r="D52" t="s">
-        <v>251</v>
+        <v>361</v>
       </c>
       <c r="E52">
-        <v>0.41867074370384222</v>
+        <v>0.45092225074768072</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="C53" t="s">
-        <v>176</v>
+        <v>332</v>
       </c>
       <c r="D53" t="s">
-        <v>251</v>
+        <v>361</v>
       </c>
       <c r="E53">
-        <v>0.56203490495681763</v>
+        <v>0.44759547710418701</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="C54" t="s">
-        <v>177</v>
+        <v>335</v>
       </c>
       <c r="D54" t="s">
-        <v>251</v>
+        <v>361</v>
       </c>
       <c r="E54">
-        <v>0.48925957083702087</v>
+        <v>0.44522732496261602</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2262,19 +2572,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="C55" t="s">
-        <v>178</v>
+        <v>330</v>
       </c>
       <c r="D55" t="s">
-        <v>251</v>
+        <v>361</v>
       </c>
       <c r="E55">
-        <v>0.41412928700447083</v>
+        <v>0.44429567456245422</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2285,16 +2595,16 @@
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>157</v>
       </c>
       <c r="C56" t="s">
-        <v>179</v>
+        <v>327</v>
       </c>
       <c r="D56" t="s">
-        <v>251</v>
+        <v>361</v>
       </c>
       <c r="E56">
-        <v>0.4065936803817749</v>
+        <v>0.44256499409675598</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2305,16 +2615,16 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>163</v>
       </c>
       <c r="C57" t="s">
-        <v>180</v>
+        <v>333</v>
       </c>
       <c r="D57" t="s">
-        <v>251</v>
+        <v>361</v>
       </c>
       <c r="E57">
-        <v>0.40215909481048578</v>
+        <v>0.4393208920955658</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2322,19 +2632,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
       <c r="C58" t="s">
-        <v>181</v>
+        <v>331</v>
       </c>
       <c r="D58" t="s">
-        <v>252</v>
+        <v>361</v>
       </c>
       <c r="E58">
-        <v>0.40184247493743902</v>
+        <v>0.43556708097457891</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2342,19 +2652,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="C59" t="s">
-        <v>182</v>
+        <v>334</v>
       </c>
       <c r="D59" t="s">
-        <v>252</v>
+        <v>361</v>
       </c>
       <c r="E59">
-        <v>0.48330262303352362</v>
+        <v>0.43392020463943481</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -2362,39 +2672,39 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="C60" t="s">
-        <v>183</v>
+        <v>329</v>
       </c>
       <c r="D60" t="s">
-        <v>252</v>
+        <v>361</v>
       </c>
       <c r="E60">
-        <v>0.47308537364006042</v>
+        <v>0.43370687961578369</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>65</v>
+        <v>158</v>
       </c>
       <c r="C61" t="s">
-        <v>184</v>
+        <v>328</v>
       </c>
       <c r="D61" t="s">
-        <v>252</v>
+        <v>361</v>
       </c>
       <c r="E61">
-        <v>0.42696177959442139</v>
+        <v>0.43253254890441889</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -2405,59 +2715,59 @@
         <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>66</v>
+        <v>171</v>
       </c>
       <c r="C62" t="s">
-        <v>185</v>
+        <v>341</v>
       </c>
       <c r="D62" t="s">
-        <v>252</v>
+        <v>362</v>
       </c>
       <c r="E62">
-        <v>0.45117861032485962</v>
+        <v>0.55240517854690552</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>173</v>
       </c>
       <c r="C63" t="s">
-        <v>186</v>
+        <v>343</v>
       </c>
       <c r="D63" t="s">
-        <v>252</v>
+        <v>362</v>
       </c>
       <c r="E63">
-        <v>0.43266481161117548</v>
+        <v>0.51703464984893799</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>170</v>
       </c>
       <c r="C64" t="s">
-        <v>187</v>
+        <v>340</v>
       </c>
       <c r="D64" t="s">
-        <v>252</v>
+        <v>362</v>
       </c>
       <c r="E64">
-        <v>0.41612717509269709</v>
+        <v>0.49451744556427002</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -2465,16 +2775,16 @@
         <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="C65" t="s">
-        <v>188</v>
+        <v>345</v>
       </c>
       <c r="D65" t="s">
-        <v>253</v>
+        <v>362</v>
       </c>
       <c r="E65">
-        <v>0.4172598123550415</v>
+        <v>0.47677174210548401</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -2482,22 +2792,22 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="C66" t="s">
-        <v>189</v>
+        <v>339</v>
       </c>
       <c r="D66" t="s">
-        <v>253</v>
+        <v>362</v>
       </c>
       <c r="E66">
-        <v>0.45297509431838989</v>
+        <v>0.47611856460571289</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -2505,19 +2815,19 @@
         <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="C67" t="s">
-        <v>190</v>
+        <v>338</v>
       </c>
       <c r="D67" t="s">
-        <v>253</v>
+        <v>362</v>
       </c>
       <c r="E67">
-        <v>0.45021158456802368</v>
+        <v>0.46977102756500239</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -2525,36 +2835,36 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="C68" t="s">
-        <v>191</v>
+        <v>337</v>
       </c>
       <c r="D68" t="s">
-        <v>253</v>
+        <v>362</v>
       </c>
       <c r="E68">
-        <v>0.50900977849960327</v>
+        <v>0.45941996574401861</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B69" t="s">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="C69" t="s">
-        <v>192</v>
+        <v>342</v>
       </c>
       <c r="D69" t="s">
-        <v>253</v>
+        <v>362</v>
       </c>
       <c r="E69">
-        <v>0.43221721053123469</v>
+        <v>0.44767996668815607</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -2565,16 +2875,16 @@
         <v>1</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>166</v>
       </c>
       <c r="C70" t="s">
-        <v>193</v>
+        <v>336</v>
       </c>
       <c r="D70" t="s">
-        <v>253</v>
+        <v>362</v>
       </c>
       <c r="E70">
-        <v>0.41063153743743902</v>
+        <v>0.44363734126090998</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -2582,19 +2892,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>174</v>
       </c>
       <c r="C71" t="s">
-        <v>194</v>
+        <v>344</v>
       </c>
       <c r="D71" t="s">
-        <v>253</v>
+        <v>362</v>
       </c>
       <c r="E71">
-        <v>0.48053571581840521</v>
+        <v>0.43112301826477051</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -2602,22 +2912,22 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D72" t="s">
-        <v>254</v>
+        <v>346</v>
       </c>
       <c r="E72">
-        <v>0.46616789698600769</v>
+        <v>0.5355837345123291</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -2625,36 +2935,36 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C73" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="D73" t="s">
-        <v>254</v>
+        <v>346</v>
       </c>
       <c r="E73">
-        <v>0.43825662136077881</v>
+        <v>0.52838230133056641</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B74" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="C74" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="D74" t="s">
-        <v>254</v>
+        <v>346</v>
       </c>
       <c r="E74">
-        <v>0.46027138829231262</v>
+        <v>0.5245741605758667</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2662,62 +2972,62 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B75" t="s">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D75" t="s">
-        <v>254</v>
+        <v>346</v>
       </c>
       <c r="E75">
-        <v>0.42180317640304571</v>
+        <v>0.49706807732582092</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B76" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D76" t="s">
-        <v>254</v>
+        <v>346</v>
       </c>
       <c r="E76">
-        <v>0.41760203242301941</v>
+        <v>0.4866161048412323</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="C77" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="D77" t="s">
-        <v>254</v>
+        <v>346</v>
       </c>
       <c r="E77">
-        <v>0.40824753046035772</v>
+        <v>0.47645813226699829</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -2725,16 +3035,16 @@
         <v>1</v>
       </c>
       <c r="B78" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="D78" t="s">
-        <v>254</v>
+        <v>346</v>
       </c>
       <c r="E78">
-        <v>0.41642993688583368</v>
+        <v>0.4584965705871582</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2742,19 +3052,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B79" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="C79" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="D79" t="s">
-        <v>255</v>
+        <v>346</v>
       </c>
       <c r="E79">
-        <v>0.4116491973400116</v>
+        <v>0.45842096209526062</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -2762,19 +3072,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B80" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="C80" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="D80" t="s">
-        <v>255</v>
+        <v>346</v>
       </c>
       <c r="E80">
-        <v>0.50876307487487793</v>
+        <v>0.4538174569606781</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -2782,19 +3092,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B81" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="D81" t="s">
-        <v>255</v>
+        <v>346</v>
       </c>
       <c r="E81">
-        <v>0.46482911705970759</v>
+        <v>0.44515758752822882</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -2802,79 +3112,79 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="C82" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="D82" t="s">
-        <v>255</v>
+        <v>347</v>
       </c>
       <c r="E82">
-        <v>0.41679781675338751</v>
+        <v>0.52892708778381348</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="C83" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="D83" t="s">
-        <v>255</v>
+        <v>347</v>
       </c>
       <c r="E83">
-        <v>0.40763267874717712</v>
+        <v>0.51179254055023193</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="C84" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="D84" t="s">
-        <v>255</v>
+        <v>347</v>
       </c>
       <c r="E84">
-        <v>0.43168851733207703</v>
+        <v>0.48132485151290888</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="C85" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="D85" t="s">
-        <v>255</v>
+        <v>347</v>
       </c>
       <c r="E85">
-        <v>0.45425736904144293</v>
+        <v>0.46655040979385382</v>
       </c>
       <c r="F85">
         <v>1</v>
@@ -2882,19 +3192,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B86" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="C86" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D86" t="s">
-        <v>256</v>
+        <v>347</v>
       </c>
       <c r="E86">
-        <v>0.51298803091049194</v>
+        <v>0.46558362245559692</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -2905,59 +3215,59 @@
         <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="C87" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="D87" t="s">
-        <v>256</v>
+        <v>347</v>
       </c>
       <c r="E87">
-        <v>0.43567174673080439</v>
+        <v>0.44759154319763178</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="C88" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="D88" t="s">
-        <v>256</v>
+        <v>347</v>
       </c>
       <c r="E88">
-        <v>0.40702453255653381</v>
+        <v>0.44280251860618591</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="C89" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="D89" t="s">
-        <v>256</v>
+        <v>347</v>
       </c>
       <c r="E89">
-        <v>0.46923252940177917</v>
+        <v>0.44119825959205627</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -2965,16 +3275,16 @@
         <v>1</v>
       </c>
       <c r="B90" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="C90" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="D90" t="s">
-        <v>256</v>
+        <v>347</v>
       </c>
       <c r="E90">
-        <v>0.41908115148544312</v>
+        <v>0.43722915649414063</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -2982,19 +3292,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="C91" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="D91" t="s">
-        <v>256</v>
+        <v>347</v>
       </c>
       <c r="E91">
-        <v>0.40424668788909912</v>
+        <v>0.43132078647613531</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -3002,22 +3312,22 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B92" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="C92" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="D92" t="s">
-        <v>256</v>
+        <v>348</v>
       </c>
       <c r="E92">
-        <v>0.45938310027122498</v>
+        <v>0.47852456569671631</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3025,16 +3335,16 @@
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="C93" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="D93" t="s">
-        <v>257</v>
+        <v>348</v>
       </c>
       <c r="E93">
-        <v>0.48334640264511108</v>
+        <v>0.47382622957229609</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -3045,16 +3355,16 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="C94" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D94" t="s">
-        <v>257</v>
+        <v>348</v>
       </c>
       <c r="E94">
-        <v>0.41065192222595209</v>
+        <v>0.46731498837471008</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -3062,19 +3372,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B95" t="s">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="C95" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D95" t="s">
-        <v>257</v>
+        <v>348</v>
       </c>
       <c r="E95">
-        <v>0.45696890354156489</v>
+        <v>0.46001049876213068</v>
       </c>
       <c r="F95">
         <v>1</v>
@@ -3082,19 +3392,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B96" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="C96" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="D96" t="s">
-        <v>257</v>
+        <v>348</v>
       </c>
       <c r="E96">
-        <v>0.46000951528549189</v>
+        <v>0.45952001214027399</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -3102,39 +3412,39 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B97" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="C97" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="D97" t="s">
-        <v>257</v>
+        <v>348</v>
       </c>
       <c r="E97">
-        <v>0.45503976941108698</v>
+        <v>0.4555092453956604</v>
       </c>
       <c r="F97">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="C98" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="D98" t="s">
-        <v>257</v>
+        <v>348</v>
       </c>
       <c r="E98">
-        <v>0.40014457702636719</v>
+        <v>0.45444920659065252</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -3142,22 +3452,22 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B99" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="C99" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="D99" t="s">
-        <v>257</v>
+        <v>348</v>
       </c>
       <c r="E99">
-        <v>0.41766142845153809</v>
+        <v>0.4450613260269165</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
@@ -3165,16 +3475,16 @@
         <v>1</v>
       </c>
       <c r="B100" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="C100" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="D100" t="s">
-        <v>258</v>
+        <v>348</v>
       </c>
       <c r="E100">
-        <v>0.42363575100898743</v>
+        <v>0.43880051374435419</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -3182,19 +3492,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B101" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="C101" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="D101" t="s">
-        <v>258</v>
+        <v>348</v>
       </c>
       <c r="E101">
-        <v>0.44689995050430298</v>
+        <v>0.43127700686454767</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -3202,59 +3512,59 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B102" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="C102" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="D102" t="s">
-        <v>258</v>
+        <v>349</v>
       </c>
       <c r="E102">
-        <v>0.44875320792198181</v>
+        <v>0.48519766330718989</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B103" t="s">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="C103" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="D103" t="s">
-        <v>258</v>
+        <v>349</v>
       </c>
       <c r="E103">
-        <v>0.47130924463272089</v>
+        <v>0.48291593790054321</v>
       </c>
       <c r="F103">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B104" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="C104" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="D104" t="s">
-        <v>258</v>
+        <v>349</v>
       </c>
       <c r="E104">
-        <v>0.44987413287162781</v>
+        <v>0.46386462450027471</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -3262,19 +3572,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="C105" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D105" t="s">
-        <v>258</v>
+        <v>349</v>
       </c>
       <c r="E105">
-        <v>0.40533304214477539</v>
+        <v>0.46347469091415411</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -3285,16 +3595,16 @@
         <v>1</v>
       </c>
       <c r="B106" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="C106" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="D106" t="s">
-        <v>258</v>
+        <v>349</v>
       </c>
       <c r="E106">
-        <v>0.44943851232528692</v>
+        <v>0.45933559536933899</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -3302,19 +3612,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="C107" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="D107" t="s">
-        <v>259</v>
+        <v>349</v>
       </c>
       <c r="E107">
-        <v>0.45382058620452881</v>
+        <v>0.44972515106201172</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -3322,19 +3632,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B108" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="C108" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="D108" t="s">
-        <v>259</v>
+        <v>349</v>
       </c>
       <c r="E108">
-        <v>0.4658108651638031</v>
+        <v>0.44905239343643188</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -3342,19 +3652,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B109" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="C109" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="D109" t="s">
-        <v>259</v>
+        <v>349</v>
       </c>
       <c r="E109">
-        <v>0.43964973092079163</v>
+        <v>0.44114050269126892</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -3362,19 +3672,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="C110" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="D110" t="s">
-        <v>259</v>
+        <v>349</v>
       </c>
       <c r="E110">
-        <v>0.42659205198287958</v>
+        <v>0.4409366250038147</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -3382,19 +3692,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B111" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="C111" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="D111" t="s">
-        <v>259</v>
+        <v>349</v>
       </c>
       <c r="E111">
-        <v>0.40218445658683782</v>
+        <v>0.43181693553924561</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -3402,22 +3712,22 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B112" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="C112" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="D112" t="s">
-        <v>259</v>
+        <v>350</v>
       </c>
       <c r="E112">
-        <v>0.43326705694198608</v>
+        <v>0.52547025680541992</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -3425,36 +3735,36 @@
         <v>2</v>
       </c>
       <c r="B113" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="C113" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="D113" t="s">
-        <v>259</v>
+        <v>350</v>
       </c>
       <c r="E113">
-        <v>0.42127442359924322</v>
+        <v>0.4758143424987793</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B114" t="s">
-        <v>118</v>
+        <v>47</v>
       </c>
       <c r="C114" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="D114" t="s">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="E114">
-        <v>0.42329484224319458</v>
+        <v>0.46991908550262451</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -3462,19 +3772,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="C115" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="D115" t="s">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="E115">
-        <v>0.5398324728012085</v>
+        <v>0.4699016809463501</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -3482,19 +3792,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B116" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="C116" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="D116" t="s">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="E116">
-        <v>0.41119906306266779</v>
+        <v>0.46944791078567499</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -3505,16 +3815,16 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="C117" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="D117" t="s">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="E117">
-        <v>0.40443113446235662</v>
+        <v>0.46806168556213379</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -3522,19 +3832,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B118" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="C118" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="D118" t="s">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="E118">
-        <v>0.44581064581871033</v>
+        <v>0.4590650200843811</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -3542,19 +3852,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="C119" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="D119" t="s">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="E119">
-        <v>0.49317476153373718</v>
+        <v>0.44192972779273992</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -3562,25 +3872,1050 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B120" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="C120" t="s">
+        <v>216</v>
+      </c>
+      <c r="D120" t="s">
+        <v>350</v>
+      </c>
+      <c r="E120">
+        <v>0.43331128358840942</v>
+      </c>
+      <c r="F120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>3</v>
+      </c>
+      <c r="B121" t="s">
+        <v>55</v>
+      </c>
+      <c r="C121" t="s">
+        <v>225</v>
+      </c>
+      <c r="D121" t="s">
+        <v>350</v>
+      </c>
+      <c r="E121">
+        <v>0.43254843354225159</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>1</v>
+      </c>
+      <c r="B122" t="s">
+        <v>62</v>
+      </c>
+      <c r="C122" t="s">
+        <v>232</v>
+      </c>
+      <c r="D122" t="s">
+        <v>351</v>
+      </c>
+      <c r="E122">
+        <v>0.55346935987472534</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>6</v>
+      </c>
+      <c r="B123" t="s">
+        <v>64</v>
+      </c>
+      <c r="C123" t="s">
+        <v>234</v>
+      </c>
+      <c r="D123" t="s">
+        <v>351</v>
+      </c>
+      <c r="E123">
+        <v>0.52979713678359985</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>0</v>
+      </c>
+      <c r="B124" t="s">
+        <v>56</v>
+      </c>
+      <c r="C124" t="s">
+        <v>226</v>
+      </c>
+      <c r="D124" t="s">
+        <v>351</v>
+      </c>
+      <c r="E124">
+        <v>0.5125507116317749</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>1</v>
+      </c>
+      <c r="B125" t="s">
+        <v>63</v>
+      </c>
+      <c r="C125" t="s">
+        <v>233</v>
+      </c>
+      <c r="D125" t="s">
+        <v>351</v>
+      </c>
+      <c r="E125">
+        <v>0.47744041681289667</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>3</v>
+      </c>
+      <c r="B126" t="s">
+        <v>59</v>
+      </c>
+      <c r="C126" t="s">
+        <v>229</v>
+      </c>
+      <c r="D126" t="s">
+        <v>351</v>
+      </c>
+      <c r="E126">
+        <v>0.47740811109542852</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>1</v>
+      </c>
+      <c r="B127" t="s">
+        <v>60</v>
+      </c>
+      <c r="C127" t="s">
+        <v>230</v>
+      </c>
+      <c r="D127" t="s">
+        <v>351</v>
+      </c>
+      <c r="E127">
+        <v>0.46266019344329828</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>2</v>
+      </c>
+      <c r="B128" t="s">
+        <v>58</v>
+      </c>
+      <c r="C128" t="s">
+        <v>228</v>
+      </c>
+      <c r="D128" t="s">
+        <v>351</v>
+      </c>
+      <c r="E128">
+        <v>0.4502653181552887</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>0</v>
+      </c>
+      <c r="B129" t="s">
+        <v>65</v>
+      </c>
+      <c r="C129" t="s">
+        <v>235</v>
+      </c>
+      <c r="D129" t="s">
+        <v>351</v>
+      </c>
+      <c r="E129">
+        <v>0.45013344287872309</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>0</v>
+      </c>
+      <c r="B130" t="s">
+        <v>57</v>
+      </c>
+      <c r="C130" t="s">
+        <v>227</v>
+      </c>
+      <c r="D130" t="s">
+        <v>351</v>
+      </c>
+      <c r="E130">
+        <v>0.44780170917510992</v>
+      </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>0</v>
+      </c>
+      <c r="B131" t="s">
+        <v>61</v>
+      </c>
+      <c r="C131" t="s">
+        <v>231</v>
+      </c>
+      <c r="D131" t="s">
+        <v>351</v>
+      </c>
+      <c r="E131">
+        <v>0.44152998924255371</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>0</v>
+      </c>
+      <c r="B132" t="s">
+        <v>68</v>
+      </c>
+      <c r="C132" t="s">
+        <v>238</v>
+      </c>
+      <c r="D132" t="s">
+        <v>352</v>
+      </c>
+      <c r="E132">
+        <v>0.5285678505897522</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>1</v>
+      </c>
+      <c r="B133" t="s">
+        <v>72</v>
+      </c>
+      <c r="C133" t="s">
+        <v>242</v>
+      </c>
+      <c r="D133" t="s">
+        <v>352</v>
+      </c>
+      <c r="E133">
+        <v>0.48128834366798401</v>
+      </c>
+      <c r="F133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>1</v>
+      </c>
+      <c r="B134" t="s">
+        <v>70</v>
+      </c>
+      <c r="C134" t="s">
+        <v>240</v>
+      </c>
+      <c r="D134" t="s">
+        <v>352</v>
+      </c>
+      <c r="E134">
+        <v>0.48051878809928888</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>4</v>
+      </c>
+      <c r="B135" t="s">
+        <v>74</v>
+      </c>
+      <c r="C135" t="s">
+        <v>244</v>
+      </c>
+      <c r="D135" t="s">
+        <v>352</v>
+      </c>
+      <c r="E135">
+        <v>0.4619353711605072</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>4</v>
+      </c>
+      <c r="B136" t="s">
+        <v>71</v>
+      </c>
+      <c r="C136" t="s">
+        <v>241</v>
+      </c>
+      <c r="D136" t="s">
+        <v>352</v>
+      </c>
+      <c r="E136">
+        <v>0.45694577693939209</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>1</v>
+      </c>
+      <c r="B137" t="s">
+        <v>69</v>
+      </c>
+      <c r="C137" t="s">
+        <v>239</v>
+      </c>
+      <c r="D137" t="s">
+        <v>352</v>
+      </c>
+      <c r="E137">
+        <v>0.44429492950439448</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>1</v>
+      </c>
+      <c r="B138" t="s">
+        <v>66</v>
+      </c>
+      <c r="C138" t="s">
+        <v>236</v>
+      </c>
+      <c r="D138" t="s">
+        <v>352</v>
+      </c>
+      <c r="E138">
+        <v>0.43738240003585821</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>2</v>
+      </c>
+      <c r="B139" t="s">
+        <v>73</v>
+      </c>
+      <c r="C139" t="s">
         <v>243</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D139" t="s">
+        <v>352</v>
+      </c>
+      <c r="E139">
+        <v>0.4329228401184082</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>2</v>
+      </c>
+      <c r="B140" t="s">
+        <v>67</v>
+      </c>
+      <c r="C140" t="s">
+        <v>237</v>
+      </c>
+      <c r="D140" t="s">
+        <v>352</v>
+      </c>
+      <c r="E140">
+        <v>0.43257951736450201</v>
+      </c>
+      <c r="F140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>0</v>
+      </c>
+      <c r="B141" t="s">
+        <v>75</v>
+      </c>
+      <c r="C141" t="s">
+        <v>245</v>
+      </c>
+      <c r="D141" t="s">
+        <v>352</v>
+      </c>
+      <c r="E141">
+        <v>0.43163320422172552</v>
+      </c>
+      <c r="F141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>1</v>
+      </c>
+      <c r="B142" t="s">
+        <v>79</v>
+      </c>
+      <c r="C142" t="s">
+        <v>249</v>
+      </c>
+      <c r="D142" t="s">
+        <v>353</v>
+      </c>
+      <c r="E142">
+        <v>0.5339362621307373</v>
+      </c>
+      <c r="F142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>0</v>
+      </c>
+      <c r="B143" t="s">
+        <v>77</v>
+      </c>
+      <c r="C143" t="s">
+        <v>247</v>
+      </c>
+      <c r="D143" t="s">
+        <v>353</v>
+      </c>
+      <c r="E143">
+        <v>0.48625841736793518</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>5</v>
+      </c>
+      <c r="B144" t="s">
+        <v>83</v>
+      </c>
+      <c r="C144" t="s">
+        <v>253</v>
+      </c>
+      <c r="D144" t="s">
+        <v>353</v>
+      </c>
+      <c r="E144">
+        <v>0.47802269458770752</v>
+      </c>
+      <c r="F144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>3</v>
+      </c>
+      <c r="B145" t="s">
+        <v>82</v>
+      </c>
+      <c r="C145" t="s">
+        <v>252</v>
+      </c>
+      <c r="D145" t="s">
+        <v>353</v>
+      </c>
+      <c r="E145">
+        <v>0.47025039792060852</v>
+      </c>
+      <c r="F145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>3</v>
+      </c>
+      <c r="B146" t="s">
+        <v>76</v>
+      </c>
+      <c r="C146" t="s">
+        <v>246</v>
+      </c>
+      <c r="D146" t="s">
+        <v>353</v>
+      </c>
+      <c r="E146">
+        <v>0.46590906381607061</v>
+      </c>
+      <c r="F146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>1</v>
+      </c>
+      <c r="B147" t="s">
+        <v>85</v>
+      </c>
+      <c r="C147" t="s">
+        <v>255</v>
+      </c>
+      <c r="D147" t="s">
+        <v>353</v>
+      </c>
+      <c r="E147">
+        <v>0.44507259130477911</v>
+      </c>
+      <c r="F147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>3</v>
+      </c>
+      <c r="B148" t="s">
+        <v>80</v>
+      </c>
+      <c r="C148" t="s">
+        <v>250</v>
+      </c>
+      <c r="D148" t="s">
+        <v>353</v>
+      </c>
+      <c r="E148">
+        <v>0.44289147853851318</v>
+      </c>
+      <c r="F148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>1</v>
+      </c>
+      <c r="B149" t="s">
+        <v>81</v>
+      </c>
+      <c r="C149" t="s">
+        <v>251</v>
+      </c>
+      <c r="D149" t="s">
+        <v>353</v>
+      </c>
+      <c r="E149">
+        <v>0.44063004851341248</v>
+      </c>
+      <c r="F149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>0</v>
+      </c>
+      <c r="B150" t="s">
+        <v>84</v>
+      </c>
+      <c r="C150" t="s">
+        <v>254</v>
+      </c>
+      <c r="D150" t="s">
+        <v>353</v>
+      </c>
+      <c r="E150">
+        <v>0.43121474981307978</v>
+      </c>
+      <c r="F150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <v>2</v>
+      </c>
+      <c r="B151" t="s">
+        <v>78</v>
+      </c>
+      <c r="C151" t="s">
+        <v>248</v>
+      </c>
+      <c r="D151" t="s">
+        <v>353</v>
+      </c>
+      <c r="E151">
+        <v>0.43001139163970947</v>
+      </c>
+      <c r="F151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>1</v>
+      </c>
+      <c r="B152" t="s">
+        <v>92</v>
+      </c>
+      <c r="C152" t="s">
+        <v>262</v>
+      </c>
+      <c r="D152" t="s">
+        <v>354</v>
+      </c>
+      <c r="E152">
+        <v>0.52562099695205688</v>
+      </c>
+      <c r="F152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>1</v>
+      </c>
+      <c r="B153" t="s">
+        <v>91</v>
+      </c>
+      <c r="C153" t="s">
+        <v>261</v>
+      </c>
+      <c r="D153" t="s">
+        <v>354</v>
+      </c>
+      <c r="E153">
+        <v>0.50767481327056885</v>
+      </c>
+      <c r="F153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>1</v>
+      </c>
+      <c r="B154" t="s">
+        <v>90</v>
+      </c>
+      <c r="C154" t="s">
         <v>260</v>
       </c>
-      <c r="E120">
-        <v>0.46563950181007391</v>
-      </c>
-      <c r="F120">
-        <v>1</v>
+      <c r="D154" t="s">
+        <v>354</v>
+      </c>
+      <c r="E154">
+        <v>0.49163073301315308</v>
+      </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>2</v>
+      </c>
+      <c r="B155" t="s">
+        <v>93</v>
+      </c>
+      <c r="C155" t="s">
+        <v>263</v>
+      </c>
+      <c r="D155" t="s">
+        <v>354</v>
+      </c>
+      <c r="E155">
+        <v>0.49015897512435908</v>
+      </c>
+      <c r="F155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>1</v>
+      </c>
+      <c r="B156" t="s">
+        <v>94</v>
+      </c>
+      <c r="C156" t="s">
+        <v>264</v>
+      </c>
+      <c r="D156" t="s">
+        <v>354</v>
+      </c>
+      <c r="E156">
+        <v>0.48700448870658869</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>0</v>
+      </c>
+      <c r="B157" t="s">
+        <v>87</v>
+      </c>
+      <c r="C157" t="s">
+        <v>257</v>
+      </c>
+      <c r="D157" t="s">
+        <v>354</v>
+      </c>
+      <c r="E157">
+        <v>0.47430342435836792</v>
+      </c>
+      <c r="F157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>4</v>
+      </c>
+      <c r="B158" t="s">
+        <v>86</v>
+      </c>
+      <c r="C158" t="s">
+        <v>256</v>
+      </c>
+      <c r="D158" t="s">
+        <v>354</v>
+      </c>
+      <c r="E158">
+        <v>0.47308537364006042</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <v>1</v>
+      </c>
+      <c r="B159" t="s">
+        <v>95</v>
+      </c>
+      <c r="C159" t="s">
+        <v>265</v>
+      </c>
+      <c r="D159" t="s">
+        <v>354</v>
+      </c>
+      <c r="E159">
+        <v>0.45931470394134521</v>
+      </c>
+      <c r="F159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>3</v>
+      </c>
+      <c r="B160" t="s">
+        <v>88</v>
+      </c>
+      <c r="C160" t="s">
+        <v>258</v>
+      </c>
+      <c r="D160" t="s">
+        <v>354</v>
+      </c>
+      <c r="E160">
+        <v>0.43731164932250982</v>
+      </c>
+      <c r="F160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>4</v>
+      </c>
+      <c r="B161" t="s">
+        <v>89</v>
+      </c>
+      <c r="C161" t="s">
+        <v>259</v>
+      </c>
+      <c r="D161" t="s">
+        <v>354</v>
+      </c>
+      <c r="E161">
+        <v>0.43652072548866272</v>
+      </c>
+      <c r="F161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>2</v>
+      </c>
+      <c r="B162" t="s">
+        <v>105</v>
+      </c>
+      <c r="C162" t="s">
+        <v>275</v>
+      </c>
+      <c r="D162" t="s">
+        <v>355</v>
+      </c>
+      <c r="E162">
+        <v>0.53846436738967896</v>
+      </c>
+      <c r="F162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <v>3</v>
+      </c>
+      <c r="B163" t="s">
+        <v>99</v>
+      </c>
+      <c r="C163" t="s">
+        <v>269</v>
+      </c>
+      <c r="D163" t="s">
+        <v>355</v>
+      </c>
+      <c r="E163">
+        <v>0.50159788131713867</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>2</v>
+      </c>
+      <c r="B164" t="s">
+        <v>104</v>
+      </c>
+      <c r="C164" t="s">
+        <v>274</v>
+      </c>
+      <c r="D164" t="s">
+        <v>355</v>
+      </c>
+      <c r="E164">
+        <v>0.45998987555503851</v>
+      </c>
+      <c r="F164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>1</v>
+      </c>
+      <c r="B165" t="s">
+        <v>102</v>
+      </c>
+      <c r="C165" t="s">
+        <v>272</v>
+      </c>
+      <c r="D165" t="s">
+        <v>355</v>
+      </c>
+      <c r="E165">
+        <v>0.45239797234535217</v>
+      </c>
+      <c r="F165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>1</v>
+      </c>
+      <c r="B166" t="s">
+        <v>101</v>
+      </c>
+      <c r="C166" t="s">
+        <v>271</v>
+      </c>
+      <c r="D166" t="s">
+        <v>355</v>
+      </c>
+      <c r="E166">
+        <v>0.45021158456802368</v>
+      </c>
+      <c r="F166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>1</v>
+      </c>
+      <c r="B167" t="s">
+        <v>96</v>
+      </c>
+      <c r="C167" t="s">
+        <v>266</v>
+      </c>
+      <c r="D167" t="s">
+        <v>355</v>
+      </c>
+      <c r="E167">
+        <v>0.44970709085464478</v>
+      </c>
+      <c r="F167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>2</v>
+      </c>
+      <c r="B168" t="s">
+        <v>98</v>
+      </c>
+      <c r="C168" t="s">
+        <v>268</v>
+      </c>
+      <c r="D168" t="s">
+        <v>355</v>
+      </c>
+      <c r="E168">
+        <v>0.44641637802124018</v>
+      </c>
+      <c r="F168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>0</v>
+      </c>
+      <c r="B169" t="s">
+        <v>100</v>
+      </c>
+      <c r="C169" t="s">
+        <v>270</v>
+      </c>
+      <c r="D169" t="s">
+        <v>355</v>
+      </c>
+      <c r="E169">
+        <v>0.43494066596031189</v>
+      </c>
+      <c r="F169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>3</v>
+      </c>
+      <c r="B170" t="s">
+        <v>97</v>
+      </c>
+      <c r="C170" t="s">
+        <v>267</v>
+      </c>
+      <c r="D170" t="s">
+        <v>355</v>
+      </c>
+      <c r="E170">
+        <v>0.43484371900558472</v>
+      </c>
+      <c r="F170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>3</v>
+      </c>
+      <c r="B171" t="s">
+        <v>103</v>
+      </c>
+      <c r="C171" t="s">
+        <v>273</v>
+      </c>
+      <c r="D171" t="s">
+        <v>355</v>
+      </c>
+      <c r="E171">
+        <v>0.43249133229255682</v>
+      </c>
+      <c r="F171">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F171" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F171">
+      <sortCondition ref="D1:D171"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>